--- a/Data_Master.xlsx
+++ b/Data_Master.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Kantin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68027639-6CD5-4A31-96D1-B03086DC6D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AC0B54-8C16-4C4E-8087-67EFF32BB460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFC52FFA-175C-4E6E-9BE3-CE0A8ECCF11B}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Lembar1!$S$1:$S$1390</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7648" uniqueCount="449">
   <si>
     <t>product</t>
   </si>
@@ -1298,9 +1301,6 @@
     <t>6907992825076</t>
   </si>
   <si>
-    <t>AKAN DI BAHAS</t>
-  </si>
-  <si>
     <t>Kopi Botol Besar</t>
   </si>
   <si>
@@ -1383,6 +1383,9 @@
   </si>
   <si>
     <t>Jus Mangga RKN</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KATEGORY</t>
   </si>
 </sst>
 </file>
@@ -1761,13 +1764,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}">
-  <dimension ref="A1:S1191"/>
+  <dimension ref="A1:S1390"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
@@ -1782,7 +1785,7 @@
     <col min="16" max="16" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
@@ -46542,7 +46545,7 @@
         <v>417</v>
       </c>
       <c r="S975" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="976" spans="1:19" x14ac:dyDescent="0.3">
@@ -48696,13 +48699,13 @@
     </row>
     <row r="1023" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D1023" t="s">
         <v>107</v>
       </c>
       <c r="E1023" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1023">
         <v>8</v>
@@ -48738,7 +48741,7 @@
         <v>417</v>
       </c>
       <c r="S1023" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1024" spans="1:19" x14ac:dyDescent="0.3">
@@ -50522,7 +50525,7 @@
     </row>
     <row r="1063" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C1063" t="s">
         <v>250</v>
@@ -50564,12 +50567,12 @@
         <v>417</v>
       </c>
       <c r="S1063" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1064" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C1064" t="s">
         <v>251</v>
@@ -50611,12 +50614,12 @@
         <v>417</v>
       </c>
       <c r="S1064" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1065" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C1065" t="s">
         <v>252</v>
@@ -50658,12 +50661,12 @@
         <v>417</v>
       </c>
       <c r="S1065" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1066" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C1066" t="s">
         <v>253</v>
@@ -50705,7 +50708,7 @@
         <v>417</v>
       </c>
       <c r="S1066" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1067" spans="1:19" x14ac:dyDescent="0.3">
@@ -53095,10 +53098,10 @@
     </row>
     <row r="1118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1118" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1118" t="s">
         <v>424</v>
-      </c>
-      <c r="C1118" t="s">
-        <v>425</v>
       </c>
       <c r="D1118" t="s">
         <v>280</v>
@@ -53137,15 +53140,15 @@
         <v>417</v>
       </c>
       <c r="S1118" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1119" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1119" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D1119" t="s">
         <v>280</v>
@@ -53184,15 +53187,15 @@
         <v>417</v>
       </c>
       <c r="S1119" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1120" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1120" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D1120" t="s">
         <v>280</v>
@@ -53231,15 +53234,15 @@
         <v>417</v>
       </c>
       <c r="S1120" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1121" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1121" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D1121" t="s">
         <v>280</v>
@@ -53278,15 +53281,15 @@
         <v>417</v>
       </c>
       <c r="S1121" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1122" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1122" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D1122" t="s">
         <v>280</v>
@@ -53325,15 +53328,15 @@
         <v>417</v>
       </c>
       <c r="S1122" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1123" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1123" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D1123" t="s">
         <v>280</v>
@@ -53372,15 +53375,15 @@
         <v>417</v>
       </c>
       <c r="S1123" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1124" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C1124" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D1124" t="s">
         <v>280</v>
@@ -53419,7 +53422,7 @@
         <v>417</v>
       </c>
       <c r="S1124" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1125" spans="1:19" x14ac:dyDescent="0.3">
@@ -53427,7 +53430,7 @@
         <v>413</v>
       </c>
       <c r="C1125" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D1125" t="s">
         <v>280</v>
@@ -53518,10 +53521,10 @@
     </row>
     <row r="1127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1127" t="s">
+        <v>432</v>
+      </c>
+      <c r="C1127" t="s">
         <v>433</v>
-      </c>
-      <c r="C1127" t="s">
-        <v>434</v>
       </c>
       <c r="D1127" t="s">
         <v>280</v>
@@ -53560,7 +53563,7 @@
         <v>417</v>
       </c>
       <c r="S1127" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1128" spans="1:19" x14ac:dyDescent="0.3">
@@ -54684,7 +54687,7 @@
     </row>
     <row r="1152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1152" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D1152" t="s">
         <v>341</v>
@@ -54723,7 +54726,7 @@
         <v>417</v>
       </c>
       <c r="S1152" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1153" spans="1:19" x14ac:dyDescent="0.3">
@@ -54860,7 +54863,7 @@
     </row>
     <row r="1156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1156" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D1156" t="s">
         <v>341</v>
@@ -54899,7 +54902,7 @@
         <v>417</v>
       </c>
       <c r="S1156" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1157" spans="1:19" x14ac:dyDescent="0.3">
@@ -55256,7 +55259,7 @@
     </row>
     <row r="1165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1165" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D1165" t="s">
         <v>341</v>
@@ -55295,7 +55298,7 @@
         <v>417</v>
       </c>
       <c r="S1165" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1166" spans="1:19" x14ac:dyDescent="0.3">
@@ -55344,7 +55347,7 @@
     </row>
     <row r="1167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1167" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D1167" t="s">
         <v>341</v>
@@ -55383,7 +55386,7 @@
         <v>417</v>
       </c>
       <c r="S1167" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1168" spans="1:19" x14ac:dyDescent="0.3">
@@ -55432,7 +55435,7 @@
     </row>
     <row r="1169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D1169" t="s">
         <v>341</v>
@@ -55471,7 +55474,7 @@
         <v>417</v>
       </c>
       <c r="S1169" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1170" spans="1:19" x14ac:dyDescent="0.3">
@@ -56010,10 +56013,10 @@
     </row>
     <row r="1182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1182" t="s">
         <v>440</v>
-      </c>
-      <c r="D1182" t="s">
-        <v>441</v>
       </c>
       <c r="E1182" t="s">
         <v>387</v>
@@ -56052,15 +56055,15 @@
         <v>417</v>
       </c>
       <c r="S1182" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1183" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D1183" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1183" t="s">
         <v>304</v>
@@ -56099,15 +56102,15 @@
         <v>417</v>
       </c>
       <c r="S1183" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1184" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D1184" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1184" t="s">
         <v>306</v>
@@ -56146,15 +56149,15 @@
         <v>417</v>
       </c>
       <c r="S1184" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D1185" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1185" t="s">
         <v>310</v>
@@ -56198,10 +56201,10 @@
     </row>
     <row r="1186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D1186" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1186" t="s">
         <v>312</v>
@@ -56245,10 +56248,10 @@
     </row>
     <row r="1187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1187" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D1187" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1187" t="s">
         <v>314</v>
@@ -56292,10 +56295,10 @@
     </row>
     <row r="1188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1188" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D1188" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1188" t="s">
         <v>318</v>
@@ -56339,10 +56342,10 @@
     </row>
     <row r="1189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1189" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D1189" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E1189" t="s">
         <v>320</v>
@@ -56478,7 +56481,8542 @@
         <v>23</v>
       </c>
     </row>
+    <row r="1192" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1192" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1192">
+        <v>360</v>
+      </c>
+      <c r="I1192" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1192">
+        <v>5760000</v>
+      </c>
+      <c r="K1192">
+        <v>0</v>
+      </c>
+      <c r="L1192">
+        <v>0</v>
+      </c>
+      <c r="M1192">
+        <v>5760000</v>
+      </c>
+      <c r="N1192">
+        <v>3960000</v>
+      </c>
+      <c r="O1192">
+        <v>1800000</v>
+      </c>
+      <c r="P1192">
+        <v>299</v>
+      </c>
+      <c r="Q1192">
+        <v>1.2</v>
+      </c>
+      <c r="R1192" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1192" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1193" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1193">
+        <v>62</v>
+      </c>
+      <c r="I1193" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1193">
+        <v>992000</v>
+      </c>
+      <c r="K1193">
+        <v>0</v>
+      </c>
+      <c r="L1193">
+        <v>0</v>
+      </c>
+      <c r="M1193">
+        <v>992000</v>
+      </c>
+      <c r="N1193">
+        <v>651000</v>
+      </c>
+      <c r="O1193">
+        <v>341000</v>
+      </c>
+      <c r="P1193">
+        <v>46</v>
+      </c>
+      <c r="Q1193">
+        <v>1.35</v>
+      </c>
+      <c r="S1193" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1194" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1194">
+        <v>25</v>
+      </c>
+      <c r="I1194" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1194">
+        <v>500000</v>
+      </c>
+      <c r="K1194">
+        <v>0</v>
+      </c>
+      <c r="L1194">
+        <v>0</v>
+      </c>
+      <c r="M1194">
+        <v>500000</v>
+      </c>
+      <c r="N1194">
+        <v>337500</v>
+      </c>
+      <c r="O1194">
+        <v>162500</v>
+      </c>
+      <c r="P1194">
+        <v>19</v>
+      </c>
+      <c r="Q1194">
+        <v>1.32</v>
+      </c>
+      <c r="S1194" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1195" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1195">
+        <v>341</v>
+      </c>
+      <c r="I1195" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1195">
+        <v>6820000</v>
+      </c>
+      <c r="K1195">
+        <v>0</v>
+      </c>
+      <c r="L1195">
+        <v>0</v>
+      </c>
+      <c r="M1195">
+        <v>6820000</v>
+      </c>
+      <c r="N1195">
+        <v>4603500</v>
+      </c>
+      <c r="O1195">
+        <v>2216500</v>
+      </c>
+      <c r="P1195">
+        <v>254</v>
+      </c>
+      <c r="Q1195">
+        <v>1.34</v>
+      </c>
+      <c r="S1195" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1196" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1196">
+        <v>75</v>
+      </c>
+      <c r="I1196" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1196">
+        <v>750000</v>
+      </c>
+      <c r="K1196">
+        <v>0</v>
+      </c>
+      <c r="L1196">
+        <v>0</v>
+      </c>
+      <c r="M1196">
+        <v>750000</v>
+      </c>
+      <c r="N1196">
+        <v>450000</v>
+      </c>
+      <c r="O1196">
+        <v>300000</v>
+      </c>
+      <c r="P1196">
+        <v>60</v>
+      </c>
+      <c r="Q1196">
+        <v>1.25</v>
+      </c>
+      <c r="S1196" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1197" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1197">
+        <v>12</v>
+      </c>
+      <c r="I1197" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1197">
+        <v>84000</v>
+      </c>
+      <c r="K1197">
+        <v>0</v>
+      </c>
+      <c r="L1197">
+        <v>0</v>
+      </c>
+      <c r="M1197">
+        <v>84000</v>
+      </c>
+      <c r="N1197">
+        <v>72000</v>
+      </c>
+      <c r="O1197">
+        <v>12000</v>
+      </c>
+      <c r="P1197">
+        <v>12</v>
+      </c>
+      <c r="Q1197">
+        <v>1</v>
+      </c>
+      <c r="S1197" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1198" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1198">
+        <v>176</v>
+      </c>
+      <c r="I1198" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1198">
+        <v>704000</v>
+      </c>
+      <c r="K1198">
+        <v>0</v>
+      </c>
+      <c r="L1198">
+        <v>0</v>
+      </c>
+      <c r="M1198">
+        <v>704000</v>
+      </c>
+      <c r="N1198">
+        <v>528000</v>
+      </c>
+      <c r="O1198">
+        <v>176000</v>
+      </c>
+      <c r="P1198">
+        <v>88</v>
+      </c>
+      <c r="Q1198">
+        <v>2</v>
+      </c>
+      <c r="S1198" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1199" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1199">
+        <v>22</v>
+      </c>
+      <c r="I1199" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1199">
+        <v>110000</v>
+      </c>
+      <c r="K1199">
+        <v>0</v>
+      </c>
+      <c r="L1199">
+        <v>0</v>
+      </c>
+      <c r="M1199">
+        <v>110000</v>
+      </c>
+      <c r="N1199">
+        <v>88000</v>
+      </c>
+      <c r="O1199">
+        <v>22000</v>
+      </c>
+      <c r="P1199">
+        <v>19</v>
+      </c>
+      <c r="Q1199">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="S1199" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1200" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1200">
+        <v>42</v>
+      </c>
+      <c r="I1200" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1200">
+        <v>840000</v>
+      </c>
+      <c r="K1200">
+        <v>0</v>
+      </c>
+      <c r="L1200">
+        <v>0</v>
+      </c>
+      <c r="M1200">
+        <v>842000</v>
+      </c>
+      <c r="N1200">
+        <v>631554.35</v>
+      </c>
+      <c r="O1200">
+        <v>210445.65</v>
+      </c>
+      <c r="P1200">
+        <v>35</v>
+      </c>
+      <c r="Q1200">
+        <v>1.2</v>
+      </c>
+      <c r="S1200" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1201" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1201">
+        <v>120</v>
+      </c>
+      <c r="I1201" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1201">
+        <v>1800000</v>
+      </c>
+      <c r="K1201">
+        <v>0</v>
+      </c>
+      <c r="L1201">
+        <v>0</v>
+      </c>
+      <c r="M1201">
+        <v>1802000</v>
+      </c>
+      <c r="N1201">
+        <v>1321554.3500000001</v>
+      </c>
+      <c r="O1201">
+        <v>480445.65</v>
+      </c>
+      <c r="P1201">
+        <v>105</v>
+      </c>
+      <c r="Q1201">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="S1201" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1202" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1202">
+        <v>63</v>
+      </c>
+      <c r="I1202" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1202">
+        <v>1134000</v>
+      </c>
+      <c r="K1202">
+        <v>0</v>
+      </c>
+      <c r="L1202">
+        <v>0</v>
+      </c>
+      <c r="M1202">
+        <v>1136000</v>
+      </c>
+      <c r="N1202">
+        <v>820554.35</v>
+      </c>
+      <c r="O1202">
+        <v>315445.65000000002</v>
+      </c>
+      <c r="P1202">
+        <v>51</v>
+      </c>
+      <c r="Q1202">
+        <v>1.24</v>
+      </c>
+      <c r="S1202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1203" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1203">
+        <v>122</v>
+      </c>
+      <c r="I1203" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1203">
+        <v>444000</v>
+      </c>
+      <c r="K1203">
+        <v>0</v>
+      </c>
+      <c r="L1203">
+        <v>0</v>
+      </c>
+      <c r="M1203">
+        <v>444000</v>
+      </c>
+      <c r="N1203">
+        <v>244000</v>
+      </c>
+      <c r="O1203">
+        <v>200000</v>
+      </c>
+      <c r="P1203">
+        <v>73</v>
+      </c>
+      <c r="Q1203">
+        <v>1.67</v>
+      </c>
+      <c r="S1203" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1204" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1204">
+        <v>1</v>
+      </c>
+      <c r="I1204" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1204">
+        <v>0</v>
+      </c>
+      <c r="K1204">
+        <v>0</v>
+      </c>
+      <c r="L1204">
+        <v>0</v>
+      </c>
+      <c r="M1204">
+        <v>0</v>
+      </c>
+      <c r="N1204">
+        <v>0</v>
+      </c>
+      <c r="O1204">
+        <v>0</v>
+      </c>
+      <c r="P1204">
+        <v>1</v>
+      </c>
+      <c r="Q1204">
+        <v>1</v>
+      </c>
+      <c r="S1204" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1205" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1205">
+        <v>21</v>
+      </c>
+      <c r="I1205" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1205">
+        <v>315000</v>
+      </c>
+      <c r="K1205">
+        <v>0</v>
+      </c>
+      <c r="L1205">
+        <v>0</v>
+      </c>
+      <c r="M1205">
+        <v>315000</v>
+      </c>
+      <c r="N1205">
+        <v>285600</v>
+      </c>
+      <c r="O1205">
+        <v>29400</v>
+      </c>
+      <c r="P1205">
+        <v>21</v>
+      </c>
+      <c r="Q1205">
+        <v>1</v>
+      </c>
+      <c r="S1205" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1206" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1206">
+        <v>2</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1206">
+        <v>24000</v>
+      </c>
+      <c r="K1206">
+        <v>0</v>
+      </c>
+      <c r="L1206">
+        <v>0</v>
+      </c>
+      <c r="M1206">
+        <v>24000</v>
+      </c>
+      <c r="N1206">
+        <v>17000</v>
+      </c>
+      <c r="O1206">
+        <v>7000</v>
+      </c>
+      <c r="P1206">
+        <v>2</v>
+      </c>
+      <c r="Q1206">
+        <v>1</v>
+      </c>
+      <c r="S1206" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1207" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1207">
+        <v>3</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1207">
+        <v>45000</v>
+      </c>
+      <c r="K1207">
+        <v>0</v>
+      </c>
+      <c r="L1207">
+        <v>0</v>
+      </c>
+      <c r="M1207">
+        <v>45000</v>
+      </c>
+      <c r="N1207">
+        <v>33525</v>
+      </c>
+      <c r="O1207">
+        <v>11475</v>
+      </c>
+      <c r="P1207">
+        <v>3</v>
+      </c>
+      <c r="Q1207">
+        <v>1</v>
+      </c>
+      <c r="S1207" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1208" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1208">
+        <v>60</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1208">
+        <v>1260000</v>
+      </c>
+      <c r="K1208">
+        <v>0</v>
+      </c>
+      <c r="L1208">
+        <v>0</v>
+      </c>
+      <c r="M1208">
+        <v>1282000</v>
+      </c>
+      <c r="N1208">
+        <v>362075.75</v>
+      </c>
+      <c r="O1208">
+        <v>919924.25</v>
+      </c>
+      <c r="P1208">
+        <v>51</v>
+      </c>
+      <c r="Q1208">
+        <v>1.18</v>
+      </c>
+      <c r="S1208" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1209" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1209">
+        <v>91</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1209">
+        <v>2002000</v>
+      </c>
+      <c r="K1209">
+        <v>0</v>
+      </c>
+      <c r="L1209">
+        <v>0</v>
+      </c>
+      <c r="M1209">
+        <v>2231000</v>
+      </c>
+      <c r="N1209">
+        <v>646654.32999999996</v>
+      </c>
+      <c r="O1209">
+        <v>1584345.67</v>
+      </c>
+      <c r="P1209">
+        <v>79</v>
+      </c>
+      <c r="Q1209">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="S1209" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1210" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1210">
+        <v>39</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1210">
+        <v>936000</v>
+      </c>
+      <c r="K1210">
+        <v>0</v>
+      </c>
+      <c r="L1210">
+        <v>0</v>
+      </c>
+      <c r="M1210">
+        <v>938000</v>
+      </c>
+      <c r="N1210">
+        <v>282390.62</v>
+      </c>
+      <c r="O1210">
+        <v>655609.38</v>
+      </c>
+      <c r="P1210">
+        <v>34</v>
+      </c>
+      <c r="Q1210">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="S1210" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1211" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1211">
+        <v>11</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1211">
+        <v>55000</v>
+      </c>
+      <c r="K1211">
+        <v>0</v>
+      </c>
+      <c r="L1211">
+        <v>0</v>
+      </c>
+      <c r="M1211">
+        <v>55000</v>
+      </c>
+      <c r="N1211">
+        <v>28405.73</v>
+      </c>
+      <c r="O1211">
+        <v>26594.27</v>
+      </c>
+      <c r="P1211">
+        <v>8</v>
+      </c>
+      <c r="Q1211">
+        <v>1.38</v>
+      </c>
+      <c r="S1211" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1212" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1212">
+        <v>257</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1212">
+        <v>1285000</v>
+      </c>
+      <c r="K1212">
+        <v>0</v>
+      </c>
+      <c r="L1212">
+        <v>0</v>
+      </c>
+      <c r="M1212">
+        <v>1285000</v>
+      </c>
+      <c r="N1212">
+        <v>418812.34</v>
+      </c>
+      <c r="O1212">
+        <v>866187.66</v>
+      </c>
+      <c r="P1212">
+        <v>229</v>
+      </c>
+      <c r="Q1212">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S1212" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1213" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1213">
+        <v>10</v>
+      </c>
+      <c r="I1213" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1213">
+        <v>50000</v>
+      </c>
+      <c r="K1213">
+        <v>0</v>
+      </c>
+      <c r="L1213">
+        <v>0</v>
+      </c>
+      <c r="M1213">
+        <v>50000</v>
+      </c>
+      <c r="N1213">
+        <v>22916.7</v>
+      </c>
+      <c r="O1213">
+        <v>27083.3</v>
+      </c>
+      <c r="P1213">
+        <v>10</v>
+      </c>
+      <c r="Q1213">
+        <v>1</v>
+      </c>
+      <c r="S1213" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1214" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1214">
+        <v>24</v>
+      </c>
+      <c r="I1214" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1214">
+        <v>120000</v>
+      </c>
+      <c r="K1214">
+        <v>0</v>
+      </c>
+      <c r="L1214">
+        <v>0</v>
+      </c>
+      <c r="M1214">
+        <v>120000</v>
+      </c>
+      <c r="N1214">
+        <v>0</v>
+      </c>
+      <c r="O1214">
+        <v>120000</v>
+      </c>
+      <c r="P1214">
+        <v>19</v>
+      </c>
+      <c r="Q1214">
+        <v>1.26</v>
+      </c>
+      <c r="S1214" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1215" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1215">
+        <v>7</v>
+      </c>
+      <c r="I1215" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1215">
+        <v>56000</v>
+      </c>
+      <c r="K1215">
+        <v>0</v>
+      </c>
+      <c r="L1215">
+        <v>0</v>
+      </c>
+      <c r="M1215">
+        <v>56000</v>
+      </c>
+      <c r="N1215">
+        <v>39900</v>
+      </c>
+      <c r="O1215">
+        <v>16100</v>
+      </c>
+      <c r="P1215">
+        <v>6</v>
+      </c>
+      <c r="Q1215">
+        <v>1.17</v>
+      </c>
+      <c r="S1215" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1216" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1216">
+        <v>39</v>
+      </c>
+      <c r="I1216" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1216">
+        <v>234000</v>
+      </c>
+      <c r="K1216">
+        <v>0</v>
+      </c>
+      <c r="L1216">
+        <v>0</v>
+      </c>
+      <c r="M1216">
+        <v>234000</v>
+      </c>
+      <c r="N1216">
+        <v>139749.87</v>
+      </c>
+      <c r="O1216">
+        <v>94250.13</v>
+      </c>
+      <c r="P1216">
+        <v>34</v>
+      </c>
+      <c r="Q1216">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="S1216" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1217" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1217">
+        <v>3</v>
+      </c>
+      <c r="I1217" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1217">
+        <v>24000</v>
+      </c>
+      <c r="K1217">
+        <v>0</v>
+      </c>
+      <c r="L1217">
+        <v>0</v>
+      </c>
+      <c r="M1217">
+        <v>24000</v>
+      </c>
+      <c r="N1217">
+        <v>15600</v>
+      </c>
+      <c r="O1217">
+        <v>8400</v>
+      </c>
+      <c r="P1217">
+        <v>3</v>
+      </c>
+      <c r="Q1217">
+        <v>1</v>
+      </c>
+      <c r="S1217" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1218" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1218">
+        <v>928</v>
+      </c>
+      <c r="I1218" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1218">
+        <v>4640000</v>
+      </c>
+      <c r="K1218">
+        <v>0</v>
+      </c>
+      <c r="L1218">
+        <v>0</v>
+      </c>
+      <c r="M1218">
+        <v>4640000</v>
+      </c>
+      <c r="N1218">
+        <v>1512287.36</v>
+      </c>
+      <c r="O1218">
+        <v>3127712.64</v>
+      </c>
+      <c r="P1218">
+        <v>448</v>
+      </c>
+      <c r="Q1218">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="S1218" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1219" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1219">
+        <v>30</v>
+      </c>
+      <c r="I1219" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1219">
+        <v>210000</v>
+      </c>
+      <c r="K1219">
+        <v>0</v>
+      </c>
+      <c r="L1219">
+        <v>0</v>
+      </c>
+      <c r="M1219">
+        <v>210000</v>
+      </c>
+      <c r="N1219">
+        <v>156750</v>
+      </c>
+      <c r="O1219">
+        <v>53250</v>
+      </c>
+      <c r="P1219">
+        <v>24</v>
+      </c>
+      <c r="Q1219">
+        <v>1.25</v>
+      </c>
+      <c r="S1219" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1220" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1220">
+        <v>15</v>
+      </c>
+      <c r="I1220" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1220">
+        <v>105000</v>
+      </c>
+      <c r="K1220">
+        <v>0</v>
+      </c>
+      <c r="L1220">
+        <v>0</v>
+      </c>
+      <c r="M1220">
+        <v>105000</v>
+      </c>
+      <c r="N1220">
+        <v>76875</v>
+      </c>
+      <c r="O1220">
+        <v>28125</v>
+      </c>
+      <c r="P1220">
+        <v>10</v>
+      </c>
+      <c r="Q1220">
+        <v>1.5</v>
+      </c>
+      <c r="S1220" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1221" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1221">
+        <v>60</v>
+      </c>
+      <c r="I1221" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1221">
+        <v>600000</v>
+      </c>
+      <c r="K1221">
+        <v>0</v>
+      </c>
+      <c r="L1221">
+        <v>0</v>
+      </c>
+      <c r="M1221">
+        <v>600000</v>
+      </c>
+      <c r="N1221">
+        <v>437500.2</v>
+      </c>
+      <c r="O1221">
+        <v>162499.79999999999</v>
+      </c>
+      <c r="P1221">
+        <v>46</v>
+      </c>
+      <c r="Q1221">
+        <v>1.3</v>
+      </c>
+      <c r="S1221" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1222" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1222">
+        <v>71</v>
+      </c>
+      <c r="I1222" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1222">
+        <v>1775000</v>
+      </c>
+      <c r="K1222">
+        <v>0</v>
+      </c>
+      <c r="L1222">
+        <v>0</v>
+      </c>
+      <c r="M1222">
+        <v>1775000</v>
+      </c>
+      <c r="N1222">
+        <v>1420000</v>
+      </c>
+      <c r="O1222">
+        <v>355000</v>
+      </c>
+      <c r="P1222">
+        <v>62</v>
+      </c>
+      <c r="Q1222">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="S1222" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1223" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1223">
+        <v>1</v>
+      </c>
+      <c r="I1223" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1223">
+        <v>8000</v>
+      </c>
+      <c r="K1223">
+        <v>0</v>
+      </c>
+      <c r="L1223">
+        <v>0</v>
+      </c>
+      <c r="M1223">
+        <v>8000</v>
+      </c>
+      <c r="N1223">
+        <v>5660.69</v>
+      </c>
+      <c r="O1223">
+        <v>2339.31</v>
+      </c>
+      <c r="P1223">
+        <v>1</v>
+      </c>
+      <c r="Q1223">
+        <v>1</v>
+      </c>
+      <c r="S1223" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1224" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1224">
+        <v>3</v>
+      </c>
+      <c r="I1224" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1224">
+        <v>18000</v>
+      </c>
+      <c r="K1224">
+        <v>0</v>
+      </c>
+      <c r="L1224">
+        <v>0</v>
+      </c>
+      <c r="M1224">
+        <v>18000</v>
+      </c>
+      <c r="N1224">
+        <v>12650.28</v>
+      </c>
+      <c r="O1224">
+        <v>5349.72</v>
+      </c>
+      <c r="P1224">
+        <v>2</v>
+      </c>
+      <c r="Q1224">
+        <v>1.5</v>
+      </c>
+      <c r="S1224" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1225" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1225">
+        <v>71</v>
+      </c>
+      <c r="I1225" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1225">
+        <v>497000</v>
+      </c>
+      <c r="K1225">
+        <v>0</v>
+      </c>
+      <c r="L1225">
+        <v>0</v>
+      </c>
+      <c r="M1225">
+        <v>497000</v>
+      </c>
+      <c r="N1225">
+        <v>367171.53</v>
+      </c>
+      <c r="O1225">
+        <v>129828.47</v>
+      </c>
+      <c r="P1225">
+        <v>54</v>
+      </c>
+      <c r="Q1225">
+        <v>1.31</v>
+      </c>
+      <c r="S1225" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1226" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1226" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1226">
+        <v>19</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1226">
+        <v>285000</v>
+      </c>
+      <c r="K1226">
+        <v>0</v>
+      </c>
+      <c r="L1226">
+        <v>0</v>
+      </c>
+      <c r="M1226">
+        <v>285000</v>
+      </c>
+      <c r="N1226">
+        <v>228000</v>
+      </c>
+      <c r="O1226">
+        <v>57000</v>
+      </c>
+      <c r="P1226">
+        <v>15</v>
+      </c>
+      <c r="Q1226">
+        <v>1.27</v>
+      </c>
+      <c r="S1226" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1227" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1227">
+        <v>50</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1227">
+        <v>600000</v>
+      </c>
+      <c r="K1227">
+        <v>0</v>
+      </c>
+      <c r="L1227">
+        <v>0</v>
+      </c>
+      <c r="M1227">
+        <v>600000</v>
+      </c>
+      <c r="N1227">
+        <v>500000</v>
+      </c>
+      <c r="O1227">
+        <v>100000</v>
+      </c>
+      <c r="P1227">
+        <v>30</v>
+      </c>
+      <c r="Q1227">
+        <v>1.67</v>
+      </c>
+      <c r="S1227" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1228" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1228">
+        <v>9</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1228">
+        <v>63000</v>
+      </c>
+      <c r="K1228">
+        <v>0</v>
+      </c>
+      <c r="L1228">
+        <v>0</v>
+      </c>
+      <c r="M1228">
+        <v>63000</v>
+      </c>
+      <c r="N1228">
+        <v>28500.03</v>
+      </c>
+      <c r="O1228">
+        <v>34499.97</v>
+      </c>
+      <c r="P1228">
+        <v>7</v>
+      </c>
+      <c r="Q1228">
+        <v>1.29</v>
+      </c>
+      <c r="S1228" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1229" t="s">
+        <v>405</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>406</v>
+      </c>
+      <c r="H1229">
+        <v>12</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1229">
+        <v>72000</v>
+      </c>
+      <c r="K1229">
+        <v>0</v>
+      </c>
+      <c r="L1229">
+        <v>0</v>
+      </c>
+      <c r="M1229">
+        <v>72000</v>
+      </c>
+      <c r="N1229">
+        <v>57800.04</v>
+      </c>
+      <c r="O1229">
+        <v>14199.96</v>
+      </c>
+      <c r="P1229">
+        <v>9</v>
+      </c>
+      <c r="Q1229">
+        <v>1.33</v>
+      </c>
+      <c r="S1229" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1230" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1230">
+        <v>15</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1230">
+        <v>120000</v>
+      </c>
+      <c r="K1230">
+        <v>0</v>
+      </c>
+      <c r="L1230">
+        <v>0</v>
+      </c>
+      <c r="M1230">
+        <v>120000</v>
+      </c>
+      <c r="N1230">
+        <v>90193.09</v>
+      </c>
+      <c r="O1230">
+        <v>29806.91</v>
+      </c>
+      <c r="P1230">
+        <v>11</v>
+      </c>
+      <c r="Q1230">
+        <v>1.36</v>
+      </c>
+      <c r="S1230" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1231" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1231">
+        <v>26</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1231">
+        <v>390000</v>
+      </c>
+      <c r="K1231">
+        <v>0</v>
+      </c>
+      <c r="L1231">
+        <v>0</v>
+      </c>
+      <c r="M1231">
+        <v>390000</v>
+      </c>
+      <c r="N1231">
+        <v>241800</v>
+      </c>
+      <c r="O1231">
+        <v>148200</v>
+      </c>
+      <c r="P1231">
+        <v>25</v>
+      </c>
+      <c r="Q1231">
+        <v>1.04</v>
+      </c>
+      <c r="S1231" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1232" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1232">
+        <v>66</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1232">
+        <v>330000</v>
+      </c>
+      <c r="K1232">
+        <v>0</v>
+      </c>
+      <c r="L1232">
+        <v>0</v>
+      </c>
+      <c r="M1232">
+        <v>330000</v>
+      </c>
+      <c r="N1232">
+        <v>170458.36</v>
+      </c>
+      <c r="O1232">
+        <v>159541.64000000001</v>
+      </c>
+      <c r="P1232">
+        <v>52</v>
+      </c>
+      <c r="Q1232">
+        <v>1.27</v>
+      </c>
+      <c r="S1232" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1233" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1233">
+        <v>18</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1233">
+        <v>216000</v>
+      </c>
+      <c r="K1233">
+        <v>0</v>
+      </c>
+      <c r="L1233">
+        <v>0</v>
+      </c>
+      <c r="M1233">
+        <v>216000</v>
+      </c>
+      <c r="N1233">
+        <v>168544.46</v>
+      </c>
+      <c r="O1233">
+        <v>47455.54</v>
+      </c>
+      <c r="P1233">
+        <v>15</v>
+      </c>
+      <c r="Q1233">
+        <v>1.2</v>
+      </c>
+      <c r="S1233" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1234" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1234">
+        <v>25</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1234">
+        <v>300000</v>
+      </c>
+      <c r="K1234">
+        <v>0</v>
+      </c>
+      <c r="L1234">
+        <v>0</v>
+      </c>
+      <c r="M1234">
+        <v>300000</v>
+      </c>
+      <c r="N1234">
+        <v>220833.5</v>
+      </c>
+      <c r="O1234">
+        <v>79166.5</v>
+      </c>
+      <c r="P1234">
+        <v>23</v>
+      </c>
+      <c r="Q1234">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1234" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1235" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1235">
+        <v>45</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1235">
+        <v>450000</v>
+      </c>
+      <c r="K1235">
+        <v>0</v>
+      </c>
+      <c r="L1235">
+        <v>0</v>
+      </c>
+      <c r="M1235">
+        <v>450000</v>
+      </c>
+      <c r="N1235">
+        <v>365625</v>
+      </c>
+      <c r="O1235">
+        <v>84375</v>
+      </c>
+      <c r="P1235">
+        <v>40</v>
+      </c>
+      <c r="Q1235">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1235" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1236" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1236">
+        <v>53</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1236">
+        <v>424000</v>
+      </c>
+      <c r="K1236">
+        <v>0</v>
+      </c>
+      <c r="L1236">
+        <v>0</v>
+      </c>
+      <c r="M1236">
+        <v>424000</v>
+      </c>
+      <c r="N1236">
+        <v>331256.36</v>
+      </c>
+      <c r="O1236">
+        <v>92743.64</v>
+      </c>
+      <c r="P1236">
+        <v>42</v>
+      </c>
+      <c r="Q1236">
+        <v>1.26</v>
+      </c>
+      <c r="S1236" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1237" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1237">
+        <v>68</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1237">
+        <v>544000</v>
+      </c>
+      <c r="K1237">
+        <v>0</v>
+      </c>
+      <c r="L1237">
+        <v>0</v>
+      </c>
+      <c r="M1237">
+        <v>544000</v>
+      </c>
+      <c r="N1237">
+        <v>423158.56</v>
+      </c>
+      <c r="O1237">
+        <v>120841.44</v>
+      </c>
+      <c r="P1237">
+        <v>56</v>
+      </c>
+      <c r="Q1237">
+        <v>1.21</v>
+      </c>
+      <c r="S1237" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1238" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1238">
+        <v>30</v>
+      </c>
+      <c r="I1238" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1238">
+        <v>270000</v>
+      </c>
+      <c r="K1238">
+        <v>0</v>
+      </c>
+      <c r="L1238">
+        <v>0</v>
+      </c>
+      <c r="M1238">
+        <v>270000</v>
+      </c>
+      <c r="N1238">
+        <v>230918.7</v>
+      </c>
+      <c r="O1238">
+        <v>39081.300000000003</v>
+      </c>
+      <c r="P1238">
+        <v>29</v>
+      </c>
+      <c r="Q1238">
+        <v>1.03</v>
+      </c>
+      <c r="S1238" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1239" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1239">
+        <v>60</v>
+      </c>
+      <c r="I1239" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1239">
+        <v>300000</v>
+      </c>
+      <c r="K1239">
+        <v>0</v>
+      </c>
+      <c r="L1239">
+        <v>0</v>
+      </c>
+      <c r="M1239">
+        <v>300000</v>
+      </c>
+      <c r="N1239">
+        <v>198873.60000000001</v>
+      </c>
+      <c r="O1239">
+        <v>101126.39999999999</v>
+      </c>
+      <c r="P1239">
+        <v>44</v>
+      </c>
+      <c r="Q1239">
+        <v>1.36</v>
+      </c>
+      <c r="S1239" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1240" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1240">
+        <v>26</v>
+      </c>
+      <c r="I1240" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1240">
+        <v>208000</v>
+      </c>
+      <c r="K1240">
+        <v>0</v>
+      </c>
+      <c r="L1240">
+        <v>0</v>
+      </c>
+      <c r="M1240">
+        <v>208000</v>
+      </c>
+      <c r="N1240">
+        <v>150184.57999999999</v>
+      </c>
+      <c r="O1240">
+        <v>57815.42</v>
+      </c>
+      <c r="P1240">
+        <v>23</v>
+      </c>
+      <c r="Q1240">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1240" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1241" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1241">
+        <v>99</v>
+      </c>
+      <c r="I1241" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1241">
+        <v>594000</v>
+      </c>
+      <c r="K1241">
+        <v>0</v>
+      </c>
+      <c r="L1241">
+        <v>0</v>
+      </c>
+      <c r="M1241">
+        <v>594000</v>
+      </c>
+      <c r="N1241">
+        <v>376612.83</v>
+      </c>
+      <c r="O1241">
+        <v>217387.17</v>
+      </c>
+      <c r="P1241">
+        <v>71</v>
+      </c>
+      <c r="Q1241">
+        <v>1.39</v>
+      </c>
+      <c r="S1241" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1242" t="s">
+        <v>420</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1242">
+        <v>26</v>
+      </c>
+      <c r="I1242" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1242">
+        <v>780000</v>
+      </c>
+      <c r="K1242">
+        <v>0</v>
+      </c>
+      <c r="L1242">
+        <v>0</v>
+      </c>
+      <c r="M1242">
+        <v>780000</v>
+      </c>
+      <c r="N1242">
+        <v>650000</v>
+      </c>
+      <c r="O1242">
+        <v>130000</v>
+      </c>
+      <c r="P1242">
+        <v>23</v>
+      </c>
+      <c r="Q1242">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1242" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1243">
+        <v>43</v>
+      </c>
+      <c r="I1243" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1243">
+        <v>516000</v>
+      </c>
+      <c r="K1243">
+        <v>0</v>
+      </c>
+      <c r="L1243">
+        <v>0</v>
+      </c>
+      <c r="M1243">
+        <v>516000</v>
+      </c>
+      <c r="N1243">
+        <v>208177.03</v>
+      </c>
+      <c r="O1243">
+        <v>307822.96999999997</v>
+      </c>
+      <c r="P1243">
+        <v>27</v>
+      </c>
+      <c r="Q1243">
+        <v>1.59</v>
+      </c>
+      <c r="S1243" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1244" t="s">
+        <v>397</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1244">
+        <v>86</v>
+      </c>
+      <c r="I1244" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1244">
+        <v>602000</v>
+      </c>
+      <c r="K1244">
+        <v>0</v>
+      </c>
+      <c r="L1244">
+        <v>0</v>
+      </c>
+      <c r="M1244">
+        <v>602000</v>
+      </c>
+      <c r="N1244">
+        <v>430000</v>
+      </c>
+      <c r="O1244">
+        <v>172000</v>
+      </c>
+      <c r="P1244">
+        <v>39</v>
+      </c>
+      <c r="Q1244">
+        <v>2.21</v>
+      </c>
+      <c r="S1244" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1245" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1245">
+        <v>25</v>
+      </c>
+      <c r="I1245" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1245">
+        <v>450000</v>
+      </c>
+      <c r="K1245">
+        <v>0</v>
+      </c>
+      <c r="L1245">
+        <v>0</v>
+      </c>
+      <c r="M1245">
+        <v>450000</v>
+      </c>
+      <c r="N1245">
+        <v>375000</v>
+      </c>
+      <c r="O1245">
+        <v>75000</v>
+      </c>
+      <c r="P1245">
+        <v>18</v>
+      </c>
+      <c r="Q1245">
+        <v>1.39</v>
+      </c>
+      <c r="S1245" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1246" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1246">
+        <v>367</v>
+      </c>
+      <c r="I1246" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1246">
+        <v>4771000</v>
+      </c>
+      <c r="K1246">
+        <v>0</v>
+      </c>
+      <c r="L1246">
+        <v>0</v>
+      </c>
+      <c r="M1246">
+        <v>4771000</v>
+      </c>
+      <c r="N1246">
+        <v>3670000</v>
+      </c>
+      <c r="O1246">
+        <v>1101000</v>
+      </c>
+      <c r="P1246">
+        <v>147</v>
+      </c>
+      <c r="Q1246">
+        <v>2.5</v>
+      </c>
+      <c r="S1246" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1247" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1247">
+        <v>62</v>
+      </c>
+      <c r="I1247" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1247">
+        <v>992000</v>
+      </c>
+      <c r="K1247">
+        <v>0</v>
+      </c>
+      <c r="L1247">
+        <v>0</v>
+      </c>
+      <c r="M1247">
+        <v>992000</v>
+      </c>
+      <c r="N1247">
+        <v>744000</v>
+      </c>
+      <c r="O1247">
+        <v>248000</v>
+      </c>
+      <c r="P1247">
+        <v>37</v>
+      </c>
+      <c r="Q1247">
+        <v>1.68</v>
+      </c>
+      <c r="S1247" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1248" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1248">
+        <v>95</v>
+      </c>
+      <c r="I1248" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1248">
+        <v>570000</v>
+      </c>
+      <c r="K1248">
+        <v>0</v>
+      </c>
+      <c r="L1248">
+        <v>0</v>
+      </c>
+      <c r="M1248">
+        <v>570000</v>
+      </c>
+      <c r="N1248">
+        <v>380000</v>
+      </c>
+      <c r="O1248">
+        <v>190000</v>
+      </c>
+      <c r="P1248">
+        <v>33</v>
+      </c>
+      <c r="Q1248">
+        <v>2.88</v>
+      </c>
+      <c r="S1248" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1249" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1249">
+        <v>600</v>
+      </c>
+      <c r="I1249" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1249">
+        <v>4200000</v>
+      </c>
+      <c r="K1249">
+        <v>0</v>
+      </c>
+      <c r="L1249">
+        <v>0</v>
+      </c>
+      <c r="M1249">
+        <v>4200000</v>
+      </c>
+      <c r="N1249">
+        <v>3000000</v>
+      </c>
+      <c r="O1249">
+        <v>1200000</v>
+      </c>
+      <c r="P1249">
+        <v>183</v>
+      </c>
+      <c r="Q1249">
+        <v>3.28</v>
+      </c>
+      <c r="S1249" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1250" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1250">
+        <v>92</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1250">
+        <v>1196000</v>
+      </c>
+      <c r="K1250">
+        <v>0</v>
+      </c>
+      <c r="L1250">
+        <v>0</v>
+      </c>
+      <c r="M1250">
+        <v>1196000</v>
+      </c>
+      <c r="N1250">
+        <v>920000</v>
+      </c>
+      <c r="O1250">
+        <v>276000</v>
+      </c>
+      <c r="P1250">
+        <v>38</v>
+      </c>
+      <c r="Q1250">
+        <v>2.42</v>
+      </c>
+      <c r="S1250" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1251" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1251">
+        <v>3</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1251">
+        <v>30000</v>
+      </c>
+      <c r="K1251">
+        <v>0</v>
+      </c>
+      <c r="L1251">
+        <v>0</v>
+      </c>
+      <c r="M1251">
+        <v>30000</v>
+      </c>
+      <c r="N1251">
+        <v>24000</v>
+      </c>
+      <c r="O1251">
+        <v>6000</v>
+      </c>
+      <c r="P1251">
+        <v>3</v>
+      </c>
+      <c r="Q1251">
+        <v>1</v>
+      </c>
+      <c r="S1251" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1252" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1252">
+        <v>304</v>
+      </c>
+      <c r="I1252" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1252">
+        <v>912000</v>
+      </c>
+      <c r="K1252">
+        <v>0</v>
+      </c>
+      <c r="L1252">
+        <v>0</v>
+      </c>
+      <c r="M1252">
+        <v>912000</v>
+      </c>
+      <c r="N1252">
+        <v>608000</v>
+      </c>
+      <c r="O1252">
+        <v>304000</v>
+      </c>
+      <c r="P1252">
+        <v>74</v>
+      </c>
+      <c r="Q1252">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="S1252" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1253" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1253">
+        <v>378</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1253">
+        <v>2268000</v>
+      </c>
+      <c r="K1253">
+        <v>0</v>
+      </c>
+      <c r="L1253">
+        <v>0</v>
+      </c>
+      <c r="M1253">
+        <v>2268000</v>
+      </c>
+      <c r="N1253">
+        <v>1512000</v>
+      </c>
+      <c r="O1253">
+        <v>756000</v>
+      </c>
+      <c r="P1253">
+        <v>85</v>
+      </c>
+      <c r="Q1253">
+        <v>4.45</v>
+      </c>
+      <c r="S1253" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1254" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1254">
+        <v>91</v>
+      </c>
+      <c r="I1254" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1254">
+        <v>455000</v>
+      </c>
+      <c r="K1254">
+        <v>0</v>
+      </c>
+      <c r="L1254">
+        <v>0</v>
+      </c>
+      <c r="M1254">
+        <v>455000</v>
+      </c>
+      <c r="N1254">
+        <v>273000</v>
+      </c>
+      <c r="O1254">
+        <v>182000</v>
+      </c>
+      <c r="P1254">
+        <v>37</v>
+      </c>
+      <c r="Q1254">
+        <v>2.46</v>
+      </c>
+      <c r="S1254" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1255" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1255">
+        <v>16</v>
+      </c>
+      <c r="I1255" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1255">
+        <v>208000</v>
+      </c>
+      <c r="K1255">
+        <v>0</v>
+      </c>
+      <c r="L1255">
+        <v>0</v>
+      </c>
+      <c r="M1255">
+        <v>208000</v>
+      </c>
+      <c r="N1255">
+        <v>160000</v>
+      </c>
+      <c r="O1255">
+        <v>48000</v>
+      </c>
+      <c r="P1255">
+        <v>14</v>
+      </c>
+      <c r="Q1255">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="S1255" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1256" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1256">
+        <v>66</v>
+      </c>
+      <c r="I1256" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1256">
+        <v>858000</v>
+      </c>
+      <c r="K1256">
+        <v>0</v>
+      </c>
+      <c r="L1256">
+        <v>0</v>
+      </c>
+      <c r="M1256">
+        <v>858000</v>
+      </c>
+      <c r="N1256">
+        <v>726000</v>
+      </c>
+      <c r="O1256">
+        <v>132000</v>
+      </c>
+      <c r="P1256">
+        <v>30</v>
+      </c>
+      <c r="Q1256">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S1256" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1257" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1257">
+        <v>149</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1257">
+        <v>1937000</v>
+      </c>
+      <c r="K1257">
+        <v>0</v>
+      </c>
+      <c r="L1257">
+        <v>0</v>
+      </c>
+      <c r="M1257">
+        <v>1937000</v>
+      </c>
+      <c r="N1257">
+        <v>1490000</v>
+      </c>
+      <c r="O1257">
+        <v>447000</v>
+      </c>
+      <c r="P1257">
+        <v>54</v>
+      </c>
+      <c r="Q1257">
+        <v>2.76</v>
+      </c>
+      <c r="S1257" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1258" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1258">
+        <v>100</v>
+      </c>
+      <c r="I1258" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1258">
+        <v>1500000</v>
+      </c>
+      <c r="K1258">
+        <v>0</v>
+      </c>
+      <c r="L1258">
+        <v>0</v>
+      </c>
+      <c r="M1258">
+        <v>1500000</v>
+      </c>
+      <c r="N1258">
+        <v>1200000</v>
+      </c>
+      <c r="O1258">
+        <v>300000</v>
+      </c>
+      <c r="P1258">
+        <v>61</v>
+      </c>
+      <c r="Q1258">
+        <v>1.64</v>
+      </c>
+      <c r="S1258" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1259" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1259">
+        <v>1</v>
+      </c>
+      <c r="I1259" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1259">
+        <v>6000</v>
+      </c>
+      <c r="K1259">
+        <v>0</v>
+      </c>
+      <c r="L1259">
+        <v>0</v>
+      </c>
+      <c r="M1259">
+        <v>6000</v>
+      </c>
+      <c r="N1259">
+        <v>4000</v>
+      </c>
+      <c r="O1259">
+        <v>2000</v>
+      </c>
+      <c r="P1259">
+        <v>1</v>
+      </c>
+      <c r="Q1259">
+        <v>1</v>
+      </c>
+      <c r="S1259" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1260" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1260">
+        <v>68</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1260">
+        <v>1224000</v>
+      </c>
+      <c r="K1260">
+        <v>0</v>
+      </c>
+      <c r="L1260">
+        <v>0</v>
+      </c>
+      <c r="M1260">
+        <v>1224000</v>
+      </c>
+      <c r="N1260">
+        <v>1020000</v>
+      </c>
+      <c r="O1260">
+        <v>204000</v>
+      </c>
+      <c r="P1260">
+        <v>26</v>
+      </c>
+      <c r="Q1260">
+        <v>2.62</v>
+      </c>
+      <c r="S1260" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1261" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1261">
+        <v>6</v>
+      </c>
+      <c r="I1261" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1261">
+        <v>18000</v>
+      </c>
+      <c r="K1261">
+        <v>0</v>
+      </c>
+      <c r="L1261">
+        <v>0</v>
+      </c>
+      <c r="M1261">
+        <v>18000</v>
+      </c>
+      <c r="N1261">
+        <v>0</v>
+      </c>
+      <c r="O1261">
+        <v>18000</v>
+      </c>
+      <c r="P1261">
+        <v>4</v>
+      </c>
+      <c r="Q1261">
+        <v>1.5</v>
+      </c>
+      <c r="S1261" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1262" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1262">
+        <v>3</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1262">
+        <v>9000</v>
+      </c>
+      <c r="K1262">
+        <v>0</v>
+      </c>
+      <c r="L1262">
+        <v>0</v>
+      </c>
+      <c r="M1262">
+        <v>9000</v>
+      </c>
+      <c r="N1262">
+        <v>0</v>
+      </c>
+      <c r="O1262">
+        <v>9000</v>
+      </c>
+      <c r="P1262">
+        <v>3</v>
+      </c>
+      <c r="Q1262">
+        <v>1</v>
+      </c>
+      <c r="S1262" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1263" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1263">
+        <v>16</v>
+      </c>
+      <c r="I1263" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1263">
+        <v>48000</v>
+      </c>
+      <c r="K1263">
+        <v>0</v>
+      </c>
+      <c r="L1263">
+        <v>0</v>
+      </c>
+      <c r="M1263">
+        <v>48000</v>
+      </c>
+      <c r="N1263">
+        <v>0</v>
+      </c>
+      <c r="O1263">
+        <v>48000</v>
+      </c>
+      <c r="P1263">
+        <v>15</v>
+      </c>
+      <c r="Q1263">
+        <v>1.07</v>
+      </c>
+      <c r="S1263" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1264" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1264">
+        <v>4</v>
+      </c>
+      <c r="I1264" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1264">
+        <v>12000</v>
+      </c>
+      <c r="K1264">
+        <v>0</v>
+      </c>
+      <c r="L1264">
+        <v>0</v>
+      </c>
+      <c r="M1264">
+        <v>12000</v>
+      </c>
+      <c r="N1264">
+        <v>2584.88</v>
+      </c>
+      <c r="O1264">
+        <v>9415.1200000000008</v>
+      </c>
+      <c r="P1264">
+        <v>4</v>
+      </c>
+      <c r="Q1264">
+        <v>1</v>
+      </c>
+      <c r="S1264" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1265" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1265">
+        <v>26</v>
+      </c>
+      <c r="I1265" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1265">
+        <v>182000</v>
+      </c>
+      <c r="K1265">
+        <v>0</v>
+      </c>
+      <c r="L1265">
+        <v>0</v>
+      </c>
+      <c r="M1265">
+        <v>185000</v>
+      </c>
+      <c r="N1265">
+        <v>42133.42</v>
+      </c>
+      <c r="O1265">
+        <v>142866.57999999999</v>
+      </c>
+      <c r="P1265">
+        <v>19</v>
+      </c>
+      <c r="Q1265">
+        <v>1.37</v>
+      </c>
+      <c r="S1265" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1266" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1266">
+        <v>12</v>
+      </c>
+      <c r="I1266" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1266">
+        <v>60000</v>
+      </c>
+      <c r="K1266">
+        <v>0</v>
+      </c>
+      <c r="L1266">
+        <v>0</v>
+      </c>
+      <c r="M1266">
+        <v>60000</v>
+      </c>
+      <c r="N1266">
+        <v>19100.04</v>
+      </c>
+      <c r="O1266">
+        <v>40899.96</v>
+      </c>
+      <c r="P1266">
+        <v>11</v>
+      </c>
+      <c r="Q1266">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1266" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1267" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1267">
+        <v>92</v>
+      </c>
+      <c r="I1267" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1267">
+        <v>460000</v>
+      </c>
+      <c r="K1267">
+        <v>0</v>
+      </c>
+      <c r="L1267">
+        <v>0</v>
+      </c>
+      <c r="M1267">
+        <v>460000</v>
+      </c>
+      <c r="N1267">
+        <v>146933.64000000001</v>
+      </c>
+      <c r="O1267">
+        <v>313066.36</v>
+      </c>
+      <c r="P1267">
+        <v>55</v>
+      </c>
+      <c r="Q1267">
+        <v>1.67</v>
+      </c>
+      <c r="S1267" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1268" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1268">
+        <v>53</v>
+      </c>
+      <c r="I1268" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1268">
+        <v>1166000</v>
+      </c>
+      <c r="K1268">
+        <v>0</v>
+      </c>
+      <c r="L1268">
+        <v>0</v>
+      </c>
+      <c r="M1268">
+        <v>1169000</v>
+      </c>
+      <c r="N1268">
+        <v>720800</v>
+      </c>
+      <c r="O1268">
+        <v>448200</v>
+      </c>
+      <c r="P1268">
+        <v>37</v>
+      </c>
+      <c r="Q1268">
+        <v>1.43</v>
+      </c>
+      <c r="S1268" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1269" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1269">
+        <v>7</v>
+      </c>
+      <c r="I1269" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1269">
+        <v>119000</v>
+      </c>
+      <c r="K1269">
+        <v>0</v>
+      </c>
+      <c r="L1269">
+        <v>0</v>
+      </c>
+      <c r="M1269">
+        <v>119000</v>
+      </c>
+      <c r="N1269">
+        <v>73500</v>
+      </c>
+      <c r="O1269">
+        <v>45500</v>
+      </c>
+      <c r="P1269">
+        <v>7</v>
+      </c>
+      <c r="Q1269">
+        <v>1</v>
+      </c>
+      <c r="S1269" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1270" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1270">
+        <v>1</v>
+      </c>
+      <c r="I1270" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1270">
+        <v>34000</v>
+      </c>
+      <c r="K1270">
+        <v>0</v>
+      </c>
+      <c r="L1270">
+        <v>0</v>
+      </c>
+      <c r="M1270">
+        <v>34000</v>
+      </c>
+      <c r="N1270">
+        <v>23600</v>
+      </c>
+      <c r="O1270">
+        <v>10400</v>
+      </c>
+      <c r="P1270">
+        <v>1</v>
+      </c>
+      <c r="Q1270">
+        <v>1</v>
+      </c>
+      <c r="S1270" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1271" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1271">
+        <v>7</v>
+      </c>
+      <c r="I1271" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1271">
+        <v>273000</v>
+      </c>
+      <c r="K1271">
+        <v>0</v>
+      </c>
+      <c r="L1271">
+        <v>0</v>
+      </c>
+      <c r="M1271">
+        <v>273000</v>
+      </c>
+      <c r="N1271">
+        <v>167279.49</v>
+      </c>
+      <c r="O1271">
+        <v>105720.51</v>
+      </c>
+      <c r="P1271">
+        <v>6</v>
+      </c>
+      <c r="Q1271">
+        <v>1.17</v>
+      </c>
+      <c r="S1271" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1272" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1272">
+        <v>1</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1272">
+        <v>39000</v>
+      </c>
+      <c r="K1272">
+        <v>0</v>
+      </c>
+      <c r="L1272">
+        <v>0</v>
+      </c>
+      <c r="M1272">
+        <v>39000</v>
+      </c>
+      <c r="N1272">
+        <v>23897.07</v>
+      </c>
+      <c r="O1272">
+        <v>15102.93</v>
+      </c>
+      <c r="P1272">
+        <v>1</v>
+      </c>
+      <c r="Q1272">
+        <v>1</v>
+      </c>
+      <c r="S1272" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1273" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1273">
+        <v>2</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1273">
+        <v>78000</v>
+      </c>
+      <c r="K1273">
+        <v>0</v>
+      </c>
+      <c r="L1273">
+        <v>0</v>
+      </c>
+      <c r="M1273">
+        <v>78000</v>
+      </c>
+      <c r="N1273">
+        <v>47794.14</v>
+      </c>
+      <c r="O1273">
+        <v>30205.86</v>
+      </c>
+      <c r="P1273">
+        <v>2</v>
+      </c>
+      <c r="Q1273">
+        <v>1</v>
+      </c>
+      <c r="S1273" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1274" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1274">
+        <v>1</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1274">
+        <v>35000</v>
+      </c>
+      <c r="K1274">
+        <v>0</v>
+      </c>
+      <c r="L1274">
+        <v>0</v>
+      </c>
+      <c r="M1274">
+        <v>35000</v>
+      </c>
+      <c r="N1274">
+        <v>80800.009999999995</v>
+      </c>
+      <c r="O1274">
+        <v>-45800.01</v>
+      </c>
+      <c r="P1274">
+        <v>1</v>
+      </c>
+      <c r="Q1274">
+        <v>1</v>
+      </c>
+      <c r="S1274" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1275" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1275">
+        <v>57</v>
+      </c>
+      <c r="I1275" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1275">
+        <v>1482000</v>
+      </c>
+      <c r="K1275">
+        <v>0</v>
+      </c>
+      <c r="L1275">
+        <v>0</v>
+      </c>
+      <c r="M1275">
+        <v>1482000</v>
+      </c>
+      <c r="N1275">
+        <v>463670.89</v>
+      </c>
+      <c r="O1275">
+        <v>1018329.06</v>
+      </c>
+      <c r="P1275">
+        <v>51</v>
+      </c>
+      <c r="Q1275">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S1275" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1276" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1276">
+        <v>44</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1276">
+        <v>1144000</v>
+      </c>
+      <c r="K1276">
+        <v>0</v>
+      </c>
+      <c r="L1276">
+        <v>0</v>
+      </c>
+      <c r="M1276">
+        <v>1144000</v>
+      </c>
+      <c r="N1276">
+        <v>420606.32</v>
+      </c>
+      <c r="O1276">
+        <v>723393.68</v>
+      </c>
+      <c r="P1276">
+        <v>38</v>
+      </c>
+      <c r="Q1276">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="S1276" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1277" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1277">
+        <v>12</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1277">
+        <v>276000</v>
+      </c>
+      <c r="K1277">
+        <v>0</v>
+      </c>
+      <c r="L1277">
+        <v>0</v>
+      </c>
+      <c r="M1277">
+        <v>276000</v>
+      </c>
+      <c r="N1277">
+        <v>159499.32</v>
+      </c>
+      <c r="O1277">
+        <v>116500.68</v>
+      </c>
+      <c r="P1277">
+        <v>11</v>
+      </c>
+      <c r="Q1277">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1277" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1278" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1278">
+        <v>3</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1278">
+        <v>90000</v>
+      </c>
+      <c r="K1278">
+        <v>0</v>
+      </c>
+      <c r="L1278">
+        <v>0</v>
+      </c>
+      <c r="M1278">
+        <v>90000</v>
+      </c>
+      <c r="N1278">
+        <v>68100</v>
+      </c>
+      <c r="O1278">
+        <v>21900</v>
+      </c>
+      <c r="P1278">
+        <v>3</v>
+      </c>
+      <c r="Q1278">
+        <v>1</v>
+      </c>
+      <c r="S1278" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1279" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1279">
+        <v>89</v>
+      </c>
+      <c r="I1279" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1279">
+        <v>2047000</v>
+      </c>
+      <c r="K1279">
+        <v>0</v>
+      </c>
+      <c r="L1279">
+        <v>0</v>
+      </c>
+      <c r="M1279">
+        <v>2047000</v>
+      </c>
+      <c r="N1279">
+        <v>782809.98</v>
+      </c>
+      <c r="O1279">
+        <v>1264190.02</v>
+      </c>
+      <c r="P1279">
+        <v>68</v>
+      </c>
+      <c r="Q1279">
+        <v>1.31</v>
+      </c>
+      <c r="S1279" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1280" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1280">
+        <v>21</v>
+      </c>
+      <c r="I1280" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1280">
+        <v>483000</v>
+      </c>
+      <c r="K1280">
+        <v>0</v>
+      </c>
+      <c r="L1280">
+        <v>0</v>
+      </c>
+      <c r="M1280">
+        <v>483000</v>
+      </c>
+      <c r="N1280">
+        <v>184660.92</v>
+      </c>
+      <c r="O1280">
+        <v>298339.08</v>
+      </c>
+      <c r="P1280">
+        <v>17</v>
+      </c>
+      <c r="Q1280">
+        <v>1.24</v>
+      </c>
+      <c r="S1280" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1281" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1281">
+        <v>40</v>
+      </c>
+      <c r="I1281" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1281">
+        <v>920000</v>
+      </c>
+      <c r="K1281">
+        <v>0</v>
+      </c>
+      <c r="L1281">
+        <v>0</v>
+      </c>
+      <c r="M1281">
+        <v>920000</v>
+      </c>
+      <c r="N1281">
+        <v>351763.89</v>
+      </c>
+      <c r="O1281">
+        <v>568236.11</v>
+      </c>
+      <c r="P1281">
+        <v>34</v>
+      </c>
+      <c r="Q1281">
+        <v>1.18</v>
+      </c>
+      <c r="S1281" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1282" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1282">
+        <v>21</v>
+      </c>
+      <c r="I1282" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1282">
+        <v>504000</v>
+      </c>
+      <c r="K1282">
+        <v>0</v>
+      </c>
+      <c r="L1282">
+        <v>0</v>
+      </c>
+      <c r="M1282">
+        <v>504000</v>
+      </c>
+      <c r="N1282">
+        <v>197943.36</v>
+      </c>
+      <c r="O1282">
+        <v>306056.64</v>
+      </c>
+      <c r="P1282">
+        <v>16</v>
+      </c>
+      <c r="Q1282">
+        <v>1.31</v>
+      </c>
+      <c r="S1282" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1283" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1283">
+        <v>75</v>
+      </c>
+      <c r="I1283" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1283">
+        <v>2250000</v>
+      </c>
+      <c r="K1283">
+        <v>0</v>
+      </c>
+      <c r="L1283">
+        <v>0</v>
+      </c>
+      <c r="M1283">
+        <v>2250000</v>
+      </c>
+      <c r="N1283">
+        <v>1081285.6299999999</v>
+      </c>
+      <c r="O1283">
+        <v>1168714.3700000001</v>
+      </c>
+      <c r="P1283">
+        <v>63</v>
+      </c>
+      <c r="Q1283">
+        <v>1.19</v>
+      </c>
+      <c r="S1283" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1284" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1284">
+        <v>62</v>
+      </c>
+      <c r="I1284" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1284">
+        <v>1860000</v>
+      </c>
+      <c r="K1284">
+        <v>0</v>
+      </c>
+      <c r="L1284">
+        <v>0</v>
+      </c>
+      <c r="M1284">
+        <v>1867000</v>
+      </c>
+      <c r="N1284">
+        <v>893728.85</v>
+      </c>
+      <c r="O1284">
+        <v>973271.15</v>
+      </c>
+      <c r="P1284">
+        <v>57</v>
+      </c>
+      <c r="Q1284">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1284" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1285" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1285">
+        <v>271</v>
+      </c>
+      <c r="I1285" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1285">
+        <v>8130000</v>
+      </c>
+      <c r="K1285">
+        <v>0</v>
+      </c>
+      <c r="L1285">
+        <v>0</v>
+      </c>
+      <c r="M1285">
+        <v>8130000</v>
+      </c>
+      <c r="N1285">
+        <v>3906609.82</v>
+      </c>
+      <c r="O1285">
+        <v>4223390.18</v>
+      </c>
+      <c r="P1285">
+        <v>197</v>
+      </c>
+      <c r="Q1285">
+        <v>1.38</v>
+      </c>
+      <c r="S1285" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1286" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1286">
+        <v>422</v>
+      </c>
+      <c r="I1286" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1286">
+        <v>12660000</v>
+      </c>
+      <c r="K1286">
+        <v>0</v>
+      </c>
+      <c r="L1286">
+        <v>0</v>
+      </c>
+      <c r="M1286">
+        <v>12666000</v>
+      </c>
+      <c r="N1286">
+        <v>6350870.0800000001</v>
+      </c>
+      <c r="O1286">
+        <v>6315129.9199999999</v>
+      </c>
+      <c r="P1286">
+        <v>334</v>
+      </c>
+      <c r="Q1286">
+        <v>1.26</v>
+      </c>
+      <c r="S1286" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1287" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1287">
+        <v>55</v>
+      </c>
+      <c r="I1287" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1287">
+        <v>1430000</v>
+      </c>
+      <c r="K1287">
+        <v>0</v>
+      </c>
+      <c r="L1287">
+        <v>0</v>
+      </c>
+      <c r="M1287">
+        <v>1433000</v>
+      </c>
+      <c r="N1287">
+        <v>720776.96</v>
+      </c>
+      <c r="O1287">
+        <v>712223.04</v>
+      </c>
+      <c r="P1287">
+        <v>51</v>
+      </c>
+      <c r="Q1287">
+        <v>1.08</v>
+      </c>
+      <c r="S1287" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1288" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1288">
+        <v>24</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1288">
+        <v>624000</v>
+      </c>
+      <c r="K1288">
+        <v>0</v>
+      </c>
+      <c r="L1288">
+        <v>0</v>
+      </c>
+      <c r="M1288">
+        <v>624000</v>
+      </c>
+      <c r="N1288">
+        <v>300602.46000000002</v>
+      </c>
+      <c r="O1288">
+        <v>323397.53999999998</v>
+      </c>
+      <c r="P1288">
+        <v>24</v>
+      </c>
+      <c r="Q1288">
+        <v>1</v>
+      </c>
+      <c r="S1288" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1289" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1289">
+        <v>44</v>
+      </c>
+      <c r="I1289" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1289">
+        <v>1144000</v>
+      </c>
+      <c r="K1289">
+        <v>0</v>
+      </c>
+      <c r="L1289">
+        <v>0</v>
+      </c>
+      <c r="M1289">
+        <v>1146000</v>
+      </c>
+      <c r="N1289">
+        <v>576203.87</v>
+      </c>
+      <c r="O1289">
+        <v>569796.13</v>
+      </c>
+      <c r="P1289">
+        <v>41</v>
+      </c>
+      <c r="Q1289">
+        <v>1.07</v>
+      </c>
+      <c r="S1289" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1290" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1290">
+        <v>41</v>
+      </c>
+      <c r="I1290" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1290">
+        <v>1066000</v>
+      </c>
+      <c r="K1290">
+        <v>0</v>
+      </c>
+      <c r="L1290">
+        <v>0</v>
+      </c>
+      <c r="M1290">
+        <v>1071000</v>
+      </c>
+      <c r="N1290">
+        <v>442612.66</v>
+      </c>
+      <c r="O1290">
+        <v>628387.34</v>
+      </c>
+      <c r="P1290">
+        <v>34</v>
+      </c>
+      <c r="Q1290">
+        <v>1.21</v>
+      </c>
+      <c r="S1290" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1291" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1291">
+        <v>351</v>
+      </c>
+      <c r="I1291" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1291">
+        <v>6318000</v>
+      </c>
+      <c r="K1291">
+        <v>0</v>
+      </c>
+      <c r="L1291">
+        <v>0</v>
+      </c>
+      <c r="M1291">
+        <v>6715000</v>
+      </c>
+      <c r="N1291">
+        <v>3081945.74</v>
+      </c>
+      <c r="O1291">
+        <v>3633054.26</v>
+      </c>
+      <c r="P1291">
+        <v>303</v>
+      </c>
+      <c r="Q1291">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="S1291" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1292" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1292">
+        <v>42</v>
+      </c>
+      <c r="I1292" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1292">
+        <v>840000</v>
+      </c>
+      <c r="K1292">
+        <v>0</v>
+      </c>
+      <c r="L1292">
+        <v>0</v>
+      </c>
+      <c r="M1292">
+        <v>879000</v>
+      </c>
+      <c r="N1292">
+        <v>355720.85</v>
+      </c>
+      <c r="O1292">
+        <v>523279.15</v>
+      </c>
+      <c r="P1292">
+        <v>39</v>
+      </c>
+      <c r="Q1292">
+        <v>1.08</v>
+      </c>
+      <c r="S1292" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1293" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1293">
+        <v>1</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1293">
+        <v>35000</v>
+      </c>
+      <c r="K1293">
+        <v>0</v>
+      </c>
+      <c r="L1293">
+        <v>0</v>
+      </c>
+      <c r="M1293">
+        <v>35000</v>
+      </c>
+      <c r="N1293">
+        <v>16300</v>
+      </c>
+      <c r="O1293">
+        <v>18700</v>
+      </c>
+      <c r="P1293">
+        <v>1</v>
+      </c>
+      <c r="Q1293">
+        <v>1</v>
+      </c>
+      <c r="S1293" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1294" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1294">
+        <v>3</v>
+      </c>
+      <c r="I1294" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1294">
+        <v>105000</v>
+      </c>
+      <c r="K1294">
+        <v>0</v>
+      </c>
+      <c r="L1294">
+        <v>0</v>
+      </c>
+      <c r="M1294">
+        <v>105000</v>
+      </c>
+      <c r="N1294">
+        <v>47169.68</v>
+      </c>
+      <c r="O1294">
+        <v>57830.32</v>
+      </c>
+      <c r="P1294">
+        <v>3</v>
+      </c>
+      <c r="Q1294">
+        <v>1</v>
+      </c>
+      <c r="S1294" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1295" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1295">
+        <v>4</v>
+      </c>
+      <c r="I1295" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1295">
+        <v>140000</v>
+      </c>
+      <c r="K1295">
+        <v>0</v>
+      </c>
+      <c r="L1295">
+        <v>0</v>
+      </c>
+      <c r="M1295">
+        <v>140000</v>
+      </c>
+      <c r="N1295">
+        <v>56000</v>
+      </c>
+      <c r="O1295">
+        <v>84000</v>
+      </c>
+      <c r="P1295">
+        <v>4</v>
+      </c>
+      <c r="Q1295">
+        <v>1</v>
+      </c>
+      <c r="S1295" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1296" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1296">
+        <v>22</v>
+      </c>
+      <c r="I1296" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1296">
+        <v>616000</v>
+      </c>
+      <c r="K1296">
+        <v>0</v>
+      </c>
+      <c r="L1296">
+        <v>0</v>
+      </c>
+      <c r="M1296">
+        <v>619000</v>
+      </c>
+      <c r="N1296">
+        <v>292201.53000000003</v>
+      </c>
+      <c r="O1296">
+        <v>326798.46999999997</v>
+      </c>
+      <c r="P1296">
+        <v>20</v>
+      </c>
+      <c r="Q1296">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S1296" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1297" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1297">
+        <v>18</v>
+      </c>
+      <c r="I1297" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1297">
+        <v>540000</v>
+      </c>
+      <c r="K1297">
+        <v>0</v>
+      </c>
+      <c r="L1297">
+        <v>0</v>
+      </c>
+      <c r="M1297">
+        <v>542000</v>
+      </c>
+      <c r="N1297">
+        <v>238652.63</v>
+      </c>
+      <c r="O1297">
+        <v>303347.37</v>
+      </c>
+      <c r="P1297">
+        <v>18</v>
+      </c>
+      <c r="Q1297">
+        <v>1</v>
+      </c>
+      <c r="S1297" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1298" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1298">
+        <v>18</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1298">
+        <v>468000</v>
+      </c>
+      <c r="K1298">
+        <v>0</v>
+      </c>
+      <c r="L1298">
+        <v>0</v>
+      </c>
+      <c r="M1298">
+        <v>474000</v>
+      </c>
+      <c r="N1298">
+        <v>243685.09</v>
+      </c>
+      <c r="O1298">
+        <v>230314.91</v>
+      </c>
+      <c r="P1298">
+        <v>16</v>
+      </c>
+      <c r="Q1298">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1298" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1299" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1299">
+        <v>64</v>
+      </c>
+      <c r="I1299" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1299">
+        <v>1344000</v>
+      </c>
+      <c r="K1299">
+        <v>0</v>
+      </c>
+      <c r="L1299">
+        <v>0</v>
+      </c>
+      <c r="M1299">
+        <v>1346000</v>
+      </c>
+      <c r="N1299">
+        <v>716754.35</v>
+      </c>
+      <c r="O1299">
+        <v>629245.65</v>
+      </c>
+      <c r="P1299">
+        <v>59</v>
+      </c>
+      <c r="Q1299">
+        <v>1.08</v>
+      </c>
+      <c r="S1299" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1300" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1300">
+        <v>69</v>
+      </c>
+      <c r="I1300" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1300">
+        <v>1863000</v>
+      </c>
+      <c r="K1300">
+        <v>0</v>
+      </c>
+      <c r="L1300">
+        <v>0</v>
+      </c>
+      <c r="M1300">
+        <v>1863000</v>
+      </c>
+      <c r="N1300">
+        <v>695278.85</v>
+      </c>
+      <c r="O1300">
+        <v>1167721.06</v>
+      </c>
+      <c r="P1300">
+        <v>57</v>
+      </c>
+      <c r="Q1300">
+        <v>1.21</v>
+      </c>
+      <c r="S1300" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1301" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1301">
+        <v>6</v>
+      </c>
+      <c r="I1301" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1301">
+        <v>150000</v>
+      </c>
+      <c r="K1301">
+        <v>0</v>
+      </c>
+      <c r="L1301">
+        <v>0</v>
+      </c>
+      <c r="M1301">
+        <v>150000</v>
+      </c>
+      <c r="N1301">
+        <v>59418.63</v>
+      </c>
+      <c r="O1301">
+        <v>90581.37</v>
+      </c>
+      <c r="P1301">
+        <v>6</v>
+      </c>
+      <c r="Q1301">
+        <v>1</v>
+      </c>
+      <c r="S1301" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1302" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1302">
+        <v>42</v>
+      </c>
+      <c r="I1302" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1302">
+        <v>1302000</v>
+      </c>
+      <c r="K1302">
+        <v>0</v>
+      </c>
+      <c r="L1302">
+        <v>0</v>
+      </c>
+      <c r="M1302">
+        <v>1302000</v>
+      </c>
+      <c r="N1302">
+        <v>571609.18000000005</v>
+      </c>
+      <c r="O1302">
+        <v>730390.82</v>
+      </c>
+      <c r="P1302">
+        <v>32</v>
+      </c>
+      <c r="Q1302">
+        <v>1.31</v>
+      </c>
+      <c r="S1302" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1303" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1303">
+        <v>41</v>
+      </c>
+      <c r="I1303" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1303">
+        <v>1230000</v>
+      </c>
+      <c r="K1303">
+        <v>0</v>
+      </c>
+      <c r="L1303">
+        <v>0</v>
+      </c>
+      <c r="M1303">
+        <v>1230000</v>
+      </c>
+      <c r="N1303">
+        <v>531466.81000000006</v>
+      </c>
+      <c r="O1303">
+        <v>698533.19</v>
+      </c>
+      <c r="P1303">
+        <v>34</v>
+      </c>
+      <c r="Q1303">
+        <v>1.21</v>
+      </c>
+      <c r="S1303" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1304" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1304">
+        <v>29</v>
+      </c>
+      <c r="I1304" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1304">
+        <v>870000</v>
+      </c>
+      <c r="K1304">
+        <v>0</v>
+      </c>
+      <c r="L1304">
+        <v>0</v>
+      </c>
+      <c r="M1304">
+        <v>870000</v>
+      </c>
+      <c r="N1304">
+        <v>375860.57</v>
+      </c>
+      <c r="O1304">
+        <v>494139.43</v>
+      </c>
+      <c r="P1304">
+        <v>22</v>
+      </c>
+      <c r="Q1304">
+        <v>1.32</v>
+      </c>
+      <c r="S1304" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1305" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1305">
+        <v>43</v>
+      </c>
+      <c r="I1305" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1305">
+        <v>1290000</v>
+      </c>
+      <c r="K1305">
+        <v>0</v>
+      </c>
+      <c r="L1305">
+        <v>0</v>
+      </c>
+      <c r="M1305">
+        <v>1290000</v>
+      </c>
+      <c r="N1305">
+        <v>557311.56999999995</v>
+      </c>
+      <c r="O1305">
+        <v>732688.43</v>
+      </c>
+      <c r="P1305">
+        <v>39</v>
+      </c>
+      <c r="Q1305">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S1305" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1306" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1306">
+        <v>23</v>
+      </c>
+      <c r="I1306" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1306">
+        <v>828000</v>
+      </c>
+      <c r="K1306">
+        <v>0</v>
+      </c>
+      <c r="L1306">
+        <v>0</v>
+      </c>
+      <c r="M1306">
+        <v>828000</v>
+      </c>
+      <c r="N1306">
+        <v>528886.07999999996</v>
+      </c>
+      <c r="O1306">
+        <v>299113.92</v>
+      </c>
+      <c r="P1306">
+        <v>19</v>
+      </c>
+      <c r="Q1306">
+        <v>1.21</v>
+      </c>
+      <c r="S1306" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1307" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1307">
+        <v>1</v>
+      </c>
+      <c r="I1307" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1307">
+        <v>35000</v>
+      </c>
+      <c r="K1307">
+        <v>0</v>
+      </c>
+      <c r="L1307">
+        <v>0</v>
+      </c>
+      <c r="M1307">
+        <v>35000</v>
+      </c>
+      <c r="N1307">
+        <v>22935.51</v>
+      </c>
+      <c r="O1307">
+        <v>12064.49</v>
+      </c>
+      <c r="P1307">
+        <v>1</v>
+      </c>
+      <c r="Q1307">
+        <v>1</v>
+      </c>
+      <c r="S1307" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1308" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1308">
+        <v>27</v>
+      </c>
+      <c r="I1308" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1308">
+        <v>405000</v>
+      </c>
+      <c r="K1308">
+        <v>0</v>
+      </c>
+      <c r="L1308">
+        <v>0</v>
+      </c>
+      <c r="M1308">
+        <v>405000</v>
+      </c>
+      <c r="N1308">
+        <v>246190.86</v>
+      </c>
+      <c r="O1308">
+        <v>158809.14000000001</v>
+      </c>
+      <c r="P1308">
+        <v>16</v>
+      </c>
+      <c r="Q1308">
+        <v>1.69</v>
+      </c>
+      <c r="S1308" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1309" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1309">
+        <v>12</v>
+      </c>
+      <c r="I1309" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1309">
+        <v>240000</v>
+      </c>
+      <c r="K1309">
+        <v>0</v>
+      </c>
+      <c r="L1309">
+        <v>0</v>
+      </c>
+      <c r="M1309">
+        <v>243000</v>
+      </c>
+      <c r="N1309">
+        <v>128769.56</v>
+      </c>
+      <c r="O1309">
+        <v>114230.44</v>
+      </c>
+      <c r="P1309">
+        <v>11</v>
+      </c>
+      <c r="Q1309">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1309" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1310" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1310">
+        <v>12</v>
+      </c>
+      <c r="I1310" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1310">
+        <v>288000</v>
+      </c>
+      <c r="K1310">
+        <v>0</v>
+      </c>
+      <c r="L1310">
+        <v>0</v>
+      </c>
+      <c r="M1310">
+        <v>288000</v>
+      </c>
+      <c r="N1310">
+        <v>133144.16</v>
+      </c>
+      <c r="O1310">
+        <v>154855.84</v>
+      </c>
+      <c r="P1310">
+        <v>11</v>
+      </c>
+      <c r="Q1310">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S1310" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1311" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1311">
+        <v>7</v>
+      </c>
+      <c r="I1311" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1311">
+        <v>168000</v>
+      </c>
+      <c r="K1311">
+        <v>0</v>
+      </c>
+      <c r="L1311">
+        <v>0</v>
+      </c>
+      <c r="M1311">
+        <v>168000</v>
+      </c>
+      <c r="N1311">
+        <v>73678.8</v>
+      </c>
+      <c r="O1311">
+        <v>94321.2</v>
+      </c>
+      <c r="P1311">
+        <v>6</v>
+      </c>
+      <c r="Q1311">
+        <v>1.17</v>
+      </c>
+      <c r="S1311" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1312" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1312">
+        <v>9</v>
+      </c>
+      <c r="I1312" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1312">
+        <v>216000</v>
+      </c>
+      <c r="K1312">
+        <v>0</v>
+      </c>
+      <c r="L1312">
+        <v>0</v>
+      </c>
+      <c r="M1312">
+        <v>216000</v>
+      </c>
+      <c r="N1312">
+        <v>99852.95</v>
+      </c>
+      <c r="O1312">
+        <v>116147.05</v>
+      </c>
+      <c r="P1312">
+        <v>8</v>
+      </c>
+      <c r="Q1312">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1312" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1313" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1313">
+        <v>57</v>
+      </c>
+      <c r="I1313" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1313">
+        <v>1311000</v>
+      </c>
+      <c r="K1313">
+        <v>0</v>
+      </c>
+      <c r="L1313">
+        <v>0</v>
+      </c>
+      <c r="M1313">
+        <v>1311000</v>
+      </c>
+      <c r="N1313">
+        <v>536550.34</v>
+      </c>
+      <c r="O1313">
+        <v>774449.66</v>
+      </c>
+      <c r="P1313">
+        <v>43</v>
+      </c>
+      <c r="Q1313">
+        <v>1.33</v>
+      </c>
+      <c r="S1313" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1314" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1314">
+        <v>11</v>
+      </c>
+      <c r="I1314" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1314">
+        <v>308000</v>
+      </c>
+      <c r="K1314">
+        <v>0</v>
+      </c>
+      <c r="L1314">
+        <v>0</v>
+      </c>
+      <c r="M1314">
+        <v>308000</v>
+      </c>
+      <c r="N1314">
+        <v>114276.14</v>
+      </c>
+      <c r="O1314">
+        <v>193723.86</v>
+      </c>
+      <c r="P1314">
+        <v>11</v>
+      </c>
+      <c r="Q1314">
+        <v>1</v>
+      </c>
+      <c r="S1314" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1315" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1315">
+        <v>11</v>
+      </c>
+      <c r="I1315" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1315">
+        <v>308000</v>
+      </c>
+      <c r="K1315">
+        <v>0</v>
+      </c>
+      <c r="L1315">
+        <v>0</v>
+      </c>
+      <c r="M1315">
+        <v>308000</v>
+      </c>
+      <c r="N1315">
+        <v>114245.12</v>
+      </c>
+      <c r="O1315">
+        <v>193754.88</v>
+      </c>
+      <c r="P1315">
+        <v>10</v>
+      </c>
+      <c r="Q1315">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S1315" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1316" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1316">
+        <v>29</v>
+      </c>
+      <c r="I1316" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1316">
+        <v>812000</v>
+      </c>
+      <c r="K1316">
+        <v>0</v>
+      </c>
+      <c r="L1316">
+        <v>0</v>
+      </c>
+      <c r="M1316">
+        <v>815000</v>
+      </c>
+      <c r="N1316">
+        <v>301195.90999999997</v>
+      </c>
+      <c r="O1316">
+        <v>513804.09</v>
+      </c>
+      <c r="P1316">
+        <v>28</v>
+      </c>
+      <c r="Q1316">
+        <v>1.04</v>
+      </c>
+      <c r="S1316" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1317" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1317">
+        <v>55</v>
+      </c>
+      <c r="I1317" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1317">
+        <v>1540000</v>
+      </c>
+      <c r="K1317">
+        <v>0</v>
+      </c>
+      <c r="L1317">
+        <v>0</v>
+      </c>
+      <c r="M1317">
+        <v>1540000</v>
+      </c>
+      <c r="N1317">
+        <v>606016.53</v>
+      </c>
+      <c r="O1317">
+        <v>933983.47</v>
+      </c>
+      <c r="P1317">
+        <v>45</v>
+      </c>
+      <c r="Q1317">
+        <v>1.22</v>
+      </c>
+      <c r="S1317" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1318" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1318">
+        <v>8</v>
+      </c>
+      <c r="I1318" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1318">
+        <v>0</v>
+      </c>
+      <c r="K1318">
+        <v>0</v>
+      </c>
+      <c r="L1318">
+        <v>0</v>
+      </c>
+      <c r="M1318">
+        <v>18000</v>
+      </c>
+      <c r="N1318">
+        <v>13989.15</v>
+      </c>
+      <c r="O1318">
+        <v>4010.85</v>
+      </c>
+      <c r="P1318">
+        <v>7</v>
+      </c>
+      <c r="Q1318">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="S1318" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1319" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1319">
+        <v>5</v>
+      </c>
+      <c r="I1319" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1319">
+        <v>75000</v>
+      </c>
+      <c r="K1319">
+        <v>0</v>
+      </c>
+      <c r="L1319">
+        <v>0</v>
+      </c>
+      <c r="M1319">
+        <v>75000</v>
+      </c>
+      <c r="N1319">
+        <v>35600</v>
+      </c>
+      <c r="O1319">
+        <v>39400</v>
+      </c>
+      <c r="P1319">
+        <v>5</v>
+      </c>
+      <c r="Q1319">
+        <v>1</v>
+      </c>
+      <c r="S1319" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1320" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1320" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1320">
+        <v>25</v>
+      </c>
+      <c r="I1320" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1320">
+        <v>125000</v>
+      </c>
+      <c r="K1320">
+        <v>0</v>
+      </c>
+      <c r="L1320">
+        <v>0</v>
+      </c>
+      <c r="M1320">
+        <v>128000</v>
+      </c>
+      <c r="N1320">
+        <v>7380.22</v>
+      </c>
+      <c r="O1320">
+        <v>120619.78</v>
+      </c>
+      <c r="P1320">
+        <v>21</v>
+      </c>
+      <c r="Q1320">
+        <v>1.19</v>
+      </c>
+      <c r="S1320" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1321" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1321">
+        <v>277</v>
+      </c>
+      <c r="I1321" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1321">
+        <v>1385000</v>
+      </c>
+      <c r="K1321">
+        <v>0</v>
+      </c>
+      <c r="L1321">
+        <v>0</v>
+      </c>
+      <c r="M1321">
+        <v>1396000</v>
+      </c>
+      <c r="N1321">
+        <v>1041.6600000000001</v>
+      </c>
+      <c r="O1321">
+        <v>1394958.34</v>
+      </c>
+      <c r="P1321">
+        <v>213</v>
+      </c>
+      <c r="Q1321">
+        <v>1.3</v>
+      </c>
+      <c r="S1321" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1322" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1322">
+        <v>177</v>
+      </c>
+      <c r="I1322" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1322">
+        <v>708000</v>
+      </c>
+      <c r="K1322">
+        <v>0</v>
+      </c>
+      <c r="L1322">
+        <v>0</v>
+      </c>
+      <c r="M1322">
+        <v>708000</v>
+      </c>
+      <c r="N1322">
+        <v>531000</v>
+      </c>
+      <c r="O1322">
+        <v>177000</v>
+      </c>
+      <c r="P1322">
+        <v>79</v>
+      </c>
+      <c r="Q1322">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="S1322" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1323" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1323">
+        <v>24</v>
+      </c>
+      <c r="I1323" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1323">
+        <v>120000</v>
+      </c>
+      <c r="K1323">
+        <v>0</v>
+      </c>
+      <c r="L1323">
+        <v>0</v>
+      </c>
+      <c r="M1323">
+        <v>120000</v>
+      </c>
+      <c r="N1323">
+        <v>96000</v>
+      </c>
+      <c r="O1323">
+        <v>24000</v>
+      </c>
+      <c r="P1323">
+        <v>20</v>
+      </c>
+      <c r="Q1323">
+        <v>1.2</v>
+      </c>
+      <c r="S1323" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1324" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1324">
+        <v>5</v>
+      </c>
+      <c r="I1324" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1324">
+        <v>25000</v>
+      </c>
+      <c r="K1324">
+        <v>0</v>
+      </c>
+      <c r="L1324">
+        <v>0</v>
+      </c>
+      <c r="M1324">
+        <v>25000</v>
+      </c>
+      <c r="N1324">
+        <v>78333.350000000006</v>
+      </c>
+      <c r="O1324">
+        <v>-53333.35</v>
+      </c>
+      <c r="P1324">
+        <v>5</v>
+      </c>
+      <c r="Q1324">
+        <v>1</v>
+      </c>
+      <c r="S1324" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1325" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1325">
+        <v>8</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1325">
+        <v>120000</v>
+      </c>
+      <c r="K1325">
+        <v>0</v>
+      </c>
+      <c r="L1325">
+        <v>0</v>
+      </c>
+      <c r="M1325">
+        <v>120000</v>
+      </c>
+      <c r="N1325">
+        <v>35760</v>
+      </c>
+      <c r="O1325">
+        <v>84240</v>
+      </c>
+      <c r="P1325">
+        <v>8</v>
+      </c>
+      <c r="Q1325">
+        <v>1</v>
+      </c>
+      <c r="S1325" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1326" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1326">
+        <v>8</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1326">
+        <v>104000</v>
+      </c>
+      <c r="K1326">
+        <v>0</v>
+      </c>
+      <c r="L1326">
+        <v>0</v>
+      </c>
+      <c r="M1326">
+        <v>104000</v>
+      </c>
+      <c r="N1326">
+        <v>31291.4</v>
+      </c>
+      <c r="O1326">
+        <v>72708.600000000006</v>
+      </c>
+      <c r="P1326">
+        <v>7</v>
+      </c>
+      <c r="Q1326">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="S1326" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1327" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1327">
+        <v>4</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1327">
+        <v>52000</v>
+      </c>
+      <c r="K1327">
+        <v>0</v>
+      </c>
+      <c r="L1327">
+        <v>0</v>
+      </c>
+      <c r="M1327">
+        <v>52000</v>
+      </c>
+      <c r="N1327">
+        <v>15439</v>
+      </c>
+      <c r="O1327">
+        <v>36561</v>
+      </c>
+      <c r="P1327">
+        <v>4</v>
+      </c>
+      <c r="Q1327">
+        <v>1</v>
+      </c>
+      <c r="S1327" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1328" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1328">
+        <v>4</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1328">
+        <v>40000</v>
+      </c>
+      <c r="K1328">
+        <v>0</v>
+      </c>
+      <c r="L1328">
+        <v>0</v>
+      </c>
+      <c r="M1328">
+        <v>42000</v>
+      </c>
+      <c r="N1328">
+        <v>13408.8</v>
+      </c>
+      <c r="O1328">
+        <v>28591.200000000001</v>
+      </c>
+      <c r="P1328">
+        <v>4</v>
+      </c>
+      <c r="Q1328">
+        <v>1</v>
+      </c>
+      <c r="S1328" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1329" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1329">
+        <v>42</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1329">
+        <v>420000</v>
+      </c>
+      <c r="K1329">
+        <v>0</v>
+      </c>
+      <c r="L1329">
+        <v>0</v>
+      </c>
+      <c r="M1329">
+        <v>420000</v>
+      </c>
+      <c r="N1329">
+        <v>38455.199999999997</v>
+      </c>
+      <c r="O1329">
+        <v>381544.8</v>
+      </c>
+      <c r="P1329">
+        <v>29</v>
+      </c>
+      <c r="Q1329">
+        <v>1.45</v>
+      </c>
+      <c r="S1329" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1330" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1330">
+        <v>113</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1330">
+        <v>565000</v>
+      </c>
+      <c r="K1330">
+        <v>0</v>
+      </c>
+      <c r="L1330">
+        <v>0</v>
+      </c>
+      <c r="M1330">
+        <v>565000</v>
+      </c>
+      <c r="N1330">
+        <v>88145.65</v>
+      </c>
+      <c r="O1330">
+        <v>476854.35</v>
+      </c>
+      <c r="P1330">
+        <v>85</v>
+      </c>
+      <c r="Q1330">
+        <v>1.33</v>
+      </c>
+      <c r="S1330" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1331" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1331">
+        <v>113</v>
+      </c>
+      <c r="I1331" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1331">
+        <v>565000</v>
+      </c>
+      <c r="K1331">
+        <v>0</v>
+      </c>
+      <c r="L1331">
+        <v>0</v>
+      </c>
+      <c r="M1331">
+        <v>567000</v>
+      </c>
+      <c r="N1331">
+        <v>72828.5</v>
+      </c>
+      <c r="O1331">
+        <v>494171.5</v>
+      </c>
+      <c r="P1331">
+        <v>78</v>
+      </c>
+      <c r="Q1331">
+        <v>1.45</v>
+      </c>
+      <c r="S1331" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1332" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1332">
+        <v>57</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1332">
+        <v>456000</v>
+      </c>
+      <c r="K1332">
+        <v>0</v>
+      </c>
+      <c r="L1332">
+        <v>0</v>
+      </c>
+      <c r="M1332">
+        <v>456000</v>
+      </c>
+      <c r="N1332">
+        <v>44462.85</v>
+      </c>
+      <c r="O1332">
+        <v>411537.15</v>
+      </c>
+      <c r="P1332">
+        <v>41</v>
+      </c>
+      <c r="Q1332">
+        <v>1.39</v>
+      </c>
+      <c r="S1332" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1333" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1333" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1333">
+        <v>18</v>
+      </c>
+      <c r="I1333" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1333">
+        <v>360000</v>
+      </c>
+      <c r="K1333">
+        <v>0</v>
+      </c>
+      <c r="L1333">
+        <v>0</v>
+      </c>
+      <c r="M1333">
+        <v>360000</v>
+      </c>
+      <c r="N1333">
+        <v>306000</v>
+      </c>
+      <c r="O1333">
+        <v>54000</v>
+      </c>
+      <c r="P1333">
+        <v>17</v>
+      </c>
+      <c r="Q1333">
+        <v>1.06</v>
+      </c>
+      <c r="S1333" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1334" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1334" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1334">
+        <v>7</v>
+      </c>
+      <c r="I1334" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1334">
+        <v>140000</v>
+      </c>
+      <c r="K1334">
+        <v>0</v>
+      </c>
+      <c r="L1334">
+        <v>0</v>
+      </c>
+      <c r="M1334">
+        <v>140000</v>
+      </c>
+      <c r="N1334">
+        <v>119000</v>
+      </c>
+      <c r="O1334">
+        <v>21000</v>
+      </c>
+      <c r="P1334">
+        <v>7</v>
+      </c>
+      <c r="Q1334">
+        <v>1</v>
+      </c>
+      <c r="S1334" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1335" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1335" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1335">
+        <v>8</v>
+      </c>
+      <c r="I1335" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1335">
+        <v>120000</v>
+      </c>
+      <c r="K1335">
+        <v>0</v>
+      </c>
+      <c r="L1335">
+        <v>0</v>
+      </c>
+      <c r="M1335">
+        <v>120000</v>
+      </c>
+      <c r="N1335">
+        <v>96000</v>
+      </c>
+      <c r="O1335">
+        <v>24000</v>
+      </c>
+      <c r="P1335">
+        <v>8</v>
+      </c>
+      <c r="Q1335">
+        <v>1</v>
+      </c>
+      <c r="S1335" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1336" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1336" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1336">
+        <v>9</v>
+      </c>
+      <c r="I1336" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1336">
+        <v>180000</v>
+      </c>
+      <c r="K1336">
+        <v>0</v>
+      </c>
+      <c r="L1336">
+        <v>0</v>
+      </c>
+      <c r="M1336">
+        <v>180000</v>
+      </c>
+      <c r="N1336">
+        <v>153000</v>
+      </c>
+      <c r="O1336">
+        <v>27000</v>
+      </c>
+      <c r="P1336">
+        <v>9</v>
+      </c>
+      <c r="Q1336">
+        <v>1</v>
+      </c>
+      <c r="S1336" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1337" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1337" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1337">
+        <v>42</v>
+      </c>
+      <c r="I1337" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1337">
+        <v>420000</v>
+      </c>
+      <c r="K1337">
+        <v>0</v>
+      </c>
+      <c r="L1337">
+        <v>0</v>
+      </c>
+      <c r="M1337">
+        <v>420000</v>
+      </c>
+      <c r="N1337">
+        <v>159551.73000000001</v>
+      </c>
+      <c r="O1337">
+        <v>260448.27</v>
+      </c>
+      <c r="P1337">
+        <v>32</v>
+      </c>
+      <c r="Q1337">
+        <v>1.31</v>
+      </c>
+      <c r="S1337" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1338" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1338" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1338">
+        <v>87</v>
+      </c>
+      <c r="I1338" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1338">
+        <v>870000</v>
+      </c>
+      <c r="K1338">
+        <v>0</v>
+      </c>
+      <c r="L1338">
+        <v>0</v>
+      </c>
+      <c r="M1338">
+        <v>870000</v>
+      </c>
+      <c r="N1338">
+        <v>479112.49</v>
+      </c>
+      <c r="O1338">
+        <v>390887.51</v>
+      </c>
+      <c r="P1338">
+        <v>60</v>
+      </c>
+      <c r="Q1338">
+        <v>1.45</v>
+      </c>
+      <c r="S1338" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1339" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1339" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1339">
+        <v>4</v>
+      </c>
+      <c r="I1339" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1339">
+        <v>40000</v>
+      </c>
+      <c r="K1339">
+        <v>0</v>
+      </c>
+      <c r="L1339">
+        <v>0</v>
+      </c>
+      <c r="M1339">
+        <v>40000</v>
+      </c>
+      <c r="N1339">
+        <v>10566.3</v>
+      </c>
+      <c r="O1339">
+        <v>29433.7</v>
+      </c>
+      <c r="P1339">
+        <v>4</v>
+      </c>
+      <c r="Q1339">
+        <v>1</v>
+      </c>
+      <c r="S1339" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1340" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1340" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1340">
+        <v>5</v>
+      </c>
+      <c r="I1340" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1340">
+        <v>65000</v>
+      </c>
+      <c r="K1340">
+        <v>0</v>
+      </c>
+      <c r="L1340">
+        <v>0</v>
+      </c>
+      <c r="M1340">
+        <v>65000</v>
+      </c>
+      <c r="N1340">
+        <v>17671.45</v>
+      </c>
+      <c r="O1340">
+        <v>47328.55</v>
+      </c>
+      <c r="P1340">
+        <v>4</v>
+      </c>
+      <c r="Q1340">
+        <v>1.25</v>
+      </c>
+      <c r="S1340" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1341" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1341" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1341">
+        <v>6</v>
+      </c>
+      <c r="I1341" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1341">
+        <v>90000</v>
+      </c>
+      <c r="K1341">
+        <v>0</v>
+      </c>
+      <c r="L1341">
+        <v>0</v>
+      </c>
+      <c r="M1341">
+        <v>90000</v>
+      </c>
+      <c r="N1341">
+        <v>25115.200000000001</v>
+      </c>
+      <c r="O1341">
+        <v>64884.800000000003</v>
+      </c>
+      <c r="P1341">
+        <v>5</v>
+      </c>
+      <c r="Q1341">
+        <v>1.2</v>
+      </c>
+      <c r="S1341" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1342" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1342" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1342" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1342" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1342">
+        <v>4</v>
+      </c>
+      <c r="I1342" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1342">
+        <v>40000</v>
+      </c>
+      <c r="K1342">
+        <v>0</v>
+      </c>
+      <c r="L1342">
+        <v>0</v>
+      </c>
+      <c r="M1342">
+        <v>40000</v>
+      </c>
+      <c r="N1342">
+        <v>9148.7999999999993</v>
+      </c>
+      <c r="O1342">
+        <v>30851.200000000001</v>
+      </c>
+      <c r="P1342">
+        <v>4</v>
+      </c>
+      <c r="Q1342">
+        <v>1</v>
+      </c>
+      <c r="S1342" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1343" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1343" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1343" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1343" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1343">
+        <v>6</v>
+      </c>
+      <c r="I1343" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1343">
+        <v>78000</v>
+      </c>
+      <c r="K1343">
+        <v>0</v>
+      </c>
+      <c r="L1343">
+        <v>0</v>
+      </c>
+      <c r="M1343">
+        <v>78000</v>
+      </c>
+      <c r="N1343">
+        <v>16215</v>
+      </c>
+      <c r="O1343">
+        <v>61785</v>
+      </c>
+      <c r="P1343">
+        <v>5</v>
+      </c>
+      <c r="Q1343">
+        <v>1.2</v>
+      </c>
+      <c r="S1343" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1344" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1344" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1344" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1344" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1344" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1344">
+        <v>16</v>
+      </c>
+      <c r="I1344" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1344">
+        <v>160000</v>
+      </c>
+      <c r="K1344">
+        <v>0</v>
+      </c>
+      <c r="L1344">
+        <v>0</v>
+      </c>
+      <c r="M1344">
+        <v>160000</v>
+      </c>
+      <c r="N1344">
+        <v>49884.800000000003</v>
+      </c>
+      <c r="O1344">
+        <v>110115.2</v>
+      </c>
+      <c r="P1344">
+        <v>15</v>
+      </c>
+      <c r="Q1344">
+        <v>1.07</v>
+      </c>
+      <c r="S1344" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1345" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1345" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1345" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1345">
+        <v>39</v>
+      </c>
+      <c r="I1345" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1345">
+        <v>195000</v>
+      </c>
+      <c r="K1345">
+        <v>0</v>
+      </c>
+      <c r="L1345">
+        <v>0</v>
+      </c>
+      <c r="M1345">
+        <v>195000</v>
+      </c>
+      <c r="N1345">
+        <v>0</v>
+      </c>
+      <c r="O1345">
+        <v>195000</v>
+      </c>
+      <c r="P1345">
+        <v>36</v>
+      </c>
+      <c r="Q1345">
+        <v>1.08</v>
+      </c>
+      <c r="S1345" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1346" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1346" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1346" t="s">
+        <v>302</v>
+      </c>
+      <c r="H1346">
+        <v>41</v>
+      </c>
+      <c r="I1346" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1346">
+        <v>123000</v>
+      </c>
+      <c r="K1346">
+        <v>0</v>
+      </c>
+      <c r="L1346">
+        <v>0</v>
+      </c>
+      <c r="M1346">
+        <v>123000</v>
+      </c>
+      <c r="N1346">
+        <v>0</v>
+      </c>
+      <c r="O1346">
+        <v>123000</v>
+      </c>
+      <c r="P1346">
+        <v>34</v>
+      </c>
+      <c r="Q1346">
+        <v>1.21</v>
+      </c>
+      <c r="S1346" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1347" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1347" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1347" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1347">
+        <v>533</v>
+      </c>
+      <c r="I1347" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1347">
+        <v>2665000</v>
+      </c>
+      <c r="K1347">
+        <v>0</v>
+      </c>
+      <c r="L1347">
+        <v>0</v>
+      </c>
+      <c r="M1347">
+        <v>2683000</v>
+      </c>
+      <c r="N1347">
+        <v>870154.12</v>
+      </c>
+      <c r="O1347">
+        <v>1812845.88</v>
+      </c>
+      <c r="P1347">
+        <v>376</v>
+      </c>
+      <c r="Q1347">
+        <v>1.42</v>
+      </c>
+      <c r="S1347" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1348" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1348" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1348" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1348">
+        <v>25</v>
+      </c>
+      <c r="I1348" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1348">
+        <v>250000</v>
+      </c>
+      <c r="K1348">
+        <v>0</v>
+      </c>
+      <c r="L1348">
+        <v>0</v>
+      </c>
+      <c r="M1348">
+        <v>250000</v>
+      </c>
+      <c r="N1348">
+        <v>7432.75</v>
+      </c>
+      <c r="O1348">
+        <v>242567.25</v>
+      </c>
+      <c r="P1348">
+        <v>24</v>
+      </c>
+      <c r="Q1348">
+        <v>1.04</v>
+      </c>
+      <c r="S1348" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1349" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1349" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1349" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1349">
+        <v>36</v>
+      </c>
+      <c r="I1349" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1349">
+        <v>432000</v>
+      </c>
+      <c r="K1349">
+        <v>0</v>
+      </c>
+      <c r="L1349">
+        <v>0</v>
+      </c>
+      <c r="M1349">
+        <v>452000</v>
+      </c>
+      <c r="N1349">
+        <v>73456.31</v>
+      </c>
+      <c r="O1349">
+        <v>378543.71</v>
+      </c>
+      <c r="P1349">
+        <v>32</v>
+      </c>
+      <c r="Q1349">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1349" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1350" t="s">
+        <v>327</v>
+      </c>
+      <c r="D1350" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1350" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1350">
+        <v>8</v>
+      </c>
+      <c r="I1350" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1350">
+        <v>16000</v>
+      </c>
+      <c r="K1350">
+        <v>0</v>
+      </c>
+      <c r="L1350">
+        <v>0</v>
+      </c>
+      <c r="M1350">
+        <v>16000</v>
+      </c>
+      <c r="N1350">
+        <v>0</v>
+      </c>
+      <c r="O1350">
+        <v>16000</v>
+      </c>
+      <c r="P1350">
+        <v>8</v>
+      </c>
+      <c r="Q1350">
+        <v>1</v>
+      </c>
+      <c r="S1350" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1351" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1351" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1351">
+        <v>275</v>
+      </c>
+      <c r="I1351" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1351">
+        <v>1375000</v>
+      </c>
+      <c r="K1351">
+        <v>0</v>
+      </c>
+      <c r="L1351">
+        <v>0</v>
+      </c>
+      <c r="M1351">
+        <v>1375000</v>
+      </c>
+      <c r="N1351">
+        <v>893750</v>
+      </c>
+      <c r="O1351">
+        <v>481250</v>
+      </c>
+      <c r="P1351">
+        <v>197</v>
+      </c>
+      <c r="Q1351">
+        <v>1.4</v>
+      </c>
+      <c r="S1351" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1352" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1352">
+        <v>107</v>
+      </c>
+      <c r="I1352" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1352">
+        <v>535000</v>
+      </c>
+      <c r="K1352">
+        <v>0</v>
+      </c>
+      <c r="L1352">
+        <v>0</v>
+      </c>
+      <c r="M1352">
+        <v>535000</v>
+      </c>
+      <c r="N1352">
+        <v>347750</v>
+      </c>
+      <c r="O1352">
+        <v>187250</v>
+      </c>
+      <c r="P1352">
+        <v>93</v>
+      </c>
+      <c r="Q1352">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="S1352" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1353" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1353" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1353">
+        <v>176</v>
+      </c>
+      <c r="I1353" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1353">
+        <v>704000</v>
+      </c>
+      <c r="K1353">
+        <v>0</v>
+      </c>
+      <c r="L1353">
+        <v>0</v>
+      </c>
+      <c r="M1353">
+        <v>704000</v>
+      </c>
+      <c r="N1353">
+        <v>457600</v>
+      </c>
+      <c r="O1353">
+        <v>246400</v>
+      </c>
+      <c r="P1353">
+        <v>110</v>
+      </c>
+      <c r="Q1353">
+        <v>1.6</v>
+      </c>
+      <c r="S1353" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1354" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1354">
+        <v>120</v>
+      </c>
+      <c r="I1354" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1354">
+        <v>600000</v>
+      </c>
+      <c r="K1354">
+        <v>0</v>
+      </c>
+      <c r="L1354">
+        <v>0</v>
+      </c>
+      <c r="M1354">
+        <v>600000</v>
+      </c>
+      <c r="N1354">
+        <v>390000</v>
+      </c>
+      <c r="O1354">
+        <v>210000</v>
+      </c>
+      <c r="P1354">
+        <v>90</v>
+      </c>
+      <c r="Q1354">
+        <v>1.33</v>
+      </c>
+      <c r="S1354" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1355" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1355" t="s">
+        <v>335</v>
+      </c>
+      <c r="H1355">
+        <v>147</v>
+      </c>
+      <c r="I1355" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1355">
+        <v>1470000</v>
+      </c>
+      <c r="K1355">
+        <v>0</v>
+      </c>
+      <c r="L1355">
+        <v>0</v>
+      </c>
+      <c r="M1355">
+        <v>1470000</v>
+      </c>
+      <c r="N1355">
+        <v>955500</v>
+      </c>
+      <c r="O1355">
+        <v>514500</v>
+      </c>
+      <c r="P1355">
+        <v>109</v>
+      </c>
+      <c r="Q1355">
+        <v>1.35</v>
+      </c>
+      <c r="S1355" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1356" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1356" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1356">
+        <v>163</v>
+      </c>
+      <c r="I1356" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1356">
+        <v>815000</v>
+      </c>
+      <c r="K1356">
+        <v>0</v>
+      </c>
+      <c r="L1356">
+        <v>0</v>
+      </c>
+      <c r="M1356">
+        <v>815000</v>
+      </c>
+      <c r="N1356">
+        <v>529750</v>
+      </c>
+      <c r="O1356">
+        <v>285250</v>
+      </c>
+      <c r="P1356">
+        <v>109</v>
+      </c>
+      <c r="Q1356">
+        <v>1.5</v>
+      </c>
+      <c r="S1356" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1357" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1357" t="s">
+        <v>339</v>
+      </c>
+      <c r="H1357">
+        <v>102</v>
+      </c>
+      <c r="I1357" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1357">
+        <v>408000</v>
+      </c>
+      <c r="K1357">
+        <v>0</v>
+      </c>
+      <c r="L1357">
+        <v>0</v>
+      </c>
+      <c r="M1357">
+        <v>408000</v>
+      </c>
+      <c r="N1357">
+        <v>265200</v>
+      </c>
+      <c r="O1357">
+        <v>142800</v>
+      </c>
+      <c r="P1357">
+        <v>72</v>
+      </c>
+      <c r="Q1357">
+        <v>1.42</v>
+      </c>
+      <c r="S1357" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1358" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1358" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1358">
+        <v>7</v>
+      </c>
+      <c r="I1358" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1358">
+        <v>350000</v>
+      </c>
+      <c r="K1358">
+        <v>0</v>
+      </c>
+      <c r="L1358">
+        <v>0</v>
+      </c>
+      <c r="M1358">
+        <v>350000</v>
+      </c>
+      <c r="N1358">
+        <v>280000</v>
+      </c>
+      <c r="O1358">
+        <v>70000</v>
+      </c>
+      <c r="P1358">
+        <v>5</v>
+      </c>
+      <c r="Q1358">
+        <v>1.4</v>
+      </c>
+      <c r="S1358" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1359" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1359" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1359">
+        <v>4</v>
+      </c>
+      <c r="I1359" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1359">
+        <v>52000</v>
+      </c>
+      <c r="K1359">
+        <v>0</v>
+      </c>
+      <c r="L1359">
+        <v>0</v>
+      </c>
+      <c r="M1359">
+        <v>52000</v>
+      </c>
+      <c r="N1359">
+        <v>40000</v>
+      </c>
+      <c r="O1359">
+        <v>12000</v>
+      </c>
+      <c r="P1359">
+        <v>4</v>
+      </c>
+      <c r="Q1359">
+        <v>1</v>
+      </c>
+      <c r="S1359" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1360" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1360" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1360">
+        <v>13</v>
+      </c>
+      <c r="I1360" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1360">
+        <v>260000</v>
+      </c>
+      <c r="K1360">
+        <v>0</v>
+      </c>
+      <c r="L1360">
+        <v>0</v>
+      </c>
+      <c r="M1360">
+        <v>260000</v>
+      </c>
+      <c r="N1360">
+        <v>195000</v>
+      </c>
+      <c r="O1360">
+        <v>65000</v>
+      </c>
+      <c r="P1360">
+        <v>12</v>
+      </c>
+      <c r="Q1360">
+        <v>1.08</v>
+      </c>
+      <c r="S1360" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1361" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1361" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1361">
+        <v>22</v>
+      </c>
+      <c r="I1361" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1361">
+        <v>110000</v>
+      </c>
+      <c r="K1361">
+        <v>0</v>
+      </c>
+      <c r="L1361">
+        <v>0</v>
+      </c>
+      <c r="M1361">
+        <v>110000</v>
+      </c>
+      <c r="N1361">
+        <v>62260</v>
+      </c>
+      <c r="O1361">
+        <v>47740</v>
+      </c>
+      <c r="P1361">
+        <v>16</v>
+      </c>
+      <c r="Q1361">
+        <v>1.38</v>
+      </c>
+      <c r="S1361" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1362" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1362" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1362">
+        <v>7</v>
+      </c>
+      <c r="I1362" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1362">
+        <v>91000</v>
+      </c>
+      <c r="K1362">
+        <v>0</v>
+      </c>
+      <c r="L1362">
+        <v>0</v>
+      </c>
+      <c r="M1362">
+        <v>91000</v>
+      </c>
+      <c r="N1362">
+        <v>70000</v>
+      </c>
+      <c r="O1362">
+        <v>21000</v>
+      </c>
+      <c r="P1362">
+        <v>6</v>
+      </c>
+      <c r="Q1362">
+        <v>1.17</v>
+      </c>
+      <c r="S1362" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1363" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1363" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1363">
+        <v>12</v>
+      </c>
+      <c r="I1363" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1363">
+        <v>204000</v>
+      </c>
+      <c r="K1363">
+        <v>0</v>
+      </c>
+      <c r="L1363">
+        <v>0</v>
+      </c>
+      <c r="M1363">
+        <v>204000</v>
+      </c>
+      <c r="N1363">
+        <v>168000</v>
+      </c>
+      <c r="O1363">
+        <v>36000</v>
+      </c>
+      <c r="P1363">
+        <v>12</v>
+      </c>
+      <c r="Q1363">
+        <v>1</v>
+      </c>
+      <c r="S1363" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1364" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1364" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1364">
+        <v>40</v>
+      </c>
+      <c r="I1364" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1364">
+        <v>400000</v>
+      </c>
+      <c r="K1364">
+        <v>0</v>
+      </c>
+      <c r="L1364">
+        <v>0</v>
+      </c>
+      <c r="M1364">
+        <v>400000</v>
+      </c>
+      <c r="N1364">
+        <v>317878.8</v>
+      </c>
+      <c r="O1364">
+        <v>82121.2</v>
+      </c>
+      <c r="P1364">
+        <v>26</v>
+      </c>
+      <c r="Q1364">
+        <v>1.54</v>
+      </c>
+      <c r="S1364" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1365" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1365" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1365">
+        <v>5</v>
+      </c>
+      <c r="I1365" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1365">
+        <v>65000</v>
+      </c>
+      <c r="K1365">
+        <v>0</v>
+      </c>
+      <c r="L1365">
+        <v>0</v>
+      </c>
+      <c r="M1365">
+        <v>65000</v>
+      </c>
+      <c r="N1365">
+        <v>50000</v>
+      </c>
+      <c r="O1365">
+        <v>15000</v>
+      </c>
+      <c r="P1365">
+        <v>5</v>
+      </c>
+      <c r="Q1365">
+        <v>1</v>
+      </c>
+      <c r="S1365" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1366" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1366">
+        <v>19</v>
+      </c>
+      <c r="I1366" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1366">
+        <v>228000</v>
+      </c>
+      <c r="K1366">
+        <v>0</v>
+      </c>
+      <c r="L1366">
+        <v>0</v>
+      </c>
+      <c r="M1366">
+        <v>228000</v>
+      </c>
+      <c r="N1366">
+        <v>171000</v>
+      </c>
+      <c r="O1366">
+        <v>57000</v>
+      </c>
+      <c r="P1366">
+        <v>18</v>
+      </c>
+      <c r="Q1366">
+        <v>1.06</v>
+      </c>
+      <c r="S1366" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1367" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1367">
+        <v>29</v>
+      </c>
+      <c r="I1367" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1367">
+        <v>377000</v>
+      </c>
+      <c r="K1367">
+        <v>0</v>
+      </c>
+      <c r="L1367">
+        <v>0</v>
+      </c>
+      <c r="M1367">
+        <v>377000</v>
+      </c>
+      <c r="N1367">
+        <v>290000</v>
+      </c>
+      <c r="O1367">
+        <v>87000</v>
+      </c>
+      <c r="P1367">
+        <v>20</v>
+      </c>
+      <c r="Q1367">
+        <v>1.45</v>
+      </c>
+      <c r="S1367" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1368" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1368">
+        <v>44</v>
+      </c>
+      <c r="I1368" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1368">
+        <v>308000</v>
+      </c>
+      <c r="K1368">
+        <v>0</v>
+      </c>
+      <c r="L1368">
+        <v>0</v>
+      </c>
+      <c r="M1368">
+        <v>308000</v>
+      </c>
+      <c r="N1368">
+        <v>220000</v>
+      </c>
+      <c r="O1368">
+        <v>88000</v>
+      </c>
+      <c r="P1368">
+        <v>27</v>
+      </c>
+      <c r="Q1368">
+        <v>1.63</v>
+      </c>
+      <c r="S1368" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1369" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1369">
+        <v>14</v>
+      </c>
+      <c r="I1369" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1369">
+        <v>182000</v>
+      </c>
+      <c r="K1369">
+        <v>0</v>
+      </c>
+      <c r="L1369">
+        <v>0</v>
+      </c>
+      <c r="M1369">
+        <v>182000</v>
+      </c>
+      <c r="N1369">
+        <v>140000</v>
+      </c>
+      <c r="O1369">
+        <v>42000</v>
+      </c>
+      <c r="P1369">
+        <v>9</v>
+      </c>
+      <c r="Q1369">
+        <v>1.56</v>
+      </c>
+      <c r="S1369" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1370" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1370">
+        <v>12</v>
+      </c>
+      <c r="I1370" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1370">
+        <v>156000</v>
+      </c>
+      <c r="K1370">
+        <v>0</v>
+      </c>
+      <c r="L1370">
+        <v>0</v>
+      </c>
+      <c r="M1370">
+        <v>156000</v>
+      </c>
+      <c r="N1370">
+        <v>120000</v>
+      </c>
+      <c r="O1370">
+        <v>36000</v>
+      </c>
+      <c r="P1370">
+        <v>9</v>
+      </c>
+      <c r="Q1370">
+        <v>1.33</v>
+      </c>
+      <c r="S1370" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1371" t="s">
+        <v>354</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1371">
+        <v>32</v>
+      </c>
+      <c r="I1371" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1371">
+        <v>320000</v>
+      </c>
+      <c r="K1371">
+        <v>0</v>
+      </c>
+      <c r="L1371">
+        <v>0</v>
+      </c>
+      <c r="M1371">
+        <v>320000</v>
+      </c>
+      <c r="N1371">
+        <v>160000</v>
+      </c>
+      <c r="O1371">
+        <v>160000</v>
+      </c>
+      <c r="P1371">
+        <v>24</v>
+      </c>
+      <c r="Q1371">
+        <v>1.33</v>
+      </c>
+      <c r="S1371" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1372" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1372">
+        <v>83</v>
+      </c>
+      <c r="I1372" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1372">
+        <v>1245000</v>
+      </c>
+      <c r="K1372">
+        <v>0</v>
+      </c>
+      <c r="L1372">
+        <v>0</v>
+      </c>
+      <c r="M1372">
+        <v>1245000</v>
+      </c>
+      <c r="N1372">
+        <v>996000</v>
+      </c>
+      <c r="O1372">
+        <v>249000</v>
+      </c>
+      <c r="P1372">
+        <v>60</v>
+      </c>
+      <c r="Q1372">
+        <v>1.38</v>
+      </c>
+      <c r="S1372" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1373" t="s">
+        <v>356</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1373">
+        <v>71</v>
+      </c>
+      <c r="I1373" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1373">
+        <v>781000</v>
+      </c>
+      <c r="K1373">
+        <v>0</v>
+      </c>
+      <c r="L1373">
+        <v>0</v>
+      </c>
+      <c r="M1373">
+        <v>781000</v>
+      </c>
+      <c r="N1373">
+        <v>568000</v>
+      </c>
+      <c r="O1373">
+        <v>213000</v>
+      </c>
+      <c r="P1373">
+        <v>39</v>
+      </c>
+      <c r="Q1373">
+        <v>1.82</v>
+      </c>
+      <c r="S1373" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1374" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1374">
+        <v>56</v>
+      </c>
+      <c r="I1374" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1374">
+        <v>560000</v>
+      </c>
+      <c r="K1374">
+        <v>0</v>
+      </c>
+      <c r="L1374">
+        <v>0</v>
+      </c>
+      <c r="M1374">
+        <v>560000</v>
+      </c>
+      <c r="N1374">
+        <v>420000</v>
+      </c>
+      <c r="O1374">
+        <v>140000</v>
+      </c>
+      <c r="P1374">
+        <v>42</v>
+      </c>
+      <c r="Q1374">
+        <v>1.33</v>
+      </c>
+      <c r="S1374" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1375" t="s">
+        <v>358</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1375">
+        <v>28</v>
+      </c>
+      <c r="I1375" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1375">
+        <v>420000</v>
+      </c>
+      <c r="K1375">
+        <v>0</v>
+      </c>
+      <c r="L1375">
+        <v>0</v>
+      </c>
+      <c r="M1375">
+        <v>420000</v>
+      </c>
+      <c r="N1375">
+        <v>336000</v>
+      </c>
+      <c r="O1375">
+        <v>84000</v>
+      </c>
+      <c r="P1375">
+        <v>25</v>
+      </c>
+      <c r="Q1375">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S1375" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1376" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1376">
+        <v>61</v>
+      </c>
+      <c r="I1376" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1376">
+        <v>1220000</v>
+      </c>
+      <c r="K1376">
+        <v>0</v>
+      </c>
+      <c r="L1376">
+        <v>0</v>
+      </c>
+      <c r="M1376">
+        <v>1220000</v>
+      </c>
+      <c r="N1376">
+        <v>1098000</v>
+      </c>
+      <c r="O1376">
+        <v>122000</v>
+      </c>
+      <c r="P1376">
+        <v>47</v>
+      </c>
+      <c r="Q1376">
+        <v>1.3</v>
+      </c>
+      <c r="S1376" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1377" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1377">
+        <v>9</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1377">
+        <v>135000</v>
+      </c>
+      <c r="K1377">
+        <v>0</v>
+      </c>
+      <c r="L1377">
+        <v>0</v>
+      </c>
+      <c r="M1377">
+        <v>135000</v>
+      </c>
+      <c r="N1377">
+        <v>108000</v>
+      </c>
+      <c r="O1377">
+        <v>27000</v>
+      </c>
+      <c r="P1377">
+        <v>8</v>
+      </c>
+      <c r="Q1377">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="S1377" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1378" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1378">
+        <v>142</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1378">
+        <v>1704000</v>
+      </c>
+      <c r="K1378">
+        <v>0</v>
+      </c>
+      <c r="L1378">
+        <v>0</v>
+      </c>
+      <c r="M1378">
+        <v>1704000</v>
+      </c>
+      <c r="N1378">
+        <v>1136000</v>
+      </c>
+      <c r="O1378">
+        <v>568000</v>
+      </c>
+      <c r="P1378">
+        <v>67</v>
+      </c>
+      <c r="Q1378">
+        <v>2.12</v>
+      </c>
+      <c r="S1378" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1379" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1379">
+        <v>35</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1379">
+        <v>735000</v>
+      </c>
+      <c r="K1379">
+        <v>0</v>
+      </c>
+      <c r="L1379">
+        <v>0</v>
+      </c>
+      <c r="M1379">
+        <v>735000</v>
+      </c>
+      <c r="N1379">
+        <v>560000</v>
+      </c>
+      <c r="O1379">
+        <v>175000</v>
+      </c>
+      <c r="P1379">
+        <v>26</v>
+      </c>
+      <c r="Q1379">
+        <v>1.35</v>
+      </c>
+      <c r="S1379" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1380" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1380">
+        <v>33</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1380">
+        <v>429000</v>
+      </c>
+      <c r="K1380">
+        <v>0</v>
+      </c>
+      <c r="L1380">
+        <v>0</v>
+      </c>
+      <c r="M1380">
+        <v>429000</v>
+      </c>
+      <c r="N1380">
+        <v>330000</v>
+      </c>
+      <c r="O1380">
+        <v>99000</v>
+      </c>
+      <c r="P1380">
+        <v>28</v>
+      </c>
+      <c r="Q1380">
+        <v>1.18</v>
+      </c>
+      <c r="S1380" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1381" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1381">
+        <v>282</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1381">
+        <v>1974000</v>
+      </c>
+      <c r="K1381">
+        <v>0</v>
+      </c>
+      <c r="L1381">
+        <v>0</v>
+      </c>
+      <c r="M1381">
+        <v>1974000</v>
+      </c>
+      <c r="N1381">
+        <v>1353600</v>
+      </c>
+      <c r="O1381">
+        <v>620400</v>
+      </c>
+      <c r="P1381">
+        <v>91</v>
+      </c>
+      <c r="Q1381">
+        <v>3.1</v>
+      </c>
+      <c r="S1381" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1382" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1382">
+        <v>20</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1382">
+        <v>200000</v>
+      </c>
+      <c r="K1382">
+        <v>0</v>
+      </c>
+      <c r="L1382">
+        <v>0</v>
+      </c>
+      <c r="M1382">
+        <v>200000</v>
+      </c>
+      <c r="N1382">
+        <v>134000</v>
+      </c>
+      <c r="O1382">
+        <v>66000</v>
+      </c>
+      <c r="P1382">
+        <v>16</v>
+      </c>
+      <c r="Q1382">
+        <v>1.25</v>
+      </c>
+      <c r="S1382" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1383" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1383">
+        <v>54</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1383">
+        <v>810000</v>
+      </c>
+      <c r="K1383">
+        <v>0</v>
+      </c>
+      <c r="L1383">
+        <v>0</v>
+      </c>
+      <c r="M1383">
+        <v>810000</v>
+      </c>
+      <c r="N1383">
+        <v>420707.22</v>
+      </c>
+      <c r="O1383">
+        <v>389292.78</v>
+      </c>
+      <c r="P1383">
+        <v>37</v>
+      </c>
+      <c r="Q1383">
+        <v>1.46</v>
+      </c>
+      <c r="S1383" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1384" t="s">
+        <v>389</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1384">
+        <v>5</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1384">
+        <v>25000</v>
+      </c>
+      <c r="K1384">
+        <v>0</v>
+      </c>
+      <c r="L1384">
+        <v>0</v>
+      </c>
+      <c r="M1384">
+        <v>25000</v>
+      </c>
+      <c r="N1384">
+        <v>11202.8</v>
+      </c>
+      <c r="O1384">
+        <v>13797.2</v>
+      </c>
+      <c r="P1384">
+        <v>5</v>
+      </c>
+      <c r="Q1384">
+        <v>1</v>
+      </c>
+      <c r="S1384" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1385" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1385">
+        <v>50</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1385">
+        <v>250000</v>
+      </c>
+      <c r="K1385">
+        <v>0</v>
+      </c>
+      <c r="L1385">
+        <v>0</v>
+      </c>
+      <c r="M1385">
+        <v>250000</v>
+      </c>
+      <c r="N1385">
+        <v>50828.5</v>
+      </c>
+      <c r="O1385">
+        <v>199171.5</v>
+      </c>
+      <c r="P1385">
+        <v>43</v>
+      </c>
+      <c r="Q1385">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="S1385" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1386" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1386">
+        <v>44</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1386">
+        <v>220000</v>
+      </c>
+      <c r="K1386">
+        <v>0</v>
+      </c>
+      <c r="L1386">
+        <v>0</v>
+      </c>
+      <c r="M1386">
+        <v>220000</v>
+      </c>
+      <c r="N1386">
+        <v>98032</v>
+      </c>
+      <c r="O1386">
+        <v>121968</v>
+      </c>
+      <c r="P1386">
+        <v>40</v>
+      </c>
+      <c r="Q1386">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S1386" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1387" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1387">
+        <v>19</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1387">
+        <v>95000</v>
+      </c>
+      <c r="K1387">
+        <v>0</v>
+      </c>
+      <c r="L1387">
+        <v>0</v>
+      </c>
+      <c r="M1387">
+        <v>95000</v>
+      </c>
+      <c r="N1387">
+        <v>76000</v>
+      </c>
+      <c r="O1387">
+        <v>19000</v>
+      </c>
+      <c r="P1387">
+        <v>11</v>
+      </c>
+      <c r="Q1387">
+        <v>1.73</v>
+      </c>
+      <c r="S1387" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1388" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1388">
+        <v>46</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1388">
+        <v>230000</v>
+      </c>
+      <c r="K1388">
+        <v>0</v>
+      </c>
+      <c r="L1388">
+        <v>0</v>
+      </c>
+      <c r="M1388">
+        <v>230000</v>
+      </c>
+      <c r="N1388">
+        <v>51111.06</v>
+      </c>
+      <c r="O1388">
+        <v>178888.94</v>
+      </c>
+      <c r="P1388">
+        <v>36</v>
+      </c>
+      <c r="Q1388">
+        <v>1.28</v>
+      </c>
+      <c r="S1388" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1389" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1389">
+        <v>11</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1389">
+        <v>286000</v>
+      </c>
+      <c r="K1389">
+        <v>0</v>
+      </c>
+      <c r="L1389">
+        <v>0</v>
+      </c>
+      <c r="M1389">
+        <v>286000</v>
+      </c>
+      <c r="N1389">
+        <v>242000</v>
+      </c>
+      <c r="O1389">
+        <v>44000</v>
+      </c>
+      <c r="P1389">
+        <v>11</v>
+      </c>
+      <c r="Q1389">
+        <v>1</v>
+      </c>
+      <c r="S1389" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1390" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1390">
+        <v>76</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1390">
+        <v>1900000</v>
+      </c>
+      <c r="K1390">
+        <v>0</v>
+      </c>
+      <c r="L1390">
+        <v>0</v>
+      </c>
+      <c r="M1390">
+        <v>1900000</v>
+      </c>
+      <c r="N1390">
+        <v>1596000</v>
+      </c>
+      <c r="O1390">
+        <v>304000</v>
+      </c>
+      <c r="P1390">
+        <v>64</v>
+      </c>
+      <c r="Q1390">
+        <v>1.19</v>
+      </c>
+      <c r="S1390" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="S1:S1390" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data_Master.xlsx
+++ b/Data_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Kantin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AC0B54-8C16-4C4E-8087-67EFF32BB460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C14EA6F-BCB0-4C09-8A85-F70DDB8F24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFC52FFA-175C-4E6E-9BE3-CE0A8ECCF11B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7648" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7846" uniqueCount="450">
   <si>
     <t>product</t>
   </si>
@@ -1387,6 +1387,9 @@
   <si>
     <t>TIDAK ADA KATEGORY</t>
   </si>
+  <si>
+    <t>Juni</t>
+  </si>
 </sst>
 </file>
 
@@ -56519,7 +56522,7 @@
         <v>1.2</v>
       </c>
       <c r="R1192" t="s">
-        <v>22</v>
+        <v>449</v>
       </c>
       <c r="S1192" t="s">
         <v>23</v>
@@ -56562,6 +56565,9 @@
       <c r="Q1193">
         <v>1.35</v>
       </c>
+      <c r="R1193" t="s">
+        <v>449</v>
+      </c>
       <c r="S1193" t="s">
         <v>23</v>
       </c>
@@ -56603,6 +56609,9 @@
       <c r="Q1194">
         <v>1.32</v>
       </c>
+      <c r="R1194" t="s">
+        <v>449</v>
+      </c>
       <c r="S1194" t="s">
         <v>23</v>
       </c>
@@ -56644,6 +56653,9 @@
       <c r="Q1195">
         <v>1.34</v>
       </c>
+      <c r="R1195" t="s">
+        <v>449</v>
+      </c>
       <c r="S1195" t="s">
         <v>23</v>
       </c>
@@ -56685,6 +56697,9 @@
       <c r="Q1196">
         <v>1.25</v>
       </c>
+      <c r="R1196" t="s">
+        <v>449</v>
+      </c>
       <c r="S1196" t="s">
         <v>23</v>
       </c>
@@ -56726,6 +56741,9 @@
       <c r="Q1197">
         <v>1</v>
       </c>
+      <c r="R1197" t="s">
+        <v>449</v>
+      </c>
       <c r="S1197" t="s">
         <v>23</v>
       </c>
@@ -56770,6 +56788,9 @@
       <c r="Q1198">
         <v>2</v>
       </c>
+      <c r="R1198" t="s">
+        <v>449</v>
+      </c>
       <c r="S1198" t="s">
         <v>23</v>
       </c>
@@ -56814,6 +56835,9 @@
       <c r="Q1199">
         <v>1.1599999999999999</v>
       </c>
+      <c r="R1199" t="s">
+        <v>449</v>
+      </c>
       <c r="S1199" t="s">
         <v>23</v>
       </c>
@@ -56855,6 +56879,9 @@
       <c r="Q1200">
         <v>1.2</v>
       </c>
+      <c r="R1200" t="s">
+        <v>449</v>
+      </c>
       <c r="S1200" t="s">
         <v>23</v>
       </c>
@@ -56896,6 +56923,9 @@
       <c r="Q1201">
         <v>1.1399999999999999</v>
       </c>
+      <c r="R1201" t="s">
+        <v>449</v>
+      </c>
       <c r="S1201" t="s">
         <v>23</v>
       </c>
@@ -56937,6 +56967,9 @@
       <c r="Q1202">
         <v>1.24</v>
       </c>
+      <c r="R1202" t="s">
+        <v>449</v>
+      </c>
       <c r="S1202" t="s">
         <v>23</v>
       </c>
@@ -56978,6 +57011,9 @@
       <c r="Q1203">
         <v>1.67</v>
       </c>
+      <c r="R1203" t="s">
+        <v>449</v>
+      </c>
       <c r="S1203" t="s">
         <v>36</v>
       </c>
@@ -57022,6 +57058,9 @@
       <c r="Q1204">
         <v>1</v>
       </c>
+      <c r="R1204" t="s">
+        <v>449</v>
+      </c>
       <c r="S1204" t="s">
         <v>36</v>
       </c>
@@ -57063,6 +57102,9 @@
       <c r="Q1205">
         <v>1</v>
       </c>
+      <c r="R1205" t="s">
+        <v>449</v>
+      </c>
       <c r="S1205" t="s">
         <v>36</v>
       </c>
@@ -57104,6 +57146,9 @@
       <c r="Q1206">
         <v>1</v>
       </c>
+      <c r="R1206" t="s">
+        <v>449</v>
+      </c>
       <c r="S1206" t="s">
         <v>36</v>
       </c>
@@ -57145,6 +57190,9 @@
       <c r="Q1207">
         <v>1</v>
       </c>
+      <c r="R1207" t="s">
+        <v>449</v>
+      </c>
       <c r="S1207" t="s">
         <v>36</v>
       </c>
@@ -57186,6 +57234,9 @@
       <c r="Q1208">
         <v>1.18</v>
       </c>
+      <c r="R1208" t="s">
+        <v>449</v>
+      </c>
       <c r="S1208" t="s">
         <v>36</v>
       </c>
@@ -57227,6 +57278,9 @@
       <c r="Q1209">
         <v>1.1499999999999999</v>
       </c>
+      <c r="R1209" t="s">
+        <v>449</v>
+      </c>
       <c r="S1209" t="s">
         <v>36</v>
       </c>
@@ -57268,6 +57322,9 @@
       <c r="Q1210">
         <v>1.1499999999999999</v>
       </c>
+      <c r="R1210" t="s">
+        <v>449</v>
+      </c>
       <c r="S1210" t="s">
         <v>36</v>
       </c>
@@ -57309,6 +57366,9 @@
       <c r="Q1211">
         <v>1.38</v>
       </c>
+      <c r="R1211" t="s">
+        <v>449</v>
+      </c>
       <c r="S1211" t="s">
         <v>36</v>
       </c>
@@ -57350,6 +57410,9 @@
       <c r="Q1212">
         <v>1.1200000000000001</v>
       </c>
+      <c r="R1212" t="s">
+        <v>449</v>
+      </c>
       <c r="S1212" t="s">
         <v>36</v>
       </c>
@@ -57391,6 +57454,9 @@
       <c r="Q1213">
         <v>1</v>
       </c>
+      <c r="R1213" t="s">
+        <v>449</v>
+      </c>
       <c r="S1213" t="s">
         <v>36</v>
       </c>
@@ -57435,6 +57501,9 @@
       <c r="Q1214">
         <v>1.26</v>
       </c>
+      <c r="R1214" t="s">
+        <v>449</v>
+      </c>
       <c r="S1214" t="s">
         <v>36</v>
       </c>
@@ -57476,6 +57545,9 @@
       <c r="Q1215">
         <v>1.17</v>
       </c>
+      <c r="R1215" t="s">
+        <v>449</v>
+      </c>
       <c r="S1215" t="s">
         <v>36</v>
       </c>
@@ -57517,6 +57589,9 @@
       <c r="Q1216">
         <v>1.1499999999999999</v>
       </c>
+      <c r="R1216" t="s">
+        <v>449</v>
+      </c>
       <c r="S1216" t="s">
         <v>36</v>
       </c>
@@ -57558,6 +57633,9 @@
       <c r="Q1217">
         <v>1</v>
       </c>
+      <c r="R1217" t="s">
+        <v>449</v>
+      </c>
       <c r="S1217" t="s">
         <v>36</v>
       </c>
@@ -57599,6 +57677,9 @@
       <c r="Q1218">
         <v>2.0699999999999998</v>
       </c>
+      <c r="R1218" t="s">
+        <v>449</v>
+      </c>
       <c r="S1218" t="s">
         <v>36</v>
       </c>
@@ -57640,6 +57721,9 @@
       <c r="Q1219">
         <v>1.25</v>
       </c>
+      <c r="R1219" t="s">
+        <v>449</v>
+      </c>
       <c r="S1219" t="s">
         <v>36</v>
       </c>
@@ -57681,6 +57765,9 @@
       <c r="Q1220">
         <v>1.5</v>
       </c>
+      <c r="R1220" t="s">
+        <v>449</v>
+      </c>
       <c r="S1220" t="s">
         <v>36</v>
       </c>
@@ -57722,6 +57809,9 @@
       <c r="Q1221">
         <v>1.3</v>
       </c>
+      <c r="R1221" t="s">
+        <v>449</v>
+      </c>
       <c r="S1221" t="s">
         <v>36</v>
       </c>
@@ -57763,6 +57853,9 @@
       <c r="Q1222">
         <v>1.1499999999999999</v>
       </c>
+      <c r="R1222" t="s">
+        <v>449</v>
+      </c>
       <c r="S1222" t="s">
         <v>36</v>
       </c>
@@ -57804,6 +57897,9 @@
       <c r="Q1223">
         <v>1</v>
       </c>
+      <c r="R1223" t="s">
+        <v>449</v>
+      </c>
       <c r="S1223" t="s">
         <v>36</v>
       </c>
@@ -57845,6 +57941,9 @@
       <c r="Q1224">
         <v>1.5</v>
       </c>
+      <c r="R1224" t="s">
+        <v>449</v>
+      </c>
       <c r="S1224" t="s">
         <v>36</v>
       </c>
@@ -57886,6 +57985,9 @@
       <c r="Q1225">
         <v>1.31</v>
       </c>
+      <c r="R1225" t="s">
+        <v>449</v>
+      </c>
       <c r="S1225" t="s">
         <v>36</v>
       </c>
@@ -57933,6 +58035,9 @@
       <c r="Q1226">
         <v>1.27</v>
       </c>
+      <c r="R1226" t="s">
+        <v>449</v>
+      </c>
       <c r="S1226" t="s">
         <v>36</v>
       </c>
@@ -57977,6 +58082,9 @@
       <c r="Q1227">
         <v>1.67</v>
       </c>
+      <c r="R1227" t="s">
+        <v>449</v>
+      </c>
       <c r="S1227" t="s">
         <v>36</v>
       </c>
@@ -58021,6 +58129,9 @@
       <c r="Q1228">
         <v>1.29</v>
       </c>
+      <c r="R1228" t="s">
+        <v>449</v>
+      </c>
       <c r="S1228" t="s">
         <v>36</v>
       </c>
@@ -58065,6 +58176,9 @@
       <c r="Q1229">
         <v>1.33</v>
       </c>
+      <c r="R1229" t="s">
+        <v>449</v>
+      </c>
       <c r="S1229" t="s">
         <v>36</v>
       </c>
@@ -58109,6 +58223,9 @@
       <c r="Q1230">
         <v>1.36</v>
       </c>
+      <c r="R1230" t="s">
+        <v>449</v>
+      </c>
       <c r="S1230" t="s">
         <v>36</v>
       </c>
@@ -58153,6 +58270,9 @@
       <c r="Q1231">
         <v>1.04</v>
       </c>
+      <c r="R1231" t="s">
+        <v>449</v>
+      </c>
       <c r="S1231" t="s">
         <v>36</v>
       </c>
@@ -58197,6 +58317,9 @@
       <c r="Q1232">
         <v>1.27</v>
       </c>
+      <c r="R1232" t="s">
+        <v>449</v>
+      </c>
       <c r="S1232" t="s">
         <v>36</v>
       </c>
@@ -58241,6 +58364,9 @@
       <c r="Q1233">
         <v>1.2</v>
       </c>
+      <c r="R1233" t="s">
+        <v>449</v>
+      </c>
       <c r="S1233" t="s">
         <v>36</v>
       </c>
@@ -58285,6 +58411,9 @@
       <c r="Q1234">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1234" t="s">
+        <v>449</v>
+      </c>
       <c r="S1234" t="s">
         <v>36</v>
       </c>
@@ -58329,6 +58458,9 @@
       <c r="Q1235">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1235" t="s">
+        <v>449</v>
+      </c>
       <c r="S1235" t="s">
         <v>36</v>
       </c>
@@ -58373,6 +58505,9 @@
       <c r="Q1236">
         <v>1.26</v>
       </c>
+      <c r="R1236" t="s">
+        <v>449</v>
+      </c>
       <c r="S1236" t="s">
         <v>36</v>
       </c>
@@ -58417,6 +58552,9 @@
       <c r="Q1237">
         <v>1.21</v>
       </c>
+      <c r="R1237" t="s">
+        <v>449</v>
+      </c>
       <c r="S1237" t="s">
         <v>36</v>
       </c>
@@ -58461,6 +58599,9 @@
       <c r="Q1238">
         <v>1.03</v>
       </c>
+      <c r="R1238" t="s">
+        <v>449</v>
+      </c>
       <c r="S1238" t="s">
         <v>36</v>
       </c>
@@ -58505,6 +58646,9 @@
       <c r="Q1239">
         <v>1.36</v>
       </c>
+      <c r="R1239" t="s">
+        <v>449</v>
+      </c>
       <c r="S1239" t="s">
         <v>36</v>
       </c>
@@ -58549,6 +58693,9 @@
       <c r="Q1240">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1240" t="s">
+        <v>449</v>
+      </c>
       <c r="S1240" t="s">
         <v>36</v>
       </c>
@@ -58593,6 +58740,9 @@
       <c r="Q1241">
         <v>1.39</v>
       </c>
+      <c r="R1241" t="s">
+        <v>449</v>
+      </c>
       <c r="S1241" t="s">
         <v>36</v>
       </c>
@@ -58637,6 +58787,9 @@
       <c r="Q1242">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1242" t="s">
+        <v>449</v>
+      </c>
       <c r="S1242" t="s">
         <v>448</v>
       </c>
@@ -58681,6 +58834,9 @@
       <c r="Q1243">
         <v>1.59</v>
       </c>
+      <c r="R1243" t="s">
+        <v>449</v>
+      </c>
       <c r="S1243" t="s">
         <v>36</v>
       </c>
@@ -58722,6 +58878,9 @@
       <c r="Q1244">
         <v>2.21</v>
       </c>
+      <c r="R1244" t="s">
+        <v>449</v>
+      </c>
       <c r="S1244" t="s">
         <v>168</v>
       </c>
@@ -58763,6 +58922,9 @@
       <c r="Q1245">
         <v>1.39</v>
       </c>
+      <c r="R1245" t="s">
+        <v>449</v>
+      </c>
       <c r="S1245" t="s">
         <v>36</v>
       </c>
@@ -58804,6 +58966,9 @@
       <c r="Q1246">
         <v>2.5</v>
       </c>
+      <c r="R1246" t="s">
+        <v>449</v>
+      </c>
       <c r="S1246" t="s">
         <v>168</v>
       </c>
@@ -58845,6 +59010,9 @@
       <c r="Q1247">
         <v>1.68</v>
       </c>
+      <c r="R1247" t="s">
+        <v>449</v>
+      </c>
       <c r="S1247" t="s">
         <v>168</v>
       </c>
@@ -58886,6 +59054,9 @@
       <c r="Q1248">
         <v>2.88</v>
       </c>
+      <c r="R1248" t="s">
+        <v>449</v>
+      </c>
       <c r="S1248" t="s">
         <v>36</v>
       </c>
@@ -58927,6 +59098,9 @@
       <c r="Q1249">
         <v>3.28</v>
       </c>
+      <c r="R1249" t="s">
+        <v>449</v>
+      </c>
       <c r="S1249" t="s">
         <v>168</v>
       </c>
@@ -58968,6 +59142,9 @@
       <c r="Q1250">
         <v>2.42</v>
       </c>
+      <c r="R1250" t="s">
+        <v>449</v>
+      </c>
       <c r="S1250" t="s">
         <v>168</v>
       </c>
@@ -59009,6 +59186,9 @@
       <c r="Q1251">
         <v>1</v>
       </c>
+      <c r="R1251" t="s">
+        <v>449</v>
+      </c>
       <c r="S1251" t="s">
         <v>168</v>
       </c>
@@ -59050,6 +59230,9 @@
       <c r="Q1252">
         <v>4.1100000000000003</v>
       </c>
+      <c r="R1252" t="s">
+        <v>449</v>
+      </c>
       <c r="S1252" t="s">
         <v>168</v>
       </c>
@@ -59091,6 +59274,9 @@
       <c r="Q1253">
         <v>4.45</v>
       </c>
+      <c r="R1253" t="s">
+        <v>449</v>
+      </c>
       <c r="S1253" t="s">
         <v>168</v>
       </c>
@@ -59132,6 +59318,9 @@
       <c r="Q1254">
         <v>2.46</v>
       </c>
+      <c r="R1254" t="s">
+        <v>449</v>
+      </c>
       <c r="S1254" t="s">
         <v>168</v>
       </c>
@@ -59173,6 +59362,9 @@
       <c r="Q1255">
         <v>1.1399999999999999</v>
       </c>
+      <c r="R1255" t="s">
+        <v>449</v>
+      </c>
       <c r="S1255" t="s">
         <v>168</v>
       </c>
@@ -59217,6 +59409,9 @@
       <c r="Q1256">
         <v>2.2000000000000002</v>
       </c>
+      <c r="R1256" t="s">
+        <v>449</v>
+      </c>
       <c r="S1256" t="s">
         <v>168</v>
       </c>
@@ -59258,6 +59453,9 @@
       <c r="Q1257">
         <v>2.76</v>
       </c>
+      <c r="R1257" t="s">
+        <v>449</v>
+      </c>
       <c r="S1257" t="s">
         <v>168</v>
       </c>
@@ -59299,6 +59497,9 @@
       <c r="Q1258">
         <v>1.64</v>
       </c>
+      <c r="R1258" t="s">
+        <v>449</v>
+      </c>
       <c r="S1258" t="s">
         <v>168</v>
       </c>
@@ -59340,6 +59541,9 @@
       <c r="Q1259">
         <v>1</v>
       </c>
+      <c r="R1259" t="s">
+        <v>449</v>
+      </c>
       <c r="S1259" t="s">
         <v>168</v>
       </c>
@@ -59381,6 +59585,9 @@
       <c r="Q1260">
         <v>2.62</v>
       </c>
+      <c r="R1260" t="s">
+        <v>449</v>
+      </c>
       <c r="S1260" t="s">
         <v>168</v>
       </c>
@@ -59425,6 +59632,9 @@
       <c r="Q1261">
         <v>1.5</v>
       </c>
+      <c r="R1261" t="s">
+        <v>449</v>
+      </c>
       <c r="S1261" t="s">
         <v>36</v>
       </c>
@@ -59469,6 +59679,9 @@
       <c r="Q1262">
         <v>1</v>
       </c>
+      <c r="R1262" t="s">
+        <v>449</v>
+      </c>
       <c r="S1262" t="s">
         <v>36</v>
       </c>
@@ -59513,6 +59726,9 @@
       <c r="Q1263">
         <v>1.07</v>
       </c>
+      <c r="R1263" t="s">
+        <v>449</v>
+      </c>
       <c r="S1263" t="s">
         <v>36</v>
       </c>
@@ -59557,6 +59773,9 @@
       <c r="Q1264">
         <v>1</v>
       </c>
+      <c r="R1264" t="s">
+        <v>449</v>
+      </c>
       <c r="S1264" t="s">
         <v>36</v>
       </c>
@@ -59601,6 +59820,9 @@
       <c r="Q1265">
         <v>1.37</v>
       </c>
+      <c r="R1265" t="s">
+        <v>449</v>
+      </c>
       <c r="S1265" t="s">
         <v>36</v>
       </c>
@@ -59645,6 +59867,9 @@
       <c r="Q1266">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1266" t="s">
+        <v>449</v>
+      </c>
       <c r="S1266" t="s">
         <v>36</v>
       </c>
@@ -59689,6 +59914,9 @@
       <c r="Q1267">
         <v>1.67</v>
       </c>
+      <c r="R1267" t="s">
+        <v>449</v>
+      </c>
       <c r="S1267" t="s">
         <v>36</v>
       </c>
@@ -59733,6 +59961,9 @@
       <c r="Q1268">
         <v>1.43</v>
       </c>
+      <c r="R1268" t="s">
+        <v>449</v>
+      </c>
       <c r="S1268" t="s">
         <v>36</v>
       </c>
@@ -59777,6 +60008,9 @@
       <c r="Q1269">
         <v>1</v>
       </c>
+      <c r="R1269" t="s">
+        <v>449</v>
+      </c>
       <c r="S1269" t="s">
         <v>36</v>
       </c>
@@ -59821,6 +60055,9 @@
       <c r="Q1270">
         <v>1</v>
       </c>
+      <c r="R1270" t="s">
+        <v>449</v>
+      </c>
       <c r="S1270" t="s">
         <v>36</v>
       </c>
@@ -59865,6 +60102,9 @@
       <c r="Q1271">
         <v>1.17</v>
       </c>
+      <c r="R1271" t="s">
+        <v>449</v>
+      </c>
       <c r="S1271" t="s">
         <v>36</v>
       </c>
@@ -59909,6 +60149,9 @@
       <c r="Q1272">
         <v>1</v>
       </c>
+      <c r="R1272" t="s">
+        <v>449</v>
+      </c>
       <c r="S1272" t="s">
         <v>36</v>
       </c>
@@ -59953,6 +60196,9 @@
       <c r="Q1273">
         <v>1</v>
       </c>
+      <c r="R1273" t="s">
+        <v>449</v>
+      </c>
       <c r="S1273" t="s">
         <v>36</v>
       </c>
@@ -59997,6 +60243,9 @@
       <c r="Q1274">
         <v>1</v>
       </c>
+      <c r="R1274" t="s">
+        <v>449</v>
+      </c>
       <c r="S1274" t="s">
         <v>36</v>
       </c>
@@ -60041,6 +60290,9 @@
       <c r="Q1275">
         <v>1.1200000000000001</v>
       </c>
+      <c r="R1275" t="s">
+        <v>449</v>
+      </c>
       <c r="S1275" t="s">
         <v>36</v>
       </c>
@@ -60085,6 +60337,9 @@
       <c r="Q1276">
         <v>1.1599999999999999</v>
       </c>
+      <c r="R1276" t="s">
+        <v>449</v>
+      </c>
       <c r="S1276" t="s">
         <v>36</v>
       </c>
@@ -60129,6 +60384,9 @@
       <c r="Q1277">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1277" t="s">
+        <v>449</v>
+      </c>
       <c r="S1277" t="s">
         <v>36</v>
       </c>
@@ -60173,6 +60431,9 @@
       <c r="Q1278">
         <v>1</v>
       </c>
+      <c r="R1278" t="s">
+        <v>449</v>
+      </c>
       <c r="S1278" t="s">
         <v>36</v>
       </c>
@@ -60217,6 +60478,9 @@
       <c r="Q1279">
         <v>1.31</v>
       </c>
+      <c r="R1279" t="s">
+        <v>449</v>
+      </c>
       <c r="S1279" t="s">
         <v>448</v>
       </c>
@@ -60261,6 +60525,9 @@
       <c r="Q1280">
         <v>1.24</v>
       </c>
+      <c r="R1280" t="s">
+        <v>449</v>
+      </c>
       <c r="S1280" t="s">
         <v>448</v>
       </c>
@@ -60305,6 +60572,9 @@
       <c r="Q1281">
         <v>1.18</v>
       </c>
+      <c r="R1281" t="s">
+        <v>449</v>
+      </c>
       <c r="S1281" t="s">
         <v>448</v>
       </c>
@@ -60349,6 +60619,9 @@
       <c r="Q1282">
         <v>1.31</v>
       </c>
+      <c r="R1282" t="s">
+        <v>449</v>
+      </c>
       <c r="S1282" t="s">
         <v>448</v>
       </c>
@@ -60393,6 +60666,9 @@
       <c r="Q1283">
         <v>1.19</v>
       </c>
+      <c r="R1283" t="s">
+        <v>449</v>
+      </c>
       <c r="S1283" t="s">
         <v>36</v>
       </c>
@@ -60437,6 +60713,9 @@
       <c r="Q1284">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1284" t="s">
+        <v>449</v>
+      </c>
       <c r="S1284" t="s">
         <v>36</v>
       </c>
@@ -60481,6 +60760,9 @@
       <c r="Q1285">
         <v>1.38</v>
       </c>
+      <c r="R1285" t="s">
+        <v>449</v>
+      </c>
       <c r="S1285" t="s">
         <v>36</v>
       </c>
@@ -60525,6 +60807,9 @@
       <c r="Q1286">
         <v>1.26</v>
       </c>
+      <c r="R1286" t="s">
+        <v>449</v>
+      </c>
       <c r="S1286" t="s">
         <v>36</v>
       </c>
@@ -60569,6 +60854,9 @@
       <c r="Q1287">
         <v>1.08</v>
       </c>
+      <c r="R1287" t="s">
+        <v>449</v>
+      </c>
       <c r="S1287" t="s">
         <v>36</v>
       </c>
@@ -60613,6 +60901,9 @@
       <c r="Q1288">
         <v>1</v>
       </c>
+      <c r="R1288" t="s">
+        <v>449</v>
+      </c>
       <c r="S1288" t="s">
         <v>36</v>
       </c>
@@ -60657,6 +60948,9 @@
       <c r="Q1289">
         <v>1.07</v>
       </c>
+      <c r="R1289" t="s">
+        <v>449</v>
+      </c>
       <c r="S1289" t="s">
         <v>36</v>
       </c>
@@ -60701,6 +60995,9 @@
       <c r="Q1290">
         <v>1.21</v>
       </c>
+      <c r="R1290" t="s">
+        <v>449</v>
+      </c>
       <c r="S1290" t="s">
         <v>36</v>
       </c>
@@ -60745,6 +61042,9 @@
       <c r="Q1291">
         <v>1.1599999999999999</v>
       </c>
+      <c r="R1291" t="s">
+        <v>449</v>
+      </c>
       <c r="S1291" t="s">
         <v>36</v>
       </c>
@@ -60789,6 +61089,9 @@
       <c r="Q1292">
         <v>1.08</v>
       </c>
+      <c r="R1292" t="s">
+        <v>449</v>
+      </c>
       <c r="S1292" t="s">
         <v>36</v>
       </c>
@@ -60833,6 +61136,9 @@
       <c r="Q1293">
         <v>1</v>
       </c>
+      <c r="R1293" t="s">
+        <v>449</v>
+      </c>
       <c r="S1293" t="s">
         <v>36</v>
       </c>
@@ -60877,6 +61183,9 @@
       <c r="Q1294">
         <v>1</v>
       </c>
+      <c r="R1294" t="s">
+        <v>449</v>
+      </c>
       <c r="S1294" t="s">
         <v>36</v>
       </c>
@@ -60921,6 +61230,9 @@
       <c r="Q1295">
         <v>1</v>
       </c>
+      <c r="R1295" t="s">
+        <v>449</v>
+      </c>
       <c r="S1295" t="s">
         <v>36</v>
       </c>
@@ -60965,6 +61277,9 @@
       <c r="Q1296">
         <v>1.1000000000000001</v>
       </c>
+      <c r="R1296" t="s">
+        <v>449</v>
+      </c>
       <c r="S1296" t="s">
         <v>36</v>
       </c>
@@ -61009,6 +61324,9 @@
       <c r="Q1297">
         <v>1</v>
       </c>
+      <c r="R1297" t="s">
+        <v>449</v>
+      </c>
       <c r="S1297" t="s">
         <v>36</v>
       </c>
@@ -61053,6 +61371,9 @@
       <c r="Q1298">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1298" t="s">
+        <v>449</v>
+      </c>
       <c r="S1298" t="s">
         <v>36</v>
       </c>
@@ -61097,6 +61418,9 @@
       <c r="Q1299">
         <v>1.08</v>
       </c>
+      <c r="R1299" t="s">
+        <v>449</v>
+      </c>
       <c r="S1299" t="s">
         <v>36</v>
       </c>
@@ -61141,6 +61465,9 @@
       <c r="Q1300">
         <v>1.21</v>
       </c>
+      <c r="R1300" t="s">
+        <v>449</v>
+      </c>
       <c r="S1300" t="s">
         <v>36</v>
       </c>
@@ -61185,6 +61512,9 @@
       <c r="Q1301">
         <v>1</v>
       </c>
+      <c r="R1301" t="s">
+        <v>449</v>
+      </c>
       <c r="S1301" t="s">
         <v>36</v>
       </c>
@@ -61229,6 +61559,9 @@
       <c r="Q1302">
         <v>1.31</v>
       </c>
+      <c r="R1302" t="s">
+        <v>449</v>
+      </c>
       <c r="S1302" t="s">
         <v>36</v>
       </c>
@@ -61273,6 +61606,9 @@
       <c r="Q1303">
         <v>1.21</v>
       </c>
+      <c r="R1303" t="s">
+        <v>449</v>
+      </c>
       <c r="S1303" t="s">
         <v>36</v>
       </c>
@@ -61317,6 +61653,9 @@
       <c r="Q1304">
         <v>1.32</v>
       </c>
+      <c r="R1304" t="s">
+        <v>449</v>
+      </c>
       <c r="S1304" t="s">
         <v>36</v>
       </c>
@@ -61361,6 +61700,9 @@
       <c r="Q1305">
         <v>1.1000000000000001</v>
       </c>
+      <c r="R1305" t="s">
+        <v>449</v>
+      </c>
       <c r="S1305" t="s">
         <v>36</v>
       </c>
@@ -61405,6 +61747,9 @@
       <c r="Q1306">
         <v>1.21</v>
       </c>
+      <c r="R1306" t="s">
+        <v>449</v>
+      </c>
       <c r="S1306" t="s">
         <v>36</v>
       </c>
@@ -61449,6 +61794,9 @@
       <c r="Q1307">
         <v>1</v>
       </c>
+      <c r="R1307" t="s">
+        <v>449</v>
+      </c>
       <c r="S1307" t="s">
         <v>36</v>
       </c>
@@ -61493,6 +61841,9 @@
       <c r="Q1308">
         <v>1.69</v>
       </c>
+      <c r="R1308" t="s">
+        <v>449</v>
+      </c>
       <c r="S1308" t="s">
         <v>36</v>
       </c>
@@ -61537,6 +61888,9 @@
       <c r="Q1309">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1309" t="s">
+        <v>449</v>
+      </c>
       <c r="S1309" t="s">
         <v>36</v>
       </c>
@@ -61581,6 +61935,9 @@
       <c r="Q1310">
         <v>1.0900000000000001</v>
       </c>
+      <c r="R1310" t="s">
+        <v>449</v>
+      </c>
       <c r="S1310" t="s">
         <v>36</v>
       </c>
@@ -61625,6 +61982,9 @@
       <c r="Q1311">
         <v>1.17</v>
       </c>
+      <c r="R1311" t="s">
+        <v>449</v>
+      </c>
       <c r="S1311" t="s">
         <v>36</v>
       </c>
@@ -61669,6 +62029,9 @@
       <c r="Q1312">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1312" t="s">
+        <v>449</v>
+      </c>
       <c r="S1312" t="s">
         <v>36</v>
       </c>
@@ -61713,6 +62076,9 @@
       <c r="Q1313">
         <v>1.33</v>
       </c>
+      <c r="R1313" t="s">
+        <v>449</v>
+      </c>
       <c r="S1313" t="s">
         <v>36</v>
       </c>
@@ -61757,6 +62123,9 @@
       <c r="Q1314">
         <v>1</v>
       </c>
+      <c r="R1314" t="s">
+        <v>449</v>
+      </c>
       <c r="S1314" t="s">
         <v>36</v>
       </c>
@@ -61801,6 +62170,9 @@
       <c r="Q1315">
         <v>1.1000000000000001</v>
       </c>
+      <c r="R1315" t="s">
+        <v>449</v>
+      </c>
       <c r="S1315" t="s">
         <v>36</v>
       </c>
@@ -61845,6 +62217,9 @@
       <c r="Q1316">
         <v>1.04</v>
       </c>
+      <c r="R1316" t="s">
+        <v>449</v>
+      </c>
       <c r="S1316" t="s">
         <v>36</v>
       </c>
@@ -61889,6 +62264,9 @@
       <c r="Q1317">
         <v>1.22</v>
       </c>
+      <c r="R1317" t="s">
+        <v>449</v>
+      </c>
       <c r="S1317" t="s">
         <v>36</v>
       </c>
@@ -61933,6 +62311,9 @@
       <c r="Q1318">
         <v>1.1399999999999999</v>
       </c>
+      <c r="R1318" t="s">
+        <v>449</v>
+      </c>
       <c r="S1318" t="s">
         <v>36</v>
       </c>
@@ -61977,6 +62358,9 @@
       <c r="Q1319">
         <v>1</v>
       </c>
+      <c r="R1319" t="s">
+        <v>449</v>
+      </c>
       <c r="S1319" t="s">
         <v>36</v>
       </c>
@@ -62021,6 +62405,9 @@
       <c r="Q1320">
         <v>1.19</v>
       </c>
+      <c r="R1320" t="s">
+        <v>449</v>
+      </c>
       <c r="S1320" t="s">
         <v>36</v>
       </c>
@@ -62065,6 +62452,9 @@
       <c r="Q1321">
         <v>1.3</v>
       </c>
+      <c r="R1321" t="s">
+        <v>449</v>
+      </c>
       <c r="S1321" t="s">
         <v>36</v>
       </c>
@@ -62106,6 +62496,9 @@
       <c r="Q1322">
         <v>2.2400000000000002</v>
       </c>
+      <c r="R1322" t="s">
+        <v>449</v>
+      </c>
       <c r="S1322" t="s">
         <v>36</v>
       </c>
@@ -62147,6 +62540,9 @@
       <c r="Q1323">
         <v>1.2</v>
       </c>
+      <c r="R1323" t="s">
+        <v>449</v>
+      </c>
       <c r="S1323" t="s">
         <v>36</v>
       </c>
@@ -62188,6 +62584,9 @@
       <c r="Q1324">
         <v>1</v>
       </c>
+      <c r="R1324" t="s">
+        <v>449</v>
+      </c>
       <c r="S1324" t="s">
         <v>36</v>
       </c>
@@ -62232,6 +62631,9 @@
       <c r="Q1325">
         <v>1</v>
       </c>
+      <c r="R1325" t="s">
+        <v>449</v>
+      </c>
       <c r="S1325" t="s">
         <v>36</v>
       </c>
@@ -62276,6 +62678,9 @@
       <c r="Q1326">
         <v>1.1399999999999999</v>
       </c>
+      <c r="R1326" t="s">
+        <v>449</v>
+      </c>
       <c r="S1326" t="s">
         <v>36</v>
       </c>
@@ -62320,6 +62725,9 @@
       <c r="Q1327">
         <v>1</v>
       </c>
+      <c r="R1327" t="s">
+        <v>449</v>
+      </c>
       <c r="S1327" t="s">
         <v>36</v>
       </c>
@@ -62364,6 +62772,9 @@
       <c r="Q1328">
         <v>1</v>
       </c>
+      <c r="R1328" t="s">
+        <v>449</v>
+      </c>
       <c r="S1328" t="s">
         <v>36</v>
       </c>
@@ -62408,6 +62819,9 @@
       <c r="Q1329">
         <v>1.45</v>
       </c>
+      <c r="R1329" t="s">
+        <v>449</v>
+      </c>
       <c r="S1329" t="s">
         <v>36</v>
       </c>
@@ -62452,6 +62866,9 @@
       <c r="Q1330">
         <v>1.33</v>
       </c>
+      <c r="R1330" t="s">
+        <v>449</v>
+      </c>
       <c r="S1330" t="s">
         <v>36</v>
       </c>
@@ -62496,6 +62913,9 @@
       <c r="Q1331">
         <v>1.45</v>
       </c>
+      <c r="R1331" t="s">
+        <v>449</v>
+      </c>
       <c r="S1331" t="s">
         <v>36</v>
       </c>
@@ -62540,6 +62960,9 @@
       <c r="Q1332">
         <v>1.39</v>
       </c>
+      <c r="R1332" t="s">
+        <v>449</v>
+      </c>
       <c r="S1332" t="s">
         <v>36</v>
       </c>
@@ -62584,6 +63007,9 @@
       <c r="Q1333">
         <v>1.06</v>
       </c>
+      <c r="R1333" t="s">
+        <v>449</v>
+      </c>
       <c r="S1333" t="s">
         <v>448</v>
       </c>
@@ -62628,6 +63054,9 @@
       <c r="Q1334">
         <v>1</v>
       </c>
+      <c r="R1334" t="s">
+        <v>449</v>
+      </c>
       <c r="S1334" t="s">
         <v>448</v>
       </c>
@@ -62672,6 +63101,9 @@
       <c r="Q1335">
         <v>1</v>
       </c>
+      <c r="R1335" t="s">
+        <v>449</v>
+      </c>
       <c r="S1335" t="s">
         <v>448</v>
       </c>
@@ -62716,6 +63148,9 @@
       <c r="Q1336">
         <v>1</v>
       </c>
+      <c r="R1336" t="s">
+        <v>449</v>
+      </c>
       <c r="S1336" t="s">
         <v>448</v>
       </c>
@@ -62760,6 +63195,9 @@
       <c r="Q1337">
         <v>1.31</v>
       </c>
+      <c r="R1337" t="s">
+        <v>449</v>
+      </c>
       <c r="S1337" t="s">
         <v>168</v>
       </c>
@@ -62804,6 +63242,9 @@
       <c r="Q1338">
         <v>1.45</v>
       </c>
+      <c r="R1338" t="s">
+        <v>449</v>
+      </c>
       <c r="S1338" t="s">
         <v>168</v>
       </c>
@@ -62848,6 +63289,9 @@
       <c r="Q1339">
         <v>1</v>
       </c>
+      <c r="R1339" t="s">
+        <v>449</v>
+      </c>
       <c r="S1339" t="s">
         <v>36</v>
       </c>
@@ -62892,6 +63336,9 @@
       <c r="Q1340">
         <v>1.25</v>
       </c>
+      <c r="R1340" t="s">
+        <v>449</v>
+      </c>
       <c r="S1340" t="s">
         <v>36</v>
       </c>
@@ -62936,6 +63383,9 @@
       <c r="Q1341">
         <v>1.2</v>
       </c>
+      <c r="R1341" t="s">
+        <v>449</v>
+      </c>
       <c r="S1341" t="s">
         <v>36</v>
       </c>
@@ -62986,6 +63436,9 @@
       <c r="Q1342">
         <v>1</v>
       </c>
+      <c r="R1342" t="s">
+        <v>449</v>
+      </c>
       <c r="S1342" t="s">
         <v>36</v>
       </c>
@@ -63036,6 +63489,9 @@
       <c r="Q1343">
         <v>1.2</v>
       </c>
+      <c r="R1343" t="s">
+        <v>449</v>
+      </c>
       <c r="S1343" t="s">
         <v>36</v>
       </c>
@@ -63086,6 +63542,9 @@
       <c r="Q1344">
         <v>1.07</v>
       </c>
+      <c r="R1344" t="s">
+        <v>449</v>
+      </c>
       <c r="S1344" t="s">
         <v>36</v>
       </c>
@@ -63130,6 +63589,9 @@
       <c r="Q1345">
         <v>1.08</v>
       </c>
+      <c r="R1345" t="s">
+        <v>449</v>
+      </c>
       <c r="S1345" t="s">
         <v>36</v>
       </c>
@@ -63174,6 +63636,9 @@
       <c r="Q1346">
         <v>1.21</v>
       </c>
+      <c r="R1346" t="s">
+        <v>449</v>
+      </c>
       <c r="S1346" t="s">
         <v>36</v>
       </c>
@@ -63218,6 +63683,9 @@
       <c r="Q1347">
         <v>1.42</v>
       </c>
+      <c r="R1347" t="s">
+        <v>449</v>
+      </c>
       <c r="S1347" t="s">
         <v>36</v>
       </c>
@@ -63262,6 +63730,9 @@
       <c r="Q1348">
         <v>1.04</v>
       </c>
+      <c r="R1348" t="s">
+        <v>449</v>
+      </c>
       <c r="S1348" t="s">
         <v>36</v>
       </c>
@@ -63306,6 +63777,9 @@
       <c r="Q1349">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1349" t="s">
+        <v>449</v>
+      </c>
       <c r="S1349" t="s">
         <v>36</v>
       </c>
@@ -63350,6 +63824,9 @@
       <c r="Q1350">
         <v>1</v>
       </c>
+      <c r="R1350" t="s">
+        <v>449</v>
+      </c>
       <c r="S1350" t="s">
         <v>36</v>
       </c>
@@ -63391,6 +63868,9 @@
       <c r="Q1351">
         <v>1.4</v>
       </c>
+      <c r="R1351" t="s">
+        <v>449</v>
+      </c>
       <c r="S1351" t="s">
         <v>23</v>
       </c>
@@ -63432,6 +63912,9 @@
       <c r="Q1352">
         <v>1.1499999999999999</v>
       </c>
+      <c r="R1352" t="s">
+        <v>449</v>
+      </c>
       <c r="S1352" t="s">
         <v>23</v>
       </c>
@@ -63473,6 +63956,9 @@
       <c r="Q1353">
         <v>1.6</v>
       </c>
+      <c r="R1353" t="s">
+        <v>449</v>
+      </c>
       <c r="S1353" t="s">
         <v>23</v>
       </c>
@@ -63514,6 +64000,9 @@
       <c r="Q1354">
         <v>1.33</v>
       </c>
+      <c r="R1354" t="s">
+        <v>449</v>
+      </c>
       <c r="S1354" t="s">
         <v>23</v>
       </c>
@@ -63558,6 +64047,9 @@
       <c r="Q1355">
         <v>1.35</v>
       </c>
+      <c r="R1355" t="s">
+        <v>449</v>
+      </c>
       <c r="S1355" t="s">
         <v>23</v>
       </c>
@@ -63602,6 +64094,9 @@
       <c r="Q1356">
         <v>1.5</v>
       </c>
+      <c r="R1356" t="s">
+        <v>449</v>
+      </c>
       <c r="S1356" t="s">
         <v>23</v>
       </c>
@@ -63646,6 +64141,9 @@
       <c r="Q1357">
         <v>1.42</v>
       </c>
+      <c r="R1357" t="s">
+        <v>449</v>
+      </c>
       <c r="S1357" t="s">
         <v>23</v>
       </c>
@@ -63687,6 +64185,9 @@
       <c r="Q1358">
         <v>1.4</v>
       </c>
+      <c r="R1358" t="s">
+        <v>449</v>
+      </c>
       <c r="S1358" t="s">
         <v>36</v>
       </c>
@@ -63728,6 +64229,9 @@
       <c r="Q1359">
         <v>1</v>
       </c>
+      <c r="R1359" t="s">
+        <v>449</v>
+      </c>
       <c r="S1359" t="s">
         <v>36</v>
       </c>
@@ -63769,6 +64273,9 @@
       <c r="Q1360">
         <v>1.08</v>
       </c>
+      <c r="R1360" t="s">
+        <v>449</v>
+      </c>
       <c r="S1360" t="s">
         <v>36</v>
       </c>
@@ -63810,6 +64317,9 @@
       <c r="Q1361">
         <v>1.38</v>
       </c>
+      <c r="R1361" t="s">
+        <v>449</v>
+      </c>
       <c r="S1361" t="s">
         <v>36</v>
       </c>
@@ -63851,6 +64361,9 @@
       <c r="Q1362">
         <v>1.17</v>
       </c>
+      <c r="R1362" t="s">
+        <v>449</v>
+      </c>
       <c r="S1362" t="s">
         <v>36</v>
       </c>
@@ -63892,6 +64405,9 @@
       <c r="Q1363">
         <v>1</v>
       </c>
+      <c r="R1363" t="s">
+        <v>449</v>
+      </c>
       <c r="S1363" t="s">
         <v>448</v>
       </c>
@@ -63933,6 +64449,9 @@
       <c r="Q1364">
         <v>1.54</v>
       </c>
+      <c r="R1364" t="s">
+        <v>449</v>
+      </c>
       <c r="S1364" t="s">
         <v>36</v>
       </c>
@@ -63974,6 +64493,9 @@
       <c r="Q1365">
         <v>1</v>
       </c>
+      <c r="R1365" t="s">
+        <v>449</v>
+      </c>
       <c r="S1365" t="s">
         <v>448</v>
       </c>
@@ -64015,6 +64537,9 @@
       <c r="Q1366">
         <v>1.06</v>
       </c>
+      <c r="R1366" t="s">
+        <v>449</v>
+      </c>
       <c r="S1366" t="s">
         <v>36</v>
       </c>
@@ -64056,6 +64581,9 @@
       <c r="Q1367">
         <v>1.45</v>
       </c>
+      <c r="R1367" t="s">
+        <v>449</v>
+      </c>
       <c r="S1367" t="s">
         <v>36</v>
       </c>
@@ -64097,6 +64625,9 @@
       <c r="Q1368">
         <v>1.63</v>
       </c>
+      <c r="R1368" t="s">
+        <v>449</v>
+      </c>
       <c r="S1368" t="s">
         <v>36</v>
       </c>
@@ -64138,6 +64669,9 @@
       <c r="Q1369">
         <v>1.56</v>
       </c>
+      <c r="R1369" t="s">
+        <v>449</v>
+      </c>
       <c r="S1369" t="s">
         <v>36</v>
       </c>
@@ -64179,6 +64713,9 @@
       <c r="Q1370">
         <v>1.33</v>
       </c>
+      <c r="R1370" t="s">
+        <v>449</v>
+      </c>
       <c r="S1370" t="s">
         <v>36</v>
       </c>
@@ -64220,6 +64757,9 @@
       <c r="Q1371">
         <v>1.33</v>
       </c>
+      <c r="R1371" t="s">
+        <v>449</v>
+      </c>
       <c r="S1371" t="s">
         <v>36</v>
       </c>
@@ -64261,6 +64801,9 @@
       <c r="Q1372">
         <v>1.38</v>
       </c>
+      <c r="R1372" t="s">
+        <v>449</v>
+      </c>
       <c r="S1372" t="s">
         <v>36</v>
       </c>
@@ -64302,6 +64845,9 @@
       <c r="Q1373">
         <v>1.82</v>
       </c>
+      <c r="R1373" t="s">
+        <v>449</v>
+      </c>
       <c r="S1373" t="s">
         <v>36</v>
       </c>
@@ -64343,6 +64889,9 @@
       <c r="Q1374">
         <v>1.33</v>
       </c>
+      <c r="R1374" t="s">
+        <v>449</v>
+      </c>
       <c r="S1374" t="s">
         <v>36</v>
       </c>
@@ -64384,6 +64933,9 @@
       <c r="Q1375">
         <v>1.1200000000000001</v>
       </c>
+      <c r="R1375" t="s">
+        <v>449</v>
+      </c>
       <c r="S1375" t="s">
         <v>36</v>
       </c>
@@ -64425,6 +64977,9 @@
       <c r="Q1376">
         <v>1.3</v>
       </c>
+      <c r="R1376" t="s">
+        <v>449</v>
+      </c>
       <c r="S1376" t="s">
         <v>36</v>
       </c>
@@ -64466,6 +65021,9 @@
       <c r="Q1377">
         <v>1.1299999999999999</v>
       </c>
+      <c r="R1377" t="s">
+        <v>449</v>
+      </c>
       <c r="S1377" t="s">
         <v>448</v>
       </c>
@@ -64507,6 +65065,9 @@
       <c r="Q1378">
         <v>2.12</v>
       </c>
+      <c r="R1378" t="s">
+        <v>449</v>
+      </c>
       <c r="S1378" t="s">
         <v>36</v>
       </c>
@@ -64548,6 +65109,9 @@
       <c r="Q1379">
         <v>1.35</v>
       </c>
+      <c r="R1379" t="s">
+        <v>449</v>
+      </c>
       <c r="S1379" t="s">
         <v>36</v>
       </c>
@@ -64589,6 +65153,9 @@
       <c r="Q1380">
         <v>1.18</v>
       </c>
+      <c r="R1380" t="s">
+        <v>449</v>
+      </c>
       <c r="S1380" t="s">
         <v>36</v>
       </c>
@@ -64636,6 +65203,9 @@
       <c r="Q1381">
         <v>3.1</v>
       </c>
+      <c r="R1381" t="s">
+        <v>449</v>
+      </c>
       <c r="S1381" t="s">
         <v>36</v>
       </c>
@@ -64677,6 +65247,9 @@
       <c r="Q1382">
         <v>1.25</v>
       </c>
+      <c r="R1382" t="s">
+        <v>449</v>
+      </c>
       <c r="S1382" t="s">
         <v>36</v>
       </c>
@@ -64718,6 +65291,9 @@
       <c r="Q1383">
         <v>1.46</v>
       </c>
+      <c r="R1383" t="s">
+        <v>449</v>
+      </c>
       <c r="S1383" t="s">
         <v>36</v>
       </c>
@@ -64759,6 +65335,9 @@
       <c r="Q1384">
         <v>1</v>
       </c>
+      <c r="R1384" t="s">
+        <v>449</v>
+      </c>
       <c r="S1384" t="s">
         <v>36</v>
       </c>
@@ -64800,6 +65379,9 @@
       <c r="Q1385">
         <v>1.1599999999999999</v>
       </c>
+      <c r="R1385" t="s">
+        <v>449</v>
+      </c>
       <c r="S1385" t="s">
         <v>36</v>
       </c>
@@ -64841,6 +65423,9 @@
       <c r="Q1386">
         <v>1.1000000000000001</v>
       </c>
+      <c r="R1386" t="s">
+        <v>449</v>
+      </c>
       <c r="S1386" t="s">
         <v>36</v>
       </c>
@@ -64882,6 +65467,9 @@
       <c r="Q1387">
         <v>1.73</v>
       </c>
+      <c r="R1387" t="s">
+        <v>449</v>
+      </c>
       <c r="S1387" t="s">
         <v>36</v>
       </c>
@@ -64923,6 +65511,9 @@
       <c r="Q1388">
         <v>1.28</v>
       </c>
+      <c r="R1388" t="s">
+        <v>449</v>
+      </c>
       <c r="S1388" t="s">
         <v>36</v>
       </c>
@@ -64967,6 +65558,9 @@
       <c r="Q1389">
         <v>1</v>
       </c>
+      <c r="R1389" t="s">
+        <v>449</v>
+      </c>
       <c r="S1389" t="s">
         <v>23</v>
       </c>
@@ -65010,6 +65604,9 @@
       </c>
       <c r="Q1390">
         <v>1.19</v>
+      </c>
+      <c r="R1390" t="s">
+        <v>449</v>
       </c>
       <c r="S1390" t="s">
         <v>23</v>

--- a/Data_Master.xlsx
+++ b/Data_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Kantin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C14EA6F-BCB0-4C09-8A85-F70DDB8F24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868EC71C-120E-4407-A0D0-08F71AD3ACA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFC52FFA-175C-4E6E-9BE3-CE0A8ECCF11B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7846" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8964" uniqueCount="451">
   <si>
     <t>product</t>
   </si>
@@ -1390,6 +1390,9 @@
   <si>
     <t>Juni</t>
   </si>
+  <si>
+    <t>Roti Tawar</t>
+  </si>
 </sst>
 </file>
 
@@ -1767,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}">
-  <dimension ref="A1:S1390"/>
+  <dimension ref="A1:S1589"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -65612,6 +65615,9134 @@
         <v>23</v>
       </c>
     </row>
+    <row r="1391" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1391" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1391">
+        <v>345</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1391">
+        <v>5520000</v>
+      </c>
+      <c r="K1391">
+        <v>0</v>
+      </c>
+      <c r="L1391">
+        <v>0</v>
+      </c>
+      <c r="M1391">
+        <v>5520000</v>
+      </c>
+      <c r="N1391">
+        <v>3795000</v>
+      </c>
+      <c r="O1391">
+        <v>1725000</v>
+      </c>
+      <c r="P1391">
+        <v>289</v>
+      </c>
+      <c r="Q1391">
+        <v>1.19</v>
+      </c>
+      <c r="R1391" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1391" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1392" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1392">
+        <v>64</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1392">
+        <v>1024000</v>
+      </c>
+      <c r="K1392">
+        <v>0</v>
+      </c>
+      <c r="L1392">
+        <v>0</v>
+      </c>
+      <c r="M1392">
+        <v>1024000</v>
+      </c>
+      <c r="N1392">
+        <v>672000</v>
+      </c>
+      <c r="O1392">
+        <v>352000</v>
+      </c>
+      <c r="P1392">
+        <v>54</v>
+      </c>
+      <c r="Q1392">
+        <v>1.19</v>
+      </c>
+      <c r="R1392" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1392" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1393" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1393">
+        <v>24</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1393">
+        <v>480000</v>
+      </c>
+      <c r="K1393">
+        <v>0</v>
+      </c>
+      <c r="L1393">
+        <v>0</v>
+      </c>
+      <c r="M1393">
+        <v>480000</v>
+      </c>
+      <c r="N1393">
+        <v>324000</v>
+      </c>
+      <c r="O1393">
+        <v>156000</v>
+      </c>
+      <c r="P1393">
+        <v>19</v>
+      </c>
+      <c r="Q1393">
+        <v>1.26</v>
+      </c>
+      <c r="R1393" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1393" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1394" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1394">
+        <v>342</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1394">
+        <v>6840000</v>
+      </c>
+      <c r="K1394">
+        <v>0</v>
+      </c>
+      <c r="L1394">
+        <v>0</v>
+      </c>
+      <c r="M1394">
+        <v>6840000</v>
+      </c>
+      <c r="N1394">
+        <v>4617000</v>
+      </c>
+      <c r="O1394">
+        <v>2223000</v>
+      </c>
+      <c r="P1394">
+        <v>274</v>
+      </c>
+      <c r="Q1394">
+        <v>1.25</v>
+      </c>
+      <c r="R1394" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1394" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1395" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1395">
+        <v>87</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1395">
+        <v>870000</v>
+      </c>
+      <c r="K1395">
+        <v>0</v>
+      </c>
+      <c r="L1395">
+        <v>0</v>
+      </c>
+      <c r="M1395">
+        <v>870000</v>
+      </c>
+      <c r="N1395">
+        <v>522000</v>
+      </c>
+      <c r="O1395">
+        <v>348000</v>
+      </c>
+      <c r="P1395">
+        <v>66</v>
+      </c>
+      <c r="Q1395">
+        <v>1.32</v>
+      </c>
+      <c r="R1395" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1395" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1396" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1396">
+        <v>35</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1396">
+        <v>245000</v>
+      </c>
+      <c r="K1396">
+        <v>0</v>
+      </c>
+      <c r="L1396">
+        <v>0</v>
+      </c>
+      <c r="M1396">
+        <v>245000</v>
+      </c>
+      <c r="N1396">
+        <v>210000</v>
+      </c>
+      <c r="O1396">
+        <v>35000</v>
+      </c>
+      <c r="P1396">
+        <v>28</v>
+      </c>
+      <c r="Q1396">
+        <v>1.25</v>
+      </c>
+      <c r="R1396" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1396" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1397" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1397">
+        <v>202</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1397">
+        <v>808000</v>
+      </c>
+      <c r="K1397">
+        <v>0</v>
+      </c>
+      <c r="L1397">
+        <v>0</v>
+      </c>
+      <c r="M1397">
+        <v>808000</v>
+      </c>
+      <c r="N1397">
+        <v>606000</v>
+      </c>
+      <c r="O1397">
+        <v>202000</v>
+      </c>
+      <c r="P1397">
+        <v>106</v>
+      </c>
+      <c r="Q1397">
+        <v>1.91</v>
+      </c>
+      <c r="R1397" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1397" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1398" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1398">
+        <v>25</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1398">
+        <v>125000</v>
+      </c>
+      <c r="K1398">
+        <v>0</v>
+      </c>
+      <c r="L1398">
+        <v>0</v>
+      </c>
+      <c r="M1398">
+        <v>125000</v>
+      </c>
+      <c r="N1398">
+        <v>100000</v>
+      </c>
+      <c r="O1398">
+        <v>25000</v>
+      </c>
+      <c r="P1398">
+        <v>23</v>
+      </c>
+      <c r="Q1398">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R1398" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1398" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1399" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1399">
+        <v>43</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1399">
+        <v>860000</v>
+      </c>
+      <c r="K1399">
+        <v>0</v>
+      </c>
+      <c r="L1399">
+        <v>0</v>
+      </c>
+      <c r="M1399">
+        <v>868000</v>
+      </c>
+      <c r="N1399">
+        <v>651217.4</v>
+      </c>
+      <c r="O1399">
+        <v>216782.6</v>
+      </c>
+      <c r="P1399">
+        <v>38</v>
+      </c>
+      <c r="Q1399">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1399" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1399" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1400" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1400">
+        <v>184</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1400">
+        <v>2760000</v>
+      </c>
+      <c r="K1400">
+        <v>0</v>
+      </c>
+      <c r="L1400">
+        <v>0</v>
+      </c>
+      <c r="M1400">
+        <v>2768000</v>
+      </c>
+      <c r="N1400">
+        <v>2030217.4</v>
+      </c>
+      <c r="O1400">
+        <v>737782.6</v>
+      </c>
+      <c r="P1400">
+        <v>153</v>
+      </c>
+      <c r="Q1400">
+        <v>1.2</v>
+      </c>
+      <c r="R1400" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1400" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1401" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1401">
+        <v>84</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1401">
+        <v>1512000</v>
+      </c>
+      <c r="K1401">
+        <v>0</v>
+      </c>
+      <c r="L1401">
+        <v>0</v>
+      </c>
+      <c r="M1401">
+        <v>1538000</v>
+      </c>
+      <c r="N1401">
+        <v>1112206.55</v>
+      </c>
+      <c r="O1401">
+        <v>425793.45</v>
+      </c>
+      <c r="P1401">
+        <v>72</v>
+      </c>
+      <c r="Q1401">
+        <v>1.17</v>
+      </c>
+      <c r="R1401" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1401" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1402" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1402">
+        <v>133</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1402">
+        <v>532000</v>
+      </c>
+      <c r="K1402">
+        <v>0</v>
+      </c>
+      <c r="L1402">
+        <v>0</v>
+      </c>
+      <c r="M1402">
+        <v>532000</v>
+      </c>
+      <c r="N1402">
+        <v>399000</v>
+      </c>
+      <c r="O1402">
+        <v>133000</v>
+      </c>
+      <c r="P1402">
+        <v>82</v>
+      </c>
+      <c r="Q1402">
+        <v>1.62</v>
+      </c>
+      <c r="R1402" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1402" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1403" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1403">
+        <v>17</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1403">
+        <v>255000</v>
+      </c>
+      <c r="K1403">
+        <v>0</v>
+      </c>
+      <c r="L1403">
+        <v>0</v>
+      </c>
+      <c r="M1403">
+        <v>255000</v>
+      </c>
+      <c r="N1403">
+        <v>231200</v>
+      </c>
+      <c r="O1403">
+        <v>23800</v>
+      </c>
+      <c r="P1403">
+        <v>17</v>
+      </c>
+      <c r="Q1403">
+        <v>1</v>
+      </c>
+      <c r="R1403" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1403" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1404" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1404">
+        <v>1</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1404">
+        <v>15000</v>
+      </c>
+      <c r="K1404">
+        <v>0</v>
+      </c>
+      <c r="L1404">
+        <v>0</v>
+      </c>
+      <c r="M1404">
+        <v>15000</v>
+      </c>
+      <c r="N1404">
+        <v>11175</v>
+      </c>
+      <c r="O1404">
+        <v>3825</v>
+      </c>
+      <c r="P1404">
+        <v>1</v>
+      </c>
+      <c r="Q1404">
+        <v>1</v>
+      </c>
+      <c r="R1404" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1404" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1405" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1405">
+        <v>31</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1405">
+        <v>651000</v>
+      </c>
+      <c r="K1405">
+        <v>0</v>
+      </c>
+      <c r="L1405">
+        <v>0</v>
+      </c>
+      <c r="M1405">
+        <v>651000</v>
+      </c>
+      <c r="N1405">
+        <v>186269.39</v>
+      </c>
+      <c r="O1405">
+        <v>464730.61</v>
+      </c>
+      <c r="P1405">
+        <v>25</v>
+      </c>
+      <c r="Q1405">
+        <v>1.24</v>
+      </c>
+      <c r="R1405" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1405" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1406" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1406">
+        <v>57</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1406">
+        <v>1254000</v>
+      </c>
+      <c r="K1406">
+        <v>0</v>
+      </c>
+      <c r="L1406">
+        <v>0</v>
+      </c>
+      <c r="M1406">
+        <v>1354000</v>
+      </c>
+      <c r="N1406">
+        <v>403100.01</v>
+      </c>
+      <c r="O1406">
+        <v>950899.99</v>
+      </c>
+      <c r="P1406">
+        <v>46</v>
+      </c>
+      <c r="Q1406">
+        <v>1.24</v>
+      </c>
+      <c r="R1406" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1406" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1407" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1407">
+        <v>38</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1407">
+        <v>912000</v>
+      </c>
+      <c r="K1407">
+        <v>0</v>
+      </c>
+      <c r="L1407">
+        <v>0</v>
+      </c>
+      <c r="M1407">
+        <v>924000</v>
+      </c>
+      <c r="N1407">
+        <v>275189.69</v>
+      </c>
+      <c r="O1407">
+        <v>648810.31000000006</v>
+      </c>
+      <c r="P1407">
+        <v>32</v>
+      </c>
+      <c r="Q1407">
+        <v>1.19</v>
+      </c>
+      <c r="R1407" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1407" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1408" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1408">
+        <v>49</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1408">
+        <v>245000</v>
+      </c>
+      <c r="K1408">
+        <v>0</v>
+      </c>
+      <c r="L1408">
+        <v>0</v>
+      </c>
+      <c r="M1408">
+        <v>245000</v>
+      </c>
+      <c r="N1408">
+        <v>126583.17</v>
+      </c>
+      <c r="O1408">
+        <v>118416.83</v>
+      </c>
+      <c r="P1408">
+        <v>44</v>
+      </c>
+      <c r="Q1408">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1408" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1408" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1409" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1409">
+        <v>333</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1409">
+        <v>1665000</v>
+      </c>
+      <c r="K1409">
+        <v>0</v>
+      </c>
+      <c r="L1409">
+        <v>0</v>
+      </c>
+      <c r="M1409">
+        <v>1665000</v>
+      </c>
+      <c r="N1409">
+        <v>548953.38</v>
+      </c>
+      <c r="O1409">
+        <v>1116046.6200000001</v>
+      </c>
+      <c r="P1409">
+        <v>269</v>
+      </c>
+      <c r="Q1409">
+        <v>1.24</v>
+      </c>
+      <c r="R1409" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1409" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1410" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1410">
+        <v>4</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1410">
+        <v>20000</v>
+      </c>
+      <c r="K1410">
+        <v>0</v>
+      </c>
+      <c r="L1410">
+        <v>0</v>
+      </c>
+      <c r="M1410">
+        <v>20000</v>
+      </c>
+      <c r="N1410">
+        <v>9166.68</v>
+      </c>
+      <c r="O1410">
+        <v>10833.32</v>
+      </c>
+      <c r="P1410">
+        <v>4</v>
+      </c>
+      <c r="Q1410">
+        <v>1</v>
+      </c>
+      <c r="R1410" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1410" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1411" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1411">
+        <v>23</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1411">
+        <v>115000</v>
+      </c>
+      <c r="K1411">
+        <v>0</v>
+      </c>
+      <c r="L1411">
+        <v>0</v>
+      </c>
+      <c r="M1411">
+        <v>115000</v>
+      </c>
+      <c r="N1411">
+        <v>0</v>
+      </c>
+      <c r="O1411">
+        <v>115000</v>
+      </c>
+      <c r="P1411">
+        <v>19</v>
+      </c>
+      <c r="Q1411">
+        <v>1.21</v>
+      </c>
+      <c r="R1411" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1411" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1412" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1412">
+        <v>2</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1412">
+        <v>16000</v>
+      </c>
+      <c r="K1412">
+        <v>0</v>
+      </c>
+      <c r="L1412">
+        <v>0</v>
+      </c>
+      <c r="M1412">
+        <v>16000</v>
+      </c>
+      <c r="N1412">
+        <v>11400</v>
+      </c>
+      <c r="O1412">
+        <v>4600</v>
+      </c>
+      <c r="P1412">
+        <v>2</v>
+      </c>
+      <c r="Q1412">
+        <v>1</v>
+      </c>
+      <c r="R1412" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1412" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1413" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1413">
+        <v>17</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1413">
+        <v>255000</v>
+      </c>
+      <c r="K1413">
+        <v>0</v>
+      </c>
+      <c r="L1413">
+        <v>0</v>
+      </c>
+      <c r="M1413">
+        <v>255000</v>
+      </c>
+      <c r="N1413">
+        <v>204000</v>
+      </c>
+      <c r="O1413">
+        <v>51000</v>
+      </c>
+      <c r="P1413">
+        <v>14</v>
+      </c>
+      <c r="Q1413">
+        <v>1.21</v>
+      </c>
+      <c r="R1413" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1413" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1414" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1414">
+        <v>45</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1414">
+        <v>270000</v>
+      </c>
+      <c r="K1414">
+        <v>0</v>
+      </c>
+      <c r="L1414">
+        <v>0</v>
+      </c>
+      <c r="M1414">
+        <v>270000</v>
+      </c>
+      <c r="N1414">
+        <v>161249.85</v>
+      </c>
+      <c r="O1414">
+        <v>108750.15</v>
+      </c>
+      <c r="P1414">
+        <v>40</v>
+      </c>
+      <c r="Q1414">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1414" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1414" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1415" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1415">
+        <v>3</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1415">
+        <v>24000</v>
+      </c>
+      <c r="K1415">
+        <v>0</v>
+      </c>
+      <c r="L1415">
+        <v>0</v>
+      </c>
+      <c r="M1415">
+        <v>24000</v>
+      </c>
+      <c r="N1415">
+        <v>15600</v>
+      </c>
+      <c r="O1415">
+        <v>8400</v>
+      </c>
+      <c r="P1415">
+        <v>3</v>
+      </c>
+      <c r="Q1415">
+        <v>1</v>
+      </c>
+      <c r="R1415" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1415" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1416" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1416">
+        <v>1072</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1416">
+        <v>5360000</v>
+      </c>
+      <c r="K1416">
+        <v>0</v>
+      </c>
+      <c r="L1416">
+        <v>0</v>
+      </c>
+      <c r="M1416">
+        <v>5360000</v>
+      </c>
+      <c r="N1416">
+        <v>1768617.92</v>
+      </c>
+      <c r="O1416">
+        <v>3591382.08</v>
+      </c>
+      <c r="P1416">
+        <v>537</v>
+      </c>
+      <c r="Q1416">
+        <v>2</v>
+      </c>
+      <c r="R1416" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1416" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1417" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1417">
+        <v>13</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1417">
+        <v>91000</v>
+      </c>
+      <c r="K1417">
+        <v>0</v>
+      </c>
+      <c r="L1417">
+        <v>0</v>
+      </c>
+      <c r="M1417">
+        <v>91000</v>
+      </c>
+      <c r="N1417">
+        <v>67925</v>
+      </c>
+      <c r="O1417">
+        <v>23075</v>
+      </c>
+      <c r="P1417">
+        <v>12</v>
+      </c>
+      <c r="Q1417">
+        <v>1.08</v>
+      </c>
+      <c r="R1417" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1417" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1418" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1418">
+        <v>88</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1418">
+        <v>880000</v>
+      </c>
+      <c r="K1418">
+        <v>0</v>
+      </c>
+      <c r="L1418">
+        <v>0</v>
+      </c>
+      <c r="M1418">
+        <v>880000</v>
+      </c>
+      <c r="N1418">
+        <v>641666.96</v>
+      </c>
+      <c r="O1418">
+        <v>238333.04</v>
+      </c>
+      <c r="P1418">
+        <v>58</v>
+      </c>
+      <c r="Q1418">
+        <v>1.52</v>
+      </c>
+      <c r="R1418" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1418" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1419" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1419">
+        <v>72</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1419">
+        <v>1800000</v>
+      </c>
+      <c r="K1419">
+        <v>0</v>
+      </c>
+      <c r="L1419">
+        <v>0</v>
+      </c>
+      <c r="M1419">
+        <v>1800000</v>
+      </c>
+      <c r="N1419">
+        <v>1440000</v>
+      </c>
+      <c r="O1419">
+        <v>360000</v>
+      </c>
+      <c r="P1419">
+        <v>61</v>
+      </c>
+      <c r="Q1419">
+        <v>1.18</v>
+      </c>
+      <c r="R1419" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1419" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1420" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1420">
+        <v>6</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1420">
+        <v>48000</v>
+      </c>
+      <c r="K1420">
+        <v>0</v>
+      </c>
+      <c r="L1420">
+        <v>0</v>
+      </c>
+      <c r="M1420">
+        <v>48000</v>
+      </c>
+      <c r="N1420">
+        <v>33964.14</v>
+      </c>
+      <c r="O1420">
+        <v>14035.86</v>
+      </c>
+      <c r="P1420">
+        <v>6</v>
+      </c>
+      <c r="Q1420">
+        <v>1</v>
+      </c>
+      <c r="R1420" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1420" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1421" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1421">
+        <v>91</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1421">
+        <v>637000</v>
+      </c>
+      <c r="K1421">
+        <v>0</v>
+      </c>
+      <c r="L1421">
+        <v>0</v>
+      </c>
+      <c r="M1421">
+        <v>637000</v>
+      </c>
+      <c r="N1421">
+        <v>470600.13</v>
+      </c>
+      <c r="O1421">
+        <v>166399.87</v>
+      </c>
+      <c r="P1421">
+        <v>70</v>
+      </c>
+      <c r="Q1421">
+        <v>1.3</v>
+      </c>
+      <c r="R1421" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1421" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1422" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1422">
+        <v>36</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1422">
+        <v>540000</v>
+      </c>
+      <c r="K1422">
+        <v>0</v>
+      </c>
+      <c r="L1422">
+        <v>0</v>
+      </c>
+      <c r="M1422">
+        <v>540000</v>
+      </c>
+      <c r="N1422">
+        <v>432000</v>
+      </c>
+      <c r="O1422">
+        <v>108000</v>
+      </c>
+      <c r="P1422">
+        <v>25</v>
+      </c>
+      <c r="Q1422">
+        <v>1.44</v>
+      </c>
+      <c r="R1422" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1422" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1423" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1423">
+        <v>45</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1423">
+        <v>540000</v>
+      </c>
+      <c r="K1423">
+        <v>0</v>
+      </c>
+      <c r="L1423">
+        <v>0</v>
+      </c>
+      <c r="M1423">
+        <v>540000</v>
+      </c>
+      <c r="N1423">
+        <v>450000</v>
+      </c>
+      <c r="O1423">
+        <v>90000</v>
+      </c>
+      <c r="P1423">
+        <v>35</v>
+      </c>
+      <c r="Q1423">
+        <v>1.29</v>
+      </c>
+      <c r="R1423" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1423" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1424" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1424">
+        <v>1</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1424">
+        <v>7000</v>
+      </c>
+      <c r="K1424">
+        <v>0</v>
+      </c>
+      <c r="L1424">
+        <v>0</v>
+      </c>
+      <c r="M1424">
+        <v>7000</v>
+      </c>
+      <c r="N1424">
+        <v>3166.67</v>
+      </c>
+      <c r="O1424">
+        <v>3833.33</v>
+      </c>
+      <c r="P1424">
+        <v>1</v>
+      </c>
+      <c r="Q1424">
+        <v>1</v>
+      </c>
+      <c r="R1424" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1424" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1425" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1425" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1425">
+        <v>10</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1425">
+        <v>80000</v>
+      </c>
+      <c r="K1425">
+        <v>0</v>
+      </c>
+      <c r="L1425">
+        <v>0</v>
+      </c>
+      <c r="M1425">
+        <v>80000</v>
+      </c>
+      <c r="N1425">
+        <v>60300.6</v>
+      </c>
+      <c r="O1425">
+        <v>19699.400000000001</v>
+      </c>
+      <c r="P1425">
+        <v>10</v>
+      </c>
+      <c r="Q1425">
+        <v>1</v>
+      </c>
+      <c r="R1425" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1425" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1426" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1426">
+        <v>24</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1426">
+        <v>360000</v>
+      </c>
+      <c r="K1426">
+        <v>0</v>
+      </c>
+      <c r="L1426">
+        <v>0</v>
+      </c>
+      <c r="M1426">
+        <v>360000</v>
+      </c>
+      <c r="N1426">
+        <v>223200</v>
+      </c>
+      <c r="O1426">
+        <v>136800</v>
+      </c>
+      <c r="P1426">
+        <v>21</v>
+      </c>
+      <c r="Q1426">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1426" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1426" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1427" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1427">
+        <v>110</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1427">
+        <v>550000</v>
+      </c>
+      <c r="K1427">
+        <v>0</v>
+      </c>
+      <c r="L1427">
+        <v>0</v>
+      </c>
+      <c r="M1427">
+        <v>550000</v>
+      </c>
+      <c r="N1427">
+        <v>284166.3</v>
+      </c>
+      <c r="O1427">
+        <v>265833.7</v>
+      </c>
+      <c r="P1427">
+        <v>78</v>
+      </c>
+      <c r="Q1427">
+        <v>1.41</v>
+      </c>
+      <c r="R1427" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1427" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1428" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1428" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1428">
+        <v>18</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1428">
+        <v>216000</v>
+      </c>
+      <c r="K1428">
+        <v>0</v>
+      </c>
+      <c r="L1428">
+        <v>0</v>
+      </c>
+      <c r="M1428">
+        <v>216000</v>
+      </c>
+      <c r="N1428">
+        <v>168499.98</v>
+      </c>
+      <c r="O1428">
+        <v>47500.02</v>
+      </c>
+      <c r="P1428">
+        <v>15</v>
+      </c>
+      <c r="Q1428">
+        <v>1.2</v>
+      </c>
+      <c r="R1428" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1428" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1429" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1429">
+        <v>27</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1429">
+        <v>324000</v>
+      </c>
+      <c r="K1429">
+        <v>0</v>
+      </c>
+      <c r="L1429">
+        <v>0</v>
+      </c>
+      <c r="M1429">
+        <v>324000</v>
+      </c>
+      <c r="N1429">
+        <v>238500.18</v>
+      </c>
+      <c r="O1429">
+        <v>85499.82</v>
+      </c>
+      <c r="P1429">
+        <v>25</v>
+      </c>
+      <c r="Q1429">
+        <v>1.08</v>
+      </c>
+      <c r="R1429" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1429" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1430" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1430" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1430" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1430">
+        <v>39</v>
+      </c>
+      <c r="I1430" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1430">
+        <v>390000</v>
+      </c>
+      <c r="K1430">
+        <v>0</v>
+      </c>
+      <c r="L1430">
+        <v>0</v>
+      </c>
+      <c r="M1430">
+        <v>390000</v>
+      </c>
+      <c r="N1430">
+        <v>316875</v>
+      </c>
+      <c r="O1430">
+        <v>73125</v>
+      </c>
+      <c r="P1430">
+        <v>31</v>
+      </c>
+      <c r="Q1430">
+        <v>1.26</v>
+      </c>
+      <c r="R1430" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1430" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1431" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1431" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1431" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1431">
+        <v>43</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1431">
+        <v>344000</v>
+      </c>
+      <c r="K1431">
+        <v>0</v>
+      </c>
+      <c r="L1431">
+        <v>0</v>
+      </c>
+      <c r="M1431">
+        <v>344000</v>
+      </c>
+      <c r="N1431">
+        <v>268755.15999999997</v>
+      </c>
+      <c r="O1431">
+        <v>75244.84</v>
+      </c>
+      <c r="P1431">
+        <v>36</v>
+      </c>
+      <c r="Q1431">
+        <v>1.19</v>
+      </c>
+      <c r="R1431" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1431" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1432" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1432" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1432" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1432">
+        <v>75</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1432">
+        <v>600000</v>
+      </c>
+      <c r="K1432">
+        <v>0</v>
+      </c>
+      <c r="L1432">
+        <v>0</v>
+      </c>
+      <c r="M1432">
+        <v>600000</v>
+      </c>
+      <c r="N1432">
+        <v>466719</v>
+      </c>
+      <c r="O1432">
+        <v>133281</v>
+      </c>
+      <c r="P1432">
+        <v>64</v>
+      </c>
+      <c r="Q1432">
+        <v>1.17</v>
+      </c>
+      <c r="R1432" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1432" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1433" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1433" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1433" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1433">
+        <v>30</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1433">
+        <v>270000</v>
+      </c>
+      <c r="K1433">
+        <v>0</v>
+      </c>
+      <c r="L1433">
+        <v>0</v>
+      </c>
+      <c r="M1433">
+        <v>270000</v>
+      </c>
+      <c r="N1433">
+        <v>230918.7</v>
+      </c>
+      <c r="O1433">
+        <v>39081.300000000003</v>
+      </c>
+      <c r="P1433">
+        <v>26</v>
+      </c>
+      <c r="Q1433">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="R1433" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1433" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1434" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1434" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1434" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1434">
+        <v>44</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1434">
+        <v>220000</v>
+      </c>
+      <c r="K1434">
+        <v>0</v>
+      </c>
+      <c r="L1434">
+        <v>0</v>
+      </c>
+      <c r="M1434">
+        <v>220000</v>
+      </c>
+      <c r="N1434">
+        <v>145840.64000000001</v>
+      </c>
+      <c r="O1434">
+        <v>74159.360000000001</v>
+      </c>
+      <c r="P1434">
+        <v>28</v>
+      </c>
+      <c r="Q1434">
+        <v>1.57</v>
+      </c>
+      <c r="R1434" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1434" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1435" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1435" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1435" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1435">
+        <v>19</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1435">
+        <v>152000</v>
+      </c>
+      <c r="K1435">
+        <v>0</v>
+      </c>
+      <c r="L1435">
+        <v>0</v>
+      </c>
+      <c r="M1435">
+        <v>152000</v>
+      </c>
+      <c r="N1435">
+        <v>109750.27</v>
+      </c>
+      <c r="O1435">
+        <v>42249.73</v>
+      </c>
+      <c r="P1435">
+        <v>15</v>
+      </c>
+      <c r="Q1435">
+        <v>1.27</v>
+      </c>
+      <c r="R1435" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1435" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1436" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1436" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1436" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1436">
+        <v>10</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1436">
+        <v>60000</v>
+      </c>
+      <c r="K1436">
+        <v>0</v>
+      </c>
+      <c r="L1436">
+        <v>0</v>
+      </c>
+      <c r="M1436">
+        <v>60000</v>
+      </c>
+      <c r="N1436">
+        <v>38041.699999999997</v>
+      </c>
+      <c r="O1436">
+        <v>21958.3</v>
+      </c>
+      <c r="P1436">
+        <v>7</v>
+      </c>
+      <c r="Q1436">
+        <v>1.43</v>
+      </c>
+      <c r="R1436" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1436" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1437" t="s">
+        <v>420</v>
+      </c>
+      <c r="D1437" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1437" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1437">
+        <v>30</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1437">
+        <v>900000</v>
+      </c>
+      <c r="K1437">
+        <v>0</v>
+      </c>
+      <c r="L1437">
+        <v>0</v>
+      </c>
+      <c r="M1437">
+        <v>900000</v>
+      </c>
+      <c r="N1437">
+        <v>750000</v>
+      </c>
+      <c r="O1437">
+        <v>150000</v>
+      </c>
+      <c r="P1437">
+        <v>28</v>
+      </c>
+      <c r="Q1437">
+        <v>1.07</v>
+      </c>
+      <c r="R1437" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1437" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1438" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1438" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1438" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1438">
+        <v>14</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1438">
+        <v>168000</v>
+      </c>
+      <c r="K1438">
+        <v>0</v>
+      </c>
+      <c r="L1438">
+        <v>0</v>
+      </c>
+      <c r="M1438">
+        <v>168000</v>
+      </c>
+      <c r="N1438">
+        <v>68646.69</v>
+      </c>
+      <c r="O1438">
+        <v>99353.31</v>
+      </c>
+      <c r="P1438">
+        <v>13</v>
+      </c>
+      <c r="Q1438">
+        <v>1.08</v>
+      </c>
+      <c r="R1438" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1438" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1439" t="s">
+        <v>397</v>
+      </c>
+      <c r="D1439" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1439">
+        <v>75</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1439">
+        <v>525000</v>
+      </c>
+      <c r="K1439">
+        <v>0</v>
+      </c>
+      <c r="L1439">
+        <v>0</v>
+      </c>
+      <c r="M1439">
+        <v>525000</v>
+      </c>
+      <c r="N1439">
+        <v>375000</v>
+      </c>
+      <c r="O1439">
+        <v>150000</v>
+      </c>
+      <c r="P1439">
+        <v>36</v>
+      </c>
+      <c r="Q1439">
+        <v>2.08</v>
+      </c>
+      <c r="R1439" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1439" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1440" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1440" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1440">
+        <v>49</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1440">
+        <v>882000</v>
+      </c>
+      <c r="K1440">
+        <v>0</v>
+      </c>
+      <c r="L1440">
+        <v>0</v>
+      </c>
+      <c r="M1440">
+        <v>882000</v>
+      </c>
+      <c r="N1440">
+        <v>735000</v>
+      </c>
+      <c r="O1440">
+        <v>147000</v>
+      </c>
+      <c r="P1440">
+        <v>32</v>
+      </c>
+      <c r="Q1440">
+        <v>1.53</v>
+      </c>
+      <c r="R1440" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1440" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1441" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1441" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1441">
+        <v>421</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1441">
+        <v>5473000</v>
+      </c>
+      <c r="K1441">
+        <v>0</v>
+      </c>
+      <c r="L1441">
+        <v>0</v>
+      </c>
+      <c r="M1441">
+        <v>5473000</v>
+      </c>
+      <c r="N1441">
+        <v>4210000</v>
+      </c>
+      <c r="O1441">
+        <v>1263000</v>
+      </c>
+      <c r="P1441">
+        <v>183</v>
+      </c>
+      <c r="Q1441">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R1441" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1441" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1442" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1442" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1442">
+        <v>51</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1442">
+        <v>816000</v>
+      </c>
+      <c r="K1442">
+        <v>0</v>
+      </c>
+      <c r="L1442">
+        <v>0</v>
+      </c>
+      <c r="M1442">
+        <v>816000</v>
+      </c>
+      <c r="N1442">
+        <v>612000</v>
+      </c>
+      <c r="O1442">
+        <v>204000</v>
+      </c>
+      <c r="P1442">
+        <v>28</v>
+      </c>
+      <c r="Q1442">
+        <v>1.82</v>
+      </c>
+      <c r="R1442" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1442" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1443" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1443" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1443">
+        <v>87</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1443">
+        <v>522000</v>
+      </c>
+      <c r="K1443">
+        <v>0</v>
+      </c>
+      <c r="L1443">
+        <v>0</v>
+      </c>
+      <c r="M1443">
+        <v>522000</v>
+      </c>
+      <c r="N1443">
+        <v>348000</v>
+      </c>
+      <c r="O1443">
+        <v>174000</v>
+      </c>
+      <c r="P1443">
+        <v>28</v>
+      </c>
+      <c r="Q1443">
+        <v>3.11</v>
+      </c>
+      <c r="R1443" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1443" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1444" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1444">
+        <v>792</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1444">
+        <v>5544000</v>
+      </c>
+      <c r="K1444">
+        <v>0</v>
+      </c>
+      <c r="L1444">
+        <v>0</v>
+      </c>
+      <c r="M1444">
+        <v>5544000</v>
+      </c>
+      <c r="N1444">
+        <v>3960000</v>
+      </c>
+      <c r="O1444">
+        <v>1584000</v>
+      </c>
+      <c r="P1444">
+        <v>235</v>
+      </c>
+      <c r="Q1444">
+        <v>3.37</v>
+      </c>
+      <c r="R1444" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1444" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1445" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1445">
+        <v>139</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1445">
+        <v>1807000</v>
+      </c>
+      <c r="K1445">
+        <v>0</v>
+      </c>
+      <c r="L1445">
+        <v>0</v>
+      </c>
+      <c r="M1445">
+        <v>1807000</v>
+      </c>
+      <c r="N1445">
+        <v>1390000</v>
+      </c>
+      <c r="O1445">
+        <v>417000</v>
+      </c>
+      <c r="P1445">
+        <v>64</v>
+      </c>
+      <c r="Q1445">
+        <v>2.17</v>
+      </c>
+      <c r="R1445" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1445" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1446" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1446">
+        <v>37</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1446">
+        <v>259000</v>
+      </c>
+      <c r="K1446">
+        <v>0</v>
+      </c>
+      <c r="L1446">
+        <v>0</v>
+      </c>
+      <c r="M1446">
+        <v>259000</v>
+      </c>
+      <c r="N1446">
+        <v>185000</v>
+      </c>
+      <c r="O1446">
+        <v>74000</v>
+      </c>
+      <c r="P1446">
+        <v>13</v>
+      </c>
+      <c r="Q1446">
+        <v>2.85</v>
+      </c>
+      <c r="R1446" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1446" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1447" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1447">
+        <v>32</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1447">
+        <v>320000</v>
+      </c>
+      <c r="K1447">
+        <v>0</v>
+      </c>
+      <c r="L1447">
+        <v>0</v>
+      </c>
+      <c r="M1447">
+        <v>320000</v>
+      </c>
+      <c r="N1447">
+        <v>256000</v>
+      </c>
+      <c r="O1447">
+        <v>64000</v>
+      </c>
+      <c r="P1447">
+        <v>20</v>
+      </c>
+      <c r="Q1447">
+        <v>1.6</v>
+      </c>
+      <c r="R1447" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1447" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1448" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1448">
+        <v>302</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1448">
+        <v>906000</v>
+      </c>
+      <c r="K1448">
+        <v>0</v>
+      </c>
+      <c r="L1448">
+        <v>0</v>
+      </c>
+      <c r="M1448">
+        <v>906000</v>
+      </c>
+      <c r="N1448">
+        <v>604000</v>
+      </c>
+      <c r="O1448">
+        <v>302000</v>
+      </c>
+      <c r="P1448">
+        <v>80</v>
+      </c>
+      <c r="Q1448">
+        <v>3.78</v>
+      </c>
+      <c r="R1448" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1448" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1449" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1449">
+        <v>471</v>
+      </c>
+      <c r="I1449" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1449">
+        <v>2826000</v>
+      </c>
+      <c r="K1449">
+        <v>0</v>
+      </c>
+      <c r="L1449">
+        <v>0</v>
+      </c>
+      <c r="M1449">
+        <v>2826000</v>
+      </c>
+      <c r="N1449">
+        <v>1884000</v>
+      </c>
+      <c r="O1449">
+        <v>942000</v>
+      </c>
+      <c r="P1449">
+        <v>159</v>
+      </c>
+      <c r="Q1449">
+        <v>2.96</v>
+      </c>
+      <c r="R1449" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1449" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1450" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1450">
+        <v>148</v>
+      </c>
+      <c r="I1450" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1450">
+        <v>740000</v>
+      </c>
+      <c r="K1450">
+        <v>0</v>
+      </c>
+      <c r="L1450">
+        <v>0</v>
+      </c>
+      <c r="M1450">
+        <v>740000</v>
+      </c>
+      <c r="N1450">
+        <v>444000</v>
+      </c>
+      <c r="O1450">
+        <v>296000</v>
+      </c>
+      <c r="P1450">
+        <v>65</v>
+      </c>
+      <c r="Q1450">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="R1450" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1450" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1451" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1451">
+        <v>3</v>
+      </c>
+      <c r="I1451" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1451">
+        <v>39000</v>
+      </c>
+      <c r="K1451">
+        <v>0</v>
+      </c>
+      <c r="L1451">
+        <v>0</v>
+      </c>
+      <c r="M1451">
+        <v>39000</v>
+      </c>
+      <c r="N1451">
+        <v>30000</v>
+      </c>
+      <c r="O1451">
+        <v>9000</v>
+      </c>
+      <c r="P1451">
+        <v>3</v>
+      </c>
+      <c r="Q1451">
+        <v>1</v>
+      </c>
+      <c r="R1451" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1451" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1452" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1452">
+        <v>80</v>
+      </c>
+      <c r="I1452" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1452">
+        <v>1040000</v>
+      </c>
+      <c r="K1452">
+        <v>0</v>
+      </c>
+      <c r="L1452">
+        <v>0</v>
+      </c>
+      <c r="M1452">
+        <v>1040000</v>
+      </c>
+      <c r="N1452">
+        <v>880000</v>
+      </c>
+      <c r="O1452">
+        <v>160000</v>
+      </c>
+      <c r="P1452">
+        <v>43</v>
+      </c>
+      <c r="Q1452">
+        <v>1.86</v>
+      </c>
+      <c r="R1452" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1452" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1453" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1453">
+        <v>200</v>
+      </c>
+      <c r="I1453" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1453">
+        <v>2600000</v>
+      </c>
+      <c r="K1453">
+        <v>0</v>
+      </c>
+      <c r="L1453">
+        <v>0</v>
+      </c>
+      <c r="M1453">
+        <v>2600000</v>
+      </c>
+      <c r="N1453">
+        <v>2000000</v>
+      </c>
+      <c r="O1453">
+        <v>600000</v>
+      </c>
+      <c r="P1453">
+        <v>89</v>
+      </c>
+      <c r="Q1453">
+        <v>2.25</v>
+      </c>
+      <c r="R1453" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1453" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1454" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1454">
+        <v>113</v>
+      </c>
+      <c r="I1454" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1454">
+        <v>1695000</v>
+      </c>
+      <c r="K1454">
+        <v>0</v>
+      </c>
+      <c r="L1454">
+        <v>0</v>
+      </c>
+      <c r="M1454">
+        <v>1695000</v>
+      </c>
+      <c r="N1454">
+        <v>1356000</v>
+      </c>
+      <c r="O1454">
+        <v>339000</v>
+      </c>
+      <c r="P1454">
+        <v>68</v>
+      </c>
+      <c r="Q1454">
+        <v>1.66</v>
+      </c>
+      <c r="R1454" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1454" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1455" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1455">
+        <v>290</v>
+      </c>
+      <c r="I1455" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1455">
+        <v>1740000</v>
+      </c>
+      <c r="K1455">
+        <v>0</v>
+      </c>
+      <c r="L1455">
+        <v>0</v>
+      </c>
+      <c r="M1455">
+        <v>1740000</v>
+      </c>
+      <c r="N1455">
+        <v>1160000</v>
+      </c>
+      <c r="O1455">
+        <v>580000</v>
+      </c>
+      <c r="P1455">
+        <v>131</v>
+      </c>
+      <c r="Q1455">
+        <v>2.21</v>
+      </c>
+      <c r="R1455" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1455" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1456" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1456">
+        <v>84</v>
+      </c>
+      <c r="I1456" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1456">
+        <v>1512000</v>
+      </c>
+      <c r="K1456">
+        <v>0</v>
+      </c>
+      <c r="L1456">
+        <v>0</v>
+      </c>
+      <c r="M1456">
+        <v>1512000</v>
+      </c>
+      <c r="N1456">
+        <v>1260000</v>
+      </c>
+      <c r="O1456">
+        <v>252000</v>
+      </c>
+      <c r="P1456">
+        <v>34</v>
+      </c>
+      <c r="Q1456">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R1456" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1456" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1457" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1457">
+        <v>2</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1457">
+        <v>6000</v>
+      </c>
+      <c r="K1457">
+        <v>0</v>
+      </c>
+      <c r="L1457">
+        <v>0</v>
+      </c>
+      <c r="M1457">
+        <v>6000</v>
+      </c>
+      <c r="N1457">
+        <v>0</v>
+      </c>
+      <c r="O1457">
+        <v>6000</v>
+      </c>
+      <c r="P1457">
+        <v>2</v>
+      </c>
+      <c r="Q1457">
+        <v>1</v>
+      </c>
+      <c r="R1457" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1457" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1458" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1458">
+        <v>8</v>
+      </c>
+      <c r="I1458" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1458">
+        <v>24000</v>
+      </c>
+      <c r="K1458">
+        <v>0</v>
+      </c>
+      <c r="L1458">
+        <v>0</v>
+      </c>
+      <c r="M1458">
+        <v>24000</v>
+      </c>
+      <c r="N1458">
+        <v>0</v>
+      </c>
+      <c r="O1458">
+        <v>24000</v>
+      </c>
+      <c r="P1458">
+        <v>7</v>
+      </c>
+      <c r="Q1458">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1458" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1458" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1459" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1459">
+        <v>24</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1459">
+        <v>72000</v>
+      </c>
+      <c r="K1459">
+        <v>0</v>
+      </c>
+      <c r="L1459">
+        <v>0</v>
+      </c>
+      <c r="M1459">
+        <v>72000</v>
+      </c>
+      <c r="N1459">
+        <v>0</v>
+      </c>
+      <c r="O1459">
+        <v>72000</v>
+      </c>
+      <c r="P1459">
+        <v>21</v>
+      </c>
+      <c r="Q1459">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1459" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1459" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1460" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1460">
+        <v>3</v>
+      </c>
+      <c r="I1460" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1460">
+        <v>9000</v>
+      </c>
+      <c r="K1460">
+        <v>0</v>
+      </c>
+      <c r="L1460">
+        <v>0</v>
+      </c>
+      <c r="M1460">
+        <v>9000</v>
+      </c>
+      <c r="N1460">
+        <v>2002.5</v>
+      </c>
+      <c r="O1460">
+        <v>6997.5</v>
+      </c>
+      <c r="P1460">
+        <v>3</v>
+      </c>
+      <c r="Q1460">
+        <v>1</v>
+      </c>
+      <c r="R1460" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1460" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1461" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1461">
+        <v>25</v>
+      </c>
+      <c r="I1461" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1461">
+        <v>175000</v>
+      </c>
+      <c r="K1461">
+        <v>0</v>
+      </c>
+      <c r="L1461">
+        <v>0</v>
+      </c>
+      <c r="M1461">
+        <v>178000</v>
+      </c>
+      <c r="N1461">
+        <v>38511.019999999997</v>
+      </c>
+      <c r="O1461">
+        <v>139488.98000000001</v>
+      </c>
+      <c r="P1461">
+        <v>19</v>
+      </c>
+      <c r="Q1461">
+        <v>1.32</v>
+      </c>
+      <c r="R1461" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1461" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1462" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1462">
+        <v>9</v>
+      </c>
+      <c r="I1462" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1462">
+        <v>45000</v>
+      </c>
+      <c r="K1462">
+        <v>0</v>
+      </c>
+      <c r="L1462">
+        <v>0</v>
+      </c>
+      <c r="M1462">
+        <v>45000</v>
+      </c>
+      <c r="N1462">
+        <v>13725.67</v>
+      </c>
+      <c r="O1462">
+        <v>31274.33</v>
+      </c>
+      <c r="P1462">
+        <v>7</v>
+      </c>
+      <c r="Q1462">
+        <v>1.29</v>
+      </c>
+      <c r="R1462" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1462" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1463" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1463">
+        <v>132</v>
+      </c>
+      <c r="I1463" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1463">
+        <v>660000</v>
+      </c>
+      <c r="K1463">
+        <v>0</v>
+      </c>
+      <c r="L1463">
+        <v>0</v>
+      </c>
+      <c r="M1463">
+        <v>660000</v>
+      </c>
+      <c r="N1463">
+        <v>201505.92000000001</v>
+      </c>
+      <c r="O1463">
+        <v>458494.08</v>
+      </c>
+      <c r="P1463">
+        <v>89</v>
+      </c>
+      <c r="Q1463">
+        <v>1.48</v>
+      </c>
+      <c r="R1463" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1463" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1464" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1464">
+        <v>52</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1464">
+        <v>1144000</v>
+      </c>
+      <c r="K1464">
+        <v>0</v>
+      </c>
+      <c r="L1464">
+        <v>0</v>
+      </c>
+      <c r="M1464">
+        <v>1150000</v>
+      </c>
+      <c r="N1464">
+        <v>707720.83</v>
+      </c>
+      <c r="O1464">
+        <v>442279.17</v>
+      </c>
+      <c r="P1464">
+        <v>39</v>
+      </c>
+      <c r="Q1464">
+        <v>1.33</v>
+      </c>
+      <c r="R1464" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1464" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1465" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1465">
+        <v>6</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1465">
+        <v>102000</v>
+      </c>
+      <c r="K1465">
+        <v>0</v>
+      </c>
+      <c r="L1465">
+        <v>0</v>
+      </c>
+      <c r="M1465">
+        <v>102000</v>
+      </c>
+      <c r="N1465">
+        <v>63000</v>
+      </c>
+      <c r="O1465">
+        <v>39000</v>
+      </c>
+      <c r="P1465">
+        <v>6</v>
+      </c>
+      <c r="Q1465">
+        <v>1</v>
+      </c>
+      <c r="R1465" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1465" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1466" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1466">
+        <v>2</v>
+      </c>
+      <c r="I1466" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1466">
+        <v>68000</v>
+      </c>
+      <c r="K1466">
+        <v>0</v>
+      </c>
+      <c r="L1466">
+        <v>0</v>
+      </c>
+      <c r="M1466">
+        <v>68000</v>
+      </c>
+      <c r="N1466">
+        <v>47200</v>
+      </c>
+      <c r="O1466">
+        <v>20800</v>
+      </c>
+      <c r="P1466">
+        <v>2</v>
+      </c>
+      <c r="Q1466">
+        <v>1</v>
+      </c>
+      <c r="R1466" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1466" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1467" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1467">
+        <v>16</v>
+      </c>
+      <c r="I1467" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1467">
+        <v>624000</v>
+      </c>
+      <c r="K1467">
+        <v>0</v>
+      </c>
+      <c r="L1467">
+        <v>0</v>
+      </c>
+      <c r="M1467">
+        <v>624000</v>
+      </c>
+      <c r="N1467">
+        <v>377153.12</v>
+      </c>
+      <c r="O1467">
+        <v>246846.88</v>
+      </c>
+      <c r="P1467">
+        <v>14</v>
+      </c>
+      <c r="Q1467">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1467" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1467" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1468" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1468">
+        <v>3</v>
+      </c>
+      <c r="I1468" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1468">
+        <v>117000</v>
+      </c>
+      <c r="K1468">
+        <v>0</v>
+      </c>
+      <c r="L1468">
+        <v>0</v>
+      </c>
+      <c r="M1468">
+        <v>117000</v>
+      </c>
+      <c r="N1468">
+        <v>70491.210000000006</v>
+      </c>
+      <c r="O1468">
+        <v>46508.79</v>
+      </c>
+      <c r="P1468">
+        <v>3</v>
+      </c>
+      <c r="Q1468">
+        <v>1</v>
+      </c>
+      <c r="R1468" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1468" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1469" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1469">
+        <v>27</v>
+      </c>
+      <c r="I1469" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1469">
+        <v>1053000</v>
+      </c>
+      <c r="K1469">
+        <v>0</v>
+      </c>
+      <c r="L1469">
+        <v>0</v>
+      </c>
+      <c r="M1469">
+        <v>1059000</v>
+      </c>
+      <c r="N1469">
+        <v>636020.89</v>
+      </c>
+      <c r="O1469">
+        <v>422979.11</v>
+      </c>
+      <c r="P1469">
+        <v>23</v>
+      </c>
+      <c r="Q1469">
+        <v>1.17</v>
+      </c>
+      <c r="R1469" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1469" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1470" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1470">
+        <v>8</v>
+      </c>
+      <c r="I1470" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1470">
+        <v>312000</v>
+      </c>
+      <c r="K1470">
+        <v>0</v>
+      </c>
+      <c r="L1470">
+        <v>0</v>
+      </c>
+      <c r="M1470">
+        <v>312000</v>
+      </c>
+      <c r="N1470">
+        <v>193316.56</v>
+      </c>
+      <c r="O1470">
+        <v>118683.44</v>
+      </c>
+      <c r="P1470">
+        <v>8</v>
+      </c>
+      <c r="Q1470">
+        <v>1</v>
+      </c>
+      <c r="R1470" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1470" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1471" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1471">
+        <v>72</v>
+      </c>
+      <c r="I1471" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1471">
+        <v>1872000</v>
+      </c>
+      <c r="K1471">
+        <v>0</v>
+      </c>
+      <c r="L1471">
+        <v>0</v>
+      </c>
+      <c r="M1471">
+        <v>1875000</v>
+      </c>
+      <c r="N1471">
+        <v>577390.73</v>
+      </c>
+      <c r="O1471">
+        <v>1297609.18</v>
+      </c>
+      <c r="P1471">
+        <v>62</v>
+      </c>
+      <c r="Q1471">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R1471" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1471" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1472" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1472">
+        <v>59</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1472">
+        <v>1534000</v>
+      </c>
+      <c r="K1472">
+        <v>0</v>
+      </c>
+      <c r="L1472">
+        <v>0</v>
+      </c>
+      <c r="M1472">
+        <v>1534000</v>
+      </c>
+      <c r="N1472">
+        <v>560087.11</v>
+      </c>
+      <c r="O1472">
+        <v>973912.89</v>
+      </c>
+      <c r="P1472">
+        <v>50</v>
+      </c>
+      <c r="Q1472">
+        <v>1.18</v>
+      </c>
+      <c r="R1472" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1472" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1473" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1473">
+        <v>9</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1473">
+        <v>207000</v>
+      </c>
+      <c r="K1473">
+        <v>0</v>
+      </c>
+      <c r="L1473">
+        <v>0</v>
+      </c>
+      <c r="M1473">
+        <v>207000</v>
+      </c>
+      <c r="N1473">
+        <v>120007.53</v>
+      </c>
+      <c r="O1473">
+        <v>86992.47</v>
+      </c>
+      <c r="P1473">
+        <v>8</v>
+      </c>
+      <c r="Q1473">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1473" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1473" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1474" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1474">
+        <v>1</v>
+      </c>
+      <c r="I1474" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1474">
+        <v>30000</v>
+      </c>
+      <c r="K1474">
+        <v>0</v>
+      </c>
+      <c r="L1474">
+        <v>0</v>
+      </c>
+      <c r="M1474">
+        <v>30000</v>
+      </c>
+      <c r="N1474">
+        <v>22700</v>
+      </c>
+      <c r="O1474">
+        <v>7300</v>
+      </c>
+      <c r="P1474">
+        <v>1</v>
+      </c>
+      <c r="Q1474">
+        <v>1</v>
+      </c>
+      <c r="R1474" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1474" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1475" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1475">
+        <v>67</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1475">
+        <v>1541000</v>
+      </c>
+      <c r="K1475">
+        <v>0</v>
+      </c>
+      <c r="L1475">
+        <v>0</v>
+      </c>
+      <c r="M1475">
+        <v>1544000</v>
+      </c>
+      <c r="N1475">
+        <v>589403.68999999994</v>
+      </c>
+      <c r="O1475">
+        <v>954596.31</v>
+      </c>
+      <c r="P1475">
+        <v>54</v>
+      </c>
+      <c r="Q1475">
+        <v>1.24</v>
+      </c>
+      <c r="R1475" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1475" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1476" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1476">
+        <v>6</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1476">
+        <v>138000</v>
+      </c>
+      <c r="K1476">
+        <v>0</v>
+      </c>
+      <c r="L1476">
+        <v>0</v>
+      </c>
+      <c r="M1476">
+        <v>138000</v>
+      </c>
+      <c r="N1476">
+        <v>52782.42</v>
+      </c>
+      <c r="O1476">
+        <v>85217.58</v>
+      </c>
+      <c r="P1476">
+        <v>6</v>
+      </c>
+      <c r="Q1476">
+        <v>1</v>
+      </c>
+      <c r="R1476" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1476" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1477" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1477">
+        <v>36</v>
+      </c>
+      <c r="I1477" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1477">
+        <v>828000</v>
+      </c>
+      <c r="K1477">
+        <v>0</v>
+      </c>
+      <c r="L1477">
+        <v>0</v>
+      </c>
+      <c r="M1477">
+        <v>828000</v>
+      </c>
+      <c r="N1477">
+        <v>316694.52</v>
+      </c>
+      <c r="O1477">
+        <v>511305.48</v>
+      </c>
+      <c r="P1477">
+        <v>28</v>
+      </c>
+      <c r="Q1477">
+        <v>1.29</v>
+      </c>
+      <c r="R1477" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1477" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1478" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1478">
+        <v>20</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1478">
+        <v>480000</v>
+      </c>
+      <c r="K1478">
+        <v>0</v>
+      </c>
+      <c r="L1478">
+        <v>0</v>
+      </c>
+      <c r="M1478">
+        <v>480000</v>
+      </c>
+      <c r="N1478">
+        <v>189291.4</v>
+      </c>
+      <c r="O1478">
+        <v>290708.59999999998</v>
+      </c>
+      <c r="P1478">
+        <v>14</v>
+      </c>
+      <c r="Q1478">
+        <v>1.43</v>
+      </c>
+      <c r="R1478" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1478" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1479" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1479">
+        <v>103</v>
+      </c>
+      <c r="I1479" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1479">
+        <v>3090000</v>
+      </c>
+      <c r="K1479">
+        <v>0</v>
+      </c>
+      <c r="L1479">
+        <v>0</v>
+      </c>
+      <c r="M1479">
+        <v>3095000</v>
+      </c>
+      <c r="N1479">
+        <v>1485043.7</v>
+      </c>
+      <c r="O1479">
+        <v>1609956.3</v>
+      </c>
+      <c r="P1479">
+        <v>89</v>
+      </c>
+      <c r="Q1479">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R1479" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1479" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1480" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1480" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1480">
+        <v>95</v>
+      </c>
+      <c r="I1480" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1480">
+        <v>2850000</v>
+      </c>
+      <c r="K1480">
+        <v>0</v>
+      </c>
+      <c r="L1480">
+        <v>0</v>
+      </c>
+      <c r="M1480">
+        <v>2853000</v>
+      </c>
+      <c r="N1480">
+        <v>1369700.5</v>
+      </c>
+      <c r="O1480">
+        <v>1483299.5</v>
+      </c>
+      <c r="P1480">
+        <v>80</v>
+      </c>
+      <c r="Q1480">
+        <v>1.19</v>
+      </c>
+      <c r="R1480" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1480" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1481" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1481">
+        <v>243</v>
+      </c>
+      <c r="I1481" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1481">
+        <v>7290000</v>
+      </c>
+      <c r="K1481">
+        <v>0</v>
+      </c>
+      <c r="L1481">
+        <v>0</v>
+      </c>
+      <c r="M1481">
+        <v>7293000</v>
+      </c>
+      <c r="N1481">
+        <v>3503549.7</v>
+      </c>
+      <c r="O1481">
+        <v>3789450.3</v>
+      </c>
+      <c r="P1481">
+        <v>195</v>
+      </c>
+      <c r="Q1481">
+        <v>1.25</v>
+      </c>
+      <c r="R1481" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1481" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1482" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1482">
+        <v>403</v>
+      </c>
+      <c r="I1482" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1482">
+        <v>12090000</v>
+      </c>
+      <c r="K1482">
+        <v>0</v>
+      </c>
+      <c r="L1482">
+        <v>0</v>
+      </c>
+      <c r="M1482">
+        <v>12093000</v>
+      </c>
+      <c r="N1482">
+        <v>6079416.2000000002</v>
+      </c>
+      <c r="O1482">
+        <v>6013583.7999999998</v>
+      </c>
+      <c r="P1482">
+        <v>315</v>
+      </c>
+      <c r="Q1482">
+        <v>1.28</v>
+      </c>
+      <c r="R1482" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1482" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1483" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1483">
+        <v>90</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1483">
+        <v>2340000</v>
+      </c>
+      <c r="K1483">
+        <v>0</v>
+      </c>
+      <c r="L1483">
+        <v>0</v>
+      </c>
+      <c r="M1483">
+        <v>2340000</v>
+      </c>
+      <c r="N1483">
+        <v>1178736.3</v>
+      </c>
+      <c r="O1483">
+        <v>1161263.7</v>
+      </c>
+      <c r="P1483">
+        <v>75</v>
+      </c>
+      <c r="Q1483">
+        <v>1.2</v>
+      </c>
+      <c r="R1483" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1483" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1484" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1484">
+        <v>12</v>
+      </c>
+      <c r="I1484" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1484">
+        <v>312000</v>
+      </c>
+      <c r="K1484">
+        <v>0</v>
+      </c>
+      <c r="L1484">
+        <v>0</v>
+      </c>
+      <c r="M1484">
+        <v>312000</v>
+      </c>
+      <c r="N1484">
+        <v>149868.12</v>
+      </c>
+      <c r="O1484">
+        <v>162131.88</v>
+      </c>
+      <c r="P1484">
+        <v>12</v>
+      </c>
+      <c r="Q1484">
+        <v>1</v>
+      </c>
+      <c r="R1484" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1484" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1485" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1485">
+        <v>33</v>
+      </c>
+      <c r="I1485" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1485">
+        <v>858000</v>
+      </c>
+      <c r="K1485">
+        <v>0</v>
+      </c>
+      <c r="L1485">
+        <v>0</v>
+      </c>
+      <c r="M1485">
+        <v>858000</v>
+      </c>
+      <c r="N1485">
+        <v>432203.31</v>
+      </c>
+      <c r="O1485">
+        <v>425796.69</v>
+      </c>
+      <c r="P1485">
+        <v>32</v>
+      </c>
+      <c r="Q1485">
+        <v>1.03</v>
+      </c>
+      <c r="R1485" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1485" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1486" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1486">
+        <v>43</v>
+      </c>
+      <c r="I1486" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1486">
+        <v>1118000</v>
+      </c>
+      <c r="K1486">
+        <v>0</v>
+      </c>
+      <c r="L1486">
+        <v>0</v>
+      </c>
+      <c r="M1486">
+        <v>1118000</v>
+      </c>
+      <c r="N1486">
+        <v>464274.01</v>
+      </c>
+      <c r="O1486">
+        <v>653725.99</v>
+      </c>
+      <c r="P1486">
+        <v>30</v>
+      </c>
+      <c r="Q1486">
+        <v>1.43</v>
+      </c>
+      <c r="R1486" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1486" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1487" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1487" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1487">
+        <v>328</v>
+      </c>
+      <c r="I1487" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1487">
+        <v>5904000</v>
+      </c>
+      <c r="K1487">
+        <v>0</v>
+      </c>
+      <c r="L1487">
+        <v>0</v>
+      </c>
+      <c r="M1487">
+        <v>6267000</v>
+      </c>
+      <c r="N1487">
+        <v>2897509.44</v>
+      </c>
+      <c r="O1487">
+        <v>3369490.56</v>
+      </c>
+      <c r="P1487">
+        <v>273</v>
+      </c>
+      <c r="Q1487">
+        <v>1.2</v>
+      </c>
+      <c r="R1487" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1487" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1488" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1488" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1488">
+        <v>52</v>
+      </c>
+      <c r="I1488" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1488">
+        <v>1040000</v>
+      </c>
+      <c r="K1488">
+        <v>0</v>
+      </c>
+      <c r="L1488">
+        <v>0</v>
+      </c>
+      <c r="M1488">
+        <v>1074000</v>
+      </c>
+      <c r="N1488">
+        <v>441778.06</v>
+      </c>
+      <c r="O1488">
+        <v>632221.93999999994</v>
+      </c>
+      <c r="P1488">
+        <v>44</v>
+      </c>
+      <c r="Q1488">
+        <v>1.18</v>
+      </c>
+      <c r="R1488" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1488" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1489" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1489" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1489">
+        <v>2</v>
+      </c>
+      <c r="I1489" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1489">
+        <v>70000</v>
+      </c>
+      <c r="K1489">
+        <v>0</v>
+      </c>
+      <c r="L1489">
+        <v>0</v>
+      </c>
+      <c r="M1489">
+        <v>70000</v>
+      </c>
+      <c r="N1489">
+        <v>32600</v>
+      </c>
+      <c r="O1489">
+        <v>37400</v>
+      </c>
+      <c r="P1489">
+        <v>2</v>
+      </c>
+      <c r="Q1489">
+        <v>1</v>
+      </c>
+      <c r="R1489" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1489" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1490" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1490" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1490">
+        <v>1</v>
+      </c>
+      <c r="I1490" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1490">
+        <v>35000</v>
+      </c>
+      <c r="K1490">
+        <v>0</v>
+      </c>
+      <c r="L1490">
+        <v>0</v>
+      </c>
+      <c r="M1490">
+        <v>35000</v>
+      </c>
+      <c r="N1490">
+        <v>15691.94</v>
+      </c>
+      <c r="O1490">
+        <v>19308.060000000001</v>
+      </c>
+      <c r="P1490">
+        <v>1</v>
+      </c>
+      <c r="Q1490">
+        <v>1</v>
+      </c>
+      <c r="R1490" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1490" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1491" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1491" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1491">
+        <v>25</v>
+      </c>
+      <c r="I1491" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1491">
+        <v>700000</v>
+      </c>
+      <c r="K1491">
+        <v>0</v>
+      </c>
+      <c r="L1491">
+        <v>0</v>
+      </c>
+      <c r="M1491">
+        <v>703000</v>
+      </c>
+      <c r="N1491">
+        <v>332634.7</v>
+      </c>
+      <c r="O1491">
+        <v>370365.3</v>
+      </c>
+      <c r="P1491">
+        <v>25</v>
+      </c>
+      <c r="Q1491">
+        <v>1</v>
+      </c>
+      <c r="R1491" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1491" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1492" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1492" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1492">
+        <v>30</v>
+      </c>
+      <c r="I1492" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1492">
+        <v>900000</v>
+      </c>
+      <c r="K1492">
+        <v>0</v>
+      </c>
+      <c r="L1492">
+        <v>0</v>
+      </c>
+      <c r="M1492">
+        <v>900000</v>
+      </c>
+      <c r="N1492">
+        <v>383276.68</v>
+      </c>
+      <c r="O1492">
+        <v>516723.32</v>
+      </c>
+      <c r="P1492">
+        <v>28</v>
+      </c>
+      <c r="Q1492">
+        <v>1.07</v>
+      </c>
+      <c r="R1492" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1492" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1493" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1493" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1493">
+        <v>20</v>
+      </c>
+      <c r="I1493" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1493">
+        <v>520000</v>
+      </c>
+      <c r="K1493">
+        <v>0</v>
+      </c>
+      <c r="L1493">
+        <v>0</v>
+      </c>
+      <c r="M1493">
+        <v>527000</v>
+      </c>
+      <c r="N1493">
+        <v>269089.25</v>
+      </c>
+      <c r="O1493">
+        <v>257910.75</v>
+      </c>
+      <c r="P1493">
+        <v>18</v>
+      </c>
+      <c r="Q1493">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1493" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1493" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1494" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1494" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1494">
+        <v>68</v>
+      </c>
+      <c r="I1494" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1494">
+        <v>1428000</v>
+      </c>
+      <c r="K1494">
+        <v>0</v>
+      </c>
+      <c r="L1494">
+        <v>0</v>
+      </c>
+      <c r="M1494">
+        <v>1430000</v>
+      </c>
+      <c r="N1494">
+        <v>761454.35</v>
+      </c>
+      <c r="O1494">
+        <v>668545.65</v>
+      </c>
+      <c r="P1494">
+        <v>62</v>
+      </c>
+      <c r="Q1494">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R1494" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1494" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1495" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1495" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1495">
+        <v>87</v>
+      </c>
+      <c r="I1495" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1495">
+        <v>2349000</v>
+      </c>
+      <c r="K1495">
+        <v>0</v>
+      </c>
+      <c r="L1495">
+        <v>0</v>
+      </c>
+      <c r="M1495">
+        <v>2352000</v>
+      </c>
+      <c r="N1495">
+        <v>816952.69</v>
+      </c>
+      <c r="O1495">
+        <v>1535047.2</v>
+      </c>
+      <c r="P1495">
+        <v>74</v>
+      </c>
+      <c r="Q1495">
+        <v>1.18</v>
+      </c>
+      <c r="R1495" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1495" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1496" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1496" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1496">
+        <v>12</v>
+      </c>
+      <c r="I1496" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1496">
+        <v>300000</v>
+      </c>
+      <c r="K1496">
+        <v>0</v>
+      </c>
+      <c r="L1496">
+        <v>0</v>
+      </c>
+      <c r="M1496">
+        <v>300000</v>
+      </c>
+      <c r="N1496">
+        <v>117465.72</v>
+      </c>
+      <c r="O1496">
+        <v>182534.28</v>
+      </c>
+      <c r="P1496">
+        <v>10</v>
+      </c>
+      <c r="Q1496">
+        <v>1.2</v>
+      </c>
+      <c r="R1496" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1496" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1497" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1497" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1497">
+        <v>38</v>
+      </c>
+      <c r="I1497" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1497">
+        <v>1178000</v>
+      </c>
+      <c r="K1497">
+        <v>0</v>
+      </c>
+      <c r="L1497">
+        <v>0</v>
+      </c>
+      <c r="M1497">
+        <v>1178000</v>
+      </c>
+      <c r="N1497">
+        <v>517987.12</v>
+      </c>
+      <c r="O1497">
+        <v>660012.88</v>
+      </c>
+      <c r="P1497">
+        <v>34</v>
+      </c>
+      <c r="Q1497">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="R1497" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1497" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1498" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1498" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1498">
+        <v>61</v>
+      </c>
+      <c r="I1498" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1498">
+        <v>1830000</v>
+      </c>
+      <c r="K1498">
+        <v>0</v>
+      </c>
+      <c r="L1498">
+        <v>0</v>
+      </c>
+      <c r="M1498">
+        <v>1830000</v>
+      </c>
+      <c r="N1498">
+        <v>790788.14</v>
+      </c>
+      <c r="O1498">
+        <v>1039211.86</v>
+      </c>
+      <c r="P1498">
+        <v>48</v>
+      </c>
+      <c r="Q1498">
+        <v>1.27</v>
+      </c>
+      <c r="R1498" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1498" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1499" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1499" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1499">
+        <v>35</v>
+      </c>
+      <c r="I1499" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1499">
+        <v>1050000</v>
+      </c>
+      <c r="K1499">
+        <v>0</v>
+      </c>
+      <c r="L1499">
+        <v>0</v>
+      </c>
+      <c r="M1499">
+        <v>1053000</v>
+      </c>
+      <c r="N1499">
+        <v>453730.9</v>
+      </c>
+      <c r="O1499">
+        <v>599269.1</v>
+      </c>
+      <c r="P1499">
+        <v>31</v>
+      </c>
+      <c r="Q1499">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1499" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1499" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1500" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1500">
+        <v>52</v>
+      </c>
+      <c r="I1500" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1500">
+        <v>1560000</v>
+      </c>
+      <c r="K1500">
+        <v>0</v>
+      </c>
+      <c r="L1500">
+        <v>0</v>
+      </c>
+      <c r="M1500">
+        <v>1562000</v>
+      </c>
+      <c r="N1500">
+        <v>674114.48</v>
+      </c>
+      <c r="O1500">
+        <v>887885.52</v>
+      </c>
+      <c r="P1500">
+        <v>41</v>
+      </c>
+      <c r="Q1500">
+        <v>1.27</v>
+      </c>
+      <c r="R1500" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1500" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1501" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1501">
+        <v>35</v>
+      </c>
+      <c r="I1501" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1501">
+        <v>1260000</v>
+      </c>
+      <c r="K1501">
+        <v>0</v>
+      </c>
+      <c r="L1501">
+        <v>0</v>
+      </c>
+      <c r="M1501">
+        <v>1260000</v>
+      </c>
+      <c r="N1501">
+        <v>804897.45</v>
+      </c>
+      <c r="O1501">
+        <v>455102.55</v>
+      </c>
+      <c r="P1501">
+        <v>31</v>
+      </c>
+      <c r="Q1501">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1501" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1501" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1502" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1502">
+        <v>3</v>
+      </c>
+      <c r="I1502" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1502">
+        <v>105000</v>
+      </c>
+      <c r="K1502">
+        <v>0</v>
+      </c>
+      <c r="L1502">
+        <v>0</v>
+      </c>
+      <c r="M1502">
+        <v>105000</v>
+      </c>
+      <c r="N1502">
+        <v>68806.53</v>
+      </c>
+      <c r="O1502">
+        <v>36193.47</v>
+      </c>
+      <c r="P1502">
+        <v>2</v>
+      </c>
+      <c r="Q1502">
+        <v>1.5</v>
+      </c>
+      <c r="R1502" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1502" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1503" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1503">
+        <v>49</v>
+      </c>
+      <c r="I1503" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1503">
+        <v>735000</v>
+      </c>
+      <c r="K1503">
+        <v>0</v>
+      </c>
+      <c r="L1503">
+        <v>0</v>
+      </c>
+      <c r="M1503">
+        <v>735000</v>
+      </c>
+      <c r="N1503">
+        <v>446790.82</v>
+      </c>
+      <c r="O1503">
+        <v>288209.18</v>
+      </c>
+      <c r="P1503">
+        <v>33</v>
+      </c>
+      <c r="Q1503">
+        <v>1.48</v>
+      </c>
+      <c r="R1503" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1503" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1504" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1504">
+        <v>5</v>
+      </c>
+      <c r="I1504" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1504">
+        <v>100000</v>
+      </c>
+      <c r="K1504">
+        <v>0</v>
+      </c>
+      <c r="L1504">
+        <v>0</v>
+      </c>
+      <c r="M1504">
+        <v>100000</v>
+      </c>
+      <c r="N1504">
+        <v>53962.5</v>
+      </c>
+      <c r="O1504">
+        <v>46037.5</v>
+      </c>
+      <c r="P1504">
+        <v>4</v>
+      </c>
+      <c r="Q1504">
+        <v>1.25</v>
+      </c>
+      <c r="R1504" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1504" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1505" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1505" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1505">
+        <v>9</v>
+      </c>
+      <c r="I1505" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1505">
+        <v>216000</v>
+      </c>
+      <c r="K1505">
+        <v>0</v>
+      </c>
+      <c r="L1505">
+        <v>0</v>
+      </c>
+      <c r="M1505">
+        <v>216000</v>
+      </c>
+      <c r="N1505">
+        <v>99873.63</v>
+      </c>
+      <c r="O1505">
+        <v>116126.37</v>
+      </c>
+      <c r="P1505">
+        <v>7</v>
+      </c>
+      <c r="Q1505">
+        <v>1.29</v>
+      </c>
+      <c r="R1505" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1505" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1506" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1506">
+        <v>11</v>
+      </c>
+      <c r="I1506" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1506">
+        <v>264000</v>
+      </c>
+      <c r="K1506">
+        <v>0</v>
+      </c>
+      <c r="L1506">
+        <v>0</v>
+      </c>
+      <c r="M1506">
+        <v>264000</v>
+      </c>
+      <c r="N1506">
+        <v>115379.11</v>
+      </c>
+      <c r="O1506">
+        <v>148620.89000000001</v>
+      </c>
+      <c r="P1506">
+        <v>9</v>
+      </c>
+      <c r="Q1506">
+        <v>1.22</v>
+      </c>
+      <c r="R1506" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1506" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1507" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1507" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1507">
+        <v>3</v>
+      </c>
+      <c r="I1507" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1507">
+        <v>72000</v>
+      </c>
+      <c r="K1507">
+        <v>0</v>
+      </c>
+      <c r="L1507">
+        <v>0</v>
+      </c>
+      <c r="M1507">
+        <v>72000</v>
+      </c>
+      <c r="N1507">
+        <v>33291.21</v>
+      </c>
+      <c r="O1507">
+        <v>38708.79</v>
+      </c>
+      <c r="P1507">
+        <v>2</v>
+      </c>
+      <c r="Q1507">
+        <v>1.5</v>
+      </c>
+      <c r="R1507" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1507" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1508" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1508" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1508">
+        <v>104</v>
+      </c>
+      <c r="I1508" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1508">
+        <v>2392000</v>
+      </c>
+      <c r="K1508">
+        <v>0</v>
+      </c>
+      <c r="L1508">
+        <v>0</v>
+      </c>
+      <c r="M1508">
+        <v>2392000</v>
+      </c>
+      <c r="N1508">
+        <v>979186</v>
+      </c>
+      <c r="O1508">
+        <v>1412814</v>
+      </c>
+      <c r="P1508">
+        <v>81</v>
+      </c>
+      <c r="Q1508">
+        <v>1.28</v>
+      </c>
+      <c r="R1508" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1508" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1509" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1509">
+        <v>22</v>
+      </c>
+      <c r="I1509" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1509">
+        <v>616000</v>
+      </c>
+      <c r="K1509">
+        <v>0</v>
+      </c>
+      <c r="L1509">
+        <v>0</v>
+      </c>
+      <c r="M1509">
+        <v>616000</v>
+      </c>
+      <c r="N1509">
+        <v>229285.54</v>
+      </c>
+      <c r="O1509">
+        <v>386714.46</v>
+      </c>
+      <c r="P1509">
+        <v>17</v>
+      </c>
+      <c r="Q1509">
+        <v>1.29</v>
+      </c>
+      <c r="R1509" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1509" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1510" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1510">
+        <v>15</v>
+      </c>
+      <c r="I1510" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1510">
+        <v>420000</v>
+      </c>
+      <c r="K1510">
+        <v>0</v>
+      </c>
+      <c r="L1510">
+        <v>0</v>
+      </c>
+      <c r="M1510">
+        <v>420000</v>
+      </c>
+      <c r="N1510">
+        <v>156297.72</v>
+      </c>
+      <c r="O1510">
+        <v>263702.28000000003</v>
+      </c>
+      <c r="P1510">
+        <v>14</v>
+      </c>
+      <c r="Q1510">
+        <v>1.07</v>
+      </c>
+      <c r="R1510" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1510" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1511" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1511">
+        <v>24</v>
+      </c>
+      <c r="I1511" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1511">
+        <v>672000</v>
+      </c>
+      <c r="K1511">
+        <v>0</v>
+      </c>
+      <c r="L1511">
+        <v>0</v>
+      </c>
+      <c r="M1511">
+        <v>672000</v>
+      </c>
+      <c r="N1511">
+        <v>250063.02</v>
+      </c>
+      <c r="O1511">
+        <v>421936.98</v>
+      </c>
+      <c r="P1511">
+        <v>23</v>
+      </c>
+      <c r="Q1511">
+        <v>1.04</v>
+      </c>
+      <c r="R1511" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1511" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1512" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1512" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1512">
+        <v>70</v>
+      </c>
+      <c r="I1512" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1512">
+        <v>1960000</v>
+      </c>
+      <c r="K1512">
+        <v>0</v>
+      </c>
+      <c r="L1512">
+        <v>0</v>
+      </c>
+      <c r="M1512">
+        <v>1960000</v>
+      </c>
+      <c r="N1512">
+        <v>775736.62</v>
+      </c>
+      <c r="O1512">
+        <v>1184263.3799999999</v>
+      </c>
+      <c r="P1512">
+        <v>60</v>
+      </c>
+      <c r="Q1512">
+        <v>1.17</v>
+      </c>
+      <c r="R1512" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1512" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1513" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1513" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1513" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1513">
+        <v>4</v>
+      </c>
+      <c r="I1513" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1513">
+        <v>0</v>
+      </c>
+      <c r="K1513">
+        <v>0</v>
+      </c>
+      <c r="L1513">
+        <v>0</v>
+      </c>
+      <c r="M1513">
+        <v>14000</v>
+      </c>
+      <c r="N1513">
+        <v>7259.06</v>
+      </c>
+      <c r="O1513">
+        <v>6740.94</v>
+      </c>
+      <c r="P1513">
+        <v>4</v>
+      </c>
+      <c r="Q1513">
+        <v>1</v>
+      </c>
+      <c r="R1513" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1513" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1514" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1514" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1514" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1514">
+        <v>5</v>
+      </c>
+      <c r="I1514" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1514">
+        <v>75000</v>
+      </c>
+      <c r="K1514">
+        <v>0</v>
+      </c>
+      <c r="L1514">
+        <v>0</v>
+      </c>
+      <c r="M1514">
+        <v>75000</v>
+      </c>
+      <c r="N1514">
+        <v>35600</v>
+      </c>
+      <c r="O1514">
+        <v>39400</v>
+      </c>
+      <c r="P1514">
+        <v>5</v>
+      </c>
+      <c r="Q1514">
+        <v>1</v>
+      </c>
+      <c r="R1514" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1514" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1515" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1515" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1515" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1515">
+        <v>11</v>
+      </c>
+      <c r="I1515" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1515">
+        <v>55000</v>
+      </c>
+      <c r="K1515">
+        <v>0</v>
+      </c>
+      <c r="L1515">
+        <v>0</v>
+      </c>
+      <c r="M1515">
+        <v>55000</v>
+      </c>
+      <c r="N1515">
+        <v>3267.77</v>
+      </c>
+      <c r="O1515">
+        <v>51732.23</v>
+      </c>
+      <c r="P1515">
+        <v>11</v>
+      </c>
+      <c r="Q1515">
+        <v>1</v>
+      </c>
+      <c r="R1515" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1515" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1516" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1516" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1516">
+        <v>275</v>
+      </c>
+      <c r="I1516" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1516">
+        <v>1375000</v>
+      </c>
+      <c r="K1516">
+        <v>0</v>
+      </c>
+      <c r="L1516">
+        <v>0</v>
+      </c>
+      <c r="M1516">
+        <v>1410000</v>
+      </c>
+      <c r="N1516">
+        <v>6762.65</v>
+      </c>
+      <c r="O1516">
+        <v>1403237.35</v>
+      </c>
+      <c r="P1516">
+        <v>203</v>
+      </c>
+      <c r="Q1516">
+        <v>1.35</v>
+      </c>
+      <c r="R1516" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1516" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1517" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1517">
+        <v>175</v>
+      </c>
+      <c r="I1517" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1517">
+        <v>700000</v>
+      </c>
+      <c r="K1517">
+        <v>0</v>
+      </c>
+      <c r="L1517">
+        <v>0</v>
+      </c>
+      <c r="M1517">
+        <v>700000</v>
+      </c>
+      <c r="N1517">
+        <v>525000</v>
+      </c>
+      <c r="O1517">
+        <v>175000</v>
+      </c>
+      <c r="P1517">
+        <v>93</v>
+      </c>
+      <c r="Q1517">
+        <v>1.88</v>
+      </c>
+      <c r="R1517" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1517" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1518" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1518">
+        <v>18</v>
+      </c>
+      <c r="I1518" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1518">
+        <v>90000</v>
+      </c>
+      <c r="K1518">
+        <v>0</v>
+      </c>
+      <c r="L1518">
+        <v>0</v>
+      </c>
+      <c r="M1518">
+        <v>90000</v>
+      </c>
+      <c r="N1518">
+        <v>54000</v>
+      </c>
+      <c r="O1518">
+        <v>36000</v>
+      </c>
+      <c r="P1518">
+        <v>17</v>
+      </c>
+      <c r="Q1518">
+        <v>1.06</v>
+      </c>
+      <c r="R1518" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1518" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1519" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1519">
+        <v>150</v>
+      </c>
+      <c r="I1519" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1519">
+        <v>750000</v>
+      </c>
+      <c r="K1519">
+        <v>0</v>
+      </c>
+      <c r="L1519">
+        <v>0</v>
+      </c>
+      <c r="M1519">
+        <v>750000</v>
+      </c>
+      <c r="N1519">
+        <v>600000</v>
+      </c>
+      <c r="O1519">
+        <v>150000</v>
+      </c>
+      <c r="P1519">
+        <v>110</v>
+      </c>
+      <c r="Q1519">
+        <v>1.36</v>
+      </c>
+      <c r="R1519" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1519" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1520" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1520">
+        <v>5</v>
+      </c>
+      <c r="I1520" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1520">
+        <v>25000</v>
+      </c>
+      <c r="K1520">
+        <v>0</v>
+      </c>
+      <c r="L1520">
+        <v>0</v>
+      </c>
+      <c r="M1520">
+        <v>25000</v>
+      </c>
+      <c r="N1520">
+        <v>78333.350000000006</v>
+      </c>
+      <c r="O1520">
+        <v>-53333.35</v>
+      </c>
+      <c r="P1520">
+        <v>5</v>
+      </c>
+      <c r="Q1520">
+        <v>1</v>
+      </c>
+      <c r="R1520" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1520" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1521" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1521">
+        <v>5</v>
+      </c>
+      <c r="I1521" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1521">
+        <v>75000</v>
+      </c>
+      <c r="K1521">
+        <v>0</v>
+      </c>
+      <c r="L1521">
+        <v>0</v>
+      </c>
+      <c r="M1521">
+        <v>75000</v>
+      </c>
+      <c r="N1521">
+        <v>22445.200000000001</v>
+      </c>
+      <c r="O1521">
+        <v>52554.8</v>
+      </c>
+      <c r="P1521">
+        <v>4</v>
+      </c>
+      <c r="Q1521">
+        <v>1.25</v>
+      </c>
+      <c r="R1521" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1521" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1522" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1522">
+        <v>15</v>
+      </c>
+      <c r="I1522" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1522">
+        <v>195000</v>
+      </c>
+      <c r="K1522">
+        <v>0</v>
+      </c>
+      <c r="L1522">
+        <v>0</v>
+      </c>
+      <c r="M1522">
+        <v>195000</v>
+      </c>
+      <c r="N1522">
+        <v>58935.8</v>
+      </c>
+      <c r="O1522">
+        <v>136064.20000000001</v>
+      </c>
+      <c r="P1522">
+        <v>14</v>
+      </c>
+      <c r="Q1522">
+        <v>1.07</v>
+      </c>
+      <c r="R1522" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1522" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1523" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1523">
+        <v>2</v>
+      </c>
+      <c r="I1523" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1523">
+        <v>26000</v>
+      </c>
+      <c r="K1523">
+        <v>0</v>
+      </c>
+      <c r="L1523">
+        <v>0</v>
+      </c>
+      <c r="M1523">
+        <v>26000</v>
+      </c>
+      <c r="N1523">
+        <v>7738.7</v>
+      </c>
+      <c r="O1523">
+        <v>18261.3</v>
+      </c>
+      <c r="P1523">
+        <v>2</v>
+      </c>
+      <c r="Q1523">
+        <v>1</v>
+      </c>
+      <c r="R1523" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1523" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1524" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1524">
+        <v>16</v>
+      </c>
+      <c r="I1524" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1524">
+        <v>160000</v>
+      </c>
+      <c r="K1524">
+        <v>0</v>
+      </c>
+      <c r="L1524">
+        <v>0</v>
+      </c>
+      <c r="M1524">
+        <v>160000</v>
+      </c>
+      <c r="N1524">
+        <v>53864.7</v>
+      </c>
+      <c r="O1524">
+        <v>106135.3</v>
+      </c>
+      <c r="P1524">
+        <v>16</v>
+      </c>
+      <c r="Q1524">
+        <v>1</v>
+      </c>
+      <c r="R1524" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1524" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1525" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1525">
+        <v>39</v>
+      </c>
+      <c r="I1525" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1525">
+        <v>390000</v>
+      </c>
+      <c r="K1525">
+        <v>0</v>
+      </c>
+      <c r="L1525">
+        <v>0</v>
+      </c>
+      <c r="M1525">
+        <v>390000</v>
+      </c>
+      <c r="N1525">
+        <v>37087.4</v>
+      </c>
+      <c r="O1525">
+        <v>352912.6</v>
+      </c>
+      <c r="P1525">
+        <v>36</v>
+      </c>
+      <c r="Q1525">
+        <v>1.08</v>
+      </c>
+      <c r="R1525" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1525" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1526" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1526">
+        <v>141</v>
+      </c>
+      <c r="I1526" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1526">
+        <v>705000</v>
+      </c>
+      <c r="K1526">
+        <v>0</v>
+      </c>
+      <c r="L1526">
+        <v>0</v>
+      </c>
+      <c r="M1526">
+        <v>705000</v>
+      </c>
+      <c r="N1526">
+        <v>114096.45</v>
+      </c>
+      <c r="O1526">
+        <v>590903.55000000005</v>
+      </c>
+      <c r="P1526">
+        <v>108</v>
+      </c>
+      <c r="Q1526">
+        <v>1.31</v>
+      </c>
+      <c r="R1526" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1526" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1527" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1527">
+        <v>121</v>
+      </c>
+      <c r="I1527" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1527">
+        <v>605000</v>
+      </c>
+      <c r="K1527">
+        <v>0</v>
+      </c>
+      <c r="L1527">
+        <v>0</v>
+      </c>
+      <c r="M1527">
+        <v>605000</v>
+      </c>
+      <c r="N1527">
+        <v>81046.5</v>
+      </c>
+      <c r="O1527">
+        <v>523953.5</v>
+      </c>
+      <c r="P1527">
+        <v>98</v>
+      </c>
+      <c r="Q1527">
+        <v>1.23</v>
+      </c>
+      <c r="R1527" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1527" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1528" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1528">
+        <v>54</v>
+      </c>
+      <c r="I1528" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1528">
+        <v>432000</v>
+      </c>
+      <c r="K1528">
+        <v>0</v>
+      </c>
+      <c r="L1528">
+        <v>0</v>
+      </c>
+      <c r="M1528">
+        <v>434000</v>
+      </c>
+      <c r="N1528">
+        <v>43685.7</v>
+      </c>
+      <c r="O1528">
+        <v>390314.3</v>
+      </c>
+      <c r="P1528">
+        <v>42</v>
+      </c>
+      <c r="Q1528">
+        <v>1.29</v>
+      </c>
+      <c r="R1528" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1528" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1529" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1529">
+        <v>7</v>
+      </c>
+      <c r="I1529" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1529">
+        <v>140000</v>
+      </c>
+      <c r="K1529">
+        <v>0</v>
+      </c>
+      <c r="L1529">
+        <v>0</v>
+      </c>
+      <c r="M1529">
+        <v>140000</v>
+      </c>
+      <c r="N1529">
+        <v>119000</v>
+      </c>
+      <c r="O1529">
+        <v>21000</v>
+      </c>
+      <c r="P1529">
+        <v>7</v>
+      </c>
+      <c r="Q1529">
+        <v>1</v>
+      </c>
+      <c r="R1529" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1529" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1530" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>425</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1530">
+        <v>1</v>
+      </c>
+      <c r="I1530" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1530">
+        <v>15000</v>
+      </c>
+      <c r="K1530">
+        <v>0</v>
+      </c>
+      <c r="L1530">
+        <v>0</v>
+      </c>
+      <c r="M1530">
+        <v>15000</v>
+      </c>
+      <c r="N1530">
+        <v>12000</v>
+      </c>
+      <c r="O1530">
+        <v>3000</v>
+      </c>
+      <c r="P1530">
+        <v>1</v>
+      </c>
+      <c r="Q1530">
+        <v>1</v>
+      </c>
+      <c r="R1530" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1530" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1531" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1531">
+        <v>3</v>
+      </c>
+      <c r="I1531" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1531">
+        <v>60000</v>
+      </c>
+      <c r="K1531">
+        <v>0</v>
+      </c>
+      <c r="L1531">
+        <v>0</v>
+      </c>
+      <c r="M1531">
+        <v>60000</v>
+      </c>
+      <c r="N1531">
+        <v>51000</v>
+      </c>
+      <c r="O1531">
+        <v>9000</v>
+      </c>
+      <c r="P1531">
+        <v>3</v>
+      </c>
+      <c r="Q1531">
+        <v>1</v>
+      </c>
+      <c r="R1531" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1531" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1532" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1532" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1532">
+        <v>42</v>
+      </c>
+      <c r="I1532" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1532">
+        <v>630000</v>
+      </c>
+      <c r="K1532">
+        <v>0</v>
+      </c>
+      <c r="L1532">
+        <v>0</v>
+      </c>
+      <c r="M1532">
+        <v>630000</v>
+      </c>
+      <c r="N1532">
+        <v>504000</v>
+      </c>
+      <c r="O1532">
+        <v>126000</v>
+      </c>
+      <c r="P1532">
+        <v>34</v>
+      </c>
+      <c r="Q1532">
+        <v>1.24</v>
+      </c>
+      <c r="R1532" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1532" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1533" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1533">
+        <v>3</v>
+      </c>
+      <c r="I1533" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1533">
+        <v>45000</v>
+      </c>
+      <c r="K1533">
+        <v>0</v>
+      </c>
+      <c r="L1533">
+        <v>0</v>
+      </c>
+      <c r="M1533">
+        <v>45000</v>
+      </c>
+      <c r="N1533">
+        <v>36000</v>
+      </c>
+      <c r="O1533">
+        <v>9000</v>
+      </c>
+      <c r="P1533">
+        <v>3</v>
+      </c>
+      <c r="Q1533">
+        <v>1</v>
+      </c>
+      <c r="R1533" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1533" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1534" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1534" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1534">
+        <v>9</v>
+      </c>
+      <c r="I1534" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1534">
+        <v>135000</v>
+      </c>
+      <c r="K1534">
+        <v>0</v>
+      </c>
+      <c r="L1534">
+        <v>0</v>
+      </c>
+      <c r="M1534">
+        <v>135000</v>
+      </c>
+      <c r="N1534">
+        <v>108000</v>
+      </c>
+      <c r="O1534">
+        <v>27000</v>
+      </c>
+      <c r="P1534">
+        <v>6</v>
+      </c>
+      <c r="Q1534">
+        <v>1.5</v>
+      </c>
+      <c r="R1534" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1534" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1535" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1535">
+        <v>3</v>
+      </c>
+      <c r="I1535" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1535">
+        <v>60000</v>
+      </c>
+      <c r="K1535">
+        <v>0</v>
+      </c>
+      <c r="L1535">
+        <v>0</v>
+      </c>
+      <c r="M1535">
+        <v>60000</v>
+      </c>
+      <c r="N1535">
+        <v>51000</v>
+      </c>
+      <c r="O1535">
+        <v>9000</v>
+      </c>
+      <c r="P1535">
+        <v>3</v>
+      </c>
+      <c r="Q1535">
+        <v>1</v>
+      </c>
+      <c r="R1535" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1535" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1536" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1536">
+        <v>71</v>
+      </c>
+      <c r="I1536" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1536">
+        <v>710000</v>
+      </c>
+      <c r="K1536">
+        <v>0</v>
+      </c>
+      <c r="L1536">
+        <v>0</v>
+      </c>
+      <c r="M1536">
+        <v>710000</v>
+      </c>
+      <c r="N1536">
+        <v>330883.57</v>
+      </c>
+      <c r="O1536">
+        <v>379116.43</v>
+      </c>
+      <c r="P1536">
+        <v>62</v>
+      </c>
+      <c r="Q1536">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="R1536" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1536" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1537" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1537">
+        <v>81</v>
+      </c>
+      <c r="I1537" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1537">
+        <v>810000</v>
+      </c>
+      <c r="K1537">
+        <v>0</v>
+      </c>
+      <c r="L1537">
+        <v>0</v>
+      </c>
+      <c r="M1537">
+        <v>810000</v>
+      </c>
+      <c r="N1537">
+        <v>457010.43</v>
+      </c>
+      <c r="O1537">
+        <v>352989.57</v>
+      </c>
+      <c r="P1537">
+        <v>60</v>
+      </c>
+      <c r="Q1537">
+        <v>1.35</v>
+      </c>
+      <c r="R1537" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1537" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1538" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1538">
+        <v>4</v>
+      </c>
+      <c r="I1538" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1538">
+        <v>40000</v>
+      </c>
+      <c r="K1538">
+        <v>0</v>
+      </c>
+      <c r="L1538">
+        <v>0</v>
+      </c>
+      <c r="M1538">
+        <v>40000</v>
+      </c>
+      <c r="N1538">
+        <v>10645.2</v>
+      </c>
+      <c r="O1538">
+        <v>29354.799999999999</v>
+      </c>
+      <c r="P1538">
+        <v>4</v>
+      </c>
+      <c r="Q1538">
+        <v>1</v>
+      </c>
+      <c r="R1538" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1538" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1539" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1539" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1539">
+        <v>5</v>
+      </c>
+      <c r="I1539" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1539">
+        <v>65000</v>
+      </c>
+      <c r="K1539">
+        <v>0</v>
+      </c>
+      <c r="L1539">
+        <v>0</v>
+      </c>
+      <c r="M1539">
+        <v>65000</v>
+      </c>
+      <c r="N1539">
+        <v>17789.3</v>
+      </c>
+      <c r="O1539">
+        <v>47210.7</v>
+      </c>
+      <c r="P1539">
+        <v>5</v>
+      </c>
+      <c r="Q1539">
+        <v>1</v>
+      </c>
+      <c r="R1539" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1539" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1540" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1540" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1540">
+        <v>7</v>
+      </c>
+      <c r="I1540" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1540">
+        <v>105000</v>
+      </c>
+      <c r="K1540">
+        <v>0</v>
+      </c>
+      <c r="L1540">
+        <v>0</v>
+      </c>
+      <c r="M1540">
+        <v>105000</v>
+      </c>
+      <c r="N1540">
+        <v>29709.65</v>
+      </c>
+      <c r="O1540">
+        <v>75290.350000000006</v>
+      </c>
+      <c r="P1540">
+        <v>7</v>
+      </c>
+      <c r="Q1540">
+        <v>1</v>
+      </c>
+      <c r="R1540" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1540" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1541" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1541" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1541">
+        <v>10</v>
+      </c>
+      <c r="I1541" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1541">
+        <v>100000</v>
+      </c>
+      <c r="K1541">
+        <v>0</v>
+      </c>
+      <c r="L1541">
+        <v>0</v>
+      </c>
+      <c r="M1541">
+        <v>100000</v>
+      </c>
+      <c r="N1541">
+        <v>22976.400000000001</v>
+      </c>
+      <c r="O1541">
+        <v>77023.600000000006</v>
+      </c>
+      <c r="P1541">
+        <v>8</v>
+      </c>
+      <c r="Q1541">
+        <v>1.25</v>
+      </c>
+      <c r="R1541" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1541" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1542" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1542" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1542">
+        <v>4</v>
+      </c>
+      <c r="I1542" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1542">
+        <v>52000</v>
+      </c>
+      <c r="K1542">
+        <v>0</v>
+      </c>
+      <c r="L1542">
+        <v>0</v>
+      </c>
+      <c r="M1542">
+        <v>52000</v>
+      </c>
+      <c r="N1542">
+        <v>10924</v>
+      </c>
+      <c r="O1542">
+        <v>41076</v>
+      </c>
+      <c r="P1542">
+        <v>4</v>
+      </c>
+      <c r="Q1542">
+        <v>1</v>
+      </c>
+      <c r="R1542" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1542" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1543" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1543" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1543">
+        <v>10</v>
+      </c>
+      <c r="I1543" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1543">
+        <v>100000</v>
+      </c>
+      <c r="K1543">
+        <v>0</v>
+      </c>
+      <c r="L1543">
+        <v>0</v>
+      </c>
+      <c r="M1543">
+        <v>102000</v>
+      </c>
+      <c r="N1543">
+        <v>31275.8</v>
+      </c>
+      <c r="O1543">
+        <v>70724.2</v>
+      </c>
+      <c r="P1543">
+        <v>7</v>
+      </c>
+      <c r="Q1543">
+        <v>1.43</v>
+      </c>
+      <c r="R1543" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1543" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1544" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1544" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1544">
+        <v>45</v>
+      </c>
+      <c r="I1544" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1544">
+        <v>225000</v>
+      </c>
+      <c r="K1544">
+        <v>0</v>
+      </c>
+      <c r="L1544">
+        <v>0</v>
+      </c>
+      <c r="M1544">
+        <v>225000</v>
+      </c>
+      <c r="N1544">
+        <v>0</v>
+      </c>
+      <c r="O1544">
+        <v>225000</v>
+      </c>
+      <c r="P1544">
+        <v>44</v>
+      </c>
+      <c r="Q1544">
+        <v>1.02</v>
+      </c>
+      <c r="R1544" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1544" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1545" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>302</v>
+      </c>
+      <c r="H1545">
+        <v>63</v>
+      </c>
+      <c r="I1545" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1545">
+        <v>189000</v>
+      </c>
+      <c r="K1545">
+        <v>0</v>
+      </c>
+      <c r="L1545">
+        <v>0</v>
+      </c>
+      <c r="M1545">
+        <v>189000</v>
+      </c>
+      <c r="N1545">
+        <v>0</v>
+      </c>
+      <c r="O1545">
+        <v>189000</v>
+      </c>
+      <c r="P1545">
+        <v>50</v>
+      </c>
+      <c r="Q1545">
+        <v>1.26</v>
+      </c>
+      <c r="R1545" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1545" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1546" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1546" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1546">
+        <v>642</v>
+      </c>
+      <c r="I1546" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1546">
+        <v>3210000</v>
+      </c>
+      <c r="K1546">
+        <v>0</v>
+      </c>
+      <c r="L1546">
+        <v>0</v>
+      </c>
+      <c r="M1546">
+        <v>3264000</v>
+      </c>
+      <c r="N1546">
+        <v>1065299.8600000001</v>
+      </c>
+      <c r="O1546">
+        <v>2198700.15</v>
+      </c>
+      <c r="P1546">
+        <v>453</v>
+      </c>
+      <c r="Q1546">
+        <v>1.42</v>
+      </c>
+      <c r="R1546" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1546" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1547" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1547" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1547">
+        <v>14</v>
+      </c>
+      <c r="I1547" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1547">
+        <v>140000</v>
+      </c>
+      <c r="K1547">
+        <v>0</v>
+      </c>
+      <c r="L1547">
+        <v>0</v>
+      </c>
+      <c r="M1547">
+        <v>140000</v>
+      </c>
+      <c r="N1547">
+        <v>4162.34</v>
+      </c>
+      <c r="O1547">
+        <v>135837.66</v>
+      </c>
+      <c r="P1547">
+        <v>13</v>
+      </c>
+      <c r="Q1547">
+        <v>1.08</v>
+      </c>
+      <c r="R1547" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1547" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1548" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1548" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1548" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1548">
+        <v>18</v>
+      </c>
+      <c r="I1548" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1548">
+        <v>216000</v>
+      </c>
+      <c r="K1548">
+        <v>0</v>
+      </c>
+      <c r="L1548">
+        <v>0</v>
+      </c>
+      <c r="M1548">
+        <v>230000</v>
+      </c>
+      <c r="N1548">
+        <v>37903.14</v>
+      </c>
+      <c r="O1548">
+        <v>192096.86</v>
+      </c>
+      <c r="P1548">
+        <v>18</v>
+      </c>
+      <c r="Q1548">
+        <v>1</v>
+      </c>
+      <c r="R1548" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1548" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1549" t="s">
+        <v>327</v>
+      </c>
+      <c r="D1549" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1549" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1549">
+        <v>9</v>
+      </c>
+      <c r="I1549" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1549">
+        <v>18000</v>
+      </c>
+      <c r="K1549">
+        <v>0</v>
+      </c>
+      <c r="L1549">
+        <v>0</v>
+      </c>
+      <c r="M1549">
+        <v>18000</v>
+      </c>
+      <c r="N1549">
+        <v>0</v>
+      </c>
+      <c r="O1549">
+        <v>18000</v>
+      </c>
+      <c r="P1549">
+        <v>6</v>
+      </c>
+      <c r="Q1549">
+        <v>1.5</v>
+      </c>
+      <c r="R1549" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1549" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1550" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1550" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1550">
+        <v>319</v>
+      </c>
+      <c r="I1550" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1550">
+        <v>1595000</v>
+      </c>
+      <c r="K1550">
+        <v>0</v>
+      </c>
+      <c r="L1550">
+        <v>0</v>
+      </c>
+      <c r="M1550">
+        <v>1595000</v>
+      </c>
+      <c r="N1550">
+        <v>1036750</v>
+      </c>
+      <c r="O1550">
+        <v>558250</v>
+      </c>
+      <c r="P1550">
+        <v>225</v>
+      </c>
+      <c r="Q1550">
+        <v>1.42</v>
+      </c>
+      <c r="R1550" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1550" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1551" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1551" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1551">
+        <v>82</v>
+      </c>
+      <c r="I1551" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1551">
+        <v>410000</v>
+      </c>
+      <c r="K1551">
+        <v>0</v>
+      </c>
+      <c r="L1551">
+        <v>0</v>
+      </c>
+      <c r="M1551">
+        <v>410000</v>
+      </c>
+      <c r="N1551">
+        <v>266500</v>
+      </c>
+      <c r="O1551">
+        <v>143500</v>
+      </c>
+      <c r="P1551">
+        <v>72</v>
+      </c>
+      <c r="Q1551">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1551" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1551" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1552" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1552" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1552">
+        <v>199</v>
+      </c>
+      <c r="I1552" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1552">
+        <v>796000</v>
+      </c>
+      <c r="K1552">
+        <v>0</v>
+      </c>
+      <c r="L1552">
+        <v>0</v>
+      </c>
+      <c r="M1552">
+        <v>796000</v>
+      </c>
+      <c r="N1552">
+        <v>517400</v>
+      </c>
+      <c r="O1552">
+        <v>278600</v>
+      </c>
+      <c r="P1552">
+        <v>120</v>
+      </c>
+      <c r="Q1552">
+        <v>1.66</v>
+      </c>
+      <c r="R1552" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1552" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1553" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1553">
+        <v>149</v>
+      </c>
+      <c r="I1553" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1553">
+        <v>745000</v>
+      </c>
+      <c r="K1553">
+        <v>0</v>
+      </c>
+      <c r="L1553">
+        <v>0</v>
+      </c>
+      <c r="M1553">
+        <v>745000</v>
+      </c>
+      <c r="N1553">
+        <v>484250</v>
+      </c>
+      <c r="O1553">
+        <v>260750</v>
+      </c>
+      <c r="P1553">
+        <v>103</v>
+      </c>
+      <c r="Q1553">
+        <v>1.45</v>
+      </c>
+      <c r="R1553" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1553" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1554" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1554" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1554" t="s">
+        <v>335</v>
+      </c>
+      <c r="H1554">
+        <v>155</v>
+      </c>
+      <c r="I1554" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1554">
+        <v>1550000</v>
+      </c>
+      <c r="K1554">
+        <v>0</v>
+      </c>
+      <c r="L1554">
+        <v>0</v>
+      </c>
+      <c r="M1554">
+        <v>1550000</v>
+      </c>
+      <c r="N1554">
+        <v>1007500</v>
+      </c>
+      <c r="O1554">
+        <v>542500</v>
+      </c>
+      <c r="P1554">
+        <v>118</v>
+      </c>
+      <c r="Q1554">
+        <v>1.31</v>
+      </c>
+      <c r="R1554" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1554" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1555" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1555">
+        <v>178</v>
+      </c>
+      <c r="I1555" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1555">
+        <v>890000</v>
+      </c>
+      <c r="K1555">
+        <v>0</v>
+      </c>
+      <c r="L1555">
+        <v>0</v>
+      </c>
+      <c r="M1555">
+        <v>890000</v>
+      </c>
+      <c r="N1555">
+        <v>578500</v>
+      </c>
+      <c r="O1555">
+        <v>311500</v>
+      </c>
+      <c r="P1555">
+        <v>115</v>
+      </c>
+      <c r="Q1555">
+        <v>1.55</v>
+      </c>
+      <c r="R1555" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1555" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1556" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>339</v>
+      </c>
+      <c r="H1556">
+        <v>90</v>
+      </c>
+      <c r="I1556" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1556">
+        <v>360000</v>
+      </c>
+      <c r="K1556">
+        <v>0</v>
+      </c>
+      <c r="L1556">
+        <v>0</v>
+      </c>
+      <c r="M1556">
+        <v>360000</v>
+      </c>
+      <c r="N1556">
+        <v>234000</v>
+      </c>
+      <c r="O1556">
+        <v>126000</v>
+      </c>
+      <c r="P1556">
+        <v>68</v>
+      </c>
+      <c r="Q1556">
+        <v>1.32</v>
+      </c>
+      <c r="R1556" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1556" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1557" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1557">
+        <v>11</v>
+      </c>
+      <c r="I1557" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1557">
+        <v>550000</v>
+      </c>
+      <c r="K1557">
+        <v>0</v>
+      </c>
+      <c r="L1557">
+        <v>0</v>
+      </c>
+      <c r="M1557">
+        <v>550000</v>
+      </c>
+      <c r="N1557">
+        <v>440000</v>
+      </c>
+      <c r="O1557">
+        <v>110000</v>
+      </c>
+      <c r="P1557">
+        <v>11</v>
+      </c>
+      <c r="Q1557">
+        <v>1</v>
+      </c>
+      <c r="R1557" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1557" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1558" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1558">
+        <v>27</v>
+      </c>
+      <c r="I1558" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1558">
+        <v>351000</v>
+      </c>
+      <c r="K1558">
+        <v>0</v>
+      </c>
+      <c r="L1558">
+        <v>0</v>
+      </c>
+      <c r="M1558">
+        <v>351000</v>
+      </c>
+      <c r="N1558">
+        <v>270000</v>
+      </c>
+      <c r="O1558">
+        <v>81000</v>
+      </c>
+      <c r="P1558">
+        <v>20</v>
+      </c>
+      <c r="Q1558">
+        <v>1.35</v>
+      </c>
+      <c r="R1558" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1558" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1559" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1559">
+        <v>11</v>
+      </c>
+      <c r="I1559" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1559">
+        <v>220000</v>
+      </c>
+      <c r="K1559">
+        <v>0</v>
+      </c>
+      <c r="L1559">
+        <v>0</v>
+      </c>
+      <c r="M1559">
+        <v>220000</v>
+      </c>
+      <c r="N1559">
+        <v>165000</v>
+      </c>
+      <c r="O1559">
+        <v>55000</v>
+      </c>
+      <c r="P1559">
+        <v>11</v>
+      </c>
+      <c r="Q1559">
+        <v>1</v>
+      </c>
+      <c r="R1559" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1559" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1560" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1560" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1560">
+        <v>19</v>
+      </c>
+      <c r="I1560" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1560">
+        <v>95000</v>
+      </c>
+      <c r="K1560">
+        <v>0</v>
+      </c>
+      <c r="L1560">
+        <v>0</v>
+      </c>
+      <c r="M1560">
+        <v>95000</v>
+      </c>
+      <c r="N1560">
+        <v>53770</v>
+      </c>
+      <c r="O1560">
+        <v>41230</v>
+      </c>
+      <c r="P1560">
+        <v>13</v>
+      </c>
+      <c r="Q1560">
+        <v>1.46</v>
+      </c>
+      <c r="R1560" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1560" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1561" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1561" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1561">
+        <v>6</v>
+      </c>
+      <c r="I1561" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1561">
+        <v>78000</v>
+      </c>
+      <c r="K1561">
+        <v>0</v>
+      </c>
+      <c r="L1561">
+        <v>0</v>
+      </c>
+      <c r="M1561">
+        <v>78000</v>
+      </c>
+      <c r="N1561">
+        <v>60000</v>
+      </c>
+      <c r="O1561">
+        <v>18000</v>
+      </c>
+      <c r="P1561">
+        <v>5</v>
+      </c>
+      <c r="Q1561">
+        <v>1.2</v>
+      </c>
+      <c r="R1561" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1561" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1562" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1562" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1562">
+        <v>9</v>
+      </c>
+      <c r="I1562" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1562">
+        <v>153000</v>
+      </c>
+      <c r="K1562">
+        <v>0</v>
+      </c>
+      <c r="L1562">
+        <v>0</v>
+      </c>
+      <c r="M1562">
+        <v>153000</v>
+      </c>
+      <c r="N1562">
+        <v>126000</v>
+      </c>
+      <c r="O1562">
+        <v>27000</v>
+      </c>
+      <c r="P1562">
+        <v>9</v>
+      </c>
+      <c r="Q1562">
+        <v>1</v>
+      </c>
+      <c r="R1562" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1562" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1563" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1563" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1563">
+        <v>6</v>
+      </c>
+      <c r="I1563" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1563">
+        <v>96000</v>
+      </c>
+      <c r="K1563">
+        <v>0</v>
+      </c>
+      <c r="L1563">
+        <v>0</v>
+      </c>
+      <c r="M1563">
+        <v>96000</v>
+      </c>
+      <c r="N1563">
+        <v>78000</v>
+      </c>
+      <c r="O1563">
+        <v>18000</v>
+      </c>
+      <c r="P1563">
+        <v>6</v>
+      </c>
+      <c r="Q1563">
+        <v>1</v>
+      </c>
+      <c r="R1563" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1563" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1564" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1564" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1564">
+        <v>19</v>
+      </c>
+      <c r="I1564" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1564">
+        <v>190000</v>
+      </c>
+      <c r="K1564">
+        <v>0</v>
+      </c>
+      <c r="L1564">
+        <v>0</v>
+      </c>
+      <c r="M1564">
+        <v>190000</v>
+      </c>
+      <c r="N1564">
+        <v>150992.43</v>
+      </c>
+      <c r="O1564">
+        <v>39007.57</v>
+      </c>
+      <c r="P1564">
+        <v>16</v>
+      </c>
+      <c r="Q1564">
+        <v>1.19</v>
+      </c>
+      <c r="R1564" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1564" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1565" t="s">
+        <v>435</v>
+      </c>
+      <c r="D1565" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1565">
+        <v>1</v>
+      </c>
+      <c r="I1565" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1565">
+        <v>13000</v>
+      </c>
+      <c r="K1565">
+        <v>0</v>
+      </c>
+      <c r="L1565">
+        <v>0</v>
+      </c>
+      <c r="M1565">
+        <v>13000</v>
+      </c>
+      <c r="N1565">
+        <v>10000</v>
+      </c>
+      <c r="O1565">
+        <v>3000</v>
+      </c>
+      <c r="P1565">
+        <v>1</v>
+      </c>
+      <c r="Q1565">
+        <v>1</v>
+      </c>
+      <c r="R1565" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1565" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1566" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1566" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1566">
+        <v>79</v>
+      </c>
+      <c r="I1566" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1566">
+        <v>948000</v>
+      </c>
+      <c r="K1566">
+        <v>0</v>
+      </c>
+      <c r="L1566">
+        <v>0</v>
+      </c>
+      <c r="M1566">
+        <v>948000</v>
+      </c>
+      <c r="N1566">
+        <v>711000</v>
+      </c>
+      <c r="O1566">
+        <v>237000</v>
+      </c>
+      <c r="P1566">
+        <v>43</v>
+      </c>
+      <c r="Q1566">
+        <v>1.84</v>
+      </c>
+      <c r="R1566" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1566" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1567" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1567" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1567">
+        <v>40</v>
+      </c>
+      <c r="I1567" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1567">
+        <v>520000</v>
+      </c>
+      <c r="K1567">
+        <v>0</v>
+      </c>
+      <c r="L1567">
+        <v>0</v>
+      </c>
+      <c r="M1567">
+        <v>520000</v>
+      </c>
+      <c r="N1567">
+        <v>400000</v>
+      </c>
+      <c r="O1567">
+        <v>120000</v>
+      </c>
+      <c r="P1567">
+        <v>23</v>
+      </c>
+      <c r="Q1567">
+        <v>1.74</v>
+      </c>
+      <c r="R1567" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1567" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1568" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1568" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1568">
+        <v>124</v>
+      </c>
+      <c r="I1568" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1568">
+        <v>868000</v>
+      </c>
+      <c r="K1568">
+        <v>0</v>
+      </c>
+      <c r="L1568">
+        <v>0</v>
+      </c>
+      <c r="M1568">
+        <v>868000</v>
+      </c>
+      <c r="N1568">
+        <v>620000</v>
+      </c>
+      <c r="O1568">
+        <v>248000</v>
+      </c>
+      <c r="P1568">
+        <v>41</v>
+      </c>
+      <c r="Q1568">
+        <v>3.02</v>
+      </c>
+      <c r="R1568" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1568" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1569" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1569" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1569">
+        <v>18</v>
+      </c>
+      <c r="I1569" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1569">
+        <v>234000</v>
+      </c>
+      <c r="K1569">
+        <v>0</v>
+      </c>
+      <c r="L1569">
+        <v>0</v>
+      </c>
+      <c r="M1569">
+        <v>234000</v>
+      </c>
+      <c r="N1569">
+        <v>180000</v>
+      </c>
+      <c r="O1569">
+        <v>54000</v>
+      </c>
+      <c r="P1569">
+        <v>16</v>
+      </c>
+      <c r="Q1569">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1569" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1569" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1570" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1570" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1570">
+        <v>19</v>
+      </c>
+      <c r="I1570" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1570">
+        <v>247000</v>
+      </c>
+      <c r="K1570">
+        <v>0</v>
+      </c>
+      <c r="L1570">
+        <v>0</v>
+      </c>
+      <c r="M1570">
+        <v>247000</v>
+      </c>
+      <c r="N1570">
+        <v>190000</v>
+      </c>
+      <c r="O1570">
+        <v>57000</v>
+      </c>
+      <c r="P1570">
+        <v>15</v>
+      </c>
+      <c r="Q1570">
+        <v>1.27</v>
+      </c>
+      <c r="R1570" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1570" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1571" t="s">
+        <v>354</v>
+      </c>
+      <c r="D1571" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1571">
+        <v>30</v>
+      </c>
+      <c r="I1571" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1571">
+        <v>300000</v>
+      </c>
+      <c r="K1571">
+        <v>0</v>
+      </c>
+      <c r="L1571">
+        <v>0</v>
+      </c>
+      <c r="M1571">
+        <v>300000</v>
+      </c>
+      <c r="N1571">
+        <v>150000</v>
+      </c>
+      <c r="O1571">
+        <v>150000</v>
+      </c>
+      <c r="P1571">
+        <v>24</v>
+      </c>
+      <c r="Q1571">
+        <v>1.25</v>
+      </c>
+      <c r="R1571" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1571" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1572" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1572" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1572">
+        <v>34</v>
+      </c>
+      <c r="I1572" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1572">
+        <v>510000</v>
+      </c>
+      <c r="K1572">
+        <v>0</v>
+      </c>
+      <c r="L1572">
+        <v>0</v>
+      </c>
+      <c r="M1572">
+        <v>510000</v>
+      </c>
+      <c r="N1572">
+        <v>408000</v>
+      </c>
+      <c r="O1572">
+        <v>102000</v>
+      </c>
+      <c r="P1572">
+        <v>27</v>
+      </c>
+      <c r="Q1572">
+        <v>1.26</v>
+      </c>
+      <c r="R1572" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1572" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1573" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1573" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1573">
+        <v>73</v>
+      </c>
+      <c r="I1573" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1573">
+        <v>730000</v>
+      </c>
+      <c r="K1573">
+        <v>0</v>
+      </c>
+      <c r="L1573">
+        <v>0</v>
+      </c>
+      <c r="M1573">
+        <v>730000</v>
+      </c>
+      <c r="N1573">
+        <v>547500</v>
+      </c>
+      <c r="O1573">
+        <v>182500</v>
+      </c>
+      <c r="P1573">
+        <v>32</v>
+      </c>
+      <c r="Q1573">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="R1573" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1573" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1574" t="s">
+        <v>358</v>
+      </c>
+      <c r="D1574" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1574">
+        <v>50</v>
+      </c>
+      <c r="I1574" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1574">
+        <v>750000</v>
+      </c>
+      <c r="K1574">
+        <v>0</v>
+      </c>
+      <c r="L1574">
+        <v>0</v>
+      </c>
+      <c r="M1574">
+        <v>750000</v>
+      </c>
+      <c r="N1574">
+        <v>600000</v>
+      </c>
+      <c r="O1574">
+        <v>150000</v>
+      </c>
+      <c r="P1574">
+        <v>41</v>
+      </c>
+      <c r="Q1574">
+        <v>1.22</v>
+      </c>
+      <c r="R1574" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1574" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1575" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1575" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1575">
+        <v>69</v>
+      </c>
+      <c r="I1575" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1575">
+        <v>1380000</v>
+      </c>
+      <c r="K1575">
+        <v>0</v>
+      </c>
+      <c r="L1575">
+        <v>0</v>
+      </c>
+      <c r="M1575">
+        <v>1380000</v>
+      </c>
+      <c r="N1575">
+        <v>1242000</v>
+      </c>
+      <c r="O1575">
+        <v>138000</v>
+      </c>
+      <c r="P1575">
+        <v>58</v>
+      </c>
+      <c r="Q1575">
+        <v>1.19</v>
+      </c>
+      <c r="R1575" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1575" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1576" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1576" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1576">
+        <v>9</v>
+      </c>
+      <c r="I1576" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1576">
+        <v>135000</v>
+      </c>
+      <c r="K1576">
+        <v>0</v>
+      </c>
+      <c r="L1576">
+        <v>0</v>
+      </c>
+      <c r="M1576">
+        <v>135000</v>
+      </c>
+      <c r="N1576">
+        <v>108000</v>
+      </c>
+      <c r="O1576">
+        <v>27000</v>
+      </c>
+      <c r="P1576">
+        <v>9</v>
+      </c>
+      <c r="Q1576">
+        <v>1</v>
+      </c>
+      <c r="R1576" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1576" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1577" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1577" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1577">
+        <v>19</v>
+      </c>
+      <c r="I1577" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1577">
+        <v>399000</v>
+      </c>
+      <c r="K1577">
+        <v>0</v>
+      </c>
+      <c r="L1577">
+        <v>0</v>
+      </c>
+      <c r="M1577">
+        <v>399000</v>
+      </c>
+      <c r="N1577">
+        <v>304000</v>
+      </c>
+      <c r="O1577">
+        <v>95000</v>
+      </c>
+      <c r="P1577">
+        <v>17</v>
+      </c>
+      <c r="Q1577">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="R1577" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1577" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1578" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1578">
+        <v>20</v>
+      </c>
+      <c r="I1578" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1578">
+        <v>260000</v>
+      </c>
+      <c r="K1578">
+        <v>0</v>
+      </c>
+      <c r="L1578">
+        <v>0</v>
+      </c>
+      <c r="M1578">
+        <v>260000</v>
+      </c>
+      <c r="N1578">
+        <v>160000</v>
+      </c>
+      <c r="O1578">
+        <v>100000</v>
+      </c>
+      <c r="P1578">
+        <v>12</v>
+      </c>
+      <c r="Q1578">
+        <v>1.67</v>
+      </c>
+      <c r="R1578" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1578" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1579" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1579">
+        <v>70</v>
+      </c>
+      <c r="I1579" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1579">
+        <v>910000</v>
+      </c>
+      <c r="K1579">
+        <v>0</v>
+      </c>
+      <c r="L1579">
+        <v>0</v>
+      </c>
+      <c r="M1579">
+        <v>910000</v>
+      </c>
+      <c r="N1579">
+        <v>700000</v>
+      </c>
+      <c r="O1579">
+        <v>210000</v>
+      </c>
+      <c r="P1579">
+        <v>34</v>
+      </c>
+      <c r="Q1579">
+        <v>2.06</v>
+      </c>
+      <c r="R1579" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1579" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1580" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1580" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1580" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1580">
+        <v>339</v>
+      </c>
+      <c r="I1580" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1580">
+        <v>2373000</v>
+      </c>
+      <c r="K1580">
+        <v>0</v>
+      </c>
+      <c r="L1580">
+        <v>0</v>
+      </c>
+      <c r="M1580">
+        <v>2373000</v>
+      </c>
+      <c r="N1580">
+        <v>1627200</v>
+      </c>
+      <c r="O1580">
+        <v>745800</v>
+      </c>
+      <c r="P1580">
+        <v>107</v>
+      </c>
+      <c r="Q1580">
+        <v>3.17</v>
+      </c>
+      <c r="R1580" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1580" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1581" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1581" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1581">
+        <v>29</v>
+      </c>
+      <c r="I1581" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1581">
+        <v>290000</v>
+      </c>
+      <c r="K1581">
+        <v>0</v>
+      </c>
+      <c r="L1581">
+        <v>0</v>
+      </c>
+      <c r="M1581">
+        <v>290000</v>
+      </c>
+      <c r="N1581">
+        <v>194300</v>
+      </c>
+      <c r="O1581">
+        <v>95700</v>
+      </c>
+      <c r="P1581">
+        <v>22</v>
+      </c>
+      <c r="Q1581">
+        <v>1.32</v>
+      </c>
+      <c r="R1581" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1581" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1582" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1582" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1582">
+        <v>68</v>
+      </c>
+      <c r="I1582" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1582">
+        <v>1020000</v>
+      </c>
+      <c r="K1582">
+        <v>0</v>
+      </c>
+      <c r="L1582">
+        <v>0</v>
+      </c>
+      <c r="M1582">
+        <v>1020000</v>
+      </c>
+      <c r="N1582">
+        <v>521246.52</v>
+      </c>
+      <c r="O1582">
+        <v>498753.48</v>
+      </c>
+      <c r="P1582">
+        <v>45</v>
+      </c>
+      <c r="Q1582">
+        <v>1.51</v>
+      </c>
+      <c r="R1582" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1582" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1583" t="s">
+        <v>389</v>
+      </c>
+      <c r="D1583" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1583">
+        <v>3</v>
+      </c>
+      <c r="I1583" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1583">
+        <v>15000</v>
+      </c>
+      <c r="K1583">
+        <v>0</v>
+      </c>
+      <c r="L1583">
+        <v>0</v>
+      </c>
+      <c r="M1583">
+        <v>15000</v>
+      </c>
+      <c r="N1583">
+        <v>6161.55</v>
+      </c>
+      <c r="O1583">
+        <v>8838.4500000000007</v>
+      </c>
+      <c r="P1583">
+        <v>3</v>
+      </c>
+      <c r="Q1583">
+        <v>1</v>
+      </c>
+      <c r="R1583" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1583" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1584" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1584" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1584">
+        <v>43</v>
+      </c>
+      <c r="I1584" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1584">
+        <v>215000</v>
+      </c>
+      <c r="K1584">
+        <v>0</v>
+      </c>
+      <c r="L1584">
+        <v>0</v>
+      </c>
+      <c r="M1584">
+        <v>215000</v>
+      </c>
+      <c r="N1584">
+        <v>43712.51</v>
+      </c>
+      <c r="O1584">
+        <v>171287.49</v>
+      </c>
+      <c r="P1584">
+        <v>41</v>
+      </c>
+      <c r="Q1584">
+        <v>1.05</v>
+      </c>
+      <c r="R1584" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1584" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1585" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1585">
+        <v>54</v>
+      </c>
+      <c r="I1585" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1585">
+        <v>270000</v>
+      </c>
+      <c r="K1585">
+        <v>0</v>
+      </c>
+      <c r="L1585">
+        <v>0</v>
+      </c>
+      <c r="M1585">
+        <v>270000</v>
+      </c>
+      <c r="N1585">
+        <v>120312</v>
+      </c>
+      <c r="O1585">
+        <v>149688</v>
+      </c>
+      <c r="P1585">
+        <v>48</v>
+      </c>
+      <c r="Q1585">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1585" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1585" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1586" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1586">
+        <v>74</v>
+      </c>
+      <c r="I1586" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1586">
+        <v>370000</v>
+      </c>
+      <c r="K1586">
+        <v>0</v>
+      </c>
+      <c r="L1586">
+        <v>0</v>
+      </c>
+      <c r="M1586">
+        <v>370000</v>
+      </c>
+      <c r="N1586">
+        <v>296000</v>
+      </c>
+      <c r="O1586">
+        <v>74000</v>
+      </c>
+      <c r="P1586">
+        <v>53</v>
+      </c>
+      <c r="Q1586">
+        <v>1.4</v>
+      </c>
+      <c r="R1586" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1586" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1587" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1587" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1587">
+        <v>30</v>
+      </c>
+      <c r="I1587" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1587">
+        <v>150000</v>
+      </c>
+      <c r="K1587">
+        <v>0</v>
+      </c>
+      <c r="L1587">
+        <v>0</v>
+      </c>
+      <c r="M1587">
+        <v>150000</v>
+      </c>
+      <c r="N1587">
+        <v>33333.300000000003</v>
+      </c>
+      <c r="O1587">
+        <v>116666.7</v>
+      </c>
+      <c r="P1587">
+        <v>25</v>
+      </c>
+      <c r="Q1587">
+        <v>1.2</v>
+      </c>
+      <c r="R1587" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1587" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1588" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1588" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1588">
+        <v>14</v>
+      </c>
+      <c r="I1588" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1588">
+        <v>364000</v>
+      </c>
+      <c r="K1588">
+        <v>0</v>
+      </c>
+      <c r="L1588">
+        <v>0</v>
+      </c>
+      <c r="M1588">
+        <v>364000</v>
+      </c>
+      <c r="N1588">
+        <v>308000</v>
+      </c>
+      <c r="O1588">
+        <v>56000</v>
+      </c>
+      <c r="P1588">
+        <v>12</v>
+      </c>
+      <c r="Q1588">
+        <v>1.17</v>
+      </c>
+      <c r="R1588" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1588" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1589" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1589" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1589">
+        <v>101</v>
+      </c>
+      <c r="I1589" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1589">
+        <v>2525000</v>
+      </c>
+      <c r="K1589">
+        <v>0</v>
+      </c>
+      <c r="L1589">
+        <v>0</v>
+      </c>
+      <c r="M1589">
+        <v>2525000</v>
+      </c>
+      <c r="N1589">
+        <v>2121000</v>
+      </c>
+      <c r="O1589">
+        <v>404000</v>
+      </c>
+      <c r="P1589">
+        <v>85</v>
+      </c>
+      <c r="Q1589">
+        <v>1.19</v>
+      </c>
+      <c r="R1589" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1589" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="S1:S1390" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data_Master.xlsx
+++ b/Data_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dashboard_Kantin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868EC71C-120E-4407-A0D0-08F71AD3ACA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428FE55C-E062-45D7-A6B5-ACF0F3F72C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FFC52FFA-175C-4E6E-9BE3-CE0A8ECCF11B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8964" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10159" uniqueCount="458">
   <si>
     <t>product</t>
   </si>
@@ -1393,6 +1393,27 @@
   <si>
     <t>Roti Tawar</t>
   </si>
+  <si>
+    <t>Premice</t>
+  </si>
+  <si>
+    <t>6907992823843</t>
+  </si>
+  <si>
+    <t>Kue 3K</t>
+  </si>
+  <si>
+    <t>Pisang Ijo</t>
+  </si>
+  <si>
+    <t>Telur Puyuh</t>
+  </si>
+  <si>
+    <t>BANDENG GORENG PESANAN</t>
+  </si>
+  <si>
+    <t>BDGPES</t>
+  </si>
 </sst>
 </file>
 
@@ -1770,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}">
-  <dimension ref="A1:S1589"/>
+  <dimension ref="A1:S1803"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -74743,6 +74764,9815 @@
         <v>23</v>
       </c>
     </row>
+    <row r="1590" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1590" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1590" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1590">
+        <v>336</v>
+      </c>
+      <c r="I1590" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1590">
+        <v>5376000</v>
+      </c>
+      <c r="K1590">
+        <v>0</v>
+      </c>
+      <c r="L1590">
+        <v>0</v>
+      </c>
+      <c r="M1590">
+        <v>5376000</v>
+      </c>
+      <c r="N1590">
+        <v>3696000</v>
+      </c>
+      <c r="O1590">
+        <v>1680000</v>
+      </c>
+      <c r="P1590">
+        <v>271</v>
+      </c>
+      <c r="Q1590">
+        <v>1.24</v>
+      </c>
+      <c r="R1590" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1590" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1591" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1591" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1591">
+        <v>80</v>
+      </c>
+      <c r="I1591" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1591">
+        <v>1280000</v>
+      </c>
+      <c r="K1591">
+        <v>0</v>
+      </c>
+      <c r="L1591">
+        <v>0</v>
+      </c>
+      <c r="M1591">
+        <v>1280000</v>
+      </c>
+      <c r="N1591">
+        <v>840000</v>
+      </c>
+      <c r="O1591">
+        <v>440000</v>
+      </c>
+      <c r="P1591">
+        <v>73</v>
+      </c>
+      <c r="Q1591">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R1591" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1591" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1592" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1592">
+        <v>20</v>
+      </c>
+      <c r="I1592" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1592">
+        <v>400000</v>
+      </c>
+      <c r="K1592">
+        <v>0</v>
+      </c>
+      <c r="L1592">
+        <v>0</v>
+      </c>
+      <c r="M1592">
+        <v>400000</v>
+      </c>
+      <c r="N1592">
+        <v>270000</v>
+      </c>
+      <c r="O1592">
+        <v>130000</v>
+      </c>
+      <c r="P1592">
+        <v>19</v>
+      </c>
+      <c r="Q1592">
+        <v>1.05</v>
+      </c>
+      <c r="R1592" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1592" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1593" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1593" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1593">
+        <v>301</v>
+      </c>
+      <c r="I1593" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1593">
+        <v>6020000</v>
+      </c>
+      <c r="K1593">
+        <v>0</v>
+      </c>
+      <c r="L1593">
+        <v>0</v>
+      </c>
+      <c r="M1593">
+        <v>6020000</v>
+      </c>
+      <c r="N1593">
+        <v>4063500</v>
+      </c>
+      <c r="O1593">
+        <v>1956500</v>
+      </c>
+      <c r="P1593">
+        <v>236</v>
+      </c>
+      <c r="Q1593">
+        <v>1.28</v>
+      </c>
+      <c r="R1593" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1593" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1594" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1594">
+        <v>102</v>
+      </c>
+      <c r="I1594" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1594">
+        <v>1020000</v>
+      </c>
+      <c r="K1594">
+        <v>0</v>
+      </c>
+      <c r="L1594">
+        <v>0</v>
+      </c>
+      <c r="M1594">
+        <v>1020000</v>
+      </c>
+      <c r="N1594">
+        <v>612000</v>
+      </c>
+      <c r="O1594">
+        <v>408000</v>
+      </c>
+      <c r="P1594">
+        <v>72</v>
+      </c>
+      <c r="Q1594">
+        <v>1.42</v>
+      </c>
+      <c r="R1594" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1594" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1595" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1595">
+        <v>22</v>
+      </c>
+      <c r="I1595" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1595">
+        <v>154000</v>
+      </c>
+      <c r="K1595">
+        <v>0</v>
+      </c>
+      <c r="L1595">
+        <v>0</v>
+      </c>
+      <c r="M1595">
+        <v>154000</v>
+      </c>
+      <c r="N1595">
+        <v>132000</v>
+      </c>
+      <c r="O1595">
+        <v>22000</v>
+      </c>
+      <c r="P1595">
+        <v>17</v>
+      </c>
+      <c r="Q1595">
+        <v>1.29</v>
+      </c>
+      <c r="R1595" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1595" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1596" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1596" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1596">
+        <v>187</v>
+      </c>
+      <c r="I1596" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1596">
+        <v>748000</v>
+      </c>
+      <c r="K1596">
+        <v>0</v>
+      </c>
+      <c r="L1596">
+        <v>0</v>
+      </c>
+      <c r="M1596">
+        <v>748000</v>
+      </c>
+      <c r="N1596">
+        <v>561000</v>
+      </c>
+      <c r="O1596">
+        <v>187000</v>
+      </c>
+      <c r="P1596">
+        <v>103</v>
+      </c>
+      <c r="Q1596">
+        <v>1.82</v>
+      </c>
+      <c r="R1596" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1596" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1597" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1597" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1597">
+        <v>31</v>
+      </c>
+      <c r="I1597" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1597">
+        <v>155000</v>
+      </c>
+      <c r="K1597">
+        <v>0</v>
+      </c>
+      <c r="L1597">
+        <v>0</v>
+      </c>
+      <c r="M1597">
+        <v>155000</v>
+      </c>
+      <c r="N1597">
+        <v>124000</v>
+      </c>
+      <c r="O1597">
+        <v>31000</v>
+      </c>
+      <c r="P1597">
+        <v>26</v>
+      </c>
+      <c r="Q1597">
+        <v>1.19</v>
+      </c>
+      <c r="R1597" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1597" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1598" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1598" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1598">
+        <v>25</v>
+      </c>
+      <c r="I1598" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1598">
+        <v>500000</v>
+      </c>
+      <c r="K1598">
+        <v>0</v>
+      </c>
+      <c r="L1598">
+        <v>0</v>
+      </c>
+      <c r="M1598">
+        <v>500000</v>
+      </c>
+      <c r="N1598">
+        <v>375000</v>
+      </c>
+      <c r="O1598">
+        <v>125000</v>
+      </c>
+      <c r="P1598">
+        <v>21</v>
+      </c>
+      <c r="Q1598">
+        <v>1.19</v>
+      </c>
+      <c r="R1598" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1598" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1599" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1599">
+        <v>115</v>
+      </c>
+      <c r="I1599" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1599">
+        <v>1725000</v>
+      </c>
+      <c r="K1599">
+        <v>0</v>
+      </c>
+      <c r="L1599">
+        <v>0</v>
+      </c>
+      <c r="M1599">
+        <v>1727000</v>
+      </c>
+      <c r="N1599">
+        <v>1266621.1599999999</v>
+      </c>
+      <c r="O1599">
+        <v>460378.84</v>
+      </c>
+      <c r="P1599">
+        <v>91</v>
+      </c>
+      <c r="Q1599">
+        <v>1.26</v>
+      </c>
+      <c r="R1599" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1599" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1600" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1600">
+        <v>63</v>
+      </c>
+      <c r="I1600" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1600">
+        <v>1134000</v>
+      </c>
+      <c r="K1600">
+        <v>0</v>
+      </c>
+      <c r="L1600">
+        <v>0</v>
+      </c>
+      <c r="M1600">
+        <v>1164000</v>
+      </c>
+      <c r="N1600">
+        <v>842983.35</v>
+      </c>
+      <c r="O1600">
+        <v>321016.65000000002</v>
+      </c>
+      <c r="P1600">
+        <v>47</v>
+      </c>
+      <c r="Q1600">
+        <v>1.34</v>
+      </c>
+      <c r="R1600" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1600" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1601" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1601">
+        <v>99</v>
+      </c>
+      <c r="I1601" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1601">
+        <v>396000</v>
+      </c>
+      <c r="K1601">
+        <v>0</v>
+      </c>
+      <c r="L1601">
+        <v>0</v>
+      </c>
+      <c r="M1601">
+        <v>396000</v>
+      </c>
+      <c r="N1601">
+        <v>297000</v>
+      </c>
+      <c r="O1601">
+        <v>99000</v>
+      </c>
+      <c r="P1601">
+        <v>62</v>
+      </c>
+      <c r="Q1601">
+        <v>1.6</v>
+      </c>
+      <c r="R1601" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1601" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1602" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1602">
+        <v>12</v>
+      </c>
+      <c r="I1602" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1602">
+        <v>180000</v>
+      </c>
+      <c r="K1602">
+        <v>0</v>
+      </c>
+      <c r="L1602">
+        <v>0</v>
+      </c>
+      <c r="M1602">
+        <v>180000</v>
+      </c>
+      <c r="N1602">
+        <v>163200</v>
+      </c>
+      <c r="O1602">
+        <v>16800</v>
+      </c>
+      <c r="P1602">
+        <v>12</v>
+      </c>
+      <c r="Q1602">
+        <v>1</v>
+      </c>
+      <c r="R1602" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1602" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1603" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1603">
+        <v>2</v>
+      </c>
+      <c r="I1603" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1603">
+        <v>24000</v>
+      </c>
+      <c r="K1603">
+        <v>0</v>
+      </c>
+      <c r="L1603">
+        <v>0</v>
+      </c>
+      <c r="M1603">
+        <v>24000</v>
+      </c>
+      <c r="N1603">
+        <v>8500</v>
+      </c>
+      <c r="O1603">
+        <v>15500</v>
+      </c>
+      <c r="P1603">
+        <v>2</v>
+      </c>
+      <c r="Q1603">
+        <v>1</v>
+      </c>
+      <c r="R1603" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1603" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1604" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1604">
+        <v>1</v>
+      </c>
+      <c r="I1604" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1604">
+        <v>12000</v>
+      </c>
+      <c r="K1604">
+        <v>0</v>
+      </c>
+      <c r="L1604">
+        <v>0</v>
+      </c>
+      <c r="M1604">
+        <v>12000</v>
+      </c>
+      <c r="N1604">
+        <v>10125</v>
+      </c>
+      <c r="O1604">
+        <v>1875</v>
+      </c>
+      <c r="P1604">
+        <v>1</v>
+      </c>
+      <c r="Q1604">
+        <v>1</v>
+      </c>
+      <c r="R1604" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1604" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1605" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1605">
+        <v>3</v>
+      </c>
+      <c r="I1605" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1605">
+        <v>21000</v>
+      </c>
+      <c r="K1605">
+        <v>0</v>
+      </c>
+      <c r="L1605">
+        <v>0</v>
+      </c>
+      <c r="M1605">
+        <v>21000</v>
+      </c>
+      <c r="N1605">
+        <v>15900</v>
+      </c>
+      <c r="O1605">
+        <v>5100</v>
+      </c>
+      <c r="P1605">
+        <v>3</v>
+      </c>
+      <c r="Q1605">
+        <v>1</v>
+      </c>
+      <c r="R1605" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1605" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1606" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1606" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1606">
+        <v>21</v>
+      </c>
+      <c r="I1606" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1606">
+        <v>147000</v>
+      </c>
+      <c r="K1606">
+        <v>0</v>
+      </c>
+      <c r="L1606">
+        <v>0</v>
+      </c>
+      <c r="M1606">
+        <v>147000</v>
+      </c>
+      <c r="N1606">
+        <v>92531.25</v>
+      </c>
+      <c r="O1606">
+        <v>54468.75</v>
+      </c>
+      <c r="P1606">
+        <v>12</v>
+      </c>
+      <c r="Q1606">
+        <v>1.75</v>
+      </c>
+      <c r="R1606" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1606" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1607" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1607">
+        <v>11</v>
+      </c>
+      <c r="I1607" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1607">
+        <v>44000</v>
+      </c>
+      <c r="K1607">
+        <v>0</v>
+      </c>
+      <c r="L1607">
+        <v>0</v>
+      </c>
+      <c r="M1607">
+        <v>44000</v>
+      </c>
+      <c r="N1607">
+        <v>28600</v>
+      </c>
+      <c r="O1607">
+        <v>15400</v>
+      </c>
+      <c r="P1607">
+        <v>7</v>
+      </c>
+      <c r="Q1607">
+        <v>1.57</v>
+      </c>
+      <c r="R1607" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1607" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1608" t="s">
+        <v>451</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>452</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1608">
+        <v>6</v>
+      </c>
+      <c r="I1608" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1608">
+        <v>90000</v>
+      </c>
+      <c r="K1608">
+        <v>0</v>
+      </c>
+      <c r="L1608">
+        <v>0</v>
+      </c>
+      <c r="M1608">
+        <v>90000</v>
+      </c>
+      <c r="N1608">
+        <v>75000</v>
+      </c>
+      <c r="O1608">
+        <v>15000</v>
+      </c>
+      <c r="P1608">
+        <v>4</v>
+      </c>
+      <c r="Q1608">
+        <v>1.5</v>
+      </c>
+      <c r="R1608" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1608" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1609" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1609" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1609">
+        <v>7</v>
+      </c>
+      <c r="I1609" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1609">
+        <v>42000</v>
+      </c>
+      <c r="K1609">
+        <v>0</v>
+      </c>
+      <c r="L1609">
+        <v>0</v>
+      </c>
+      <c r="M1609">
+        <v>42000</v>
+      </c>
+      <c r="N1609">
+        <v>8779.19</v>
+      </c>
+      <c r="O1609">
+        <v>33220.81</v>
+      </c>
+      <c r="P1609">
+        <v>6</v>
+      </c>
+      <c r="Q1609">
+        <v>1.17</v>
+      </c>
+      <c r="R1609" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1609" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1610" t="s">
+        <v>418</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>419</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1610">
+        <v>3</v>
+      </c>
+      <c r="I1610" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1610">
+        <v>9000</v>
+      </c>
+      <c r="K1610">
+        <v>0</v>
+      </c>
+      <c r="L1610">
+        <v>0</v>
+      </c>
+      <c r="M1610">
+        <v>9000</v>
+      </c>
+      <c r="N1610">
+        <v>0</v>
+      </c>
+      <c r="O1610">
+        <v>9000</v>
+      </c>
+      <c r="P1610">
+        <v>3</v>
+      </c>
+      <c r="Q1610">
+        <v>1</v>
+      </c>
+      <c r="R1610" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1610" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1611" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1611" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1611">
+        <v>3</v>
+      </c>
+      <c r="I1611" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1611">
+        <v>27000</v>
+      </c>
+      <c r="K1611">
+        <v>0</v>
+      </c>
+      <c r="L1611">
+        <v>0</v>
+      </c>
+      <c r="M1611">
+        <v>27000</v>
+      </c>
+      <c r="N1611">
+        <v>18600</v>
+      </c>
+      <c r="O1611">
+        <v>8400</v>
+      </c>
+      <c r="P1611">
+        <v>3</v>
+      </c>
+      <c r="Q1611">
+        <v>1</v>
+      </c>
+      <c r="R1611" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1611" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1612" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1612">
+        <v>20</v>
+      </c>
+      <c r="I1612" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1612">
+        <v>420000</v>
+      </c>
+      <c r="K1612">
+        <v>0</v>
+      </c>
+      <c r="L1612">
+        <v>0</v>
+      </c>
+      <c r="M1612">
+        <v>420000</v>
+      </c>
+      <c r="N1612">
+        <v>120173.8</v>
+      </c>
+      <c r="O1612">
+        <v>299826.2</v>
+      </c>
+      <c r="P1612">
+        <v>20</v>
+      </c>
+      <c r="Q1612">
+        <v>1</v>
+      </c>
+      <c r="R1612" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1612" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1613" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1613">
+        <v>55</v>
+      </c>
+      <c r="I1613" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1613">
+        <v>1210000</v>
+      </c>
+      <c r="K1613">
+        <v>0</v>
+      </c>
+      <c r="L1613">
+        <v>0</v>
+      </c>
+      <c r="M1613">
+        <v>1387000</v>
+      </c>
+      <c r="N1613">
+        <v>390577.31</v>
+      </c>
+      <c r="O1613">
+        <v>996422.69</v>
+      </c>
+      <c r="P1613">
+        <v>50</v>
+      </c>
+      <c r="Q1613">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R1613" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1613" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1614" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1614">
+        <v>29</v>
+      </c>
+      <c r="I1614" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1614">
+        <v>696000</v>
+      </c>
+      <c r="K1614">
+        <v>0</v>
+      </c>
+      <c r="L1614">
+        <v>0</v>
+      </c>
+      <c r="M1614">
+        <v>728000</v>
+      </c>
+      <c r="N1614">
+        <v>210465.27</v>
+      </c>
+      <c r="O1614">
+        <v>517534.73</v>
+      </c>
+      <c r="P1614">
+        <v>24</v>
+      </c>
+      <c r="Q1614">
+        <v>1.21</v>
+      </c>
+      <c r="R1614" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1614" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1615" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1615">
+        <v>27</v>
+      </c>
+      <c r="I1615" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1615">
+        <v>135000</v>
+      </c>
+      <c r="K1615">
+        <v>0</v>
+      </c>
+      <c r="L1615">
+        <v>0</v>
+      </c>
+      <c r="M1615">
+        <v>135000</v>
+      </c>
+      <c r="N1615">
+        <v>69749.91</v>
+      </c>
+      <c r="O1615">
+        <v>65250.09</v>
+      </c>
+      <c r="P1615">
+        <v>23</v>
+      </c>
+      <c r="Q1615">
+        <v>1.17</v>
+      </c>
+      <c r="R1615" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1615" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1616" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1616">
+        <v>279</v>
+      </c>
+      <c r="I1616" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1616">
+        <v>1395000</v>
+      </c>
+      <c r="K1616">
+        <v>0</v>
+      </c>
+      <c r="L1616">
+        <v>0</v>
+      </c>
+      <c r="M1616">
+        <v>1395000</v>
+      </c>
+      <c r="N1616">
+        <v>461821.72</v>
+      </c>
+      <c r="O1616">
+        <v>933178.28</v>
+      </c>
+      <c r="P1616">
+        <v>226</v>
+      </c>
+      <c r="Q1616">
+        <v>1.23</v>
+      </c>
+      <c r="R1616" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1616" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1617" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1617">
+        <v>12</v>
+      </c>
+      <c r="I1617" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1617">
+        <v>60000</v>
+      </c>
+      <c r="K1617">
+        <v>0</v>
+      </c>
+      <c r="L1617">
+        <v>0</v>
+      </c>
+      <c r="M1617">
+        <v>60000</v>
+      </c>
+      <c r="N1617">
+        <v>0</v>
+      </c>
+      <c r="O1617">
+        <v>60000</v>
+      </c>
+      <c r="P1617">
+        <v>9</v>
+      </c>
+      <c r="Q1617">
+        <v>1.33</v>
+      </c>
+      <c r="R1617" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1617" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1618" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1618">
+        <v>1</v>
+      </c>
+      <c r="I1618" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1618">
+        <v>8000</v>
+      </c>
+      <c r="K1618">
+        <v>0</v>
+      </c>
+      <c r="L1618">
+        <v>0</v>
+      </c>
+      <c r="M1618">
+        <v>8000</v>
+      </c>
+      <c r="N1618">
+        <v>5700</v>
+      </c>
+      <c r="O1618">
+        <v>2300</v>
+      </c>
+      <c r="P1618">
+        <v>1</v>
+      </c>
+      <c r="Q1618">
+        <v>1</v>
+      </c>
+      <c r="R1618" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1618" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1619" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1619">
+        <v>1</v>
+      </c>
+      <c r="I1619" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1619">
+        <v>15000</v>
+      </c>
+      <c r="K1619">
+        <v>0</v>
+      </c>
+      <c r="L1619">
+        <v>0</v>
+      </c>
+      <c r="M1619">
+        <v>15000</v>
+      </c>
+      <c r="N1619">
+        <v>12000</v>
+      </c>
+      <c r="O1619">
+        <v>3000</v>
+      </c>
+      <c r="P1619">
+        <v>1</v>
+      </c>
+      <c r="Q1619">
+        <v>1</v>
+      </c>
+      <c r="R1619" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1619" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1620" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1620">
+        <v>50</v>
+      </c>
+      <c r="I1620" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1620">
+        <v>300000</v>
+      </c>
+      <c r="K1620">
+        <v>0</v>
+      </c>
+      <c r="L1620">
+        <v>0</v>
+      </c>
+      <c r="M1620">
+        <v>300000</v>
+      </c>
+      <c r="N1620">
+        <v>179166.5</v>
+      </c>
+      <c r="O1620">
+        <v>120833.5</v>
+      </c>
+      <c r="P1620">
+        <v>37</v>
+      </c>
+      <c r="Q1620">
+        <v>1.35</v>
+      </c>
+      <c r="R1620" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1620" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1621" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1621">
+        <v>1</v>
+      </c>
+      <c r="I1621" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1621">
+        <v>8000</v>
+      </c>
+      <c r="K1621">
+        <v>0</v>
+      </c>
+      <c r="L1621">
+        <v>0</v>
+      </c>
+      <c r="M1621">
+        <v>8000</v>
+      </c>
+      <c r="N1621">
+        <v>5200</v>
+      </c>
+      <c r="O1621">
+        <v>2800</v>
+      </c>
+      <c r="P1621">
+        <v>1</v>
+      </c>
+      <c r="Q1621">
+        <v>1</v>
+      </c>
+      <c r="R1621" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1621" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1622" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1622">
+        <v>787</v>
+      </c>
+      <c r="I1622" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1622">
+        <v>3935000</v>
+      </c>
+      <c r="K1622">
+        <v>0</v>
+      </c>
+      <c r="L1622">
+        <v>0</v>
+      </c>
+      <c r="M1622">
+        <v>3935000</v>
+      </c>
+      <c r="N1622">
+        <v>1311407.2</v>
+      </c>
+      <c r="O1622">
+        <v>2623592.7999999998</v>
+      </c>
+      <c r="P1622">
+        <v>396</v>
+      </c>
+      <c r="Q1622">
+        <v>1.99</v>
+      </c>
+      <c r="R1622" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1622" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1623" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1623">
+        <v>22</v>
+      </c>
+      <c r="I1623" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1623">
+        <v>154000</v>
+      </c>
+      <c r="K1623">
+        <v>0</v>
+      </c>
+      <c r="L1623">
+        <v>0</v>
+      </c>
+      <c r="M1623">
+        <v>154000</v>
+      </c>
+      <c r="N1623">
+        <v>114950</v>
+      </c>
+      <c r="O1623">
+        <v>39050</v>
+      </c>
+      <c r="P1623">
+        <v>16</v>
+      </c>
+      <c r="Q1623">
+        <v>1.38</v>
+      </c>
+      <c r="R1623" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1623" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1624" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1624">
+        <v>54</v>
+      </c>
+      <c r="I1624" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1624">
+        <v>540000</v>
+      </c>
+      <c r="K1624">
+        <v>0</v>
+      </c>
+      <c r="L1624">
+        <v>0</v>
+      </c>
+      <c r="M1624">
+        <v>540000</v>
+      </c>
+      <c r="N1624">
+        <v>393750.18</v>
+      </c>
+      <c r="O1624">
+        <v>146249.82</v>
+      </c>
+      <c r="P1624">
+        <v>45</v>
+      </c>
+      <c r="Q1624">
+        <v>1.2</v>
+      </c>
+      <c r="R1624" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1624" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1625" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1625">
+        <v>74</v>
+      </c>
+      <c r="I1625" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1625">
+        <v>1850000</v>
+      </c>
+      <c r="K1625">
+        <v>0</v>
+      </c>
+      <c r="L1625">
+        <v>0</v>
+      </c>
+      <c r="M1625">
+        <v>1850000</v>
+      </c>
+      <c r="N1625">
+        <v>1415753.7</v>
+      </c>
+      <c r="O1625">
+        <v>434246.3</v>
+      </c>
+      <c r="P1625">
+        <v>62</v>
+      </c>
+      <c r="Q1625">
+        <v>1.19</v>
+      </c>
+      <c r="R1625" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1625" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1626" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1626">
+        <v>3</v>
+      </c>
+      <c r="I1626" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1626">
+        <v>24000</v>
+      </c>
+      <c r="K1626">
+        <v>0</v>
+      </c>
+      <c r="L1626">
+        <v>0</v>
+      </c>
+      <c r="M1626">
+        <v>24000</v>
+      </c>
+      <c r="N1626">
+        <v>16982.07</v>
+      </c>
+      <c r="O1626">
+        <v>7017.93</v>
+      </c>
+      <c r="P1626">
+        <v>3</v>
+      </c>
+      <c r="Q1626">
+        <v>1</v>
+      </c>
+      <c r="R1626" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1626" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1627" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1627">
+        <v>4</v>
+      </c>
+      <c r="I1627" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1627">
+        <v>24000</v>
+      </c>
+      <c r="K1627">
+        <v>0</v>
+      </c>
+      <c r="L1627">
+        <v>0</v>
+      </c>
+      <c r="M1627">
+        <v>24000</v>
+      </c>
+      <c r="N1627">
+        <v>16867.04</v>
+      </c>
+      <c r="O1627">
+        <v>7132.96</v>
+      </c>
+      <c r="P1627">
+        <v>2</v>
+      </c>
+      <c r="Q1627">
+        <v>2</v>
+      </c>
+      <c r="R1627" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1627" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1628" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1628">
+        <v>109</v>
+      </c>
+      <c r="I1628" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1628">
+        <v>763000</v>
+      </c>
+      <c r="K1628">
+        <v>0</v>
+      </c>
+      <c r="L1628">
+        <v>0</v>
+      </c>
+      <c r="M1628">
+        <v>763000</v>
+      </c>
+      <c r="N1628">
+        <v>575278.02</v>
+      </c>
+      <c r="O1628">
+        <v>187721.98</v>
+      </c>
+      <c r="P1628">
+        <v>77</v>
+      </c>
+      <c r="Q1628">
+        <v>1.42</v>
+      </c>
+      <c r="R1628" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1628" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1629" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>107</v>
+      </c>
+      <c r="H1629">
+        <v>7</v>
+      </c>
+      <c r="I1629" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1629">
+        <v>56000</v>
+      </c>
+      <c r="K1629">
+        <v>0</v>
+      </c>
+      <c r="L1629">
+        <v>0</v>
+      </c>
+      <c r="M1629">
+        <v>56000</v>
+      </c>
+      <c r="N1629">
+        <v>37770.81</v>
+      </c>
+      <c r="O1629">
+        <v>18229.189999999999</v>
+      </c>
+      <c r="P1629">
+        <v>6</v>
+      </c>
+      <c r="Q1629">
+        <v>1.17</v>
+      </c>
+      <c r="R1629" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1629" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1630" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1630" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1630">
+        <v>6</v>
+      </c>
+      <c r="I1630" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1630">
+        <v>90000</v>
+      </c>
+      <c r="K1630">
+        <v>0</v>
+      </c>
+      <c r="L1630">
+        <v>0</v>
+      </c>
+      <c r="M1630">
+        <v>90000</v>
+      </c>
+      <c r="N1630">
+        <v>72000</v>
+      </c>
+      <c r="O1630">
+        <v>18000</v>
+      </c>
+      <c r="P1630">
+        <v>6</v>
+      </c>
+      <c r="Q1630">
+        <v>1</v>
+      </c>
+      <c r="R1630" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1630" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1631" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1631">
+        <v>53</v>
+      </c>
+      <c r="I1631" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1631">
+        <v>636000</v>
+      </c>
+      <c r="K1631">
+        <v>0</v>
+      </c>
+      <c r="L1631">
+        <v>0</v>
+      </c>
+      <c r="M1631">
+        <v>636000</v>
+      </c>
+      <c r="N1631">
+        <v>530000</v>
+      </c>
+      <c r="O1631">
+        <v>106000</v>
+      </c>
+      <c r="P1631">
+        <v>39</v>
+      </c>
+      <c r="Q1631">
+        <v>1.36</v>
+      </c>
+      <c r="R1631" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1631" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1632" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1632">
+        <v>5</v>
+      </c>
+      <c r="I1632" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1632">
+        <v>35000</v>
+      </c>
+      <c r="K1632">
+        <v>0</v>
+      </c>
+      <c r="L1632">
+        <v>0</v>
+      </c>
+      <c r="M1632">
+        <v>35000</v>
+      </c>
+      <c r="N1632">
+        <v>15833.35</v>
+      </c>
+      <c r="O1632">
+        <v>19166.650000000001</v>
+      </c>
+      <c r="P1632">
+        <v>5</v>
+      </c>
+      <c r="Q1632">
+        <v>1</v>
+      </c>
+      <c r="R1632" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1632" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1633" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1633">
+        <v>3</v>
+      </c>
+      <c r="I1633" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1633">
+        <v>21000</v>
+      </c>
+      <c r="K1633">
+        <v>0</v>
+      </c>
+      <c r="L1633">
+        <v>0</v>
+      </c>
+      <c r="M1633">
+        <v>21000</v>
+      </c>
+      <c r="N1633">
+        <v>9500.01</v>
+      </c>
+      <c r="O1633">
+        <v>11499.99</v>
+      </c>
+      <c r="P1633">
+        <v>3</v>
+      </c>
+      <c r="Q1633">
+        <v>1</v>
+      </c>
+      <c r="R1633" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1633" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1634" t="s">
+        <v>405</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>406</v>
+      </c>
+      <c r="H1634">
+        <v>21</v>
+      </c>
+      <c r="I1634" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1634">
+        <v>126000</v>
+      </c>
+      <c r="K1634">
+        <v>0</v>
+      </c>
+      <c r="L1634">
+        <v>0</v>
+      </c>
+      <c r="M1634">
+        <v>126000</v>
+      </c>
+      <c r="N1634">
+        <v>101150.07</v>
+      </c>
+      <c r="O1634">
+        <v>24849.93</v>
+      </c>
+      <c r="P1634">
+        <v>20</v>
+      </c>
+      <c r="Q1634">
+        <v>1.05</v>
+      </c>
+      <c r="R1634" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1634" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1635" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1635">
+        <v>29</v>
+      </c>
+      <c r="I1635" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1635">
+        <v>232000</v>
+      </c>
+      <c r="K1635">
+        <v>0</v>
+      </c>
+      <c r="L1635">
+        <v>0</v>
+      </c>
+      <c r="M1635">
+        <v>232000</v>
+      </c>
+      <c r="N1635">
+        <v>174871.74</v>
+      </c>
+      <c r="O1635">
+        <v>57128.26</v>
+      </c>
+      <c r="P1635">
+        <v>24</v>
+      </c>
+      <c r="Q1635">
+        <v>1.21</v>
+      </c>
+      <c r="R1635" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1635" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1636" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1636" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1636">
+        <v>14</v>
+      </c>
+      <c r="I1636" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1636">
+        <v>210000</v>
+      </c>
+      <c r="K1636">
+        <v>0</v>
+      </c>
+      <c r="L1636">
+        <v>0</v>
+      </c>
+      <c r="M1636">
+        <v>210000</v>
+      </c>
+      <c r="N1636">
+        <v>130500</v>
+      </c>
+      <c r="O1636">
+        <v>79500</v>
+      </c>
+      <c r="P1636">
+        <v>14</v>
+      </c>
+      <c r="Q1636">
+        <v>1</v>
+      </c>
+      <c r="R1636" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1636" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1637" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>138</v>
+      </c>
+      <c r="H1637">
+        <v>75</v>
+      </c>
+      <c r="I1637" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1637">
+        <v>375000</v>
+      </c>
+      <c r="K1637">
+        <v>0</v>
+      </c>
+      <c r="L1637">
+        <v>0</v>
+      </c>
+      <c r="M1637">
+        <v>375000</v>
+      </c>
+      <c r="N1637">
+        <v>193749.75</v>
+      </c>
+      <c r="O1637">
+        <v>181250.25</v>
+      </c>
+      <c r="P1637">
+        <v>61</v>
+      </c>
+      <c r="Q1637">
+        <v>1.23</v>
+      </c>
+      <c r="R1637" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1637" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1638" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1638">
+        <v>11</v>
+      </c>
+      <c r="I1638" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1638">
+        <v>132000</v>
+      </c>
+      <c r="K1638">
+        <v>0</v>
+      </c>
+      <c r="L1638">
+        <v>0</v>
+      </c>
+      <c r="M1638">
+        <v>132000</v>
+      </c>
+      <c r="N1638">
+        <v>102994.45</v>
+      </c>
+      <c r="O1638">
+        <v>29005.55</v>
+      </c>
+      <c r="P1638">
+        <v>8</v>
+      </c>
+      <c r="Q1638">
+        <v>1.38</v>
+      </c>
+      <c r="R1638" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1638" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1639" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>148</v>
+      </c>
+      <c r="H1639">
+        <v>28</v>
+      </c>
+      <c r="I1639" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1639">
+        <v>336000</v>
+      </c>
+      <c r="K1639">
+        <v>0</v>
+      </c>
+      <c r="L1639">
+        <v>0</v>
+      </c>
+      <c r="M1639">
+        <v>336000</v>
+      </c>
+      <c r="N1639">
+        <v>247333.52</v>
+      </c>
+      <c r="O1639">
+        <v>88666.48</v>
+      </c>
+      <c r="P1639">
+        <v>26</v>
+      </c>
+      <c r="Q1639">
+        <v>1.08</v>
+      </c>
+      <c r="R1639" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1639" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1640" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>150</v>
+      </c>
+      <c r="H1640">
+        <v>39</v>
+      </c>
+      <c r="I1640" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1640">
+        <v>390000</v>
+      </c>
+      <c r="K1640">
+        <v>0</v>
+      </c>
+      <c r="L1640">
+        <v>0</v>
+      </c>
+      <c r="M1640">
+        <v>390000</v>
+      </c>
+      <c r="N1640">
+        <v>316875</v>
+      </c>
+      <c r="O1640">
+        <v>73125</v>
+      </c>
+      <c r="P1640">
+        <v>35</v>
+      </c>
+      <c r="Q1640">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1640" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1640" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1641" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1641" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1641">
+        <v>24</v>
+      </c>
+      <c r="I1641" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1641">
+        <v>192000</v>
+      </c>
+      <c r="K1641">
+        <v>0</v>
+      </c>
+      <c r="L1641">
+        <v>0</v>
+      </c>
+      <c r="M1641">
+        <v>192000</v>
+      </c>
+      <c r="N1641">
+        <v>150000</v>
+      </c>
+      <c r="O1641">
+        <v>42000</v>
+      </c>
+      <c r="P1641">
+        <v>23</v>
+      </c>
+      <c r="Q1641">
+        <v>1.04</v>
+      </c>
+      <c r="R1641" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1641" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1642" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1642">
+        <v>77</v>
+      </c>
+      <c r="I1642" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1642">
+        <v>616000</v>
+      </c>
+      <c r="K1642">
+        <v>0</v>
+      </c>
+      <c r="L1642">
+        <v>0</v>
+      </c>
+      <c r="M1642">
+        <v>616000</v>
+      </c>
+      <c r="N1642">
+        <v>479164.84</v>
+      </c>
+      <c r="O1642">
+        <v>136835.16</v>
+      </c>
+      <c r="P1642">
+        <v>61</v>
+      </c>
+      <c r="Q1642">
+        <v>1.26</v>
+      </c>
+      <c r="R1642" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1642" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1643" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1643">
+        <v>45</v>
+      </c>
+      <c r="I1643" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1643">
+        <v>405000</v>
+      </c>
+      <c r="K1643">
+        <v>0</v>
+      </c>
+      <c r="L1643">
+        <v>0</v>
+      </c>
+      <c r="M1643">
+        <v>405000</v>
+      </c>
+      <c r="N1643">
+        <v>346709.25</v>
+      </c>
+      <c r="O1643">
+        <v>58290.75</v>
+      </c>
+      <c r="P1643">
+        <v>36</v>
+      </c>
+      <c r="Q1643">
+        <v>1.25</v>
+      </c>
+      <c r="R1643" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1643" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1644" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1644">
+        <v>171</v>
+      </c>
+      <c r="I1644" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1644">
+        <v>855000</v>
+      </c>
+      <c r="K1644">
+        <v>0</v>
+      </c>
+      <c r="L1644">
+        <v>0</v>
+      </c>
+      <c r="M1644">
+        <v>855000</v>
+      </c>
+      <c r="N1644">
+        <v>571110.43999999994</v>
+      </c>
+      <c r="O1644">
+        <v>283889.56</v>
+      </c>
+      <c r="P1644">
+        <v>45</v>
+      </c>
+      <c r="Q1644">
+        <v>3.8</v>
+      </c>
+      <c r="R1644" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1644" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1645" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1645">
+        <v>29</v>
+      </c>
+      <c r="I1645" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1645">
+        <v>232000</v>
+      </c>
+      <c r="K1645">
+        <v>0</v>
+      </c>
+      <c r="L1645">
+        <v>0</v>
+      </c>
+      <c r="M1645">
+        <v>232000</v>
+      </c>
+      <c r="N1645">
+        <v>167513.57</v>
+      </c>
+      <c r="O1645">
+        <v>64486.43</v>
+      </c>
+      <c r="P1645">
+        <v>21</v>
+      </c>
+      <c r="Q1645">
+        <v>1.38</v>
+      </c>
+      <c r="R1645" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1645" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1646" t="s">
+        <v>420</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1646">
+        <v>21</v>
+      </c>
+      <c r="I1646" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1646">
+        <v>630000</v>
+      </c>
+      <c r="K1646">
+        <v>0</v>
+      </c>
+      <c r="L1646">
+        <v>0</v>
+      </c>
+      <c r="M1646">
+        <v>630000</v>
+      </c>
+      <c r="N1646">
+        <v>525000</v>
+      </c>
+      <c r="O1646">
+        <v>105000</v>
+      </c>
+      <c r="P1646">
+        <v>20</v>
+      </c>
+      <c r="Q1646">
+        <v>1.05</v>
+      </c>
+      <c r="R1646" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1646" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1647" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1647">
+        <v>1</v>
+      </c>
+      <c r="I1647" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1647">
+        <v>12000</v>
+      </c>
+      <c r="K1647">
+        <v>0</v>
+      </c>
+      <c r="L1647">
+        <v>0</v>
+      </c>
+      <c r="M1647">
+        <v>12000</v>
+      </c>
+      <c r="N1647">
+        <v>4861.96</v>
+      </c>
+      <c r="O1647">
+        <v>7138.04</v>
+      </c>
+      <c r="P1647">
+        <v>1</v>
+      </c>
+      <c r="Q1647">
+        <v>1</v>
+      </c>
+      <c r="R1647" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1647" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1648" t="s">
+        <v>397</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1648">
+        <v>98</v>
+      </c>
+      <c r="I1648" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1648">
+        <v>686000</v>
+      </c>
+      <c r="K1648">
+        <v>0</v>
+      </c>
+      <c r="L1648">
+        <v>0</v>
+      </c>
+      <c r="M1648">
+        <v>686000</v>
+      </c>
+      <c r="N1648">
+        <v>490000</v>
+      </c>
+      <c r="O1648">
+        <v>196000</v>
+      </c>
+      <c r="P1648">
+        <v>41</v>
+      </c>
+      <c r="Q1648">
+        <v>2.39</v>
+      </c>
+      <c r="R1648" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1648" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1649" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1649">
+        <v>21</v>
+      </c>
+      <c r="I1649" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1649">
+        <v>378000</v>
+      </c>
+      <c r="K1649">
+        <v>0</v>
+      </c>
+      <c r="L1649">
+        <v>0</v>
+      </c>
+      <c r="M1649">
+        <v>378000</v>
+      </c>
+      <c r="N1649">
+        <v>315000</v>
+      </c>
+      <c r="O1649">
+        <v>63000</v>
+      </c>
+      <c r="P1649">
+        <v>19</v>
+      </c>
+      <c r="Q1649">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1649" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1649" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1650" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1650">
+        <v>334</v>
+      </c>
+      <c r="I1650" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1650">
+        <v>4342000</v>
+      </c>
+      <c r="K1650">
+        <v>0</v>
+      </c>
+      <c r="L1650">
+        <v>0</v>
+      </c>
+      <c r="M1650">
+        <v>4342000</v>
+      </c>
+      <c r="N1650">
+        <v>3340000</v>
+      </c>
+      <c r="O1650">
+        <v>1002000</v>
+      </c>
+      <c r="P1650">
+        <v>149</v>
+      </c>
+      <c r="Q1650">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="R1650" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1650" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1651" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1651">
+        <v>61</v>
+      </c>
+      <c r="I1651" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1651">
+        <v>976000</v>
+      </c>
+      <c r="K1651">
+        <v>0</v>
+      </c>
+      <c r="L1651">
+        <v>0</v>
+      </c>
+      <c r="M1651">
+        <v>976000</v>
+      </c>
+      <c r="N1651">
+        <v>732000</v>
+      </c>
+      <c r="O1651">
+        <v>244000</v>
+      </c>
+      <c r="P1651">
+        <v>31</v>
+      </c>
+      <c r="Q1651">
+        <v>1.97</v>
+      </c>
+      <c r="R1651" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1651" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1652" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1652">
+        <v>67</v>
+      </c>
+      <c r="I1652" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1652">
+        <v>402000</v>
+      </c>
+      <c r="K1652">
+        <v>0</v>
+      </c>
+      <c r="L1652">
+        <v>0</v>
+      </c>
+      <c r="M1652">
+        <v>402000</v>
+      </c>
+      <c r="N1652">
+        <v>268000</v>
+      </c>
+      <c r="O1652">
+        <v>134000</v>
+      </c>
+      <c r="P1652">
+        <v>17</v>
+      </c>
+      <c r="Q1652">
+        <v>3.94</v>
+      </c>
+      <c r="R1652" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1652" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1653" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1653">
+        <v>569</v>
+      </c>
+      <c r="I1653" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1653">
+        <v>3983000</v>
+      </c>
+      <c r="K1653">
+        <v>0</v>
+      </c>
+      <c r="L1653">
+        <v>0</v>
+      </c>
+      <c r="M1653">
+        <v>3983000</v>
+      </c>
+      <c r="N1653">
+        <v>2845000</v>
+      </c>
+      <c r="O1653">
+        <v>1138000</v>
+      </c>
+      <c r="P1653">
+        <v>181</v>
+      </c>
+      <c r="Q1653">
+        <v>3.14</v>
+      </c>
+      <c r="R1653" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1653" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1654" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1654">
+        <v>72</v>
+      </c>
+      <c r="I1654" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1654">
+        <v>936000</v>
+      </c>
+      <c r="K1654">
+        <v>0</v>
+      </c>
+      <c r="L1654">
+        <v>0</v>
+      </c>
+      <c r="M1654">
+        <v>936000</v>
+      </c>
+      <c r="N1654">
+        <v>720000</v>
+      </c>
+      <c r="O1654">
+        <v>216000</v>
+      </c>
+      <c r="P1654">
+        <v>45</v>
+      </c>
+      <c r="Q1654">
+        <v>1.6</v>
+      </c>
+      <c r="R1654" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1654" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1655" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1655">
+        <v>44</v>
+      </c>
+      <c r="I1655" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1655">
+        <v>308000</v>
+      </c>
+      <c r="K1655">
+        <v>0</v>
+      </c>
+      <c r="L1655">
+        <v>0</v>
+      </c>
+      <c r="M1655">
+        <v>308000</v>
+      </c>
+      <c r="N1655">
+        <v>220000</v>
+      </c>
+      <c r="O1655">
+        <v>88000</v>
+      </c>
+      <c r="P1655">
+        <v>19</v>
+      </c>
+      <c r="Q1655">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="R1655" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1655" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1656" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1656">
+        <v>28</v>
+      </c>
+      <c r="I1656" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1656">
+        <v>280000</v>
+      </c>
+      <c r="K1656">
+        <v>0</v>
+      </c>
+      <c r="L1656">
+        <v>0</v>
+      </c>
+      <c r="M1656">
+        <v>280000</v>
+      </c>
+      <c r="N1656">
+        <v>224000</v>
+      </c>
+      <c r="O1656">
+        <v>56000</v>
+      </c>
+      <c r="P1656">
+        <v>16</v>
+      </c>
+      <c r="Q1656">
+        <v>1.75</v>
+      </c>
+      <c r="R1656" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1656" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1657" t="s">
+        <v>176</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1657">
+        <v>255</v>
+      </c>
+      <c r="I1657" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1657">
+        <v>765000</v>
+      </c>
+      <c r="K1657">
+        <v>0</v>
+      </c>
+      <c r="L1657">
+        <v>0</v>
+      </c>
+      <c r="M1657">
+        <v>765000</v>
+      </c>
+      <c r="N1657">
+        <v>510000</v>
+      </c>
+      <c r="O1657">
+        <v>255000</v>
+      </c>
+      <c r="P1657">
+        <v>56</v>
+      </c>
+      <c r="Q1657">
+        <v>4.55</v>
+      </c>
+      <c r="R1657" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1657" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1658" t="s">
+        <v>453</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1658">
+        <v>79</v>
+      </c>
+      <c r="I1658" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1658">
+        <v>237000</v>
+      </c>
+      <c r="K1658">
+        <v>0</v>
+      </c>
+      <c r="L1658">
+        <v>0</v>
+      </c>
+      <c r="M1658">
+        <v>237000</v>
+      </c>
+      <c r="N1658">
+        <v>158000</v>
+      </c>
+      <c r="O1658">
+        <v>79000</v>
+      </c>
+      <c r="P1658">
+        <v>7</v>
+      </c>
+      <c r="Q1658">
+        <v>11.29</v>
+      </c>
+      <c r="R1658" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1658" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1659" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1659">
+        <v>404</v>
+      </c>
+      <c r="I1659" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1659">
+        <v>2424000</v>
+      </c>
+      <c r="K1659">
+        <v>0</v>
+      </c>
+      <c r="L1659">
+        <v>0</v>
+      </c>
+      <c r="M1659">
+        <v>2424000</v>
+      </c>
+      <c r="N1659">
+        <v>1616000</v>
+      </c>
+      <c r="O1659">
+        <v>808000</v>
+      </c>
+      <c r="P1659">
+        <v>108</v>
+      </c>
+      <c r="Q1659">
+        <v>3.74</v>
+      </c>
+      <c r="R1659" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1659" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1660" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1660">
+        <v>85</v>
+      </c>
+      <c r="I1660" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1660">
+        <v>425000</v>
+      </c>
+      <c r="K1660">
+        <v>0</v>
+      </c>
+      <c r="L1660">
+        <v>0</v>
+      </c>
+      <c r="M1660">
+        <v>425000</v>
+      </c>
+      <c r="N1660">
+        <v>255000</v>
+      </c>
+      <c r="O1660">
+        <v>170000</v>
+      </c>
+      <c r="P1660">
+        <v>36</v>
+      </c>
+      <c r="Q1660">
+        <v>2.36</v>
+      </c>
+      <c r="R1660" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1660" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1661" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1661">
+        <v>78</v>
+      </c>
+      <c r="I1661" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1661">
+        <v>1014000</v>
+      </c>
+      <c r="K1661">
+        <v>0</v>
+      </c>
+      <c r="L1661">
+        <v>0</v>
+      </c>
+      <c r="M1661">
+        <v>1014000</v>
+      </c>
+      <c r="N1661">
+        <v>858000</v>
+      </c>
+      <c r="O1661">
+        <v>156000</v>
+      </c>
+      <c r="P1661">
+        <v>30</v>
+      </c>
+      <c r="Q1661">
+        <v>2.6</v>
+      </c>
+      <c r="R1661" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1661" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1662" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1662">
+        <v>116</v>
+      </c>
+      <c r="I1662" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1662">
+        <v>1508000</v>
+      </c>
+      <c r="K1662">
+        <v>0</v>
+      </c>
+      <c r="L1662">
+        <v>0</v>
+      </c>
+      <c r="M1662">
+        <v>1508000</v>
+      </c>
+      <c r="N1662">
+        <v>1160000</v>
+      </c>
+      <c r="O1662">
+        <v>348000</v>
+      </c>
+      <c r="P1662">
+        <v>54</v>
+      </c>
+      <c r="Q1662">
+        <v>2.15</v>
+      </c>
+      <c r="R1662" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1662" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1663" t="s">
+        <v>454</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1663">
+        <v>1</v>
+      </c>
+      <c r="I1663" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1663">
+        <v>15000</v>
+      </c>
+      <c r="K1663">
+        <v>0</v>
+      </c>
+      <c r="L1663">
+        <v>0</v>
+      </c>
+      <c r="M1663">
+        <v>15000</v>
+      </c>
+      <c r="N1663">
+        <v>12000</v>
+      </c>
+      <c r="O1663">
+        <v>3000</v>
+      </c>
+      <c r="P1663">
+        <v>1</v>
+      </c>
+      <c r="Q1663">
+        <v>1</v>
+      </c>
+      <c r="R1663" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1663" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1664" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1664">
+        <v>134</v>
+      </c>
+      <c r="I1664" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1664">
+        <v>2010000</v>
+      </c>
+      <c r="K1664">
+        <v>0</v>
+      </c>
+      <c r="L1664">
+        <v>0</v>
+      </c>
+      <c r="M1664">
+        <v>2010000</v>
+      </c>
+      <c r="N1664">
+        <v>1608000</v>
+      </c>
+      <c r="O1664">
+        <v>402000</v>
+      </c>
+      <c r="P1664">
+        <v>75</v>
+      </c>
+      <c r="Q1664">
+        <v>1.79</v>
+      </c>
+      <c r="R1664" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1664" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1665" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1665">
+        <v>225</v>
+      </c>
+      <c r="I1665" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1665">
+        <v>1350000</v>
+      </c>
+      <c r="K1665">
+        <v>0</v>
+      </c>
+      <c r="L1665">
+        <v>0</v>
+      </c>
+      <c r="M1665">
+        <v>1350000</v>
+      </c>
+      <c r="N1665">
+        <v>900000</v>
+      </c>
+      <c r="O1665">
+        <v>450000</v>
+      </c>
+      <c r="P1665">
+        <v>70</v>
+      </c>
+      <c r="Q1665">
+        <v>3.21</v>
+      </c>
+      <c r="R1665" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1665" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1666" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1666">
+        <v>68</v>
+      </c>
+      <c r="I1666" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1666">
+        <v>1224000</v>
+      </c>
+      <c r="K1666">
+        <v>0</v>
+      </c>
+      <c r="L1666">
+        <v>0</v>
+      </c>
+      <c r="M1666">
+        <v>1224000</v>
+      </c>
+      <c r="N1666">
+        <v>1020000</v>
+      </c>
+      <c r="O1666">
+        <v>204000</v>
+      </c>
+      <c r="P1666">
+        <v>28</v>
+      </c>
+      <c r="Q1666">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="R1666" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1666" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1667" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1667">
+        <v>151</v>
+      </c>
+      <c r="I1667" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1667">
+        <v>1359000</v>
+      </c>
+      <c r="K1667">
+        <v>0</v>
+      </c>
+      <c r="L1667">
+        <v>0</v>
+      </c>
+      <c r="M1667">
+        <v>1359000</v>
+      </c>
+      <c r="N1667">
+        <v>817000</v>
+      </c>
+      <c r="O1667">
+        <v>542000</v>
+      </c>
+      <c r="P1667">
+        <v>72</v>
+      </c>
+      <c r="Q1667">
+        <v>2.1</v>
+      </c>
+      <c r="R1667" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1667" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1668" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1668">
+        <v>10</v>
+      </c>
+      <c r="I1668" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1668">
+        <v>30000</v>
+      </c>
+      <c r="K1668">
+        <v>0</v>
+      </c>
+      <c r="L1668">
+        <v>0</v>
+      </c>
+      <c r="M1668">
+        <v>30000</v>
+      </c>
+      <c r="N1668">
+        <v>0</v>
+      </c>
+      <c r="O1668">
+        <v>30000</v>
+      </c>
+      <c r="P1668">
+        <v>9</v>
+      </c>
+      <c r="Q1668">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1668" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1668" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1669" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1669">
+        <v>24</v>
+      </c>
+      <c r="I1669" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1669">
+        <v>72000</v>
+      </c>
+      <c r="K1669">
+        <v>0</v>
+      </c>
+      <c r="L1669">
+        <v>0</v>
+      </c>
+      <c r="M1669">
+        <v>72000</v>
+      </c>
+      <c r="N1669">
+        <v>0</v>
+      </c>
+      <c r="O1669">
+        <v>72000</v>
+      </c>
+      <c r="P1669">
+        <v>20</v>
+      </c>
+      <c r="Q1669">
+        <v>1.2</v>
+      </c>
+      <c r="R1669" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1669" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1670" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1670">
+        <v>4</v>
+      </c>
+      <c r="I1670" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1670">
+        <v>12000</v>
+      </c>
+      <c r="K1670">
+        <v>0</v>
+      </c>
+      <c r="L1670">
+        <v>0</v>
+      </c>
+      <c r="M1670">
+        <v>12000</v>
+      </c>
+      <c r="N1670">
+        <v>2670</v>
+      </c>
+      <c r="O1670">
+        <v>9330</v>
+      </c>
+      <c r="P1670">
+        <v>4</v>
+      </c>
+      <c r="Q1670">
+        <v>1</v>
+      </c>
+      <c r="R1670" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1670" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1671" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1671">
+        <v>18</v>
+      </c>
+      <c r="I1671" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1671">
+        <v>126000</v>
+      </c>
+      <c r="K1671">
+        <v>0</v>
+      </c>
+      <c r="L1671">
+        <v>0</v>
+      </c>
+      <c r="M1671">
+        <v>129000</v>
+      </c>
+      <c r="N1671">
+        <v>27560.400000000001</v>
+      </c>
+      <c r="O1671">
+        <v>101439.6</v>
+      </c>
+      <c r="P1671">
+        <v>18</v>
+      </c>
+      <c r="Q1671">
+        <v>1</v>
+      </c>
+      <c r="R1671" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1671" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1672" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>238</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1672">
+        <v>9</v>
+      </c>
+      <c r="I1672" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1672">
+        <v>45000</v>
+      </c>
+      <c r="K1672">
+        <v>0</v>
+      </c>
+      <c r="L1672">
+        <v>0</v>
+      </c>
+      <c r="M1672">
+        <v>45000</v>
+      </c>
+      <c r="N1672">
+        <v>13592.33</v>
+      </c>
+      <c r="O1672">
+        <v>31407.67</v>
+      </c>
+      <c r="P1672">
+        <v>6</v>
+      </c>
+      <c r="Q1672">
+        <v>1.5</v>
+      </c>
+      <c r="R1672" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1672" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1673" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1673">
+        <v>118</v>
+      </c>
+      <c r="I1673" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1673">
+        <v>590000</v>
+      </c>
+      <c r="K1673">
+        <v>0</v>
+      </c>
+      <c r="L1673">
+        <v>0</v>
+      </c>
+      <c r="M1673">
+        <v>590000</v>
+      </c>
+      <c r="N1673">
+        <v>177211.04</v>
+      </c>
+      <c r="O1673">
+        <v>412788.96</v>
+      </c>
+      <c r="P1673">
+        <v>72</v>
+      </c>
+      <c r="Q1673">
+        <v>1.64</v>
+      </c>
+      <c r="R1673" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1673" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1674" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1674">
+        <v>74</v>
+      </c>
+      <c r="I1674" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1674">
+        <v>1628000</v>
+      </c>
+      <c r="K1674">
+        <v>0</v>
+      </c>
+      <c r="L1674">
+        <v>0</v>
+      </c>
+      <c r="M1674">
+        <v>1628000</v>
+      </c>
+      <c r="N1674">
+        <v>1006400</v>
+      </c>
+      <c r="O1674">
+        <v>621600</v>
+      </c>
+      <c r="P1674">
+        <v>49</v>
+      </c>
+      <c r="Q1674">
+        <v>1.51</v>
+      </c>
+      <c r="R1674" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1674" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1675" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1675">
+        <v>14</v>
+      </c>
+      <c r="I1675" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1675">
+        <v>238000</v>
+      </c>
+      <c r="K1675">
+        <v>0</v>
+      </c>
+      <c r="L1675">
+        <v>0</v>
+      </c>
+      <c r="M1675">
+        <v>238000</v>
+      </c>
+      <c r="N1675">
+        <v>147000</v>
+      </c>
+      <c r="O1675">
+        <v>91000</v>
+      </c>
+      <c r="P1675">
+        <v>14</v>
+      </c>
+      <c r="Q1675">
+        <v>1</v>
+      </c>
+      <c r="R1675" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1675" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1676" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1676">
+        <v>3</v>
+      </c>
+      <c r="I1676" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1676">
+        <v>102000</v>
+      </c>
+      <c r="K1676">
+        <v>0</v>
+      </c>
+      <c r="L1676">
+        <v>0</v>
+      </c>
+      <c r="M1676">
+        <v>102000</v>
+      </c>
+      <c r="N1676">
+        <v>23200</v>
+      </c>
+      <c r="O1676">
+        <v>78800</v>
+      </c>
+      <c r="P1676">
+        <v>3</v>
+      </c>
+      <c r="Q1676">
+        <v>1</v>
+      </c>
+      <c r="R1676" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1676" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1677" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1677">
+        <v>12</v>
+      </c>
+      <c r="I1677" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1677">
+        <v>468000</v>
+      </c>
+      <c r="K1677">
+        <v>0</v>
+      </c>
+      <c r="L1677">
+        <v>0</v>
+      </c>
+      <c r="M1677">
+        <v>468000</v>
+      </c>
+      <c r="N1677">
+        <v>189164.84</v>
+      </c>
+      <c r="O1677">
+        <v>278835.15999999997</v>
+      </c>
+      <c r="P1677">
+        <v>7</v>
+      </c>
+      <c r="Q1677">
+        <v>1.71</v>
+      </c>
+      <c r="R1677" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1677" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1678" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1678">
+        <v>4</v>
+      </c>
+      <c r="I1678" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1678">
+        <v>156000</v>
+      </c>
+      <c r="K1678">
+        <v>0</v>
+      </c>
+      <c r="L1678">
+        <v>0</v>
+      </c>
+      <c r="M1678">
+        <v>156000</v>
+      </c>
+      <c r="N1678">
+        <v>93988.28</v>
+      </c>
+      <c r="O1678">
+        <v>62011.72</v>
+      </c>
+      <c r="P1678">
+        <v>4</v>
+      </c>
+      <c r="Q1678">
+        <v>1</v>
+      </c>
+      <c r="R1678" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1678" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1679" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1679">
+        <v>4</v>
+      </c>
+      <c r="I1679" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1679">
+        <v>156000</v>
+      </c>
+      <c r="K1679">
+        <v>0</v>
+      </c>
+      <c r="L1679">
+        <v>0</v>
+      </c>
+      <c r="M1679">
+        <v>156000</v>
+      </c>
+      <c r="N1679">
+        <v>70788.28</v>
+      </c>
+      <c r="O1679">
+        <v>85211.72</v>
+      </c>
+      <c r="P1679">
+        <v>4</v>
+      </c>
+      <c r="Q1679">
+        <v>1</v>
+      </c>
+      <c r="R1679" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1679" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1680" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1680">
+        <v>17</v>
+      </c>
+      <c r="I1680" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1680">
+        <v>663000</v>
+      </c>
+      <c r="K1680">
+        <v>0</v>
+      </c>
+      <c r="L1680">
+        <v>0</v>
+      </c>
+      <c r="M1680">
+        <v>663000</v>
+      </c>
+      <c r="N1680">
+        <v>225197.69</v>
+      </c>
+      <c r="O1680">
+        <v>437802.31</v>
+      </c>
+      <c r="P1680">
+        <v>14</v>
+      </c>
+      <c r="Q1680">
+        <v>1.21</v>
+      </c>
+      <c r="R1680" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1680" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1681" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1681">
+        <v>1</v>
+      </c>
+      <c r="I1681" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1681">
+        <v>35000</v>
+      </c>
+      <c r="K1681">
+        <v>0</v>
+      </c>
+      <c r="L1681">
+        <v>0</v>
+      </c>
+      <c r="M1681">
+        <v>35000</v>
+      </c>
+      <c r="N1681">
+        <v>80569.789999999994</v>
+      </c>
+      <c r="O1681">
+        <v>-45569.79</v>
+      </c>
+      <c r="P1681">
+        <v>1</v>
+      </c>
+      <c r="Q1681">
+        <v>1</v>
+      </c>
+      <c r="R1681" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1681" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1682" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1682">
+        <v>85</v>
+      </c>
+      <c r="I1682" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1682">
+        <v>2210000</v>
+      </c>
+      <c r="K1682">
+        <v>0</v>
+      </c>
+      <c r="L1682">
+        <v>0</v>
+      </c>
+      <c r="M1682">
+        <v>2213000</v>
+      </c>
+      <c r="N1682">
+        <v>639924.77</v>
+      </c>
+      <c r="O1682">
+        <v>1573075.23</v>
+      </c>
+      <c r="P1682">
+        <v>70</v>
+      </c>
+      <c r="Q1682">
+        <v>1.21</v>
+      </c>
+      <c r="R1682" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1682" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1683" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1683">
+        <v>35</v>
+      </c>
+      <c r="I1683" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1683">
+        <v>910000</v>
+      </c>
+      <c r="K1683">
+        <v>0</v>
+      </c>
+      <c r="L1683">
+        <v>0</v>
+      </c>
+      <c r="M1683">
+        <v>910000</v>
+      </c>
+      <c r="N1683">
+        <v>317507.78999999998</v>
+      </c>
+      <c r="O1683">
+        <v>592492.21</v>
+      </c>
+      <c r="P1683">
+        <v>30</v>
+      </c>
+      <c r="Q1683">
+        <v>1.17</v>
+      </c>
+      <c r="R1683" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1683" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1684" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1684">
+        <v>14</v>
+      </c>
+      <c r="I1684" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1684">
+        <v>322000</v>
+      </c>
+      <c r="K1684">
+        <v>0</v>
+      </c>
+      <c r="L1684">
+        <v>0</v>
+      </c>
+      <c r="M1684">
+        <v>322000</v>
+      </c>
+      <c r="N1684">
+        <v>186678.38</v>
+      </c>
+      <c r="O1684">
+        <v>135321.62</v>
+      </c>
+      <c r="P1684">
+        <v>12</v>
+      </c>
+      <c r="Q1684">
+        <v>1.17</v>
+      </c>
+      <c r="R1684" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1684" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1685" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1685" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1685">
+        <v>5</v>
+      </c>
+      <c r="I1685" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1685">
+        <v>150000</v>
+      </c>
+      <c r="K1685">
+        <v>0</v>
+      </c>
+      <c r="L1685">
+        <v>0</v>
+      </c>
+      <c r="M1685">
+        <v>150000</v>
+      </c>
+      <c r="N1685">
+        <v>113500</v>
+      </c>
+      <c r="O1685">
+        <v>36500</v>
+      </c>
+      <c r="P1685">
+        <v>5</v>
+      </c>
+      <c r="Q1685">
+        <v>1</v>
+      </c>
+      <c r="R1685" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1685" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1686" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1686">
+        <v>55</v>
+      </c>
+      <c r="I1686" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1686">
+        <v>1265000</v>
+      </c>
+      <c r="K1686">
+        <v>0</v>
+      </c>
+      <c r="L1686">
+        <v>0</v>
+      </c>
+      <c r="M1686">
+        <v>1268000</v>
+      </c>
+      <c r="N1686">
+        <v>348359.67999999999</v>
+      </c>
+      <c r="O1686">
+        <v>919640.32</v>
+      </c>
+      <c r="P1686">
+        <v>39</v>
+      </c>
+      <c r="Q1686">
+        <v>1.41</v>
+      </c>
+      <c r="R1686" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1686" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1687" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1687">
+        <v>11</v>
+      </c>
+      <c r="I1687" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1687">
+        <v>253000</v>
+      </c>
+      <c r="K1687">
+        <v>0</v>
+      </c>
+      <c r="L1687">
+        <v>0</v>
+      </c>
+      <c r="M1687">
+        <v>253000</v>
+      </c>
+      <c r="N1687">
+        <v>79767.77</v>
+      </c>
+      <c r="O1687">
+        <v>173232.23</v>
+      </c>
+      <c r="P1687">
+        <v>9</v>
+      </c>
+      <c r="Q1687">
+        <v>1.22</v>
+      </c>
+      <c r="R1687" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1687" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1688" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1688">
+        <v>35</v>
+      </c>
+      <c r="I1688" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1688">
+        <v>805000</v>
+      </c>
+      <c r="K1688">
+        <v>0</v>
+      </c>
+      <c r="L1688">
+        <v>0</v>
+      </c>
+      <c r="M1688">
+        <v>805000</v>
+      </c>
+      <c r="N1688">
+        <v>222897.45</v>
+      </c>
+      <c r="O1688">
+        <v>582102.55000000005</v>
+      </c>
+      <c r="P1688">
+        <v>27</v>
+      </c>
+      <c r="Q1688">
+        <v>1.3</v>
+      </c>
+      <c r="R1688" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1688" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1689" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1689">
+        <v>12</v>
+      </c>
+      <c r="I1689" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1689">
+        <v>288000</v>
+      </c>
+      <c r="K1689">
+        <v>0</v>
+      </c>
+      <c r="L1689">
+        <v>0</v>
+      </c>
+      <c r="M1689">
+        <v>288000</v>
+      </c>
+      <c r="N1689">
+        <v>105074.84</v>
+      </c>
+      <c r="O1689">
+        <v>182925.16</v>
+      </c>
+      <c r="P1689">
+        <v>11</v>
+      </c>
+      <c r="Q1689">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R1689" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1689" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1690" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1690">
+        <v>86</v>
+      </c>
+      <c r="I1690" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1690">
+        <v>2580000</v>
+      </c>
+      <c r="K1690">
+        <v>0</v>
+      </c>
+      <c r="L1690">
+        <v>0</v>
+      </c>
+      <c r="M1690">
+        <v>2590000</v>
+      </c>
+      <c r="N1690">
+        <v>1239939.3999999999</v>
+      </c>
+      <c r="O1690">
+        <v>1350060.6</v>
+      </c>
+      <c r="P1690">
+        <v>69</v>
+      </c>
+      <c r="Q1690">
+        <v>1.25</v>
+      </c>
+      <c r="R1690" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1690" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1691" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1691">
+        <v>70</v>
+      </c>
+      <c r="I1691" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1691">
+        <v>2100000</v>
+      </c>
+      <c r="K1691">
+        <v>0</v>
+      </c>
+      <c r="L1691">
+        <v>0</v>
+      </c>
+      <c r="M1691">
+        <v>2100000</v>
+      </c>
+      <c r="N1691">
+        <v>1009253</v>
+      </c>
+      <c r="O1691">
+        <v>1090747</v>
+      </c>
+      <c r="P1691">
+        <v>55</v>
+      </c>
+      <c r="Q1691">
+        <v>1.27</v>
+      </c>
+      <c r="R1691" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1691" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1692" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1692">
+        <v>204</v>
+      </c>
+      <c r="I1692" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1692">
+        <v>6120000</v>
+      </c>
+      <c r="K1692">
+        <v>0</v>
+      </c>
+      <c r="L1692">
+        <v>0</v>
+      </c>
+      <c r="M1692">
+        <v>6120000</v>
+      </c>
+      <c r="N1692">
+        <v>2927651.6</v>
+      </c>
+      <c r="O1692">
+        <v>3192348.4</v>
+      </c>
+      <c r="P1692">
+        <v>158</v>
+      </c>
+      <c r="Q1692">
+        <v>1.29</v>
+      </c>
+      <c r="R1692" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1692" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1693" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1693">
+        <v>464</v>
+      </c>
+      <c r="I1693" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1693">
+        <v>13920000</v>
+      </c>
+      <c r="K1693">
+        <v>0</v>
+      </c>
+      <c r="L1693">
+        <v>0</v>
+      </c>
+      <c r="M1693">
+        <v>13933000</v>
+      </c>
+      <c r="N1693">
+        <v>6987067.2599999998</v>
+      </c>
+      <c r="O1693">
+        <v>6945932.7400000002</v>
+      </c>
+      <c r="P1693">
+        <v>337</v>
+      </c>
+      <c r="Q1693">
+        <v>1.38</v>
+      </c>
+      <c r="R1693" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1693" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1694" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1694">
+        <v>52</v>
+      </c>
+      <c r="I1694" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1694">
+        <v>1352000</v>
+      </c>
+      <c r="K1694">
+        <v>0</v>
+      </c>
+      <c r="L1694">
+        <v>0</v>
+      </c>
+      <c r="M1694">
+        <v>1358000</v>
+      </c>
+      <c r="N1694">
+        <v>681568.47</v>
+      </c>
+      <c r="O1694">
+        <v>676431.53</v>
+      </c>
+      <c r="P1694">
+        <v>50</v>
+      </c>
+      <c r="Q1694">
+        <v>1.04</v>
+      </c>
+      <c r="R1694" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1694" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1695" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>256</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1695">
+        <v>27</v>
+      </c>
+      <c r="I1695" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1695">
+        <v>702000</v>
+      </c>
+      <c r="K1695">
+        <v>0</v>
+      </c>
+      <c r="L1695">
+        <v>0</v>
+      </c>
+      <c r="M1695">
+        <v>702000</v>
+      </c>
+      <c r="N1695">
+        <v>336313.27</v>
+      </c>
+      <c r="O1695">
+        <v>365686.73</v>
+      </c>
+      <c r="P1695">
+        <v>26</v>
+      </c>
+      <c r="Q1695">
+        <v>1.04</v>
+      </c>
+      <c r="R1695" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1695" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1696" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1696" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1696">
+        <v>47</v>
+      </c>
+      <c r="I1696" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1696">
+        <v>1222000</v>
+      </c>
+      <c r="K1696">
+        <v>0</v>
+      </c>
+      <c r="L1696">
+        <v>0</v>
+      </c>
+      <c r="M1696">
+        <v>1225000</v>
+      </c>
+      <c r="N1696">
+        <v>616083.12</v>
+      </c>
+      <c r="O1696">
+        <v>608916.88</v>
+      </c>
+      <c r="P1696">
+        <v>41</v>
+      </c>
+      <c r="Q1696">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="R1696" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1696" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1697" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1697">
+        <v>29</v>
+      </c>
+      <c r="I1697" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1697">
+        <v>754000</v>
+      </c>
+      <c r="K1697">
+        <v>0</v>
+      </c>
+      <c r="L1697">
+        <v>0</v>
+      </c>
+      <c r="M1697">
+        <v>754000</v>
+      </c>
+      <c r="N1697">
+        <v>313115.03000000003</v>
+      </c>
+      <c r="O1697">
+        <v>440884.97</v>
+      </c>
+      <c r="P1697">
+        <v>23</v>
+      </c>
+      <c r="Q1697">
+        <v>1.26</v>
+      </c>
+      <c r="R1697" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1697" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1698" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1698">
+        <v>289</v>
+      </c>
+      <c r="I1698" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1698">
+        <v>5202000</v>
+      </c>
+      <c r="K1698">
+        <v>0</v>
+      </c>
+      <c r="L1698">
+        <v>0</v>
+      </c>
+      <c r="M1698">
+        <v>5437000</v>
+      </c>
+      <c r="N1698">
+        <v>1678818.14</v>
+      </c>
+      <c r="O1698">
+        <v>3758181.86</v>
+      </c>
+      <c r="P1698">
+        <v>230</v>
+      </c>
+      <c r="Q1698">
+        <v>1.26</v>
+      </c>
+      <c r="R1698" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1698" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1699" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1699">
+        <v>45</v>
+      </c>
+      <c r="I1699" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1699">
+        <v>900000</v>
+      </c>
+      <c r="K1699">
+        <v>0</v>
+      </c>
+      <c r="L1699">
+        <v>0</v>
+      </c>
+      <c r="M1699">
+        <v>933000</v>
+      </c>
+      <c r="N1699">
+        <v>295913.53999999998</v>
+      </c>
+      <c r="O1699">
+        <v>637086.46</v>
+      </c>
+      <c r="P1699">
+        <v>40</v>
+      </c>
+      <c r="Q1699">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1699" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1699" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1700" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1700">
+        <v>1</v>
+      </c>
+      <c r="I1700" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1700">
+        <v>35000</v>
+      </c>
+      <c r="K1700">
+        <v>0</v>
+      </c>
+      <c r="L1700">
+        <v>0</v>
+      </c>
+      <c r="M1700">
+        <v>35000</v>
+      </c>
+      <c r="N1700">
+        <v>16300</v>
+      </c>
+      <c r="O1700">
+        <v>18700</v>
+      </c>
+      <c r="P1700">
+        <v>1</v>
+      </c>
+      <c r="Q1700">
+        <v>1</v>
+      </c>
+      <c r="R1700" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1700" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1701" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1701">
+        <v>1</v>
+      </c>
+      <c r="I1701" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1701">
+        <v>35000</v>
+      </c>
+      <c r="K1701">
+        <v>0</v>
+      </c>
+      <c r="L1701">
+        <v>0</v>
+      </c>
+      <c r="M1701">
+        <v>35000</v>
+      </c>
+      <c r="N1701">
+        <v>14000</v>
+      </c>
+      <c r="O1701">
+        <v>21000</v>
+      </c>
+      <c r="P1701">
+        <v>1</v>
+      </c>
+      <c r="Q1701">
+        <v>1</v>
+      </c>
+      <c r="R1701" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1701" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1702" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1702">
+        <v>20</v>
+      </c>
+      <c r="I1702" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1702">
+        <v>560000</v>
+      </c>
+      <c r="K1702">
+        <v>0</v>
+      </c>
+      <c r="L1702">
+        <v>0</v>
+      </c>
+      <c r="M1702">
+        <v>560000</v>
+      </c>
+      <c r="N1702">
+        <v>276060.34000000003</v>
+      </c>
+      <c r="O1702">
+        <v>283939.65999999997</v>
+      </c>
+      <c r="P1702">
+        <v>16</v>
+      </c>
+      <c r="Q1702">
+        <v>1.25</v>
+      </c>
+      <c r="R1702" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1702" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1703" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1703">
+        <v>18</v>
+      </c>
+      <c r="I1703" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1703">
+        <v>540000</v>
+      </c>
+      <c r="K1703">
+        <v>0</v>
+      </c>
+      <c r="L1703">
+        <v>0</v>
+      </c>
+      <c r="M1703">
+        <v>542000</v>
+      </c>
+      <c r="N1703">
+        <v>234198.18</v>
+      </c>
+      <c r="O1703">
+        <v>307801.82</v>
+      </c>
+      <c r="P1703">
+        <v>15</v>
+      </c>
+      <c r="Q1703">
+        <v>1.2</v>
+      </c>
+      <c r="R1703" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1703" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1704" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1704">
+        <v>6</v>
+      </c>
+      <c r="I1704" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1704">
+        <v>156000</v>
+      </c>
+      <c r="K1704">
+        <v>0</v>
+      </c>
+      <c r="L1704">
+        <v>0</v>
+      </c>
+      <c r="M1704">
+        <v>158000</v>
+      </c>
+      <c r="N1704">
+        <v>84099.55</v>
+      </c>
+      <c r="O1704">
+        <v>73900.45</v>
+      </c>
+      <c r="P1704">
+        <v>6</v>
+      </c>
+      <c r="Q1704">
+        <v>1</v>
+      </c>
+      <c r="R1704" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1704" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1705" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1705">
+        <v>75</v>
+      </c>
+      <c r="I1705" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1705">
+        <v>1575000</v>
+      </c>
+      <c r="K1705">
+        <v>0</v>
+      </c>
+      <c r="L1705">
+        <v>0</v>
+      </c>
+      <c r="M1705">
+        <v>1581000</v>
+      </c>
+      <c r="N1705">
+        <v>843005.62</v>
+      </c>
+      <c r="O1705">
+        <v>737994.38</v>
+      </c>
+      <c r="P1705">
+        <v>66</v>
+      </c>
+      <c r="Q1705">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1705" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1705" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1706" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1706">
+        <v>81</v>
+      </c>
+      <c r="I1706" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1706">
+        <v>2187000</v>
+      </c>
+      <c r="K1706">
+        <v>0</v>
+      </c>
+      <c r="L1706">
+        <v>0</v>
+      </c>
+      <c r="M1706">
+        <v>2187000</v>
+      </c>
+      <c r="N1706">
+        <v>721702.53</v>
+      </c>
+      <c r="O1706">
+        <v>1465297.46</v>
+      </c>
+      <c r="P1706">
+        <v>67</v>
+      </c>
+      <c r="Q1706">
+        <v>1.21</v>
+      </c>
+      <c r="R1706" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1706" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1707" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1707">
+        <v>41</v>
+      </c>
+      <c r="I1707" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1707">
+        <v>1271000</v>
+      </c>
+      <c r="K1707">
+        <v>0</v>
+      </c>
+      <c r="L1707">
+        <v>0</v>
+      </c>
+      <c r="M1707">
+        <v>1271000</v>
+      </c>
+      <c r="N1707">
+        <v>558880.84</v>
+      </c>
+      <c r="O1707">
+        <v>712119.16</v>
+      </c>
+      <c r="P1707">
+        <v>37</v>
+      </c>
+      <c r="Q1707">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1707" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1707" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1708" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1708">
+        <v>57</v>
+      </c>
+      <c r="I1708" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1708">
+        <v>1710000</v>
+      </c>
+      <c r="K1708">
+        <v>0</v>
+      </c>
+      <c r="L1708">
+        <v>0</v>
+      </c>
+      <c r="M1708">
+        <v>1710000</v>
+      </c>
+      <c r="N1708">
+        <v>738933.18</v>
+      </c>
+      <c r="O1708">
+        <v>971066.82</v>
+      </c>
+      <c r="P1708">
+        <v>48</v>
+      </c>
+      <c r="Q1708">
+        <v>1.19</v>
+      </c>
+      <c r="R1708" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1708" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1709" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1709">
+        <v>17</v>
+      </c>
+      <c r="I1709" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1709">
+        <v>510000</v>
+      </c>
+      <c r="K1709">
+        <v>0</v>
+      </c>
+      <c r="L1709">
+        <v>0</v>
+      </c>
+      <c r="M1709">
+        <v>510000</v>
+      </c>
+      <c r="N1709">
+        <v>220383.58</v>
+      </c>
+      <c r="O1709">
+        <v>289616.42</v>
+      </c>
+      <c r="P1709">
+        <v>13</v>
+      </c>
+      <c r="Q1709">
+        <v>1.31</v>
+      </c>
+      <c r="R1709" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1709" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1710" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>228</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1710">
+        <v>37</v>
+      </c>
+      <c r="I1710" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1710">
+        <v>1110000</v>
+      </c>
+      <c r="K1710">
+        <v>0</v>
+      </c>
+      <c r="L1710">
+        <v>0</v>
+      </c>
+      <c r="M1710">
+        <v>1110000</v>
+      </c>
+      <c r="N1710">
+        <v>479658.38</v>
+      </c>
+      <c r="O1710">
+        <v>630341.62</v>
+      </c>
+      <c r="P1710">
+        <v>32</v>
+      </c>
+      <c r="Q1710">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R1710" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1710" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1711" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1711">
+        <v>26</v>
+      </c>
+      <c r="I1711" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1711">
+        <v>936000</v>
+      </c>
+      <c r="K1711">
+        <v>0</v>
+      </c>
+      <c r="L1711">
+        <v>0</v>
+      </c>
+      <c r="M1711">
+        <v>936000</v>
+      </c>
+      <c r="N1711">
+        <v>597923.81999999995</v>
+      </c>
+      <c r="O1711">
+        <v>338076.18</v>
+      </c>
+      <c r="P1711">
+        <v>24</v>
+      </c>
+      <c r="Q1711">
+        <v>1.08</v>
+      </c>
+      <c r="R1711" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1711" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1712" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>230</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1712">
+        <v>4</v>
+      </c>
+      <c r="I1712" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1712">
+        <v>140000</v>
+      </c>
+      <c r="K1712">
+        <v>0</v>
+      </c>
+      <c r="L1712">
+        <v>0</v>
+      </c>
+      <c r="M1712">
+        <v>140000</v>
+      </c>
+      <c r="N1712">
+        <v>91806.84</v>
+      </c>
+      <c r="O1712">
+        <v>48193.16</v>
+      </c>
+      <c r="P1712">
+        <v>3</v>
+      </c>
+      <c r="Q1712">
+        <v>1.33</v>
+      </c>
+      <c r="R1712" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1712" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1713" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1713">
+        <v>41</v>
+      </c>
+      <c r="I1713" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1713">
+        <v>615000</v>
+      </c>
+      <c r="K1713">
+        <v>0</v>
+      </c>
+      <c r="L1713">
+        <v>0</v>
+      </c>
+      <c r="M1713">
+        <v>615000</v>
+      </c>
+      <c r="N1713">
+        <v>288845.38</v>
+      </c>
+      <c r="O1713">
+        <v>326154.62</v>
+      </c>
+      <c r="P1713">
+        <v>33</v>
+      </c>
+      <c r="Q1713">
+        <v>1.24</v>
+      </c>
+      <c r="R1713" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1713" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1714" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1714">
+        <v>10</v>
+      </c>
+      <c r="I1714" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1714">
+        <v>200000</v>
+      </c>
+      <c r="K1714">
+        <v>0</v>
+      </c>
+      <c r="L1714">
+        <v>0</v>
+      </c>
+      <c r="M1714">
+        <v>200000</v>
+      </c>
+      <c r="N1714">
+        <v>107925</v>
+      </c>
+      <c r="O1714">
+        <v>92075</v>
+      </c>
+      <c r="P1714">
+        <v>7</v>
+      </c>
+      <c r="Q1714">
+        <v>1.43</v>
+      </c>
+      <c r="R1714" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1714" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1715" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1715">
+        <v>4</v>
+      </c>
+      <c r="I1715" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1715">
+        <v>96000</v>
+      </c>
+      <c r="K1715">
+        <v>0</v>
+      </c>
+      <c r="L1715">
+        <v>0</v>
+      </c>
+      <c r="M1715">
+        <v>96000</v>
+      </c>
+      <c r="N1715">
+        <v>18888.28</v>
+      </c>
+      <c r="O1715">
+        <v>77111.72</v>
+      </c>
+      <c r="P1715">
+        <v>2</v>
+      </c>
+      <c r="Q1715">
+        <v>2</v>
+      </c>
+      <c r="R1715" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1715" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1716" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1716">
+        <v>4</v>
+      </c>
+      <c r="I1716" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1716">
+        <v>96000</v>
+      </c>
+      <c r="K1716">
+        <v>0</v>
+      </c>
+      <c r="L1716">
+        <v>0</v>
+      </c>
+      <c r="M1716">
+        <v>96000</v>
+      </c>
+      <c r="N1716">
+        <v>33325.589999999997</v>
+      </c>
+      <c r="O1716">
+        <v>62674.41</v>
+      </c>
+      <c r="P1716">
+        <v>4</v>
+      </c>
+      <c r="Q1716">
+        <v>1</v>
+      </c>
+      <c r="R1716" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1716" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1717" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1717">
+        <v>4</v>
+      </c>
+      <c r="I1717" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1717">
+        <v>96000</v>
+      </c>
+      <c r="K1717">
+        <v>0</v>
+      </c>
+      <c r="L1717">
+        <v>0</v>
+      </c>
+      <c r="M1717">
+        <v>96000</v>
+      </c>
+      <c r="N1717">
+        <v>44388.28</v>
+      </c>
+      <c r="O1717">
+        <v>51611.72</v>
+      </c>
+      <c r="P1717">
+        <v>3</v>
+      </c>
+      <c r="Q1717">
+        <v>1.33</v>
+      </c>
+      <c r="R1717" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1717" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1718" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1718">
+        <v>89</v>
+      </c>
+      <c r="I1718" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1718">
+        <v>2047000</v>
+      </c>
+      <c r="K1718">
+        <v>0</v>
+      </c>
+      <c r="L1718">
+        <v>0</v>
+      </c>
+      <c r="M1718">
+        <v>2047000</v>
+      </c>
+      <c r="N1718">
+        <v>701957.25</v>
+      </c>
+      <c r="O1718">
+        <v>1345042.75</v>
+      </c>
+      <c r="P1718">
+        <v>62</v>
+      </c>
+      <c r="Q1718">
+        <v>1.44</v>
+      </c>
+      <c r="R1718" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1718" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1719" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1719">
+        <v>5</v>
+      </c>
+      <c r="I1719" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1719">
+        <v>140000</v>
+      </c>
+      <c r="K1719">
+        <v>0</v>
+      </c>
+      <c r="L1719">
+        <v>0</v>
+      </c>
+      <c r="M1719">
+        <v>140000</v>
+      </c>
+      <c r="N1719">
+        <v>52110.35</v>
+      </c>
+      <c r="O1719">
+        <v>87889.65</v>
+      </c>
+      <c r="P1719">
+        <v>5</v>
+      </c>
+      <c r="Q1719">
+        <v>1</v>
+      </c>
+      <c r="R1719" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1719" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1720" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1720">
+        <v>15</v>
+      </c>
+      <c r="I1720" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1720">
+        <v>420000</v>
+      </c>
+      <c r="K1720">
+        <v>0</v>
+      </c>
+      <c r="L1720">
+        <v>0</v>
+      </c>
+      <c r="M1720">
+        <v>420000</v>
+      </c>
+      <c r="N1720">
+        <v>156331.04999999999</v>
+      </c>
+      <c r="O1720">
+        <v>263668.95</v>
+      </c>
+      <c r="P1720">
+        <v>9</v>
+      </c>
+      <c r="Q1720">
+        <v>1.67</v>
+      </c>
+      <c r="R1720" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1720" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1721" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1721">
+        <v>17</v>
+      </c>
+      <c r="I1721" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1721">
+        <v>476000</v>
+      </c>
+      <c r="K1721">
+        <v>0</v>
+      </c>
+      <c r="L1721">
+        <v>0</v>
+      </c>
+      <c r="M1721">
+        <v>476000</v>
+      </c>
+      <c r="N1721">
+        <v>177175.19</v>
+      </c>
+      <c r="O1721">
+        <v>298824.81</v>
+      </c>
+      <c r="P1721">
+        <v>16</v>
+      </c>
+      <c r="Q1721">
+        <v>1.06</v>
+      </c>
+      <c r="R1721" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1721" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1722" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1722">
+        <v>37</v>
+      </c>
+      <c r="I1722" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1722">
+        <v>1036000</v>
+      </c>
+      <c r="K1722">
+        <v>0</v>
+      </c>
+      <c r="L1722">
+        <v>0</v>
+      </c>
+      <c r="M1722">
+        <v>1036000</v>
+      </c>
+      <c r="N1722">
+        <v>410314.09</v>
+      </c>
+      <c r="O1722">
+        <v>625685.91</v>
+      </c>
+      <c r="P1722">
+        <v>34</v>
+      </c>
+      <c r="Q1722">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R1722" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1722" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1723" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1723">
+        <v>5</v>
+      </c>
+      <c r="I1723" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1723">
+        <v>0</v>
+      </c>
+      <c r="K1723">
+        <v>0</v>
+      </c>
+      <c r="L1723">
+        <v>0</v>
+      </c>
+      <c r="M1723">
+        <v>65000</v>
+      </c>
+      <c r="N1723">
+        <v>12558.59</v>
+      </c>
+      <c r="O1723">
+        <v>52441.41</v>
+      </c>
+      <c r="P1723">
+        <v>5</v>
+      </c>
+      <c r="Q1723">
+        <v>1</v>
+      </c>
+      <c r="R1723" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1723" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1724" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1724">
+        <v>6</v>
+      </c>
+      <c r="I1724" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1724">
+        <v>90000</v>
+      </c>
+      <c r="K1724">
+        <v>0</v>
+      </c>
+      <c r="L1724">
+        <v>0</v>
+      </c>
+      <c r="M1724">
+        <v>90000</v>
+      </c>
+      <c r="N1724">
+        <v>42720</v>
+      </c>
+      <c r="O1724">
+        <v>47280</v>
+      </c>
+      <c r="P1724">
+        <v>6</v>
+      </c>
+      <c r="Q1724">
+        <v>1</v>
+      </c>
+      <c r="R1724" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1724" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1725" t="s">
+        <v>275</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1725">
+        <v>17</v>
+      </c>
+      <c r="I1725" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1725">
+        <v>85000</v>
+      </c>
+      <c r="K1725">
+        <v>0</v>
+      </c>
+      <c r="L1725">
+        <v>0</v>
+      </c>
+      <c r="M1725">
+        <v>85000</v>
+      </c>
+      <c r="N1725">
+        <v>5050.1899999999996</v>
+      </c>
+      <c r="O1725">
+        <v>79949.81</v>
+      </c>
+      <c r="P1725">
+        <v>17</v>
+      </c>
+      <c r="Q1725">
+        <v>1</v>
+      </c>
+      <c r="R1725" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1725" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1726" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>278</v>
+      </c>
+      <c r="H1726">
+        <v>253</v>
+      </c>
+      <c r="I1726" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1726">
+        <v>1265000</v>
+      </c>
+      <c r="K1726">
+        <v>0</v>
+      </c>
+      <c r="L1726">
+        <v>0</v>
+      </c>
+      <c r="M1726">
+        <v>1270000</v>
+      </c>
+      <c r="N1726">
+        <v>1638.3</v>
+      </c>
+      <c r="O1726">
+        <v>1268361.7</v>
+      </c>
+      <c r="P1726">
+        <v>175</v>
+      </c>
+      <c r="Q1726">
+        <v>1.45</v>
+      </c>
+      <c r="R1726" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1726" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1727" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1727">
+        <v>148</v>
+      </c>
+      <c r="I1727" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1727">
+        <v>592000</v>
+      </c>
+      <c r="K1727">
+        <v>0</v>
+      </c>
+      <c r="L1727">
+        <v>0</v>
+      </c>
+      <c r="M1727">
+        <v>592000</v>
+      </c>
+      <c r="N1727">
+        <v>444000</v>
+      </c>
+      <c r="O1727">
+        <v>148000</v>
+      </c>
+      <c r="P1727">
+        <v>82</v>
+      </c>
+      <c r="Q1727">
+        <v>1.8</v>
+      </c>
+      <c r="R1727" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1727" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1728" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1728">
+        <v>26</v>
+      </c>
+      <c r="I1728" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1728">
+        <v>130000</v>
+      </c>
+      <c r="K1728">
+        <v>0</v>
+      </c>
+      <c r="L1728">
+        <v>0</v>
+      </c>
+      <c r="M1728">
+        <v>130000</v>
+      </c>
+      <c r="N1728">
+        <v>104000</v>
+      </c>
+      <c r="O1728">
+        <v>26000</v>
+      </c>
+      <c r="P1728">
+        <v>20</v>
+      </c>
+      <c r="Q1728">
+        <v>1.3</v>
+      </c>
+      <c r="R1728" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1728" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1729" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1729">
+        <v>87</v>
+      </c>
+      <c r="I1729" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1729">
+        <v>435000</v>
+      </c>
+      <c r="K1729">
+        <v>0</v>
+      </c>
+      <c r="L1729">
+        <v>0</v>
+      </c>
+      <c r="M1729">
+        <v>435000</v>
+      </c>
+      <c r="N1729">
+        <v>348000</v>
+      </c>
+      <c r="O1729">
+        <v>87000</v>
+      </c>
+      <c r="P1729">
+        <v>61</v>
+      </c>
+      <c r="Q1729">
+        <v>1.43</v>
+      </c>
+      <c r="R1729" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1729" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1730" t="s">
+        <v>455</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1730">
+        <v>13</v>
+      </c>
+      <c r="I1730" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1730">
+        <v>195000</v>
+      </c>
+      <c r="K1730">
+        <v>0</v>
+      </c>
+      <c r="L1730">
+        <v>0</v>
+      </c>
+      <c r="M1730">
+        <v>195000</v>
+      </c>
+      <c r="N1730">
+        <v>0</v>
+      </c>
+      <c r="O1730">
+        <v>195000</v>
+      </c>
+      <c r="P1730">
+        <v>13</v>
+      </c>
+      <c r="Q1730">
+        <v>1</v>
+      </c>
+      <c r="R1730" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1730" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1731" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1731">
+        <v>2</v>
+      </c>
+      <c r="I1731" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1731">
+        <v>10000</v>
+      </c>
+      <c r="K1731">
+        <v>0</v>
+      </c>
+      <c r="L1731">
+        <v>0</v>
+      </c>
+      <c r="M1731">
+        <v>10000</v>
+      </c>
+      <c r="N1731">
+        <v>31333.34</v>
+      </c>
+      <c r="O1731">
+        <v>-21333.34</v>
+      </c>
+      <c r="P1731">
+        <v>2</v>
+      </c>
+      <c r="Q1731">
+        <v>1</v>
+      </c>
+      <c r="R1731" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1731" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1732" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1732">
+        <v>8</v>
+      </c>
+      <c r="I1732" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1732">
+        <v>120000</v>
+      </c>
+      <c r="K1732">
+        <v>0</v>
+      </c>
+      <c r="L1732">
+        <v>0</v>
+      </c>
+      <c r="M1732">
+        <v>120000</v>
+      </c>
+      <c r="N1732">
+        <v>35463.199999999997</v>
+      </c>
+      <c r="O1732">
+        <v>84536.8</v>
+      </c>
+      <c r="P1732">
+        <v>8</v>
+      </c>
+      <c r="Q1732">
+        <v>1</v>
+      </c>
+      <c r="R1732" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1732" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1733" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1733">
+        <v>13</v>
+      </c>
+      <c r="I1733" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1733">
+        <v>169000</v>
+      </c>
+      <c r="K1733">
+        <v>0</v>
+      </c>
+      <c r="L1733">
+        <v>0</v>
+      </c>
+      <c r="M1733">
+        <v>169000</v>
+      </c>
+      <c r="N1733">
+        <v>50606.85</v>
+      </c>
+      <c r="O1733">
+        <v>118393.15</v>
+      </c>
+      <c r="P1733">
+        <v>10</v>
+      </c>
+      <c r="Q1733">
+        <v>1.3</v>
+      </c>
+      <c r="R1733" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1733" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1734" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1734">
+        <v>11</v>
+      </c>
+      <c r="I1734" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1734">
+        <v>143000</v>
+      </c>
+      <c r="K1734">
+        <v>0</v>
+      </c>
+      <c r="L1734">
+        <v>0</v>
+      </c>
+      <c r="M1734">
+        <v>143000</v>
+      </c>
+      <c r="N1734">
+        <v>42313.599999999999</v>
+      </c>
+      <c r="O1734">
+        <v>100686.39999999999</v>
+      </c>
+      <c r="P1734">
+        <v>10</v>
+      </c>
+      <c r="Q1734">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="R1734" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1734" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1735" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1735">
+        <v>11</v>
+      </c>
+      <c r="I1735" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1735">
+        <v>110000</v>
+      </c>
+      <c r="K1735">
+        <v>0</v>
+      </c>
+      <c r="L1735">
+        <v>0</v>
+      </c>
+      <c r="M1735">
+        <v>110000</v>
+      </c>
+      <c r="N1735">
+        <v>36477.599999999999</v>
+      </c>
+      <c r="O1735">
+        <v>73522.399999999994</v>
+      </c>
+      <c r="P1735">
+        <v>8</v>
+      </c>
+      <c r="Q1735">
+        <v>1.38</v>
+      </c>
+      <c r="R1735" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1735" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1736" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1736">
+        <v>31</v>
+      </c>
+      <c r="I1736" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1736">
+        <v>310000</v>
+      </c>
+      <c r="K1736">
+        <v>0</v>
+      </c>
+      <c r="L1736">
+        <v>0</v>
+      </c>
+      <c r="M1736">
+        <v>312000</v>
+      </c>
+      <c r="N1736">
+        <v>26749.1</v>
+      </c>
+      <c r="O1736">
+        <v>285250.90000000002</v>
+      </c>
+      <c r="P1736">
+        <v>28</v>
+      </c>
+      <c r="Q1736">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1736" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1736" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1737" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1737">
+        <v>111</v>
+      </c>
+      <c r="I1737" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1737">
+        <v>555000</v>
+      </c>
+      <c r="K1737">
+        <v>0</v>
+      </c>
+      <c r="L1737">
+        <v>0</v>
+      </c>
+      <c r="M1737">
+        <v>555000</v>
+      </c>
+      <c r="N1737">
+        <v>83254.350000000006</v>
+      </c>
+      <c r="O1737">
+        <v>471745.65</v>
+      </c>
+      <c r="P1737">
+        <v>90</v>
+      </c>
+      <c r="Q1737">
+        <v>1.23</v>
+      </c>
+      <c r="R1737" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1737" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1738" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1738">
+        <v>98</v>
+      </c>
+      <c r="I1738" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1738">
+        <v>490000</v>
+      </c>
+      <c r="K1738">
+        <v>0</v>
+      </c>
+      <c r="L1738">
+        <v>0</v>
+      </c>
+      <c r="M1738">
+        <v>490000</v>
+      </c>
+      <c r="N1738">
+        <v>63182</v>
+      </c>
+      <c r="O1738">
+        <v>426818</v>
+      </c>
+      <c r="P1738">
+        <v>82</v>
+      </c>
+      <c r="Q1738">
+        <v>1.2</v>
+      </c>
+      <c r="R1738" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1738" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1739" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1739">
+        <v>52</v>
+      </c>
+      <c r="I1739" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1739">
+        <v>416000</v>
+      </c>
+      <c r="K1739">
+        <v>0</v>
+      </c>
+      <c r="L1739">
+        <v>0</v>
+      </c>
+      <c r="M1739">
+        <v>418000</v>
+      </c>
+      <c r="N1739">
+        <v>38463.800000000003</v>
+      </c>
+      <c r="O1739">
+        <v>379536.2</v>
+      </c>
+      <c r="P1739">
+        <v>38</v>
+      </c>
+      <c r="Q1739">
+        <v>1.37</v>
+      </c>
+      <c r="R1739" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1739" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1740" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1740">
+        <v>3</v>
+      </c>
+      <c r="I1740" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1740">
+        <v>60000</v>
+      </c>
+      <c r="K1740">
+        <v>0</v>
+      </c>
+      <c r="L1740">
+        <v>0</v>
+      </c>
+      <c r="M1740">
+        <v>60000</v>
+      </c>
+      <c r="N1740">
+        <v>51000</v>
+      </c>
+      <c r="O1740">
+        <v>9000</v>
+      </c>
+      <c r="P1740">
+        <v>3</v>
+      </c>
+      <c r="Q1740">
+        <v>1</v>
+      </c>
+      <c r="R1740" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1740" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1741" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>425</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1741">
+        <v>1</v>
+      </c>
+      <c r="I1741" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1741">
+        <v>15000</v>
+      </c>
+      <c r="K1741">
+        <v>0</v>
+      </c>
+      <c r="L1741">
+        <v>0</v>
+      </c>
+      <c r="M1741">
+        <v>15000</v>
+      </c>
+      <c r="N1741">
+        <v>12000</v>
+      </c>
+      <c r="O1741">
+        <v>3000</v>
+      </c>
+      <c r="P1741">
+        <v>1</v>
+      </c>
+      <c r="Q1741">
+        <v>1</v>
+      </c>
+      <c r="R1741" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1741" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1742" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1742">
+        <v>36</v>
+      </c>
+      <c r="I1742" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1742">
+        <v>540000</v>
+      </c>
+      <c r="K1742">
+        <v>0</v>
+      </c>
+      <c r="L1742">
+        <v>0</v>
+      </c>
+      <c r="M1742">
+        <v>540000</v>
+      </c>
+      <c r="N1742">
+        <v>432000</v>
+      </c>
+      <c r="O1742">
+        <v>108000</v>
+      </c>
+      <c r="P1742">
+        <v>31</v>
+      </c>
+      <c r="Q1742">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R1742" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1742" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1743" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1743">
+        <v>5</v>
+      </c>
+      <c r="I1743" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1743">
+        <v>75000</v>
+      </c>
+      <c r="K1743">
+        <v>0</v>
+      </c>
+      <c r="L1743">
+        <v>0</v>
+      </c>
+      <c r="M1743">
+        <v>75000</v>
+      </c>
+      <c r="N1743">
+        <v>60000</v>
+      </c>
+      <c r="O1743">
+        <v>15000</v>
+      </c>
+      <c r="P1743">
+        <v>4</v>
+      </c>
+      <c r="Q1743">
+        <v>1.25</v>
+      </c>
+      <c r="R1743" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1743" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1744" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1744">
+        <v>6</v>
+      </c>
+      <c r="I1744" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1744">
+        <v>90000</v>
+      </c>
+      <c r="K1744">
+        <v>0</v>
+      </c>
+      <c r="L1744">
+        <v>0</v>
+      </c>
+      <c r="M1744">
+        <v>90000</v>
+      </c>
+      <c r="N1744">
+        <v>72000</v>
+      </c>
+      <c r="O1744">
+        <v>18000</v>
+      </c>
+      <c r="P1744">
+        <v>5</v>
+      </c>
+      <c r="Q1744">
+        <v>1.2</v>
+      </c>
+      <c r="R1744" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1744" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1745" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1745">
+        <v>9</v>
+      </c>
+      <c r="I1745" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1745">
+        <v>180000</v>
+      </c>
+      <c r="K1745">
+        <v>0</v>
+      </c>
+      <c r="L1745">
+        <v>0</v>
+      </c>
+      <c r="M1745">
+        <v>180000</v>
+      </c>
+      <c r="N1745">
+        <v>153000</v>
+      </c>
+      <c r="O1745">
+        <v>27000</v>
+      </c>
+      <c r="P1745">
+        <v>9</v>
+      </c>
+      <c r="Q1745">
+        <v>1</v>
+      </c>
+      <c r="R1745" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1745" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1746" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1746">
+        <v>56</v>
+      </c>
+      <c r="I1746" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1746">
+        <v>560000</v>
+      </c>
+      <c r="K1746">
+        <v>0</v>
+      </c>
+      <c r="L1746">
+        <v>0</v>
+      </c>
+      <c r="M1746">
+        <v>560000</v>
+      </c>
+      <c r="N1746">
+        <v>255733.52</v>
+      </c>
+      <c r="O1746">
+        <v>304266.48</v>
+      </c>
+      <c r="P1746">
+        <v>49</v>
+      </c>
+      <c r="Q1746">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="R1746" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1746" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1747" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>414</v>
+      </c>
+      <c r="D1747" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1747">
+        <v>60</v>
+      </c>
+      <c r="I1747" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1747">
+        <v>600000</v>
+      </c>
+      <c r="K1747">
+        <v>0</v>
+      </c>
+      <c r="L1747">
+        <v>0</v>
+      </c>
+      <c r="M1747">
+        <v>600000</v>
+      </c>
+      <c r="N1747">
+        <v>261499.8</v>
+      </c>
+      <c r="O1747">
+        <v>338500.2</v>
+      </c>
+      <c r="P1747">
+        <v>46</v>
+      </c>
+      <c r="Q1747">
+        <v>1.3</v>
+      </c>
+      <c r="R1747" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1747" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1748" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1748" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1748">
+        <v>5</v>
+      </c>
+      <c r="I1748" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1748">
+        <v>50000</v>
+      </c>
+      <c r="K1748">
+        <v>0</v>
+      </c>
+      <c r="L1748">
+        <v>0</v>
+      </c>
+      <c r="M1748">
+        <v>50000</v>
+      </c>
+      <c r="N1748">
+        <v>13112.55</v>
+      </c>
+      <c r="O1748">
+        <v>36887.449999999997</v>
+      </c>
+      <c r="P1748">
+        <v>4</v>
+      </c>
+      <c r="Q1748">
+        <v>1.25</v>
+      </c>
+      <c r="R1748" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1748" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1749" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1749" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1749">
+        <v>3</v>
+      </c>
+      <c r="I1749" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1749">
+        <v>39000</v>
+      </c>
+      <c r="K1749">
+        <v>0</v>
+      </c>
+      <c r="L1749">
+        <v>0</v>
+      </c>
+      <c r="M1749">
+        <v>39000</v>
+      </c>
+      <c r="N1749">
+        <v>10549.55</v>
+      </c>
+      <c r="O1749">
+        <v>28450.45</v>
+      </c>
+      <c r="P1749">
+        <v>3</v>
+      </c>
+      <c r="Q1749">
+        <v>1</v>
+      </c>
+      <c r="R1749" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1749" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1750" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1750" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1750">
+        <v>1</v>
+      </c>
+      <c r="I1750" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1750">
+        <v>15000</v>
+      </c>
+      <c r="K1750">
+        <v>0</v>
+      </c>
+      <c r="L1750">
+        <v>0</v>
+      </c>
+      <c r="M1750">
+        <v>15000</v>
+      </c>
+      <c r="N1750">
+        <v>4223.75</v>
+      </c>
+      <c r="O1750">
+        <v>10776.25</v>
+      </c>
+      <c r="P1750">
+        <v>1</v>
+      </c>
+      <c r="Q1750">
+        <v>1</v>
+      </c>
+      <c r="R1750" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1750" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1751" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1751" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1751" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1751" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1751">
+        <v>2</v>
+      </c>
+      <c r="I1751" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1751">
+        <v>26000</v>
+      </c>
+      <c r="K1751">
+        <v>0</v>
+      </c>
+      <c r="L1751">
+        <v>0</v>
+      </c>
+      <c r="M1751">
+        <v>26000</v>
+      </c>
+      <c r="N1751">
+        <v>5343</v>
+      </c>
+      <c r="O1751">
+        <v>20657</v>
+      </c>
+      <c r="P1751">
+        <v>2</v>
+      </c>
+      <c r="Q1751">
+        <v>1</v>
+      </c>
+      <c r="R1751" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1751" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1752" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1752" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1752" t="s">
+        <v>298</v>
+      </c>
+      <c r="F1752" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1752">
+        <v>7</v>
+      </c>
+      <c r="I1752" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1752">
+        <v>70000</v>
+      </c>
+      <c r="K1752">
+        <v>0</v>
+      </c>
+      <c r="L1752">
+        <v>0</v>
+      </c>
+      <c r="M1752">
+        <v>70000</v>
+      </c>
+      <c r="N1752">
+        <v>21814.400000000001</v>
+      </c>
+      <c r="O1752">
+        <v>48185.599999999999</v>
+      </c>
+      <c r="P1752">
+        <v>5</v>
+      </c>
+      <c r="Q1752">
+        <v>1.4</v>
+      </c>
+      <c r="R1752" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1752" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1753" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1753" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1753" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1753">
+        <v>40</v>
+      </c>
+      <c r="I1753" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1753">
+        <v>200000</v>
+      </c>
+      <c r="K1753">
+        <v>0</v>
+      </c>
+      <c r="L1753">
+        <v>0</v>
+      </c>
+      <c r="M1753">
+        <v>200000</v>
+      </c>
+      <c r="N1753">
+        <v>0</v>
+      </c>
+      <c r="O1753">
+        <v>200000</v>
+      </c>
+      <c r="P1753">
+        <v>38</v>
+      </c>
+      <c r="Q1753">
+        <v>1.05</v>
+      </c>
+      <c r="R1753" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1753" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1754" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1754" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1754" t="s">
+        <v>302</v>
+      </c>
+      <c r="H1754">
+        <v>68</v>
+      </c>
+      <c r="I1754" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1754">
+        <v>204000</v>
+      </c>
+      <c r="K1754">
+        <v>0</v>
+      </c>
+      <c r="L1754">
+        <v>0</v>
+      </c>
+      <c r="M1754">
+        <v>204000</v>
+      </c>
+      <c r="N1754">
+        <v>0</v>
+      </c>
+      <c r="O1754">
+        <v>204000</v>
+      </c>
+      <c r="P1754">
+        <v>57</v>
+      </c>
+      <c r="Q1754">
+        <v>1.19</v>
+      </c>
+      <c r="R1754" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1754" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1755" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1755" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1755" t="s">
+        <v>308</v>
+      </c>
+      <c r="H1755">
+        <v>577</v>
+      </c>
+      <c r="I1755" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1755">
+        <v>2885000</v>
+      </c>
+      <c r="K1755">
+        <v>0</v>
+      </c>
+      <c r="L1755">
+        <v>0</v>
+      </c>
+      <c r="M1755">
+        <v>2905000</v>
+      </c>
+      <c r="N1755">
+        <v>960843.47</v>
+      </c>
+      <c r="O1755">
+        <v>1944156.54</v>
+      </c>
+      <c r="P1755">
+        <v>402</v>
+      </c>
+      <c r="Q1755">
+        <v>1.44</v>
+      </c>
+      <c r="R1755" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1755" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1756" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1756" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1756" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1756">
+        <v>17</v>
+      </c>
+      <c r="I1756" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1756">
+        <v>170000</v>
+      </c>
+      <c r="K1756">
+        <v>0</v>
+      </c>
+      <c r="L1756">
+        <v>0</v>
+      </c>
+      <c r="M1756">
+        <v>172000</v>
+      </c>
+      <c r="N1756">
+        <v>5837.6</v>
+      </c>
+      <c r="O1756">
+        <v>166162.4</v>
+      </c>
+      <c r="P1756">
+        <v>16</v>
+      </c>
+      <c r="Q1756">
+        <v>1.06</v>
+      </c>
+      <c r="R1756" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1756" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1757" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1757" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1757" t="s">
+        <v>326</v>
+      </c>
+      <c r="H1757">
+        <v>19</v>
+      </c>
+      <c r="I1757" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1757">
+        <v>228000</v>
+      </c>
+      <c r="K1757">
+        <v>0</v>
+      </c>
+      <c r="L1757">
+        <v>0</v>
+      </c>
+      <c r="M1757">
+        <v>240000</v>
+      </c>
+      <c r="N1757">
+        <v>39747.760000000002</v>
+      </c>
+      <c r="O1757">
+        <v>200252.24</v>
+      </c>
+      <c r="P1757">
+        <v>17</v>
+      </c>
+      <c r="Q1757">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="R1757" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1757" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1758" t="s">
+        <v>327</v>
+      </c>
+      <c r="D1758" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1758">
+        <v>5</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1758">
+        <v>10000</v>
+      </c>
+      <c r="K1758">
+        <v>0</v>
+      </c>
+      <c r="L1758">
+        <v>0</v>
+      </c>
+      <c r="M1758">
+        <v>10000</v>
+      </c>
+      <c r="N1758">
+        <v>0</v>
+      </c>
+      <c r="O1758">
+        <v>10000</v>
+      </c>
+      <c r="P1758">
+        <v>5</v>
+      </c>
+      <c r="Q1758">
+        <v>1</v>
+      </c>
+      <c r="R1758" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1758" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1759" t="s">
+        <v>415</v>
+      </c>
+      <c r="D1759" t="s">
+        <v>416</v>
+      </c>
+      <c r="H1759">
+        <v>123</v>
+      </c>
+      <c r="I1759" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1759">
+        <v>3075000</v>
+      </c>
+      <c r="K1759">
+        <v>0</v>
+      </c>
+      <c r="L1759">
+        <v>0</v>
+      </c>
+      <c r="M1759">
+        <v>3075000</v>
+      </c>
+      <c r="N1759">
+        <v>1773401.7</v>
+      </c>
+      <c r="O1759">
+        <v>1301598.3</v>
+      </c>
+      <c r="P1759">
+        <v>10</v>
+      </c>
+      <c r="Q1759">
+        <v>12.3</v>
+      </c>
+      <c r="R1759" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1759" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1760" t="s">
+        <v>456</v>
+      </c>
+      <c r="D1760" t="s">
+        <v>416</v>
+      </c>
+      <c r="E1760" t="s">
+        <v>457</v>
+      </c>
+      <c r="H1760">
+        <v>3</v>
+      </c>
+      <c r="I1760" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1760">
+        <v>75000</v>
+      </c>
+      <c r="K1760">
+        <v>0</v>
+      </c>
+      <c r="L1760">
+        <v>0</v>
+      </c>
+      <c r="M1760">
+        <v>75000</v>
+      </c>
+      <c r="N1760">
+        <v>32377.5</v>
+      </c>
+      <c r="O1760">
+        <v>42622.5</v>
+      </c>
+      <c r="P1760">
+        <v>1</v>
+      </c>
+      <c r="Q1760">
+        <v>3</v>
+      </c>
+      <c r="R1760" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1760" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1761" t="s">
+        <v>329</v>
+      </c>
+      <c r="D1761" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1761">
+        <v>267</v>
+      </c>
+      <c r="I1761" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1761">
+        <v>1335000</v>
+      </c>
+      <c r="K1761">
+        <v>0</v>
+      </c>
+      <c r="L1761">
+        <v>0</v>
+      </c>
+      <c r="M1761">
+        <v>1335000</v>
+      </c>
+      <c r="N1761">
+        <v>867750</v>
+      </c>
+      <c r="O1761">
+        <v>467250</v>
+      </c>
+      <c r="P1761">
+        <v>203</v>
+      </c>
+      <c r="Q1761">
+        <v>1.32</v>
+      </c>
+      <c r="R1761" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1761" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1762" t="s">
+        <v>331</v>
+      </c>
+      <c r="D1762" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1762">
+        <v>87</v>
+      </c>
+      <c r="I1762" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1762">
+        <v>435000</v>
+      </c>
+      <c r="K1762">
+        <v>0</v>
+      </c>
+      <c r="L1762">
+        <v>0</v>
+      </c>
+      <c r="M1762">
+        <v>435000</v>
+      </c>
+      <c r="N1762">
+        <v>282750</v>
+      </c>
+      <c r="O1762">
+        <v>152250</v>
+      </c>
+      <c r="P1762">
+        <v>80</v>
+      </c>
+      <c r="Q1762">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R1762" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1762" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1763" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1763" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1763">
+        <v>191</v>
+      </c>
+      <c r="I1763" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1763">
+        <v>764000</v>
+      </c>
+      <c r="K1763">
+        <v>0</v>
+      </c>
+      <c r="L1763">
+        <v>0</v>
+      </c>
+      <c r="M1763">
+        <v>764000</v>
+      </c>
+      <c r="N1763">
+        <v>496600</v>
+      </c>
+      <c r="O1763">
+        <v>267400</v>
+      </c>
+      <c r="P1763">
+        <v>123</v>
+      </c>
+      <c r="Q1763">
+        <v>1.55</v>
+      </c>
+      <c r="R1763" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1763" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1764" t="s">
+        <v>333</v>
+      </c>
+      <c r="D1764" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1764">
+        <v>147</v>
+      </c>
+      <c r="I1764" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1764">
+        <v>735000</v>
+      </c>
+      <c r="K1764">
+        <v>0</v>
+      </c>
+      <c r="L1764">
+        <v>0</v>
+      </c>
+      <c r="M1764">
+        <v>735000</v>
+      </c>
+      <c r="N1764">
+        <v>477750</v>
+      </c>
+      <c r="O1764">
+        <v>257250</v>
+      </c>
+      <c r="P1764">
+        <v>105</v>
+      </c>
+      <c r="Q1764">
+        <v>1.4</v>
+      </c>
+      <c r="R1764" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1764" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1765" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1765" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1765" t="s">
+        <v>335</v>
+      </c>
+      <c r="H1765">
+        <v>151</v>
+      </c>
+      <c r="I1765" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1765">
+        <v>1510000</v>
+      </c>
+      <c r="K1765">
+        <v>0</v>
+      </c>
+      <c r="L1765">
+        <v>0</v>
+      </c>
+      <c r="M1765">
+        <v>1510000</v>
+      </c>
+      <c r="N1765">
+        <v>981500</v>
+      </c>
+      <c r="O1765">
+        <v>528500</v>
+      </c>
+      <c r="P1765">
+        <v>126</v>
+      </c>
+      <c r="Q1765">
+        <v>1.2</v>
+      </c>
+      <c r="R1765" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1765" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1766" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1766" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1766" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1766">
+        <v>183</v>
+      </c>
+      <c r="I1766" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1766">
+        <v>915000</v>
+      </c>
+      <c r="K1766">
+        <v>0</v>
+      </c>
+      <c r="L1766">
+        <v>0</v>
+      </c>
+      <c r="M1766">
+        <v>915000</v>
+      </c>
+      <c r="N1766">
+        <v>594750</v>
+      </c>
+      <c r="O1766">
+        <v>320250</v>
+      </c>
+      <c r="P1766">
+        <v>132</v>
+      </c>
+      <c r="Q1766">
+        <v>1.39</v>
+      </c>
+      <c r="R1766" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1766" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1767" t="s">
+        <v>338</v>
+      </c>
+      <c r="D1767" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1767" t="s">
+        <v>339</v>
+      </c>
+      <c r="H1767">
+        <v>96</v>
+      </c>
+      <c r="I1767" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1767">
+        <v>384000</v>
+      </c>
+      <c r="K1767">
+        <v>0</v>
+      </c>
+      <c r="L1767">
+        <v>0</v>
+      </c>
+      <c r="M1767">
+        <v>384000</v>
+      </c>
+      <c r="N1767">
+        <v>249600</v>
+      </c>
+      <c r="O1767">
+        <v>134400</v>
+      </c>
+      <c r="P1767">
+        <v>72</v>
+      </c>
+      <c r="Q1767">
+        <v>1.33</v>
+      </c>
+      <c r="R1767" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1767" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1768" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1768" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1768">
+        <v>10</v>
+      </c>
+      <c r="I1768" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1768">
+        <v>500000</v>
+      </c>
+      <c r="K1768">
+        <v>0</v>
+      </c>
+      <c r="L1768">
+        <v>0</v>
+      </c>
+      <c r="M1768">
+        <v>500000</v>
+      </c>
+      <c r="N1768">
+        <v>400000</v>
+      </c>
+      <c r="O1768">
+        <v>100000</v>
+      </c>
+      <c r="P1768">
+        <v>8</v>
+      </c>
+      <c r="Q1768">
+        <v>1.25</v>
+      </c>
+      <c r="R1768" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1768" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1769" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1769" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1769">
+        <v>9</v>
+      </c>
+      <c r="I1769" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1769">
+        <v>117000</v>
+      </c>
+      <c r="K1769">
+        <v>0</v>
+      </c>
+      <c r="L1769">
+        <v>0</v>
+      </c>
+      <c r="M1769">
+        <v>117000</v>
+      </c>
+      <c r="N1769">
+        <v>90000</v>
+      </c>
+      <c r="O1769">
+        <v>27000</v>
+      </c>
+      <c r="P1769">
+        <v>7</v>
+      </c>
+      <c r="Q1769">
+        <v>1.29</v>
+      </c>
+      <c r="R1769" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1769" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1770" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1770" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1770">
+        <v>3</v>
+      </c>
+      <c r="I1770" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1770">
+        <v>60000</v>
+      </c>
+      <c r="K1770">
+        <v>0</v>
+      </c>
+      <c r="L1770">
+        <v>0</v>
+      </c>
+      <c r="M1770">
+        <v>60000</v>
+      </c>
+      <c r="N1770">
+        <v>45000</v>
+      </c>
+      <c r="O1770">
+        <v>15000</v>
+      </c>
+      <c r="P1770">
+        <v>3</v>
+      </c>
+      <c r="Q1770">
+        <v>1</v>
+      </c>
+      <c r="R1770" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1770" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1771" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1771" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1771">
+        <v>16</v>
+      </c>
+      <c r="I1771" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1771">
+        <v>80000</v>
+      </c>
+      <c r="K1771">
+        <v>0</v>
+      </c>
+      <c r="L1771">
+        <v>0</v>
+      </c>
+      <c r="M1771">
+        <v>80000</v>
+      </c>
+      <c r="N1771">
+        <v>45249.52</v>
+      </c>
+      <c r="O1771">
+        <v>34750.480000000003</v>
+      </c>
+      <c r="P1771">
+        <v>12</v>
+      </c>
+      <c r="Q1771">
+        <v>1.33</v>
+      </c>
+      <c r="R1771" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1771" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1772" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1772" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1772">
+        <v>2</v>
+      </c>
+      <c r="I1772" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1772">
+        <v>26000</v>
+      </c>
+      <c r="K1772">
+        <v>0</v>
+      </c>
+      <c r="L1772">
+        <v>0</v>
+      </c>
+      <c r="M1772">
+        <v>26000</v>
+      </c>
+      <c r="N1772">
+        <v>20000</v>
+      </c>
+      <c r="O1772">
+        <v>6000</v>
+      </c>
+      <c r="P1772">
+        <v>2</v>
+      </c>
+      <c r="Q1772">
+        <v>1</v>
+      </c>
+      <c r="R1772" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1772" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1773" t="s">
+        <v>434</v>
+      </c>
+      <c r="D1773" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1773">
+        <v>5</v>
+      </c>
+      <c r="I1773" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1773">
+        <v>85000</v>
+      </c>
+      <c r="K1773">
+        <v>0</v>
+      </c>
+      <c r="L1773">
+        <v>0</v>
+      </c>
+      <c r="M1773">
+        <v>85000</v>
+      </c>
+      <c r="N1773">
+        <v>70000</v>
+      </c>
+      <c r="O1773">
+        <v>15000</v>
+      </c>
+      <c r="P1773">
+        <v>4</v>
+      </c>
+      <c r="Q1773">
+        <v>1.25</v>
+      </c>
+      <c r="R1773" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1773" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1774" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1774" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1774">
+        <v>1</v>
+      </c>
+      <c r="I1774" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1774">
+        <v>16000</v>
+      </c>
+      <c r="K1774">
+        <v>0</v>
+      </c>
+      <c r="L1774">
+        <v>0</v>
+      </c>
+      <c r="M1774">
+        <v>16000</v>
+      </c>
+      <c r="N1774">
+        <v>13000</v>
+      </c>
+      <c r="O1774">
+        <v>3000</v>
+      </c>
+      <c r="P1774">
+        <v>1</v>
+      </c>
+      <c r="Q1774">
+        <v>1</v>
+      </c>
+      <c r="R1774" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1774" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1775" t="s">
+        <v>345</v>
+      </c>
+      <c r="D1775" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1775">
+        <v>31</v>
+      </c>
+      <c r="I1775" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1775">
+        <v>310000</v>
+      </c>
+      <c r="K1775">
+        <v>0</v>
+      </c>
+      <c r="L1775">
+        <v>0</v>
+      </c>
+      <c r="M1775">
+        <v>310000</v>
+      </c>
+      <c r="N1775">
+        <v>246356.07</v>
+      </c>
+      <c r="O1775">
+        <v>63643.93</v>
+      </c>
+      <c r="P1775">
+        <v>24</v>
+      </c>
+      <c r="Q1775">
+        <v>1.29</v>
+      </c>
+      <c r="R1775" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1775" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1776" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1776" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1776">
+        <v>1</v>
+      </c>
+      <c r="I1776" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1776">
+        <v>55000</v>
+      </c>
+      <c r="K1776">
+        <v>0</v>
+      </c>
+      <c r="L1776">
+        <v>0</v>
+      </c>
+      <c r="M1776">
+        <v>55000</v>
+      </c>
+      <c r="N1776">
+        <v>47000</v>
+      </c>
+      <c r="O1776">
+        <v>8000</v>
+      </c>
+      <c r="P1776">
+        <v>1</v>
+      </c>
+      <c r="Q1776">
+        <v>1</v>
+      </c>
+      <c r="R1776" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1776" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1777" t="s">
+        <v>349</v>
+      </c>
+      <c r="D1777" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1777">
+        <v>69</v>
+      </c>
+      <c r="I1777" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1777">
+        <v>828000</v>
+      </c>
+      <c r="K1777">
+        <v>0</v>
+      </c>
+      <c r="L1777">
+        <v>0</v>
+      </c>
+      <c r="M1777">
+        <v>828000</v>
+      </c>
+      <c r="N1777">
+        <v>621000</v>
+      </c>
+      <c r="O1777">
+        <v>207000</v>
+      </c>
+      <c r="P1777">
+        <v>43</v>
+      </c>
+      <c r="Q1777">
+        <v>1.6</v>
+      </c>
+      <c r="R1777" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1777" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1778" t="s">
+        <v>350</v>
+      </c>
+      <c r="D1778" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1778">
+        <v>32</v>
+      </c>
+      <c r="I1778" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1778">
+        <v>416000</v>
+      </c>
+      <c r="K1778">
+        <v>0</v>
+      </c>
+      <c r="L1778">
+        <v>0</v>
+      </c>
+      <c r="M1778">
+        <v>416000</v>
+      </c>
+      <c r="N1778">
+        <v>320000</v>
+      </c>
+      <c r="O1778">
+        <v>96000</v>
+      </c>
+      <c r="P1778">
+        <v>23</v>
+      </c>
+      <c r="Q1778">
+        <v>1.39</v>
+      </c>
+      <c r="R1778" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1778" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1779" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1779" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1779">
+        <v>77</v>
+      </c>
+      <c r="I1779" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1779">
+        <v>539000</v>
+      </c>
+      <c r="K1779">
+        <v>0</v>
+      </c>
+      <c r="L1779">
+        <v>0</v>
+      </c>
+      <c r="M1779">
+        <v>539000</v>
+      </c>
+      <c r="N1779">
+        <v>385000</v>
+      </c>
+      <c r="O1779">
+        <v>154000</v>
+      </c>
+      <c r="P1779">
+        <v>34</v>
+      </c>
+      <c r="Q1779">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="R1779" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1779" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1780" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1780" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1780">
+        <v>3</v>
+      </c>
+      <c r="I1780" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1780">
+        <v>39000</v>
+      </c>
+      <c r="K1780">
+        <v>0</v>
+      </c>
+      <c r="L1780">
+        <v>0</v>
+      </c>
+      <c r="M1780">
+        <v>39000</v>
+      </c>
+      <c r="N1780">
+        <v>30000</v>
+      </c>
+      <c r="O1780">
+        <v>9000</v>
+      </c>
+      <c r="P1780">
+        <v>3</v>
+      </c>
+      <c r="Q1780">
+        <v>1</v>
+      </c>
+      <c r="R1780" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1780" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1781" t="s">
+        <v>353</v>
+      </c>
+      <c r="D1781" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1781">
+        <v>15</v>
+      </c>
+      <c r="I1781" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1781">
+        <v>195000</v>
+      </c>
+      <c r="K1781">
+        <v>0</v>
+      </c>
+      <c r="L1781">
+        <v>0</v>
+      </c>
+      <c r="M1781">
+        <v>195000</v>
+      </c>
+      <c r="N1781">
+        <v>150000</v>
+      </c>
+      <c r="O1781">
+        <v>45000</v>
+      </c>
+      <c r="P1781">
+        <v>11</v>
+      </c>
+      <c r="Q1781">
+        <v>1.36</v>
+      </c>
+      <c r="R1781" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1781" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1782" t="s">
+        <v>354</v>
+      </c>
+      <c r="D1782" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1782">
+        <v>7</v>
+      </c>
+      <c r="I1782" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1782">
+        <v>70000</v>
+      </c>
+      <c r="K1782">
+        <v>0</v>
+      </c>
+      <c r="L1782">
+        <v>0</v>
+      </c>
+      <c r="M1782">
+        <v>70000</v>
+      </c>
+      <c r="N1782">
+        <v>35000</v>
+      </c>
+      <c r="O1782">
+        <v>35000</v>
+      </c>
+      <c r="P1782">
+        <v>7</v>
+      </c>
+      <c r="Q1782">
+        <v>1</v>
+      </c>
+      <c r="R1782" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1782" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1783" t="s">
+        <v>355</v>
+      </c>
+      <c r="D1783" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1783">
+        <v>66</v>
+      </c>
+      <c r="I1783" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1783">
+        <v>990000</v>
+      </c>
+      <c r="K1783">
+        <v>0</v>
+      </c>
+      <c r="L1783">
+        <v>0</v>
+      </c>
+      <c r="M1783">
+        <v>990000</v>
+      </c>
+      <c r="N1783">
+        <v>792000</v>
+      </c>
+      <c r="O1783">
+        <v>198000</v>
+      </c>
+      <c r="P1783">
+        <v>53</v>
+      </c>
+      <c r="Q1783">
+        <v>1.25</v>
+      </c>
+      <c r="R1783" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1783" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1784" t="s">
+        <v>356</v>
+      </c>
+      <c r="D1784" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1784">
+        <v>92</v>
+      </c>
+      <c r="I1784" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1784">
+        <v>1012000</v>
+      </c>
+      <c r="K1784">
+        <v>0</v>
+      </c>
+      <c r="L1784">
+        <v>0</v>
+      </c>
+      <c r="M1784">
+        <v>1012000</v>
+      </c>
+      <c r="N1784">
+        <v>736000</v>
+      </c>
+      <c r="O1784">
+        <v>276000</v>
+      </c>
+      <c r="P1784">
+        <v>59</v>
+      </c>
+      <c r="Q1784">
+        <v>1.56</v>
+      </c>
+      <c r="R1784" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1784" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1785" t="s">
+        <v>357</v>
+      </c>
+      <c r="D1785" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1785">
+        <v>21</v>
+      </c>
+      <c r="I1785" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1785">
+        <v>210000</v>
+      </c>
+      <c r="K1785">
+        <v>0</v>
+      </c>
+      <c r="L1785">
+        <v>0</v>
+      </c>
+      <c r="M1785">
+        <v>210000</v>
+      </c>
+      <c r="N1785">
+        <v>157500</v>
+      </c>
+      <c r="O1785">
+        <v>52500</v>
+      </c>
+      <c r="P1785">
+        <v>19</v>
+      </c>
+      <c r="Q1785">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="R1785" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1785" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1786" t="s">
+        <v>358</v>
+      </c>
+      <c r="D1786" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1786">
+        <v>44</v>
+      </c>
+      <c r="I1786" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1786">
+        <v>660000</v>
+      </c>
+      <c r="K1786">
+        <v>0</v>
+      </c>
+      <c r="L1786">
+        <v>0</v>
+      </c>
+      <c r="M1786">
+        <v>660000</v>
+      </c>
+      <c r="N1786">
+        <v>528000</v>
+      </c>
+      <c r="O1786">
+        <v>132000</v>
+      </c>
+      <c r="P1786">
+        <v>33</v>
+      </c>
+      <c r="Q1786">
+        <v>1.33</v>
+      </c>
+      <c r="R1786" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1786" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1787" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1787" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1787">
+        <v>19</v>
+      </c>
+      <c r="I1787" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1787">
+        <v>228000</v>
+      </c>
+      <c r="K1787">
+        <v>0</v>
+      </c>
+      <c r="L1787">
+        <v>0</v>
+      </c>
+      <c r="M1787">
+        <v>228000</v>
+      </c>
+      <c r="N1787">
+        <v>171000</v>
+      </c>
+      <c r="O1787">
+        <v>57000</v>
+      </c>
+      <c r="P1787">
+        <v>9</v>
+      </c>
+      <c r="Q1787">
+        <v>2.11</v>
+      </c>
+      <c r="R1787" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1787" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1788" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1788" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1788">
+        <v>82</v>
+      </c>
+      <c r="I1788" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1788">
+        <v>1640000</v>
+      </c>
+      <c r="K1788">
+        <v>0</v>
+      </c>
+      <c r="L1788">
+        <v>0</v>
+      </c>
+      <c r="M1788">
+        <v>1640000</v>
+      </c>
+      <c r="N1788">
+        <v>1476000</v>
+      </c>
+      <c r="O1788">
+        <v>164000</v>
+      </c>
+      <c r="P1788">
+        <v>52</v>
+      </c>
+      <c r="Q1788">
+        <v>1.58</v>
+      </c>
+      <c r="R1788" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1788" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1789" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1789" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1789">
+        <v>7</v>
+      </c>
+      <c r="I1789" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1789">
+        <v>105000</v>
+      </c>
+      <c r="K1789">
+        <v>0</v>
+      </c>
+      <c r="L1789">
+        <v>0</v>
+      </c>
+      <c r="M1789">
+        <v>105000</v>
+      </c>
+      <c r="N1789">
+        <v>84000</v>
+      </c>
+      <c r="O1789">
+        <v>21000</v>
+      </c>
+      <c r="P1789">
+        <v>6</v>
+      </c>
+      <c r="Q1789">
+        <v>1.17</v>
+      </c>
+      <c r="R1789" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1789" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1790" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1790" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1790">
+        <v>123</v>
+      </c>
+      <c r="I1790" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1790">
+        <v>1476000</v>
+      </c>
+      <c r="K1790">
+        <v>0</v>
+      </c>
+      <c r="L1790">
+        <v>0</v>
+      </c>
+      <c r="M1790">
+        <v>1476000</v>
+      </c>
+      <c r="N1790">
+        <v>984000</v>
+      </c>
+      <c r="O1790">
+        <v>492000</v>
+      </c>
+      <c r="P1790">
+        <v>73</v>
+      </c>
+      <c r="Q1790">
+        <v>1.68</v>
+      </c>
+      <c r="R1790" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1790" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1791" t="s">
+        <v>361</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1791">
+        <v>19</v>
+      </c>
+      <c r="I1791" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1791">
+        <v>399000</v>
+      </c>
+      <c r="K1791">
+        <v>0</v>
+      </c>
+      <c r="L1791">
+        <v>0</v>
+      </c>
+      <c r="M1791">
+        <v>399000</v>
+      </c>
+      <c r="N1791">
+        <v>304000</v>
+      </c>
+      <c r="O1791">
+        <v>95000</v>
+      </c>
+      <c r="P1791">
+        <v>17</v>
+      </c>
+      <c r="Q1791">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="R1791" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1791" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1792" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1792" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1792">
+        <v>13</v>
+      </c>
+      <c r="I1792" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1792">
+        <v>169000</v>
+      </c>
+      <c r="K1792">
+        <v>0</v>
+      </c>
+      <c r="L1792">
+        <v>0</v>
+      </c>
+      <c r="M1792">
+        <v>169000</v>
+      </c>
+      <c r="N1792">
+        <v>104000</v>
+      </c>
+      <c r="O1792">
+        <v>65000</v>
+      </c>
+      <c r="P1792">
+        <v>11</v>
+      </c>
+      <c r="Q1792">
+        <v>1.18</v>
+      </c>
+      <c r="R1792" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1792" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1793" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1793" t="s">
+        <v>341</v>
+      </c>
+      <c r="H1793">
+        <v>34</v>
+      </c>
+      <c r="I1793" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1793">
+        <v>442000</v>
+      </c>
+      <c r="K1793">
+        <v>0</v>
+      </c>
+      <c r="L1793">
+        <v>0</v>
+      </c>
+      <c r="M1793">
+        <v>442000</v>
+      </c>
+      <c r="N1793">
+        <v>340000</v>
+      </c>
+      <c r="O1793">
+        <v>102000</v>
+      </c>
+      <c r="P1793">
+        <v>27</v>
+      </c>
+      <c r="Q1793">
+        <v>1.26</v>
+      </c>
+      <c r="R1793" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1793" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1794" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1794" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1794" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>365</v>
+      </c>
+      <c r="H1794">
+        <v>401</v>
+      </c>
+      <c r="I1794" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1794">
+        <v>2807000</v>
+      </c>
+      <c r="K1794">
+        <v>0</v>
+      </c>
+      <c r="L1794">
+        <v>0</v>
+      </c>
+      <c r="M1794">
+        <v>2807000</v>
+      </c>
+      <c r="N1794">
+        <v>1924800</v>
+      </c>
+      <c r="O1794">
+        <v>882200</v>
+      </c>
+      <c r="P1794">
+        <v>80</v>
+      </c>
+      <c r="Q1794">
+        <v>5.01</v>
+      </c>
+      <c r="R1794" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1794" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1795" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1795" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1795">
+        <v>30</v>
+      </c>
+      <c r="I1795" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1795">
+        <v>300000</v>
+      </c>
+      <c r="K1795">
+        <v>0</v>
+      </c>
+      <c r="L1795">
+        <v>0</v>
+      </c>
+      <c r="M1795">
+        <v>300000</v>
+      </c>
+      <c r="N1795">
+        <v>173000</v>
+      </c>
+      <c r="O1795">
+        <v>127000</v>
+      </c>
+      <c r="P1795">
+        <v>22</v>
+      </c>
+      <c r="Q1795">
+        <v>1.36</v>
+      </c>
+      <c r="R1795" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1795" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1796" t="s">
+        <v>368</v>
+      </c>
+      <c r="D1796" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1796">
+        <v>52</v>
+      </c>
+      <c r="I1796" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1796">
+        <v>780000</v>
+      </c>
+      <c r="K1796">
+        <v>0</v>
+      </c>
+      <c r="L1796">
+        <v>0</v>
+      </c>
+      <c r="M1796">
+        <v>780000</v>
+      </c>
+      <c r="N1796">
+        <v>385861.56</v>
+      </c>
+      <c r="O1796">
+        <v>394138.44</v>
+      </c>
+      <c r="P1796">
+        <v>40</v>
+      </c>
+      <c r="Q1796">
+        <v>1.3</v>
+      </c>
+      <c r="R1796" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1796" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1797" t="s">
+        <v>389</v>
+      </c>
+      <c r="D1797" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1797">
+        <v>32</v>
+      </c>
+      <c r="I1797" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1797">
+        <v>160000</v>
+      </c>
+      <c r="K1797">
+        <v>0</v>
+      </c>
+      <c r="L1797">
+        <v>0</v>
+      </c>
+      <c r="M1797">
+        <v>160000</v>
+      </c>
+      <c r="N1797">
+        <v>65723.199999999997</v>
+      </c>
+      <c r="O1797">
+        <v>94276.800000000003</v>
+      </c>
+      <c r="P1797">
+        <v>27</v>
+      </c>
+      <c r="Q1797">
+        <v>1.19</v>
+      </c>
+      <c r="R1797" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1797" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1798" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1798" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1798">
+        <v>61</v>
+      </c>
+      <c r="I1798" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1798">
+        <v>305000</v>
+      </c>
+      <c r="K1798">
+        <v>0</v>
+      </c>
+      <c r="L1798">
+        <v>0</v>
+      </c>
+      <c r="M1798">
+        <v>305000</v>
+      </c>
+      <c r="N1798">
+        <v>68206.429999999993</v>
+      </c>
+      <c r="O1798">
+        <v>236793.57</v>
+      </c>
+      <c r="P1798">
+        <v>54</v>
+      </c>
+      <c r="Q1798">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="R1798" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1798" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1799" t="s">
+        <v>373</v>
+      </c>
+      <c r="D1799" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1799">
+        <v>50</v>
+      </c>
+      <c r="I1799" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1799">
+        <v>250000</v>
+      </c>
+      <c r="K1799">
+        <v>0</v>
+      </c>
+      <c r="L1799">
+        <v>0</v>
+      </c>
+      <c r="M1799">
+        <v>250000</v>
+      </c>
+      <c r="N1799">
+        <v>122802.82</v>
+      </c>
+      <c r="O1799">
+        <v>127197.18</v>
+      </c>
+      <c r="P1799">
+        <v>47</v>
+      </c>
+      <c r="Q1799">
+        <v>1.06</v>
+      </c>
+      <c r="R1799" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1799" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1800" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1800" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1800">
+        <v>16</v>
+      </c>
+      <c r="I1800" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1800">
+        <v>80000</v>
+      </c>
+      <c r="K1800">
+        <v>0</v>
+      </c>
+      <c r="L1800">
+        <v>0</v>
+      </c>
+      <c r="M1800">
+        <v>80000</v>
+      </c>
+      <c r="N1800">
+        <v>64000</v>
+      </c>
+      <c r="O1800">
+        <v>16000</v>
+      </c>
+      <c r="P1800">
+        <v>15</v>
+      </c>
+      <c r="Q1800">
+        <v>1.07</v>
+      </c>
+      <c r="R1800" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1800" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1801" t="s">
+        <v>374</v>
+      </c>
+      <c r="D1801" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1801">
+        <v>31</v>
+      </c>
+      <c r="I1801" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1801">
+        <v>155000</v>
+      </c>
+      <c r="K1801">
+        <v>0</v>
+      </c>
+      <c r="L1801">
+        <v>0</v>
+      </c>
+      <c r="M1801">
+        <v>155000</v>
+      </c>
+      <c r="N1801">
+        <v>34444.410000000003</v>
+      </c>
+      <c r="O1801">
+        <v>120555.59</v>
+      </c>
+      <c r="P1801">
+        <v>25</v>
+      </c>
+      <c r="Q1801">
+        <v>1.24</v>
+      </c>
+      <c r="R1801" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1801" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1802" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1802" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1802" t="s">
+        <v>377</v>
+      </c>
+      <c r="H1802">
+        <v>12</v>
+      </c>
+      <c r="I1802" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1802">
+        <v>312000</v>
+      </c>
+      <c r="K1802">
+        <v>0</v>
+      </c>
+      <c r="L1802">
+        <v>0</v>
+      </c>
+      <c r="M1802">
+        <v>312000</v>
+      </c>
+      <c r="N1802">
+        <v>264000</v>
+      </c>
+      <c r="O1802">
+        <v>48000</v>
+      </c>
+      <c r="P1802">
+        <v>11</v>
+      </c>
+      <c r="Q1802">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R1802" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1802" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1803" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1803" t="s">
+        <v>376</v>
+      </c>
+      <c r="E1803" t="s">
+        <v>379</v>
+      </c>
+      <c r="H1803">
+        <v>73</v>
+      </c>
+      <c r="I1803" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1803">
+        <v>1825000</v>
+      </c>
+      <c r="K1803">
+        <v>0</v>
+      </c>
+      <c r="L1803">
+        <v>0</v>
+      </c>
+      <c r="M1803">
+        <v>1825000</v>
+      </c>
+      <c r="N1803">
+        <v>1533000</v>
+      </c>
+      <c r="O1803">
+        <v>292000</v>
+      </c>
+      <c r="P1803">
+        <v>57</v>
+      </c>
+      <c r="Q1803">
+        <v>1.28</v>
+      </c>
+      <c r="R1803" t="s">
+        <v>449</v>
+      </c>
+      <c r="S1803" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="S1:S1390" xr:uid="{8D1DFB33-3B61-4DC1-8B6B-F6B42AEB4CBA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
